--- a/Assets/Originals/Excels/Talk/TalkMessage.xlsx
+++ b/Assets/Originals/Excels/Talk/TalkMessage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Talk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50EFD1D2-21A4-4599-B3DA-D7E128248495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78E1D82F-4DE5-47EA-8B43-B72C799C1516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="91">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -659,6 +659,10 @@
     <rPh sb="25" eb="26">
       <t>スス</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>isplayerBackRotateStatus</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1008,14 +1012,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C102"/>
+  <dimension ref="A1:D102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="63.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="17.625" customWidth="1"/>
+    <col min="4" max="4" width="27.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1025,13 +1030,19 @@
       <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1041,8 +1052,11 @@
       <c r="C3" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
+      <c r="D3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1052,8 +1066,11 @@
       <c r="C4" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="37.5">
+      <c r="D4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="37.5">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1063,8 +1080,11 @@
       <c r="C5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
+      <c r="D5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1074,8 +1094,11 @@
       <c r="C6" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
+      <c r="D6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1085,8 +1108,11 @@
       <c r="C7" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" ht="37.5">
+      <c r="D7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="37.5">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1096,8 +1122,11 @@
       <c r="C8" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
+      <c r="D8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1107,8 +1136,11 @@
       <c r="C9" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
+      <c r="D9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1118,8 +1150,11 @@
       <c r="C10" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="11" spans="1:3">
+      <c r="D10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1129,8 +1164,11 @@
       <c r="C11" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
+      <c r="D11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1140,8 +1178,11 @@
       <c r="C12" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:3">
+      <c r="D12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1151,8 +1192,11 @@
       <c r="C13" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="14" spans="1:3">
+      <c r="D13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1162,8 +1206,11 @@
       <c r="C14" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="15" spans="1:3">
+      <c r="D14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1173,8 +1220,11 @@
       <c r="C15" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:3">
+      <c r="D15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1184,8 +1234,11 @@
       <c r="C16" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
+      <c r="D16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1195,8 +1248,11 @@
       <c r="C17" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
+      <c r="D17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1206,8 +1262,11 @@
       <c r="C18" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" ht="37.5">
+      <c r="D18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="37.5">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1217,8 +1276,11 @@
       <c r="C19" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
+      <c r="D19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
       <c r="A20">
         <v>18</v>
       </c>
@@ -1228,8 +1290,11 @@
       <c r="C20" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="21" spans="1:3">
+      <c r="D20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
       <c r="A21">
         <v>19</v>
       </c>
@@ -1239,8 +1304,11 @@
       <c r="C21" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" ht="37.5">
+      <c r="D21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="37.5">
       <c r="A22">
         <v>20</v>
       </c>
@@ -1250,8 +1318,11 @@
       <c r="C22" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:3">
+      <c r="D22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
       <c r="A23">
         <v>21</v>
       </c>
@@ -1261,8 +1332,11 @@
       <c r="C23" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:3">
+      <c r="D23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
       <c r="A24">
         <v>22</v>
       </c>
@@ -1272,8 +1346,11 @@
       <c r="C24" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="25" spans="1:3">
+      <c r="D24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
       <c r="A25">
         <v>23</v>
       </c>
@@ -1283,8 +1360,11 @@
       <c r="C25" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="26" spans="1:3">
+      <c r="D25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
       <c r="A26">
         <v>24</v>
       </c>
@@ -1294,8 +1374,11 @@
       <c r="C26" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:3">
+      <c r="D26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
       <c r="A27">
         <v>25</v>
       </c>
@@ -1305,8 +1388,11 @@
       <c r="C27" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" ht="37.5">
+      <c r="D27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="37.5">
       <c r="A28">
         <v>26</v>
       </c>
@@ -1316,8 +1402,11 @@
       <c r="C28" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" ht="37.5">
+      <c r="D28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="37.5">
       <c r="A29">
         <v>27</v>
       </c>
@@ -1327,8 +1416,11 @@
       <c r="C29" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:3">
+      <c r="D29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
       <c r="A30">
         <v>28</v>
       </c>
@@ -1338,8 +1430,11 @@
       <c r="C30" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:3">
+      <c r="D30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
       <c r="A31">
         <v>29</v>
       </c>
@@ -1349,8 +1444,11 @@
       <c r="C31" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="32" spans="1:3">
+      <c r="D31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
       <c r="A32">
         <v>30</v>
       </c>
@@ -1360,8 +1458,11 @@
       <c r="C32" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="33" spans="1:3">
+      <c r="D32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
       <c r="A33">
         <v>31</v>
       </c>
@@ -1371,8 +1472,11 @@
       <c r="C33" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:3">
+      <c r="D33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
       <c r="A34">
         <v>32</v>
       </c>
@@ -1382,8 +1486,11 @@
       <c r="C34" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:3">
+      <c r="D34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
       <c r="A35">
         <v>33</v>
       </c>
@@ -1393,8 +1500,11 @@
       <c r="C35" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="36" spans="1:3">
+      <c r="D35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
       <c r="A36">
         <v>34</v>
       </c>
@@ -1404,8 +1514,11 @@
       <c r="C36" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="1:3">
+      <c r="D36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
       <c r="A37">
         <v>35</v>
       </c>
@@ -1415,8 +1528,11 @@
       <c r="C37" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" ht="37.5">
+      <c r="D37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="37.5">
       <c r="A38">
         <v>36</v>
       </c>
@@ -1426,13 +1542,19 @@
       <c r="C38" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="1:3">
+      <c r="D38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
       <c r="A39">
         <v>37</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" ht="37.5">
+      <c r="D39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="37.5">
       <c r="A40">
         <v>38</v>
       </c>
@@ -1442,8 +1564,11 @@
       <c r="C40" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" ht="37.5">
+      <c r="D40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="37.5">
       <c r="A41">
         <v>39</v>
       </c>
@@ -1453,8 +1578,11 @@
       <c r="C41" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="1:3">
+      <c r="D41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
       <c r="A42">
         <v>40</v>
       </c>
@@ -1464,8 +1592,11 @@
       <c r="C42" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" ht="37.5">
+      <c r="D42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="37.5">
       <c r="A43">
         <v>41</v>
       </c>
@@ -1475,8 +1606,11 @@
       <c r="C43" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" ht="37.5">
+      <c r="D43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="37.5">
       <c r="A44">
         <v>42</v>
       </c>
@@ -1486,8 +1620,11 @@
       <c r="C44" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="1:3">
+      <c r="D44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
       <c r="A45">
         <v>43</v>
       </c>
@@ -1497,8 +1634,11 @@
       <c r="C45" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="1:3">
+      <c r="D45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
       <c r="A46">
         <v>44</v>
       </c>
@@ -1508,8 +1648,11 @@
       <c r="C46" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="1:3">
+      <c r="D46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
       <c r="A47">
         <v>45</v>
       </c>
@@ -1519,8 +1662,11 @@
       <c r="C47" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="1:3">
+      <c r="D47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
       <c r="A48">
         <v>46</v>
       </c>
@@ -1530,8 +1676,11 @@
       <c r="C48" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="1:3">
+      <c r="D48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
       <c r="A49">
         <v>47</v>
       </c>
@@ -1541,8 +1690,11 @@
       <c r="C49" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" ht="37.5">
+      <c r="D49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="37.5">
       <c r="A50">
         <v>48</v>
       </c>
@@ -1552,8 +1704,11 @@
       <c r="C50" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" ht="37.5">
+      <c r="D50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="37.5">
       <c r="A51">
         <v>49</v>
       </c>
@@ -1563,8 +1718,11 @@
       <c r="C51" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="52" spans="1:3">
+      <c r="D51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
       <c r="A52">
         <v>50</v>
       </c>
@@ -1574,8 +1732,11 @@
       <c r="C52" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="53" spans="1:3">
+      <c r="D52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
       <c r="A53">
         <v>51</v>
       </c>
@@ -1585,8 +1746,11 @@
       <c r="C53" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="54" spans="1:3">
+      <c r="D53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
       <c r="A54">
         <v>52</v>
       </c>
@@ -1596,8 +1760,11 @@
       <c r="C54" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="55" spans="1:3">
+      <c r="D54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
       <c r="A55">
         <v>53</v>
       </c>
@@ -1607,8 +1774,11 @@
       <c r="C55" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" ht="37.5">
+      <c r="D55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="37.5">
       <c r="A56">
         <v>54</v>
       </c>
@@ -1618,8 +1788,11 @@
       <c r="C56" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="57" spans="1:3">
+      <c r="D56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
       <c r="A57">
         <v>55</v>
       </c>
@@ -1629,8 +1802,11 @@
       <c r="C57" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" ht="37.5">
+      <c r="D57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="37.5">
       <c r="A58">
         <v>56</v>
       </c>
@@ -1640,8 +1816,11 @@
       <c r="C58" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="1:3">
+      <c r="D58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
       <c r="A59">
         <v>57</v>
       </c>
@@ -1651,8 +1830,11 @@
       <c r="C59" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="1:3">
+      <c r="D59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
       <c r="A60">
         <v>58</v>
       </c>
@@ -1662,8 +1844,11 @@
       <c r="C60" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="61" spans="1:3">
+      <c r="D60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
       <c r="A61">
         <v>59</v>
       </c>
@@ -1673,8 +1858,11 @@
       <c r="C61" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="62" spans="1:3">
+      <c r="D61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
       <c r="A62">
         <v>60</v>
       </c>
@@ -1684,8 +1872,11 @@
       <c r="C62" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="63" spans="1:3">
+      <c r="D62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
       <c r="A63">
         <v>61</v>
       </c>
@@ -1695,8 +1886,11 @@
       <c r="C63" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="64" spans="1:3">
+      <c r="D63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
       <c r="A64">
         <v>62</v>
       </c>
@@ -1706,8 +1900,11 @@
       <c r="C64" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="65" spans="1:3">
+      <c r="D64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
       <c r="A65">
         <v>63</v>
       </c>
@@ -1717,8 +1914,11 @@
       <c r="C65" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="66" spans="1:3">
+      <c r="D65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
       <c r="A66">
         <v>64</v>
       </c>
@@ -1728,8 +1928,11 @@
       <c r="C66" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="1:3">
+      <c r="D66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
       <c r="A67">
         <v>65</v>
       </c>
@@ -1739,8 +1942,11 @@
       <c r="C67" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="68" spans="1:3">
+      <c r="D67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
       <c r="A68">
         <v>66</v>
       </c>
@@ -1750,8 +1956,11 @@
       <c r="C68" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" ht="37.5">
+      <c r="D68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="37.5">
       <c r="A69">
         <v>67</v>
       </c>
@@ -1761,8 +1970,11 @@
       <c r="C69" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="70" spans="1:3">
+      <c r="D69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
       <c r="A70">
         <v>68</v>
       </c>
@@ -1772,13 +1984,19 @@
       <c r="C70" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="71" spans="1:3">
+      <c r="D70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
       <c r="A71">
         <v>69</v>
       </c>
-    </row>
-    <row r="72" spans="1:3">
+      <c r="D71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
       <c r="A72">
         <v>70</v>
       </c>
@@ -1788,8 +2006,11 @@
       <c r="C72" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="73" spans="1:3">
+      <c r="D72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
       <c r="A73">
         <v>71</v>
       </c>
@@ -1799,8 +2020,11 @@
       <c r="C73" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="74" spans="1:3">
+      <c r="D73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
       <c r="A74">
         <v>72</v>
       </c>
@@ -1810,8 +2034,11 @@
       <c r="C74" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="75" spans="1:3">
+      <c r="D74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
       <c r="A75">
         <v>73</v>
       </c>
@@ -1821,8 +2048,11 @@
       <c r="C75" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="76" spans="1:3">
+      <c r="D75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
       <c r="A76">
         <v>74</v>
       </c>
@@ -1832,8 +2062,11 @@
       <c r="C76" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="1:3">
+      <c r="D76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
       <c r="A77">
         <v>75</v>
       </c>
@@ -1843,8 +2076,11 @@
       <c r="C77" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" ht="37.5">
+      <c r="D77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="37.5">
       <c r="A78">
         <v>76</v>
       </c>
@@ -1854,8 +2090,11 @@
       <c r="C78" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="79" spans="1:3">
+      <c r="D78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
       <c r="A79">
         <v>77</v>
       </c>
@@ -1865,8 +2104,11 @@
       <c r="C79" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="80" spans="1:3">
+      <c r="D79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
       <c r="A80">
         <v>78</v>
       </c>
@@ -1876,8 +2118,11 @@
       <c r="C80" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" ht="37.5">
+      <c r="D80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="37.5">
       <c r="A81">
         <v>79</v>
       </c>
@@ -1887,8 +2132,11 @@
       <c r="C81" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="1:3">
+      <c r="D81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
       <c r="A82">
         <v>80</v>
       </c>
@@ -1898,8 +2146,11 @@
       <c r="C82" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="83" spans="1:3">
+      <c r="D82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
       <c r="A83">
         <v>81</v>
       </c>
@@ -1909,8 +2160,11 @@
       <c r="C83" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="1:3">
+      <c r="D83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
       <c r="A84">
         <v>82</v>
       </c>
@@ -1920,8 +2174,11 @@
       <c r="C84" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="85" spans="1:3">
+      <c r="D84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
       <c r="A85">
         <v>83</v>
       </c>
@@ -1931,8 +2188,11 @@
       <c r="C85" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="86" spans="1:3">
+      <c r="D85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
       <c r="A86">
         <v>84</v>
       </c>
@@ -1942,8 +2202,11 @@
       <c r="C86" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="87" spans="1:3">
+      <c r="D86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
       <c r="A87">
         <v>85</v>
       </c>
@@ -1953,8 +2216,11 @@
       <c r="C87" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="88" spans="1:3">
+      <c r="D87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
       <c r="A88">
         <v>86</v>
       </c>
@@ -1964,8 +2230,11 @@
       <c r="C88" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="89" spans="1:3">
+      <c r="D88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
       <c r="A89">
         <v>87</v>
       </c>
@@ -1975,38 +2244,44 @@
       <c r="C89" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="1:3">
+      <c r="D89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
       <c r="A90">
         <v>88</v>
       </c>
-    </row>
-    <row r="91" spans="1:3">
+      <c r="D90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
       <c r="A91">
         <v>89</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
+    <row r="92" spans="1:4">
       <c r="A92">
         <v>90</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
+    <row r="93" spans="1:4">
       <c r="A93">
         <v>91</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
+    <row r="94" spans="1:4">
       <c r="A94">
         <v>92</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
+    <row r="95" spans="1:4">
       <c r="A95">
         <v>93</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
+    <row r="96" spans="1:4">
       <c r="A96">
         <v>94</v>
       </c>

--- a/Assets/Originals/Excels/Talk/TalkMessage.xlsx
+++ b/Assets/Originals/Excels/Talk/TalkMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Talk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78E1D82F-4DE5-47EA-8B43-B72C799C1516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9874B821-4476-430B-B23D-C5AD948B54E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="92">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -663,6 +663,10 @@
   </si>
   <si>
     <t>isplayerBackRotateStatus</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>isPlaySoundNoiseStatus</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1012,15 +1016,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D102"/>
+  <dimension ref="A1:E102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="63.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="17.625" customWidth="1"/>
     <col min="4" max="4" width="27.75" customWidth="1"/>
+    <col min="5" max="5" width="22.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1033,16 +1038,22 @@
       <c r="D1" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1055,8 +1066,11 @@
       <c r="D3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="E3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1069,8 +1083,11 @@
       <c r="D4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="37.5">
+      <c r="E4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="37.5">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1083,8 +1100,11 @@
       <c r="D5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="E5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1097,8 +1117,11 @@
       <c r="D6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="E6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1111,8 +1134,11 @@
       <c r="D7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="37.5">
+      <c r="E7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="37.5">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1125,8 +1151,11 @@
       <c r="D8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="E8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1139,8 +1168,11 @@
       <c r="D9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:4">
+      <c r="E9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1153,8 +1185,11 @@
       <c r="D10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:4">
+      <c r="E10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1167,8 +1202,11 @@
       <c r="D11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:4">
+      <c r="E11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1181,8 +1219,11 @@
       <c r="D12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="E12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1195,8 +1236,11 @@
       <c r="D13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:4">
+      <c r="E13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1209,8 +1253,11 @@
       <c r="D14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:4">
+      <c r="E14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1223,8 +1270,11 @@
       <c r="D15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:4">
+      <c r="E15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1237,8 +1287,11 @@
       <c r="D16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:4">
+      <c r="E16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1251,8 +1304,11 @@
       <c r="D17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:4">
+      <c r="E17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1265,8 +1321,11 @@
       <c r="D18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" ht="37.5">
+      <c r="E18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="37.5">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1279,8 +1338,11 @@
       <c r="D19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:4">
+      <c r="E19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20">
         <v>18</v>
       </c>
@@ -1293,8 +1355,11 @@
       <c r="D20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:4">
+      <c r="E20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21">
         <v>19</v>
       </c>
@@ -1307,8 +1372,11 @@
       <c r="D21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" ht="37.5">
+      <c r="E21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="37.5">
       <c r="A22">
         <v>20</v>
       </c>
@@ -1321,8 +1389,11 @@
       <c r="D22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:4">
+      <c r="E22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23">
         <v>21</v>
       </c>
@@ -1335,8 +1406,11 @@
       <c r="D23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:4">
+      <c r="E23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24">
         <v>22</v>
       </c>
@@ -1349,8 +1423,11 @@
       <c r="D24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:4">
+      <c r="E24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25">
         <v>23</v>
       </c>
@@ -1363,8 +1440,11 @@
       <c r="D25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:4">
+      <c r="E25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26">
         <v>24</v>
       </c>
@@ -1377,8 +1457,11 @@
       <c r="D26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:4">
+      <c r="E26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27">
         <v>25</v>
       </c>
@@ -1391,8 +1474,11 @@
       <c r="D27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" ht="37.5">
+      <c r="E27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="37.5">
       <c r="A28">
         <v>26</v>
       </c>
@@ -1405,8 +1491,11 @@
       <c r="D28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" ht="37.5">
+      <c r="E28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="37.5">
       <c r="A29">
         <v>27</v>
       </c>
@@ -1419,8 +1508,11 @@
       <c r="D29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:4">
+      <c r="E29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30">
         <v>28</v>
       </c>
@@ -1433,8 +1525,11 @@
       <c r="D30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:4">
+      <c r="E30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
       <c r="A31">
         <v>29</v>
       </c>
@@ -1447,8 +1542,11 @@
       <c r="D31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:4">
+      <c r="E31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
       <c r="A32">
         <v>30</v>
       </c>
@@ -1461,8 +1559,11 @@
       <c r="D32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:4">
+      <c r="E32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
       <c r="A33">
         <v>31</v>
       </c>
@@ -1475,8 +1576,11 @@
       <c r="D33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:4">
+      <c r="E33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
       <c r="A34">
         <v>32</v>
       </c>
@@ -1489,8 +1593,11 @@
       <c r="D34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:4">
+      <c r="E34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
       <c r="A35">
         <v>33</v>
       </c>
@@ -1503,8 +1610,11 @@
       <c r="D35">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:4">
+      <c r="E35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
       <c r="A36">
         <v>34</v>
       </c>
@@ -1517,8 +1627,11 @@
       <c r="D36">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:4">
+      <c r="E36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
       <c r="A37">
         <v>35</v>
       </c>
@@ -1531,8 +1644,11 @@
       <c r="D37">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" ht="37.5">
+      <c r="E37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="37.5">
       <c r="A38">
         <v>36</v>
       </c>
@@ -1545,16 +1661,22 @@
       <c r="D38">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:4">
+      <c r="E38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
       <c r="A39">
         <v>37</v>
       </c>
       <c r="D39">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" ht="37.5">
+      <c r="E39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="37.5">
       <c r="A40">
         <v>38</v>
       </c>
@@ -1567,8 +1689,11 @@
       <c r="D40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" ht="37.5">
+      <c r="E40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="37.5">
       <c r="A41">
         <v>39</v>
       </c>
@@ -1581,8 +1706,11 @@
       <c r="D41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:4">
+      <c r="E41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
       <c r="A42">
         <v>40</v>
       </c>
@@ -1595,8 +1723,11 @@
       <c r="D42">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" ht="37.5">
+      <c r="E42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="37.5">
       <c r="A43">
         <v>41</v>
       </c>
@@ -1609,8 +1740,11 @@
       <c r="D43">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" ht="37.5">
+      <c r="E43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="37.5">
       <c r="A44">
         <v>42</v>
       </c>
@@ -1623,8 +1757,11 @@
       <c r="D44">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:4">
+      <c r="E44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
       <c r="A45">
         <v>43</v>
       </c>
@@ -1637,8 +1774,11 @@
       <c r="D45">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:4">
+      <c r="E45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
       <c r="A46">
         <v>44</v>
       </c>
@@ -1651,8 +1791,11 @@
       <c r="D46">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:4">
+      <c r="E46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
       <c r="A47">
         <v>45</v>
       </c>
@@ -1665,8 +1808,11 @@
       <c r="D47">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:4">
+      <c r="E47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
       <c r="A48">
         <v>46</v>
       </c>
@@ -1679,8 +1825,11 @@
       <c r="D48">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:4">
+      <c r="E48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
       <c r="A49">
         <v>47</v>
       </c>
@@ -1693,8 +1842,11 @@
       <c r="D49">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" ht="37.5">
+      <c r="E49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="37.5">
       <c r="A50">
         <v>48</v>
       </c>
@@ -1707,8 +1859,11 @@
       <c r="D50">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" ht="37.5">
+      <c r="E50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="37.5">
       <c r="A51">
         <v>49</v>
       </c>
@@ -1721,8 +1876,11 @@
       <c r="D51">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:4">
+      <c r="E51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
       <c r="A52">
         <v>50</v>
       </c>
@@ -1735,8 +1893,11 @@
       <c r="D52">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:4">
+      <c r="E52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
       <c r="A53">
         <v>51</v>
       </c>
@@ -1749,8 +1910,11 @@
       <c r="D53">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:4">
+      <c r="E53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
       <c r="A54">
         <v>52</v>
       </c>
@@ -1763,8 +1927,11 @@
       <c r="D54">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:4">
+      <c r="E54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
       <c r="A55">
         <v>53</v>
       </c>
@@ -1777,8 +1944,11 @@
       <c r="D55">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" ht="37.5">
+      <c r="E55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="37.5">
       <c r="A56">
         <v>54</v>
       </c>
@@ -1791,8 +1961,11 @@
       <c r="D56">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:4">
+      <c r="E56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
       <c r="A57">
         <v>55</v>
       </c>
@@ -1805,8 +1978,11 @@
       <c r="D57">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" ht="37.5">
+      <c r="E57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="37.5">
       <c r="A58">
         <v>56</v>
       </c>
@@ -1819,8 +1995,11 @@
       <c r="D58">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:4">
+      <c r="E58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
       <c r="A59">
         <v>57</v>
       </c>
@@ -1833,8 +2012,11 @@
       <c r="D59">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:4">
+      <c r="E59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
       <c r="A60">
         <v>58</v>
       </c>
@@ -1847,8 +2029,11 @@
       <c r="D60">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:4">
+      <c r="E60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
       <c r="A61">
         <v>59</v>
       </c>
@@ -1861,8 +2046,11 @@
       <c r="D61">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:4">
+      <c r="E61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
       <c r="A62">
         <v>60</v>
       </c>
@@ -1875,8 +2063,11 @@
       <c r="D62">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:4">
+      <c r="E62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
       <c r="A63">
         <v>61</v>
       </c>
@@ -1889,8 +2080,11 @@
       <c r="D63">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:4">
+      <c r="E63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
       <c r="A64">
         <v>62</v>
       </c>
@@ -1903,8 +2097,11 @@
       <c r="D64">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:4">
+      <c r="E64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
       <c r="A65">
         <v>63</v>
       </c>
@@ -1917,8 +2114,11 @@
       <c r="D65">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:4">
+      <c r="E65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
       <c r="A66">
         <v>64</v>
       </c>
@@ -1931,8 +2131,11 @@
       <c r="D66">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:4">
+      <c r="E66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
       <c r="A67">
         <v>65</v>
       </c>
@@ -1945,8 +2148,11 @@
       <c r="D67">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:4">
+      <c r="E67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
       <c r="A68">
         <v>66</v>
       </c>
@@ -1959,8 +2165,11 @@
       <c r="D68">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" ht="37.5">
+      <c r="E68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="37.5">
       <c r="A69">
         <v>67</v>
       </c>
@@ -1973,8 +2182,11 @@
       <c r="D69">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:4">
+      <c r="E69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
       <c r="A70">
         <v>68</v>
       </c>
@@ -1987,16 +2199,22 @@
       <c r="D70">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:4">
+      <c r="E70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
       <c r="A71">
         <v>69</v>
       </c>
       <c r="D71">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:4">
+      <c r="E71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
       <c r="A72">
         <v>70</v>
       </c>
@@ -2009,8 +2227,11 @@
       <c r="D72">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:4">
+      <c r="E72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
       <c r="A73">
         <v>71</v>
       </c>
@@ -2023,8 +2244,11 @@
       <c r="D73">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:4">
+      <c r="E73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
       <c r="A74">
         <v>72</v>
       </c>
@@ -2037,8 +2261,11 @@
       <c r="D74">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="1:4">
+      <c r="E74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
       <c r="A75">
         <v>73</v>
       </c>
@@ -2051,8 +2278,11 @@
       <c r="D75">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:4">
+      <c r="E75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
       <c r="A76">
         <v>74</v>
       </c>
@@ -2065,8 +2295,11 @@
       <c r="D76">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:4">
+      <c r="E76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
       <c r="A77">
         <v>75</v>
       </c>
@@ -2079,8 +2312,11 @@
       <c r="D77">
         <v>0</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" ht="37.5">
+      <c r="E77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="37.5">
       <c r="A78">
         <v>76</v>
       </c>
@@ -2093,8 +2329,11 @@
       <c r="D78">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="1:4">
+      <c r="E78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
       <c r="A79">
         <v>77</v>
       </c>
@@ -2107,8 +2346,11 @@
       <c r="D79">
         <v>0</v>
       </c>
-    </row>
-    <row r="80" spans="1:4">
+      <c r="E79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
       <c r="A80">
         <v>78</v>
       </c>
@@ -2121,8 +2363,11 @@
       <c r="D80">
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" ht="37.5">
+      <c r="E80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="37.5">
       <c r="A81">
         <v>79</v>
       </c>
@@ -2135,8 +2380,11 @@
       <c r="D81">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="1:4">
+      <c r="E81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
       <c r="A82">
         <v>80</v>
       </c>
@@ -2149,8 +2397,11 @@
       <c r="D82">
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="1:4">
+      <c r="E82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
       <c r="A83">
         <v>81</v>
       </c>
@@ -2163,8 +2414,11 @@
       <c r="D83">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:4">
+      <c r="E83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
       <c r="A84">
         <v>82</v>
       </c>
@@ -2177,8 +2431,11 @@
       <c r="D84">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:4">
+      <c r="E84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
       <c r="A85">
         <v>83</v>
       </c>
@@ -2191,8 +2448,11 @@
       <c r="D85">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="1:4">
+      <c r="E85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
       <c r="A86">
         <v>84</v>
       </c>
@@ -2205,8 +2465,11 @@
       <c r="D86">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="1:4">
+      <c r="E86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
       <c r="A87">
         <v>85</v>
       </c>
@@ -2219,8 +2482,11 @@
       <c r="D87">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="1:4">
+      <c r="E87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
       <c r="A88">
         <v>86</v>
       </c>
@@ -2233,8 +2499,11 @@
       <c r="D88">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="1:4">
+      <c r="E88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
       <c r="A89">
         <v>87</v>
       </c>
@@ -2247,41 +2516,47 @@
       <c r="D89">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="1:4">
+      <c r="E89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
       <c r="A90">
         <v>88</v>
       </c>
       <c r="D90">
         <v>0</v>
       </c>
-    </row>
-    <row r="91" spans="1:4">
+      <c r="E90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
       <c r="A91">
         <v>89</v>
       </c>
     </row>
-    <row r="92" spans="1:4">
+    <row r="92" spans="1:5">
       <c r="A92">
         <v>90</v>
       </c>
     </row>
-    <row r="93" spans="1:4">
+    <row r="93" spans="1:5">
       <c r="A93">
         <v>91</v>
       </c>
     </row>
-    <row r="94" spans="1:4">
+    <row r="94" spans="1:5">
       <c r="A94">
         <v>92</v>
       </c>
     </row>
-    <row r="95" spans="1:4">
+    <row r="95" spans="1:5">
       <c r="A95">
         <v>93</v>
       </c>
     </row>
-    <row r="96" spans="1:4">
+    <row r="96" spans="1:5">
       <c r="A96">
         <v>94</v>
       </c>

--- a/Assets/Originals/Excels/Talk/TalkMessage.xlsx
+++ b/Assets/Originals/Excels/Talk/TalkMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Talk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9874B821-4476-430B-B23D-C5AD948B54E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEA97DCB-525A-431E-8CC1-F665A88F5E98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="98">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -667,6 +667,30 @@
   </si>
   <si>
     <t>isPlaySoundNoiseStatus</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>isWaitStatus</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>waitTime</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>isTutorialStatus</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>showSystemMessageNumber</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>isEndStatus</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>isBlackOutStatus</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1016,16 +1040,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E102"/>
+  <dimension ref="A1:K102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="63.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="17.625" customWidth="1"/>
     <col min="4" max="4" width="27.75" customWidth="1"/>
     <col min="5" max="5" width="22.5" customWidth="1"/>
+    <col min="6" max="6" width="13.625" customWidth="1"/>
+    <col min="8" max="8" width="17.125" customWidth="1"/>
+    <col min="9" max="9" width="28.125" customWidth="1"/>
+    <col min="10" max="10" width="13.125" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1041,8 +1070,26 @@
       <c r="E1" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" t="s">
+        <v>92</v>
+      </c>
+      <c r="G1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H1" t="s">
+        <v>94</v>
+      </c>
+      <c r="I1" t="s">
+        <v>95</v>
+      </c>
+      <c r="J1" t="s">
+        <v>96</v>
+      </c>
+      <c r="K1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1052,8 +1099,26 @@
       <c r="E2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1069,8 +1134,26 @@
       <c r="E3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1086,8 +1169,26 @@
       <c r="E4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="37.5">
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>3</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="37.5">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1103,8 +1204,26 @@
       <c r="E5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1120,8 +1239,26 @@
       <c r="E6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1137,8 +1274,26 @@
       <c r="E7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="37.5">
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="37.5">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1154,8 +1309,26 @@
       <c r="E8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1171,8 +1344,26 @@
       <c r="E9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1188,8 +1379,26 @@
       <c r="E10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1205,8 +1414,26 @@
       <c r="E11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:5">
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1222,8 +1449,26 @@
       <c r="E12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:5">
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1239,8 +1484,26 @@
       <c r="E13">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1256,8 +1519,26 @@
       <c r="E14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:5">
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1273,8 +1554,26 @@
       <c r="E15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:5">
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1290,8 +1589,26 @@
       <c r="E16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1307,8 +1624,26 @@
       <c r="E17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1324,8 +1659,26 @@
       <c r="E18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" ht="37.5">
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="37.5">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1341,8 +1694,26 @@
       <c r="E19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20">
         <v>18</v>
       </c>
@@ -1358,8 +1729,26 @@
       <c r="E20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:5">
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21">
         <v>19</v>
       </c>
@@ -1375,8 +1764,26 @@
       <c r="E21">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" ht="37.5">
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="37.5">
       <c r="A22">
         <v>20</v>
       </c>
@@ -1392,8 +1799,26 @@
       <c r="E22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:5">
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
       <c r="A23">
         <v>21</v>
       </c>
@@ -1409,8 +1834,26 @@
       <c r="E23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:5">
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
       <c r="A24">
         <v>22</v>
       </c>
@@ -1426,8 +1869,26 @@
       <c r="E24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:5">
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
       <c r="A25">
         <v>23</v>
       </c>
@@ -1443,8 +1904,26 @@
       <c r="E25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:5">
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26">
         <v>24</v>
       </c>
@@ -1460,8 +1939,26 @@
       <c r="E26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:5">
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
       <c r="A27">
         <v>25</v>
       </c>
@@ -1477,8 +1974,26 @@
       <c r="E27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" ht="37.5">
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="37.5">
       <c r="A28">
         <v>26</v>
       </c>
@@ -1494,8 +2009,26 @@
       <c r="E28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" ht="37.5">
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="37.5">
       <c r="A29">
         <v>27</v>
       </c>
@@ -1511,8 +2044,26 @@
       <c r="E29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:5">
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
       <c r="A30">
         <v>28</v>
       </c>
@@ -1528,8 +2079,26 @@
       <c r="E30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:5">
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
       <c r="A31">
         <v>29</v>
       </c>
@@ -1545,8 +2114,26 @@
       <c r="E31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:5">
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
       <c r="A32">
         <v>30</v>
       </c>
@@ -1562,8 +2149,26 @@
       <c r="E32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:5">
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
       <c r="A33">
         <v>31</v>
       </c>
@@ -1579,8 +2184,26 @@
       <c r="E33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:5">
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
       <c r="A34">
         <v>32</v>
       </c>
@@ -1596,8 +2219,26 @@
       <c r="E34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:5">
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
       <c r="A35">
         <v>33</v>
       </c>
@@ -1613,8 +2254,26 @@
       <c r="E35">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:5">
+      <c r="F35">
+        <v>1</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
       <c r="A36">
         <v>34</v>
       </c>
@@ -1630,8 +2289,26 @@
       <c r="E36">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:5">
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
       <c r="A37">
         <v>35</v>
       </c>
@@ -1647,8 +2324,26 @@
       <c r="E37">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" ht="37.5">
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="37.5">
       <c r="A38">
         <v>36</v>
       </c>
@@ -1664,8 +2359,26 @@
       <c r="E38">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:5">
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>1</v>
+      </c>
+      <c r="I38">
+        <v>9</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
       <c r="A39">
         <v>37</v>
       </c>
@@ -1675,8 +2388,26 @@
       <c r="E39">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" ht="37.5">
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="37.5">
       <c r="A40">
         <v>38</v>
       </c>
@@ -1692,8 +2423,26 @@
       <c r="E40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" ht="37.5">
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="37.5">
       <c r="A41">
         <v>39</v>
       </c>
@@ -1709,8 +2458,26 @@
       <c r="E41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:5">
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
       <c r="A42">
         <v>40</v>
       </c>
@@ -1726,8 +2493,26 @@
       <c r="E42">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" ht="37.5">
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="37.5">
       <c r="A43">
         <v>41</v>
       </c>
@@ -1743,8 +2528,26 @@
       <c r="E43">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" ht="37.5">
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="37.5">
       <c r="A44">
         <v>42</v>
       </c>
@@ -1760,8 +2563,26 @@
       <c r="E44">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:5">
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>2</v>
+      </c>
+      <c r="I44">
+        <v>10</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
       <c r="A45">
         <v>43</v>
       </c>
@@ -1777,8 +2598,26 @@
       <c r="E45">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:5">
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>2</v>
+      </c>
+      <c r="I45">
+        <v>11</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
       <c r="A46">
         <v>44</v>
       </c>
@@ -1794,8 +2633,26 @@
       <c r="E46">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:5">
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
       <c r="A47">
         <v>45</v>
       </c>
@@ -1811,8 +2668,26 @@
       <c r="E47">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:5">
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>3</v>
+      </c>
+      <c r="I47">
+        <v>12</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
       <c r="A48">
         <v>46</v>
       </c>
@@ -1828,8 +2703,26 @@
       <c r="E48">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:5">
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>2</v>
+      </c>
+      <c r="I48">
+        <v>13</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
       <c r="A49">
         <v>47</v>
       </c>
@@ -1845,8 +2738,26 @@
       <c r="E49">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" ht="37.5">
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" ht="37.5">
       <c r="A50">
         <v>48</v>
       </c>
@@ -1862,8 +2773,26 @@
       <c r="E50">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" ht="37.5">
+      <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>2</v>
+      </c>
+      <c r="I50">
+        <v>14</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="37.5">
       <c r="A51">
         <v>49</v>
       </c>
@@ -1879,8 +2808,26 @@
       <c r="E51">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:5">
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11">
       <c r="A52">
         <v>50</v>
       </c>
@@ -1896,8 +2843,26 @@
       <c r="E52">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:5">
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11">
       <c r="A53">
         <v>51</v>
       </c>
@@ -1913,8 +2878,26 @@
       <c r="E53">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:5">
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11">
       <c r="A54">
         <v>52</v>
       </c>
@@ -1930,8 +2913,26 @@
       <c r="E54">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:5">
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11">
       <c r="A55">
         <v>53</v>
       </c>
@@ -1947,8 +2948,26 @@
       <c r="E55">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" ht="37.5">
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="37.5">
       <c r="A56">
         <v>54</v>
       </c>
@@ -1964,8 +2983,26 @@
       <c r="E56">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:5">
+      <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11">
       <c r="A57">
         <v>55</v>
       </c>
@@ -1981,8 +3018,26 @@
       <c r="E57">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:5" ht="37.5">
+      <c r="F57">
+        <v>0</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" ht="37.5">
       <c r="A58">
         <v>56</v>
       </c>
@@ -1998,8 +3053,26 @@
       <c r="E58">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:5">
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11">
       <c r="A59">
         <v>57</v>
       </c>
@@ -2015,8 +3088,26 @@
       <c r="E59">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:5">
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11">
       <c r="A60">
         <v>58</v>
       </c>
@@ -2032,8 +3123,26 @@
       <c r="E60">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:5">
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11">
       <c r="A61">
         <v>59</v>
       </c>
@@ -2049,8 +3158,26 @@
       <c r="E61">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:5">
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11">
       <c r="A62">
         <v>60</v>
       </c>
@@ -2066,8 +3193,26 @@
       <c r="E62">
         <v>1</v>
       </c>
-    </row>
-    <row r="63" spans="1:5">
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11">
       <c r="A63">
         <v>61</v>
       </c>
@@ -2083,8 +3228,26 @@
       <c r="E63">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:5">
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11">
       <c r="A64">
         <v>62</v>
       </c>
@@ -2100,8 +3263,26 @@
       <c r="E64">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:5">
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11">
       <c r="A65">
         <v>63</v>
       </c>
@@ -2117,8 +3298,26 @@
       <c r="E65">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:5">
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11">
       <c r="A66">
         <v>64</v>
       </c>
@@ -2134,8 +3333,26 @@
       <c r="E66">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:5">
+      <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11">
       <c r="A67">
         <v>65</v>
       </c>
@@ -2151,8 +3368,26 @@
       <c r="E67">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:5">
+      <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11">
       <c r="A68">
         <v>66</v>
       </c>
@@ -2168,8 +3403,26 @@
       <c r="E68">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="1:5" ht="37.5">
+      <c r="F68">
+        <v>0</v>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" ht="37.5">
       <c r="A69">
         <v>67</v>
       </c>
@@ -2185,8 +3438,26 @@
       <c r="E69">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:5">
+      <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11">
       <c r="A70">
         <v>68</v>
       </c>
@@ -2202,8 +3473,26 @@
       <c r="E70">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:5">
+      <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>1</v>
+      </c>
+      <c r="K70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11">
       <c r="A71">
         <v>69</v>
       </c>
@@ -2213,8 +3502,26 @@
       <c r="E71">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:5">
+      <c r="F71">
+        <v>0</v>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11">
       <c r="A72">
         <v>70</v>
       </c>
@@ -2230,8 +3537,26 @@
       <c r="E72">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:5">
+      <c r="F72">
+        <v>0</v>
+      </c>
+      <c r="G72">
+        <v>1</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>0</v>
+      </c>
+      <c r="K72">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11">
       <c r="A73">
         <v>71</v>
       </c>
@@ -2247,8 +3572,26 @@
       <c r="E73">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:5">
+      <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+      <c r="K73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11">
       <c r="A74">
         <v>72</v>
       </c>
@@ -2264,8 +3607,26 @@
       <c r="E74">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="1:5">
+      <c r="F74">
+        <v>0</v>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74">
+        <v>0</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>0</v>
+      </c>
+      <c r="K74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11">
       <c r="A75">
         <v>73</v>
       </c>
@@ -2281,8 +3642,26 @@
       <c r="E75">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:5">
+      <c r="F75">
+        <v>0</v>
+      </c>
+      <c r="G75">
+        <v>0</v>
+      </c>
+      <c r="H75">
+        <v>0</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11">
       <c r="A76">
         <v>74</v>
       </c>
@@ -2298,8 +3677,26 @@
       <c r="E76">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:5">
+      <c r="F76">
+        <v>0</v>
+      </c>
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11">
       <c r="A77">
         <v>75</v>
       </c>
@@ -2315,8 +3712,26 @@
       <c r="E77">
         <v>0</v>
       </c>
-    </row>
-    <row r="78" spans="1:5" ht="37.5">
+      <c r="F77">
+        <v>0</v>
+      </c>
+      <c r="G77">
+        <v>0</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" ht="37.5">
       <c r="A78">
         <v>76</v>
       </c>
@@ -2332,8 +3747,26 @@
       <c r="E78">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="1:5">
+      <c r="F78">
+        <v>0</v>
+      </c>
+      <c r="G78">
+        <v>0</v>
+      </c>
+      <c r="H78">
+        <v>0</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>0</v>
+      </c>
+      <c r="K78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11">
       <c r="A79">
         <v>77</v>
       </c>
@@ -2349,8 +3782,26 @@
       <c r="E79">
         <v>0</v>
       </c>
-    </row>
-    <row r="80" spans="1:5">
+      <c r="F79">
+        <v>0</v>
+      </c>
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79">
+        <v>0</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>0</v>
+      </c>
+      <c r="K79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11">
       <c r="A80">
         <v>78</v>
       </c>
@@ -2366,8 +3817,26 @@
       <c r="E80">
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="1:5" ht="37.5">
+      <c r="F80">
+        <v>0</v>
+      </c>
+      <c r="G80">
+        <v>0</v>
+      </c>
+      <c r="H80">
+        <v>0</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>0</v>
+      </c>
+      <c r="K80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" ht="37.5">
       <c r="A81">
         <v>79</v>
       </c>
@@ -2383,8 +3852,26 @@
       <c r="E81">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="1:5">
+      <c r="F81">
+        <v>0</v>
+      </c>
+      <c r="G81">
+        <v>0</v>
+      </c>
+      <c r="H81">
+        <v>0</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>0</v>
+      </c>
+      <c r="K81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11">
       <c r="A82">
         <v>80</v>
       </c>
@@ -2400,8 +3887,26 @@
       <c r="E82">
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="1:5">
+      <c r="F82">
+        <v>0</v>
+      </c>
+      <c r="G82">
+        <v>0</v>
+      </c>
+      <c r="H82">
+        <v>0</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>0</v>
+      </c>
+      <c r="K82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11">
       <c r="A83">
         <v>81</v>
       </c>
@@ -2417,8 +3922,26 @@
       <c r="E83">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:5">
+      <c r="F83">
+        <v>0</v>
+      </c>
+      <c r="G83">
+        <v>0</v>
+      </c>
+      <c r="H83">
+        <v>0</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>0</v>
+      </c>
+      <c r="K83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11">
       <c r="A84">
         <v>82</v>
       </c>
@@ -2434,8 +3957,26 @@
       <c r="E84">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:5">
+      <c r="F84">
+        <v>0</v>
+      </c>
+      <c r="G84">
+        <v>0</v>
+      </c>
+      <c r="H84">
+        <v>0</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>0</v>
+      </c>
+      <c r="K84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11">
       <c r="A85">
         <v>83</v>
       </c>
@@ -2451,8 +3992,26 @@
       <c r="E85">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="1:5">
+      <c r="F85">
+        <v>0</v>
+      </c>
+      <c r="G85">
+        <v>0</v>
+      </c>
+      <c r="H85">
+        <v>0</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>0</v>
+      </c>
+      <c r="K85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11">
       <c r="A86">
         <v>84</v>
       </c>
@@ -2468,8 +4027,26 @@
       <c r="E86">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="1:5">
+      <c r="F86">
+        <v>0</v>
+      </c>
+      <c r="G86">
+        <v>0</v>
+      </c>
+      <c r="H86">
+        <v>0</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>0</v>
+      </c>
+      <c r="K86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11">
       <c r="A87">
         <v>85</v>
       </c>
@@ -2485,8 +4062,26 @@
       <c r="E87">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="1:5">
+      <c r="F87">
+        <v>0</v>
+      </c>
+      <c r="G87">
+        <v>0</v>
+      </c>
+      <c r="H87">
+        <v>0</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>0</v>
+      </c>
+      <c r="K87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11">
       <c r="A88">
         <v>86</v>
       </c>
@@ -2500,10 +4095,28 @@
         <v>0</v>
       </c>
       <c r="E88">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5">
+        <v>2</v>
+      </c>
+      <c r="F88">
+        <v>0</v>
+      </c>
+      <c r="G88">
+        <v>1</v>
+      </c>
+      <c r="H88">
+        <v>0</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>0</v>
+      </c>
+      <c r="K88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11">
       <c r="A89">
         <v>87</v>
       </c>
@@ -2519,8 +4132,26 @@
       <c r="E89">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="1:5">
+      <c r="F89">
+        <v>0</v>
+      </c>
+      <c r="G89">
+        <v>0</v>
+      </c>
+      <c r="H89">
+        <v>0</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>0</v>
+      </c>
+      <c r="K89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11">
       <c r="A90">
         <v>88</v>
       </c>
@@ -2530,33 +4161,51 @@
       <c r="E90">
         <v>0</v>
       </c>
-    </row>
-    <row r="91" spans="1:5">
+      <c r="F90">
+        <v>0</v>
+      </c>
+      <c r="G90">
+        <v>0</v>
+      </c>
+      <c r="H90">
+        <v>0</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>0</v>
+      </c>
+      <c r="K90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11">
       <c r="A91">
         <v>89</v>
       </c>
     </row>
-    <row r="92" spans="1:5">
+    <row r="92" spans="1:11">
       <c r="A92">
         <v>90</v>
       </c>
     </row>
-    <row r="93" spans="1:5">
+    <row r="93" spans="1:11">
       <c r="A93">
         <v>91</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:11">
       <c r="A94">
         <v>92</v>
       </c>
     </row>
-    <row r="95" spans="1:5">
+    <row r="95" spans="1:11">
       <c r="A95">
         <v>93</v>
       </c>
     </row>
-    <row r="96" spans="1:5">
+    <row r="96" spans="1:11">
       <c r="A96">
         <v>94</v>
       </c>

--- a/Assets/Originals/Excels/Talk/TalkMessage.xlsx
+++ b/Assets/Originals/Excels/Talk/TalkMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Talk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEA97DCB-525A-431E-8CC1-F665A88F5E98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BE5FC2F-12B4-43B0-8C18-18A09138736C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="189">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -691,6 +691,387 @@
   </si>
   <si>
     <t>isBlackOutStatus</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>messageSizeJapanese</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>messageEnglish</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>messageSizeEnglish</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>speakerNameEnglish</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>You</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Kaname</t>
+  </si>
+  <si>
+    <t>Kaname</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Where... where am I?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Looks like you've woken up.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Mumei...?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>You died in the living world after committing a "sin."
+Everyone who has committed a sin is imprisoned here in Mumei.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>In other words, you're one of them too.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>My name is Kaname. 
+I'm your guide to "Mumei" .</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A sin...?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>That's right. A very, very grave sin.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>By the way, do you remember your own name?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Um... my name is... Huh...?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>I can't remember…</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>It's only natural that you can't.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Your name was discarded before you arrived at this labyrinth.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>My name... discarded?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>What do you mean?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>It’s a massive labyrinth located here in eternal world.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Those whose names are discarded 
+in the eternal world can never recall them on their own.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Eh..</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>And those who cannot remember their name…</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>...will wander this labyrinth forever, 
+enduring endless suffering.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>You'll end up the same way eventually.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>No... that's too cruel…</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Why...?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Because sinners don't need names.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>But don't worry.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>That way, you won't have to suffer or wander endlessly.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>...Do you want to escape this place?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>...I want to escape!</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>But... how do I get out?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>...There is one way.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>You must take on and overcome my trial.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>If you do that, you can escape.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>...Will you accept my trial?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>...I'll do it!</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>...Understood. 
+Then let me explain what the trial entails.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>To overcome the trial, 
+you must fulfill two conditions.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>If you can remember the sin you committed in the living world and escape this labyrinth, 
+I'll tell you your name.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>First: Escape this labyrinth. 
+Second: Remember the sin you committed in the living world.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Let me explain how to escape.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>To escape, you need to find and collect 'Documents' and 'Mystery Items' scattered 
+throughout every area of the labyrinth.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>First, obtain a Document. 
+Go ahead and pick up the one right in front of you.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Now, check the contents of the Document you just picked up.
+</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Next, obtain a Mystery Item.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Pick up the two Mystery Items in front of you.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Now, examine the Mystery Items you just picked up.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Finally, touch the "Blue Orb of Judgment" in the back.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>You must choose the Mystery Item that has 
+a deep connection to the content of the Document.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>That's all for the explanation. 
+Any questions?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Huh? You're not going to explain the sin I committed?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Nope.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Eh…</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Don't "eh" me.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>If you truly feel remorse for what you did, 
+you should be able to remember your sin right away.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>That's why the explanation ends here.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>That's okay with you, right?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Eh... Y-yeah…</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>One last thing — 
+there's an important warning about this labyrinth.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A warning?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Never let yourself be caught by the "Wanderers."</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Wanderers...?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>They're the monsters that lurk within Mumei.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Also, since not having a name would be inconvenient, 
+I'll temporarily call you 'IF'.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>IF, just don't let them catch you.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Got it?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>......Y-yeah…</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Alright then, let's begin the trial. 
+Please proceed down the passage behind you.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>IF, I'm rooting for you to clear the trial.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>...Finally... I can escape this labyrinth…</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Eh...? What is this...?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Why is the labyrinth still going!?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Isn't it obvious?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Because you still haven't escaped yet.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>..What do you mean I haven't escaped?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>I collected all the Documents and Mystery Items!</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Did you really think that was all?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>There are Documents and Mystery Items 
+in other areas, too.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>No way…</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Plus, you still haven't remembered the sin you committed, right?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>...!</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>That's why the trial isn't over yet.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>No…</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>The true terror of Mumei starts from here, IF.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>I know it's tough,</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>but let's keep going, okay? I'm counting on you, IF.</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1040,21 +1421,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K102"/>
+  <dimension ref="A1:O102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="63.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="17.625" customWidth="1"/>
-    <col min="4" max="4" width="27.75" customWidth="1"/>
-    <col min="5" max="5" width="22.5" customWidth="1"/>
-    <col min="6" max="6" width="13.625" customWidth="1"/>
-    <col min="8" max="8" width="17.125" customWidth="1"/>
-    <col min="9" max="9" width="28.125" customWidth="1"/>
-    <col min="10" max="10" width="13.125" customWidth="1"/>
-    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="4" max="4" width="19.75" customWidth="1"/>
+    <col min="5" max="5" width="47.125" customWidth="1"/>
+    <col min="6" max="7" width="19.75" customWidth="1"/>
+    <col min="8" max="8" width="27.75" customWidth="1"/>
+    <col min="9" max="9" width="22.5" customWidth="1"/>
+    <col min="10" max="10" width="13.625" customWidth="1"/>
+    <col min="12" max="12" width="17.125" customWidth="1"/>
+    <col min="13" max="13" width="28.125" customWidth="1"/>
+    <col min="14" max="14" width="13.125" customWidth="1"/>
+    <col min="15" max="15" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1065,43 +1449,49 @@
         <v>4</v>
       </c>
       <c r="D1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G1" t="s">
+        <v>100</v>
+      </c>
+      <c r="H1" t="s">
         <v>90</v>
       </c>
-      <c r="E1" t="s">
+      <c r="I1" t="s">
         <v>91</v>
       </c>
-      <c r="F1" t="s">
+      <c r="J1" t="s">
         <v>92</v>
       </c>
-      <c r="G1" t="s">
+      <c r="K1" t="s">
         <v>93</v>
       </c>
-      <c r="H1" t="s">
+      <c r="L1" t="s">
         <v>94</v>
       </c>
-      <c r="I1" t="s">
+      <c r="M1" t="s">
         <v>95</v>
       </c>
-      <c r="J1" t="s">
+      <c r="N1" t="s">
         <v>96</v>
       </c>
-      <c r="K1" t="s">
+      <c r="O1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:15">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
         <v>0</v>
       </c>
@@ -1117,8 +1507,20 @@
       <c r="K2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1129,16 +1531,16 @@
         <v>83</v>
       </c>
       <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E3" t="s">
+        <v>105</v>
+      </c>
+      <c r="F3" t="s">
+        <v>102</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -1152,8 +1554,20 @@
       <c r="K3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1164,20 +1578,20 @@
         <v>84</v>
       </c>
       <c r="D4">
+        <v>22</v>
+      </c>
+      <c r="E4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F4" t="s">
+        <v>84</v>
+      </c>
+      <c r="G4">
+        <v>22</v>
+      </c>
+      <c r="H4">
         <v>1</v>
       </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>3</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
       <c r="I4">
         <v>0</v>
       </c>
@@ -1185,10 +1599,22 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="37.5">
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="37.5">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1199,16 +1625,16 @@
         <v>3</v>
       </c>
       <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F5" t="s">
+        <v>104</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -1222,8 +1648,20 @@
       <c r="K5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1234,16 +1672,16 @@
         <v>82</v>
       </c>
       <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E6" t="s">
+        <v>107</v>
+      </c>
+      <c r="F6" t="s">
+        <v>102</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -1257,8 +1695,20 @@
       <c r="K6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1269,16 +1719,16 @@
         <v>3</v>
       </c>
       <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E7" t="s">
+        <v>120</v>
+      </c>
+      <c r="F7" t="s">
+        <v>103</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -1292,8 +1742,20 @@
       <c r="K7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" ht="37.5">
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="56.25">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1304,16 +1766,16 @@
         <v>3</v>
       </c>
       <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F8" t="s">
+        <v>103</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -1327,8 +1789,20 @@
       <c r="K8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1339,16 +1813,16 @@
         <v>3</v>
       </c>
       <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E9" t="s">
+        <v>109</v>
+      </c>
+      <c r="F9" t="s">
+        <v>103</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -1362,8 +1836,20 @@
       <c r="K9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1374,16 +1860,16 @@
         <v>82</v>
       </c>
       <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F10" t="s">
+        <v>102</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -1397,8 +1883,20 @@
       <c r="K10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1409,16 +1907,16 @@
         <v>3</v>
       </c>
       <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E11" t="s">
+        <v>112</v>
+      </c>
+      <c r="F11" t="s">
+        <v>103</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -1432,8 +1930,20 @@
       <c r="K11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1444,16 +1954,16 @@
         <v>3</v>
       </c>
       <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F12" t="s">
+        <v>103</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -1467,8 +1977,20 @@
       <c r="K12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:11">
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1479,31 +2001,43 @@
         <v>82</v>
       </c>
       <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
+        <v>22</v>
+      </c>
+      <c r="E13" t="s">
+        <v>114</v>
+      </c>
+      <c r="F13" t="s">
+        <v>102</v>
+      </c>
+      <c r="G13">
+        <v>22</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
         <v>1</v>
       </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
       <c r="J13">
         <v>0</v>
       </c>
       <c r="K13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11">
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1514,16 +2048,16 @@
         <v>82</v>
       </c>
       <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F14" t="s">
+        <v>102</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -1537,8 +2071,20 @@
       <c r="K14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:11">
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1549,16 +2095,16 @@
         <v>3</v>
       </c>
       <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F15" t="s">
+        <v>103</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -1572,8 +2118,20 @@
       <c r="K15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:11">
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="37.5">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1584,16 +2142,16 @@
         <v>3</v>
       </c>
       <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F16" t="s">
+        <v>103</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -1607,8 +2165,20 @@
       <c r="K16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:11">
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1619,16 +2189,16 @@
         <v>82</v>
       </c>
       <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E17" t="s">
+        <v>118</v>
+      </c>
+      <c r="F17" t="s">
+        <v>102</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -1642,8 +2212,20 @@
       <c r="K17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:11">
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1654,16 +2236,16 @@
         <v>82</v>
       </c>
       <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F18" t="s">
+        <v>102</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -1677,8 +2259,20 @@
       <c r="K18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" ht="37.5">
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="56.25">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1689,16 +2283,16 @@
         <v>3</v>
       </c>
       <c r="D19">
-        <v>0</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F19" t="s">
+        <v>103</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H19">
         <v>0</v>
@@ -1712,8 +2306,20 @@
       <c r="K19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:11">
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
       <c r="A20">
         <v>18</v>
       </c>
@@ -1724,16 +2330,16 @@
         <v>82</v>
       </c>
       <c r="D20">
-        <v>0</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="F20" t="s">
+        <v>102</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H20">
         <v>0</v>
@@ -1747,8 +2353,20 @@
       <c r="K20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:11">
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
       <c r="A21">
         <v>19</v>
       </c>
@@ -1759,31 +2377,40 @@
         <v>3</v>
       </c>
       <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21">
+        <v>22</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="G21">
+        <v>22</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
         <v>1</v>
       </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
       <c r="J21">
         <v>0</v>
       </c>
       <c r="K21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" ht="37.5">
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="37.5">
       <c r="A22">
         <v>20</v>
       </c>
@@ -1794,16 +2421,16 @@
         <v>3</v>
       </c>
       <c r="D22">
-        <v>0</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="F22" t="s">
+        <v>103</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H22">
         <v>0</v>
@@ -1817,8 +2444,20 @@
       <c r="K22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:11">
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
       <c r="A23">
         <v>21</v>
       </c>
@@ -1829,16 +2468,16 @@
         <v>3</v>
       </c>
       <c r="D23">
-        <v>0</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-      <c r="F23">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="F23" t="s">
+        <v>103</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -1852,8 +2491,20 @@
       <c r="K23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:11">
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
       <c r="A24">
         <v>22</v>
       </c>
@@ -1864,16 +2515,16 @@
         <v>82</v>
       </c>
       <c r="D24">
-        <v>0</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-      <c r="F24">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F24" t="s">
+        <v>102</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -1887,8 +2538,20 @@
       <c r="K24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:11">
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15">
       <c r="A25">
         <v>23</v>
       </c>
@@ -1899,16 +2562,16 @@
         <v>82</v>
       </c>
       <c r="D25">
-        <v>0</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-      <c r="F25">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="F25" t="s">
+        <v>102</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -1922,8 +2585,20 @@
       <c r="K25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:11">
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15">
       <c r="A26">
         <v>24</v>
       </c>
@@ -1934,16 +2609,16 @@
         <v>3</v>
       </c>
       <c r="D26">
-        <v>0</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-      <c r="F26">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F26" t="s">
+        <v>103</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -1957,8 +2632,20 @@
       <c r="K26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:11">
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15">
       <c r="A27">
         <v>25</v>
       </c>
@@ -1969,16 +2656,16 @@
         <v>3</v>
       </c>
       <c r="D27">
-        <v>0</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-      <c r="F27">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F27" t="s">
+        <v>103</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H27">
         <v>0</v>
@@ -1992,8 +2679,20 @@
       <c r="K27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" ht="37.5">
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" ht="56.25">
       <c r="A28">
         <v>26</v>
       </c>
@@ -2004,16 +2703,16 @@
         <v>3</v>
       </c>
       <c r="D28">
-        <v>0</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-      <c r="F28">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F28" t="s">
+        <v>103</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H28">
         <v>0</v>
@@ -2027,8 +2726,20 @@
       <c r="K28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" ht="37.5">
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" ht="37.5">
       <c r="A29">
         <v>27</v>
       </c>
@@ -2039,31 +2750,43 @@
         <v>3</v>
       </c>
       <c r="D29">
-        <v>0</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-      <c r="F29">
+        <v>22</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F29" t="s">
+        <v>103</v>
+      </c>
+      <c r="G29">
+        <v>22</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
         <v>1</v>
       </c>
-      <c r="G29">
+      <c r="K29">
         <v>1</v>
       </c>
-      <c r="H29">
-        <v>0</v>
-      </c>
-      <c r="I29">
-        <v>0</v>
-      </c>
-      <c r="J29">
-        <v>0</v>
-      </c>
-      <c r="K29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11">
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15">
       <c r="A30">
         <v>28</v>
       </c>
@@ -2074,16 +2797,16 @@
         <v>3</v>
       </c>
       <c r="D30">
-        <v>0</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-      <c r="F30">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F30" t="s">
+        <v>103</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H30">
         <v>0</v>
@@ -2097,8 +2820,20 @@
       <c r="K30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:11">
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15">
       <c r="A31">
         <v>29</v>
       </c>
@@ -2109,16 +2844,16 @@
         <v>82</v>
       </c>
       <c r="D31">
-        <v>0</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-      <c r="F31">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F31" t="s">
+        <v>102</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H31">
         <v>0</v>
@@ -2132,8 +2867,20 @@
       <c r="K31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:11">
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15">
       <c r="A32">
         <v>30</v>
       </c>
@@ -2144,16 +2891,16 @@
         <v>82</v>
       </c>
       <c r="D32">
-        <v>0</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-      <c r="F32">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F32" t="s">
+        <v>102</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H32">
         <v>0</v>
@@ -2167,8 +2914,20 @@
       <c r="K32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:11">
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15">
       <c r="A33">
         <v>31</v>
       </c>
@@ -2179,16 +2938,16 @@
         <v>3</v>
       </c>
       <c r="D33">
-        <v>0</v>
-      </c>
-      <c r="E33">
-        <v>0</v>
-      </c>
-      <c r="F33">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F33" t="s">
+        <v>103</v>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H33">
         <v>0</v>
@@ -2202,8 +2961,20 @@
       <c r="K33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:11">
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15">
       <c r="A34">
         <v>32</v>
       </c>
@@ -2214,16 +2985,16 @@
         <v>3</v>
       </c>
       <c r="D34">
-        <v>0</v>
-      </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
-      <c r="F34">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F34" t="s">
+        <v>103</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -2237,8 +3008,20 @@
       <c r="K34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:11">
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15">
       <c r="A35">
         <v>33</v>
       </c>
@@ -2249,31 +3032,43 @@
         <v>3</v>
       </c>
       <c r="D35">
-        <v>0</v>
-      </c>
-      <c r="E35">
-        <v>0</v>
-      </c>
-      <c r="F35">
+        <v>22</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F35" t="s">
+        <v>103</v>
+      </c>
+      <c r="G35">
+        <v>22</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
         <v>1</v>
       </c>
-      <c r="G35">
+      <c r="K35">
         <v>1</v>
       </c>
-      <c r="H35">
-        <v>0</v>
-      </c>
-      <c r="I35">
-        <v>0</v>
-      </c>
-      <c r="J35">
-        <v>0</v>
-      </c>
-      <c r="K35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11">
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15">
       <c r="A36">
         <v>34</v>
       </c>
@@ -2284,16 +3079,16 @@
         <v>3</v>
       </c>
       <c r="D36">
-        <v>0</v>
-      </c>
-      <c r="E36">
-        <v>0</v>
-      </c>
-      <c r="F36">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F36" t="s">
+        <v>103</v>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H36">
         <v>0</v>
@@ -2307,8 +3102,20 @@
       <c r="K36">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:11">
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15">
       <c r="A37">
         <v>35</v>
       </c>
@@ -2319,16 +3126,16 @@
         <v>82</v>
       </c>
       <c r="D37">
-        <v>0</v>
-      </c>
-      <c r="E37">
-        <v>0</v>
-      </c>
-      <c r="F37">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F37" t="s">
+        <v>102</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H37">
         <v>0</v>
@@ -2342,8 +3149,20 @@
       <c r="K37">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:11" ht="37.5">
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" ht="37.5">
       <c r="A38">
         <v>36</v>
       </c>
@@ -2354,43 +3173,49 @@
         <v>3</v>
       </c>
       <c r="D38">
-        <v>0</v>
-      </c>
-      <c r="E38">
-        <v>0</v>
-      </c>
-      <c r="F38">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F38" t="s">
+        <v>103</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38">
         <v>1</v>
       </c>
-      <c r="I38">
+      <c r="M38">
         <v>9</v>
       </c>
-      <c r="J38">
-        <v>0</v>
-      </c>
-      <c r="K38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11">
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15">
       <c r="A39">
         <v>37</v>
       </c>
       <c r="D39">
         <v>0</v>
       </c>
-      <c r="E39">
-        <v>0</v>
-      </c>
-      <c r="F39">
-        <v>0</v>
-      </c>
       <c r="G39">
         <v>0</v>
       </c>
@@ -2406,8 +3231,20 @@
       <c r="K39">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:11" ht="37.5">
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" ht="37.5">
       <c r="A40">
         <v>38</v>
       </c>
@@ -2418,16 +3255,16 @@
         <v>3</v>
       </c>
       <c r="D40">
-        <v>0</v>
-      </c>
-      <c r="E40">
-        <v>0</v>
-      </c>
-      <c r="F40">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F40" t="s">
+        <v>103</v>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H40">
         <v>0</v>
@@ -2441,8 +3278,20 @@
       <c r="K40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:11" ht="37.5">
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" ht="56.25">
       <c r="A41">
         <v>39</v>
       </c>
@@ -2453,16 +3302,16 @@
         <v>3</v>
       </c>
       <c r="D41">
-        <v>0</v>
-      </c>
-      <c r="E41">
-        <v>0</v>
-      </c>
-      <c r="F41">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F41" t="s">
+        <v>103</v>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H41">
         <v>0</v>
@@ -2476,8 +3325,20 @@
       <c r="K41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:11">
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15">
       <c r="A42">
         <v>40</v>
       </c>
@@ -2488,16 +3349,16 @@
         <v>3</v>
       </c>
       <c r="D42">
-        <v>0</v>
-      </c>
-      <c r="E42">
-        <v>0</v>
-      </c>
-      <c r="F42">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="F42" t="s">
+        <v>103</v>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H42">
         <v>0</v>
@@ -2511,8 +3372,20 @@
       <c r="K42">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:11" ht="37.5">
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" ht="56.25">
       <c r="A43">
         <v>41</v>
       </c>
@@ -2523,16 +3396,16 @@
         <v>3</v>
       </c>
       <c r="D43">
-        <v>0</v>
-      </c>
-      <c r="E43">
-        <v>0</v>
-      </c>
-      <c r="F43">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F43" t="s">
+        <v>103</v>
       </c>
       <c r="G43">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H43">
         <v>0</v>
@@ -2546,8 +3419,20 @@
       <c r="K43">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:11" ht="37.5">
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" ht="37.5">
       <c r="A44">
         <v>42</v>
       </c>
@@ -2558,31 +3443,43 @@
         <v>3</v>
       </c>
       <c r="D44">
-        <v>0</v>
-      </c>
-      <c r="E44">
-        <v>0</v>
-      </c>
-      <c r="F44">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F44" t="s">
+        <v>103</v>
       </c>
       <c r="G44">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="L44">
         <v>2</v>
       </c>
-      <c r="I44">
+      <c r="M44">
         <v>10</v>
       </c>
-      <c r="J44">
-        <v>0</v>
-      </c>
-      <c r="K44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11">
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" ht="56.25">
       <c r="A45">
         <v>43</v>
       </c>
@@ -2593,31 +3490,43 @@
         <v>3</v>
       </c>
       <c r="D45">
-        <v>0</v>
-      </c>
-      <c r="E45">
-        <v>0</v>
-      </c>
-      <c r="F45">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="F45" t="s">
+        <v>103</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>0</v>
+      </c>
+      <c r="L45">
         <v>2</v>
       </c>
-      <c r="I45">
+      <c r="M45">
         <v>11</v>
       </c>
-      <c r="J45">
-        <v>0</v>
-      </c>
-      <c r="K45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11">
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15">
       <c r="A46">
         <v>44</v>
       </c>
@@ -2628,16 +3537,16 @@
         <v>3</v>
       </c>
       <c r="D46">
-        <v>0</v>
-      </c>
-      <c r="E46">
-        <v>0</v>
-      </c>
-      <c r="F46">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="F46" t="s">
+        <v>103</v>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H46">
         <v>0</v>
@@ -2651,8 +3560,20 @@
       <c r="K46">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:11">
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15">
       <c r="A47">
         <v>45</v>
       </c>
@@ -2663,31 +3584,43 @@
         <v>3</v>
       </c>
       <c r="D47">
-        <v>0</v>
-      </c>
-      <c r="E47">
-        <v>0</v>
-      </c>
-      <c r="F47">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="F47" t="s">
+        <v>103</v>
       </c>
       <c r="G47">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H47">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+      <c r="L47">
+        <v>3</v>
+      </c>
+      <c r="M47">
         <v>12</v>
       </c>
-      <c r="J47">
-        <v>0</v>
-      </c>
-      <c r="K47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11">
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15">
       <c r="A48">
         <v>46</v>
       </c>
@@ -2698,31 +3631,43 @@
         <v>3</v>
       </c>
       <c r="D48">
-        <v>0</v>
-      </c>
-      <c r="E48">
-        <v>0</v>
-      </c>
-      <c r="F48">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="F48" t="s">
+        <v>103</v>
       </c>
       <c r="G48">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48">
         <v>2</v>
       </c>
-      <c r="I48">
+      <c r="M48">
         <v>13</v>
       </c>
-      <c r="J48">
-        <v>0</v>
-      </c>
-      <c r="K48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11">
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15">
       <c r="A49">
         <v>47</v>
       </c>
@@ -2733,16 +3678,16 @@
         <v>3</v>
       </c>
       <c r="D49">
-        <v>0</v>
-      </c>
-      <c r="E49">
-        <v>0</v>
-      </c>
-      <c r="F49">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="F49" t="s">
+        <v>103</v>
       </c>
       <c r="G49">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H49">
         <v>0</v>
@@ -2756,8 +3701,20 @@
       <c r="K49">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:11" ht="37.5">
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" ht="37.5">
       <c r="A50">
         <v>48</v>
       </c>
@@ -2768,31 +3725,43 @@
         <v>3</v>
       </c>
       <c r="D50">
-        <v>0</v>
-      </c>
-      <c r="E50">
-        <v>0</v>
-      </c>
-      <c r="F50">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="F50" t="s">
+        <v>103</v>
       </c>
       <c r="G50">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="L50">
         <v>2</v>
       </c>
-      <c r="I50">
+      <c r="M50">
         <v>14</v>
       </c>
-      <c r="J50">
-        <v>0</v>
-      </c>
-      <c r="K50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" ht="37.5">
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" ht="37.5">
       <c r="A51">
         <v>49</v>
       </c>
@@ -2803,16 +3772,16 @@
         <v>3</v>
       </c>
       <c r="D51">
-        <v>0</v>
-      </c>
-      <c r="E51">
-        <v>0</v>
-      </c>
-      <c r="F51">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="F51" t="s">
+        <v>103</v>
       </c>
       <c r="G51">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H51">
         <v>0</v>
@@ -2826,8 +3795,20 @@
       <c r="K51">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:11">
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <v>0</v>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15">
       <c r="A52">
         <v>50</v>
       </c>
@@ -2838,16 +3819,16 @@
         <v>82</v>
       </c>
       <c r="D52">
-        <v>0</v>
-      </c>
-      <c r="E52">
-        <v>0</v>
-      </c>
-      <c r="F52">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F52" t="s">
+        <v>102</v>
       </c>
       <c r="G52">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H52">
         <v>0</v>
@@ -2861,8 +3842,20 @@
       <c r="K52">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:11">
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52">
+        <v>0</v>
+      </c>
+      <c r="N52">
+        <v>0</v>
+      </c>
+      <c r="O52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15">
       <c r="A53">
         <v>51</v>
       </c>
@@ -2873,16 +3866,16 @@
         <v>3</v>
       </c>
       <c r="D53">
-        <v>0</v>
-      </c>
-      <c r="E53">
-        <v>0</v>
-      </c>
-      <c r="F53">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="F53" t="s">
+        <v>103</v>
       </c>
       <c r="G53">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H53">
         <v>0</v>
@@ -2896,8 +3889,20 @@
       <c r="K53">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:11">
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53">
+        <v>0</v>
+      </c>
+      <c r="N53">
+        <v>0</v>
+      </c>
+      <c r="O53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15">
       <c r="A54">
         <v>52</v>
       </c>
@@ -2908,16 +3913,16 @@
         <v>82</v>
       </c>
       <c r="D54">
-        <v>0</v>
-      </c>
-      <c r="E54">
-        <v>0</v>
-      </c>
-      <c r="F54">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="F54" t="s">
+        <v>102</v>
       </c>
       <c r="G54">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H54">
         <v>0</v>
@@ -2931,8 +3936,20 @@
       <c r="K54">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:11">
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54">
+        <v>0</v>
+      </c>
+      <c r="N54">
+        <v>0</v>
+      </c>
+      <c r="O54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15">
       <c r="A55">
         <v>53</v>
       </c>
@@ -2943,16 +3960,16 @@
         <v>3</v>
       </c>
       <c r="D55">
-        <v>0</v>
-      </c>
-      <c r="E55">
-        <v>0</v>
-      </c>
-      <c r="F55">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="F55" t="s">
+        <v>103</v>
       </c>
       <c r="G55">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H55">
         <v>0</v>
@@ -2966,8 +3983,20 @@
       <c r="K55">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:11" ht="37.5">
+      <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55">
+        <v>0</v>
+      </c>
+      <c r="N55">
+        <v>0</v>
+      </c>
+      <c r="O55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" ht="37.5">
       <c r="A56">
         <v>54</v>
       </c>
@@ -2978,16 +4007,16 @@
         <v>3</v>
       </c>
       <c r="D56">
-        <v>0</v>
-      </c>
-      <c r="E56">
-        <v>0</v>
-      </c>
-      <c r="F56">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="F56" t="s">
+        <v>103</v>
       </c>
       <c r="G56">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H56">
         <v>0</v>
@@ -3001,8 +4030,20 @@
       <c r="K56">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:11">
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56">
+        <v>0</v>
+      </c>
+      <c r="N56">
+        <v>0</v>
+      </c>
+      <c r="O56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15">
       <c r="A57">
         <v>55</v>
       </c>
@@ -3013,16 +4054,16 @@
         <v>3</v>
       </c>
       <c r="D57">
-        <v>0</v>
-      </c>
-      <c r="E57">
-        <v>0</v>
-      </c>
-      <c r="F57">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F57" t="s">
+        <v>103</v>
       </c>
       <c r="G57">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H57">
         <v>0</v>
@@ -3036,8 +4077,20 @@
       <c r="K57">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:11" ht="37.5">
+      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57">
+        <v>0</v>
+      </c>
+      <c r="N57">
+        <v>0</v>
+      </c>
+      <c r="O57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" ht="37.5">
       <c r="A58">
         <v>56</v>
       </c>
@@ -3048,16 +4101,16 @@
         <v>3</v>
       </c>
       <c r="D58">
-        <v>0</v>
-      </c>
-      <c r="E58">
-        <v>0</v>
-      </c>
-      <c r="F58">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="F58" t="s">
+        <v>103</v>
       </c>
       <c r="G58">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H58">
         <v>0</v>
@@ -3071,8 +4124,20 @@
       <c r="K58">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:11">
+      <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58">
+        <v>0</v>
+      </c>
+      <c r="N58">
+        <v>0</v>
+      </c>
+      <c r="O58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15">
       <c r="A59">
         <v>57</v>
       </c>
@@ -3083,16 +4148,16 @@
         <v>3</v>
       </c>
       <c r="D59">
-        <v>0</v>
-      </c>
-      <c r="E59">
-        <v>0</v>
-      </c>
-      <c r="F59">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F59" t="s">
+        <v>103</v>
       </c>
       <c r="G59">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H59">
         <v>0</v>
@@ -3106,8 +4171,20 @@
       <c r="K59">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:11">
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59">
+        <v>0</v>
+      </c>
+      <c r="N59">
+        <v>0</v>
+      </c>
+      <c r="O59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15">
       <c r="A60">
         <v>58</v>
       </c>
@@ -3118,16 +4195,16 @@
         <v>82</v>
       </c>
       <c r="D60">
-        <v>0</v>
-      </c>
-      <c r="E60">
-        <v>0</v>
-      </c>
-      <c r="F60">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="F60" t="s">
+        <v>102</v>
       </c>
       <c r="G60">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H60">
         <v>0</v>
@@ -3141,8 +4218,20 @@
       <c r="K60">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:11">
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60">
+        <v>0</v>
+      </c>
+      <c r="N60">
+        <v>0</v>
+      </c>
+      <c r="O60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" ht="37.5">
       <c r="A61">
         <v>59</v>
       </c>
@@ -3153,16 +4242,16 @@
         <v>3</v>
       </c>
       <c r="D61">
-        <v>0</v>
-      </c>
-      <c r="E61">
-        <v>0</v>
-      </c>
-      <c r="F61">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="F61" t="s">
+        <v>103</v>
       </c>
       <c r="G61">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H61">
         <v>0</v>
@@ -3176,8 +4265,20 @@
       <c r="K61">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:11">
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61">
+        <v>0</v>
+      </c>
+      <c r="N61">
+        <v>0</v>
+      </c>
+      <c r="O61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15">
       <c r="A62">
         <v>60</v>
       </c>
@@ -3188,31 +4289,43 @@
         <v>82</v>
       </c>
       <c r="D62">
-        <v>0</v>
-      </c>
-      <c r="E62">
+        <v>22</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F62" t="s">
+        <v>102</v>
+      </c>
+      <c r="G62">
+        <v>22</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+      <c r="I62">
         <v>1</v>
       </c>
-      <c r="F62">
-        <v>0</v>
-      </c>
-      <c r="G62">
-        <v>0</v>
-      </c>
-      <c r="H62">
-        <v>0</v>
-      </c>
-      <c r="I62">
-        <v>0</v>
-      </c>
       <c r="J62">
         <v>0</v>
       </c>
       <c r="K62">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:11">
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62">
+        <v>0</v>
+      </c>
+      <c r="N62">
+        <v>0</v>
+      </c>
+      <c r="O62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15">
       <c r="A63">
         <v>61</v>
       </c>
@@ -3223,16 +4336,16 @@
         <v>3</v>
       </c>
       <c r="D63">
-        <v>0</v>
-      </c>
-      <c r="E63">
-        <v>0</v>
-      </c>
-      <c r="F63">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="F63" t="s">
+        <v>103</v>
       </c>
       <c r="G63">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H63">
         <v>0</v>
@@ -3246,8 +4359,20 @@
       <c r="K63">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:11">
+      <c r="L63">
+        <v>0</v>
+      </c>
+      <c r="M63">
+        <v>0</v>
+      </c>
+      <c r="N63">
+        <v>0</v>
+      </c>
+      <c r="O63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15">
       <c r="A64">
         <v>62</v>
       </c>
@@ -3258,16 +4383,16 @@
         <v>82</v>
       </c>
       <c r="D64">
-        <v>0</v>
-      </c>
-      <c r="E64">
-        <v>0</v>
-      </c>
-      <c r="F64">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F64" t="s">
+        <v>102</v>
       </c>
       <c r="G64">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H64">
         <v>0</v>
@@ -3281,8 +4406,20 @@
       <c r="K64">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:11">
+      <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64">
+        <v>0</v>
+      </c>
+      <c r="N64">
+        <v>0</v>
+      </c>
+      <c r="O64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15">
       <c r="A65">
         <v>63</v>
       </c>
@@ -3293,16 +4430,16 @@
         <v>3</v>
       </c>
       <c r="D65">
-        <v>0</v>
-      </c>
-      <c r="E65">
-        <v>0</v>
-      </c>
-      <c r="F65">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="F65" t="s">
+        <v>103</v>
       </c>
       <c r="G65">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H65">
         <v>0</v>
@@ -3316,8 +4453,20 @@
       <c r="K65">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:11">
+      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65">
+        <v>0</v>
+      </c>
+      <c r="N65">
+        <v>0</v>
+      </c>
+      <c r="O65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15">
       <c r="A66">
         <v>64</v>
       </c>
@@ -3328,16 +4477,16 @@
         <v>3</v>
       </c>
       <c r="D66">
-        <v>0</v>
-      </c>
-      <c r="E66">
-        <v>0</v>
-      </c>
-      <c r="F66">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="F66" t="s">
+        <v>103</v>
       </c>
       <c r="G66">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H66">
         <v>0</v>
@@ -3351,8 +4500,20 @@
       <c r="K66">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:11">
+      <c r="L66">
+        <v>0</v>
+      </c>
+      <c r="M66">
+        <v>0</v>
+      </c>
+      <c r="N66">
+        <v>0</v>
+      </c>
+      <c r="O66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15">
       <c r="A67">
         <v>65</v>
       </c>
@@ -3363,16 +4524,16 @@
         <v>3</v>
       </c>
       <c r="D67">
-        <v>0</v>
-      </c>
-      <c r="E67">
-        <v>0</v>
-      </c>
-      <c r="F67">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="F67" t="s">
+        <v>103</v>
       </c>
       <c r="G67">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H67">
         <v>0</v>
@@ -3386,8 +4547,20 @@
       <c r="K67">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:11">
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67">
+        <v>0</v>
+      </c>
+      <c r="N67">
+        <v>0</v>
+      </c>
+      <c r="O67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15">
       <c r="A68">
         <v>66</v>
       </c>
@@ -3398,16 +4571,16 @@
         <v>82</v>
       </c>
       <c r="D68">
-        <v>0</v>
-      </c>
-      <c r="E68">
-        <v>0</v>
-      </c>
-      <c r="F68">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F68" t="s">
+        <v>102</v>
       </c>
       <c r="G68">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H68">
         <v>0</v>
@@ -3421,8 +4594,20 @@
       <c r="K68">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="1:11" ht="37.5">
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68">
+        <v>0</v>
+      </c>
+      <c r="N68">
+        <v>0</v>
+      </c>
+      <c r="O68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" ht="37.5">
       <c r="A69">
         <v>67</v>
       </c>
@@ -3433,16 +4618,16 @@
         <v>3</v>
       </c>
       <c r="D69">
-        <v>0</v>
-      </c>
-      <c r="E69">
-        <v>0</v>
-      </c>
-      <c r="F69">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F69" t="s">
+        <v>103</v>
       </c>
       <c r="G69">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H69">
         <v>0</v>
@@ -3456,8 +4641,20 @@
       <c r="K69">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:11">
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69">
+        <v>0</v>
+      </c>
+      <c r="N69">
+        <v>0</v>
+      </c>
+      <c r="O69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15">
       <c r="A70">
         <v>68</v>
       </c>
@@ -3468,16 +4665,16 @@
         <v>3</v>
       </c>
       <c r="D70">
-        <v>0</v>
-      </c>
-      <c r="E70">
-        <v>0</v>
-      </c>
-      <c r="F70">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="F70" t="s">
+        <v>103</v>
       </c>
       <c r="G70">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H70">
         <v>0</v>
@@ -3486,25 +4683,31 @@
         <v>0</v>
       </c>
       <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70">
+        <v>0</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70">
+        <v>0</v>
+      </c>
+      <c r="N70">
         <v>1</v>
       </c>
-      <c r="K70">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11">
+      <c r="O70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15">
       <c r="A71">
         <v>69</v>
       </c>
       <c r="D71">
         <v>0</v>
       </c>
-      <c r="E71">
-        <v>0</v>
-      </c>
-      <c r="F71">
-        <v>0</v>
-      </c>
       <c r="G71">
         <v>0</v>
       </c>
@@ -3520,8 +4723,20 @@
       <c r="K71">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:11">
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71">
+        <v>0</v>
+      </c>
+      <c r="N71">
+        <v>0</v>
+      </c>
+      <c r="O71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15">
       <c r="A72">
         <v>70</v>
       </c>
@@ -3532,31 +4747,43 @@
         <v>82</v>
       </c>
       <c r="D72">
-        <v>0</v>
-      </c>
-      <c r="E72">
-        <v>0</v>
-      </c>
-      <c r="F72">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="F72" t="s">
+        <v>102</v>
       </c>
       <c r="G72">
+        <v>22</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>0</v>
+      </c>
+      <c r="K72">
         <v>1</v>
       </c>
-      <c r="H72">
-        <v>0</v>
-      </c>
-      <c r="I72">
-        <v>0</v>
-      </c>
-      <c r="J72">
-        <v>0</v>
-      </c>
-      <c r="K72">
+      <c r="L72">
+        <v>0</v>
+      </c>
+      <c r="M72">
+        <v>0</v>
+      </c>
+      <c r="N72">
+        <v>0</v>
+      </c>
+      <c r="O72">
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:11">
+    <row r="73" spans="1:15">
       <c r="A73">
         <v>71</v>
       </c>
@@ -3567,16 +4794,16 @@
         <v>82</v>
       </c>
       <c r="D73">
-        <v>0</v>
-      </c>
-      <c r="E73">
-        <v>0</v>
-      </c>
-      <c r="F73">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="F73" t="s">
+        <v>102</v>
       </c>
       <c r="G73">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H73">
         <v>0</v>
@@ -3590,8 +4817,20 @@
       <c r="K73">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:11">
+      <c r="L73">
+        <v>0</v>
+      </c>
+      <c r="M73">
+        <v>0</v>
+      </c>
+      <c r="N73">
+        <v>0</v>
+      </c>
+      <c r="O73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15">
       <c r="A74">
         <v>72</v>
       </c>
@@ -3602,16 +4841,16 @@
         <v>82</v>
       </c>
       <c r="D74">
-        <v>0</v>
-      </c>
-      <c r="E74">
-        <v>0</v>
-      </c>
-      <c r="F74">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="F74" t="s">
+        <v>102</v>
       </c>
       <c r="G74">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H74">
         <v>0</v>
@@ -3625,8 +4864,20 @@
       <c r="K74">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="1:11">
+      <c r="L74">
+        <v>0</v>
+      </c>
+      <c r="M74">
+        <v>0</v>
+      </c>
+      <c r="N74">
+        <v>0</v>
+      </c>
+      <c r="O74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15">
       <c r="A75">
         <v>73</v>
       </c>
@@ -3637,16 +4888,16 @@
         <v>3</v>
       </c>
       <c r="D75">
-        <v>0</v>
-      </c>
-      <c r="E75">
-        <v>0</v>
-      </c>
-      <c r="F75">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="F75" t="s">
+        <v>103</v>
       </c>
       <c r="G75">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H75">
         <v>0</v>
@@ -3660,8 +4911,20 @@
       <c r="K75">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:11">
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75">
+        <v>0</v>
+      </c>
+      <c r="N75">
+        <v>0</v>
+      </c>
+      <c r="O75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15">
       <c r="A76">
         <v>74</v>
       </c>
@@ -3672,16 +4935,16 @@
         <v>3</v>
       </c>
       <c r="D76">
-        <v>0</v>
-      </c>
-      <c r="E76">
-        <v>0</v>
-      </c>
-      <c r="F76">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="F76" t="s">
+        <v>103</v>
       </c>
       <c r="G76">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H76">
         <v>0</v>
@@ -3695,8 +4958,20 @@
       <c r="K76">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:11">
+      <c r="L76">
+        <v>0</v>
+      </c>
+      <c r="M76">
+        <v>0</v>
+      </c>
+      <c r="N76">
+        <v>0</v>
+      </c>
+      <c r="O76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15">
       <c r="A77">
         <v>75</v>
       </c>
@@ -3707,16 +4982,16 @@
         <v>82</v>
       </c>
       <c r="D77">
-        <v>0</v>
-      </c>
-      <c r="E77">
-        <v>0</v>
-      </c>
-      <c r="F77">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="F77" t="s">
+        <v>102</v>
       </c>
       <c r="G77">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H77">
         <v>0</v>
@@ -3730,8 +5005,20 @@
       <c r="K77">
         <v>0</v>
       </c>
-    </row>
-    <row r="78" spans="1:11" ht="37.5">
+      <c r="L77">
+        <v>0</v>
+      </c>
+      <c r="M77">
+        <v>0</v>
+      </c>
+      <c r="N77">
+        <v>0</v>
+      </c>
+      <c r="O77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" ht="37.5">
       <c r="A78">
         <v>76</v>
       </c>
@@ -3742,16 +5029,16 @@
         <v>82</v>
       </c>
       <c r="D78">
-        <v>0</v>
-      </c>
-      <c r="E78">
-        <v>0</v>
-      </c>
-      <c r="F78">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="F78" t="s">
+        <v>102</v>
       </c>
       <c r="G78">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H78">
         <v>0</v>
@@ -3765,8 +5052,20 @@
       <c r="K78">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="1:11">
+      <c r="L78">
+        <v>0</v>
+      </c>
+      <c r="M78">
+        <v>0</v>
+      </c>
+      <c r="N78">
+        <v>0</v>
+      </c>
+      <c r="O78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15">
       <c r="A79">
         <v>77</v>
       </c>
@@ -3777,16 +5076,16 @@
         <v>3</v>
       </c>
       <c r="D79">
-        <v>0</v>
-      </c>
-      <c r="E79">
-        <v>0</v>
-      </c>
-      <c r="F79">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="F79" t="s">
+        <v>103</v>
       </c>
       <c r="G79">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H79">
         <v>0</v>
@@ -3800,8 +5099,20 @@
       <c r="K79">
         <v>0</v>
       </c>
-    </row>
-    <row r="80" spans="1:11">
+      <c r="L79">
+        <v>0</v>
+      </c>
+      <c r="M79">
+        <v>0</v>
+      </c>
+      <c r="N79">
+        <v>0</v>
+      </c>
+      <c r="O79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15">
       <c r="A80">
         <v>78</v>
       </c>
@@ -3812,16 +5123,16 @@
         <v>82</v>
       </c>
       <c r="D80">
-        <v>0</v>
-      </c>
-      <c r="E80">
-        <v>0</v>
-      </c>
-      <c r="F80">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="F80" t="s">
+        <v>102</v>
       </c>
       <c r="G80">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H80">
         <v>0</v>
@@ -3835,8 +5146,20 @@
       <c r="K80">
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="1:11" ht="37.5">
+      <c r="L80">
+        <v>0</v>
+      </c>
+      <c r="M80">
+        <v>0</v>
+      </c>
+      <c r="N80">
+        <v>0</v>
+      </c>
+      <c r="O80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" ht="37.5">
       <c r="A81">
         <v>79</v>
       </c>
@@ -3847,16 +5170,16 @@
         <v>3</v>
       </c>
       <c r="D81">
-        <v>0</v>
-      </c>
-      <c r="E81">
-        <v>0</v>
-      </c>
-      <c r="F81">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="F81" t="s">
+        <v>103</v>
       </c>
       <c r="G81">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H81">
         <v>0</v>
@@ -3870,8 +5193,20 @@
       <c r="K81">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="1:11">
+      <c r="L81">
+        <v>0</v>
+      </c>
+      <c r="M81">
+        <v>0</v>
+      </c>
+      <c r="N81">
+        <v>0</v>
+      </c>
+      <c r="O81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15">
       <c r="A82">
         <v>80</v>
       </c>
@@ -3882,16 +5217,16 @@
         <v>82</v>
       </c>
       <c r="D82">
-        <v>0</v>
-      </c>
-      <c r="E82">
-        <v>0</v>
-      </c>
-      <c r="F82">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F82" t="s">
+        <v>102</v>
       </c>
       <c r="G82">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H82">
         <v>0</v>
@@ -3905,8 +5240,20 @@
       <c r="K82">
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="1:11">
+      <c r="L82">
+        <v>0</v>
+      </c>
+      <c r="M82">
+        <v>0</v>
+      </c>
+      <c r="N82">
+        <v>0</v>
+      </c>
+      <c r="O82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" ht="37.5">
       <c r="A83">
         <v>81</v>
       </c>
@@ -3917,16 +5264,16 @@
         <v>3</v>
       </c>
       <c r="D83">
-        <v>0</v>
-      </c>
-      <c r="E83">
-        <v>0</v>
-      </c>
-      <c r="F83">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F83" t="s">
+        <v>103</v>
       </c>
       <c r="G83">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H83">
         <v>0</v>
@@ -3940,8 +5287,20 @@
       <c r="K83">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:11">
+      <c r="L83">
+        <v>0</v>
+      </c>
+      <c r="M83">
+        <v>0</v>
+      </c>
+      <c r="N83">
+        <v>0</v>
+      </c>
+      <c r="O83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15">
       <c r="A84">
         <v>82</v>
       </c>
@@ -3952,16 +5311,16 @@
         <v>82</v>
       </c>
       <c r="D84">
-        <v>0</v>
-      </c>
-      <c r="E84">
-        <v>0</v>
-      </c>
-      <c r="F84">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="F84" t="s">
+        <v>102</v>
       </c>
       <c r="G84">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H84">
         <v>0</v>
@@ -3975,8 +5334,20 @@
       <c r="K84">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:11">
+      <c r="L84">
+        <v>0</v>
+      </c>
+      <c r="M84">
+        <v>0</v>
+      </c>
+      <c r="N84">
+        <v>0</v>
+      </c>
+      <c r="O84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15">
       <c r="A85">
         <v>83</v>
       </c>
@@ -3987,16 +5358,16 @@
         <v>3</v>
       </c>
       <c r="D85">
-        <v>0</v>
-      </c>
-      <c r="E85">
-        <v>0</v>
-      </c>
-      <c r="F85">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="F85" t="s">
+        <v>103</v>
       </c>
       <c r="G85">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H85">
         <v>0</v>
@@ -4010,8 +5381,20 @@
       <c r="K85">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="1:11">
+      <c r="L85">
+        <v>0</v>
+      </c>
+      <c r="M85">
+        <v>0</v>
+      </c>
+      <c r="N85">
+        <v>0</v>
+      </c>
+      <c r="O85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15">
       <c r="A86">
         <v>84</v>
       </c>
@@ -4022,16 +5405,16 @@
         <v>82</v>
       </c>
       <c r="D86">
-        <v>0</v>
-      </c>
-      <c r="E86">
-        <v>0</v>
-      </c>
-      <c r="F86">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="F86" t="s">
+        <v>102</v>
       </c>
       <c r="G86">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H86">
         <v>0</v>
@@ -4045,8 +5428,20 @@
       <c r="K86">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="1:11">
+      <c r="L86">
+        <v>0</v>
+      </c>
+      <c r="M86">
+        <v>0</v>
+      </c>
+      <c r="N86">
+        <v>0</v>
+      </c>
+      <c r="O86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15">
       <c r="A87">
         <v>85</v>
       </c>
@@ -4057,16 +5452,16 @@
         <v>3</v>
       </c>
       <c r="D87">
-        <v>0</v>
-      </c>
-      <c r="E87">
-        <v>0</v>
-      </c>
-      <c r="F87">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="F87" t="s">
+        <v>103</v>
       </c>
       <c r="G87">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H87">
         <v>0</v>
@@ -4080,8 +5475,20 @@
       <c r="K87">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="1:11">
+      <c r="L87">
+        <v>0</v>
+      </c>
+      <c r="M87">
+        <v>0</v>
+      </c>
+      <c r="N87">
+        <v>0</v>
+      </c>
+      <c r="O87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15">
       <c r="A88">
         <v>86</v>
       </c>
@@ -4092,31 +5499,43 @@
         <v>3</v>
       </c>
       <c r="D88">
-        <v>0</v>
-      </c>
-      <c r="E88">
+        <v>22</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="F88" t="s">
+        <v>103</v>
+      </c>
+      <c r="G88">
+        <v>22</v>
+      </c>
+      <c r="H88">
+        <v>0</v>
+      </c>
+      <c r="I88">
         <v>2</v>
       </c>
-      <c r="F88">
-        <v>0</v>
-      </c>
-      <c r="G88">
+      <c r="J88">
+        <v>0</v>
+      </c>
+      <c r="K88">
         <v>1</v>
       </c>
-      <c r="H88">
-        <v>0</v>
-      </c>
-      <c r="I88">
-        <v>0</v>
-      </c>
-      <c r="J88">
-        <v>0</v>
-      </c>
-      <c r="K88">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11">
+      <c r="L88">
+        <v>0</v>
+      </c>
+      <c r="M88">
+        <v>0</v>
+      </c>
+      <c r="N88">
+        <v>0</v>
+      </c>
+      <c r="O88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15">
       <c r="A89">
         <v>87</v>
       </c>
@@ -4127,16 +5546,16 @@
         <v>3</v>
       </c>
       <c r="D89">
-        <v>0</v>
-      </c>
-      <c r="E89">
-        <v>0</v>
-      </c>
-      <c r="F89">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="F89" t="s">
+        <v>103</v>
       </c>
       <c r="G89">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H89">
         <v>0</v>
@@ -4150,23 +5569,23 @@
       <c r="K89">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="1:11">
+      <c r="L89">
+        <v>0</v>
+      </c>
+      <c r="M89">
+        <v>0</v>
+      </c>
+      <c r="N89">
+        <v>0</v>
+      </c>
+      <c r="O89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15">
       <c r="A90">
         <v>88</v>
       </c>
-      <c r="D90">
-        <v>0</v>
-      </c>
-      <c r="E90">
-        <v>0</v>
-      </c>
-      <c r="F90">
-        <v>0</v>
-      </c>
-      <c r="G90">
-        <v>0</v>
-      </c>
       <c r="H90">
         <v>0</v>
       </c>
@@ -4179,33 +5598,45 @@
       <c r="K90">
         <v>0</v>
       </c>
-    </row>
-    <row r="91" spans="1:11">
+      <c r="L90">
+        <v>0</v>
+      </c>
+      <c r="M90">
+        <v>0</v>
+      </c>
+      <c r="N90">
+        <v>0</v>
+      </c>
+      <c r="O90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15">
       <c r="A91">
         <v>89</v>
       </c>
     </row>
-    <row r="92" spans="1:11">
+    <row r="92" spans="1:15">
       <c r="A92">
         <v>90</v>
       </c>
     </row>
-    <row r="93" spans="1:11">
+    <row r="93" spans="1:15">
       <c r="A93">
         <v>91</v>
       </c>
     </row>
-    <row r="94" spans="1:11">
+    <row r="94" spans="1:15">
       <c r="A94">
         <v>92</v>
       </c>
     </row>
-    <row r="95" spans="1:11">
+    <row r="95" spans="1:15">
       <c r="A95">
         <v>93</v>
       </c>
     </row>
-    <row r="96" spans="1:11">
+    <row r="96" spans="1:15">
       <c r="A96">
         <v>94</v>
       </c>

--- a/Assets/Originals/Excels/Talk/TalkMessage.xlsx
+++ b/Assets/Originals/Excels/Talk/TalkMessage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Talk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BE5FC2F-12B4-43B0-8C18-18A09138736C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DC5E619-E3F7-4F8F-864F-EC1C5E6636B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -284,10 +284,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>目の前にある2つのミステリーアイテムを手に取ってごらん</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>今手に取ったミステリーアイテムを確認してごらん</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -628,11 +624,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>まず　ドキュメントを入手すること
-試しに目の前にあるドキュメントを手に取ってごらん</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>次に　ミステリーアイテムを入手すること</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -890,11 +881,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>First, obtain a Document. 
-Go ahead and pick up the one right in front of you.</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t xml:space="preserve">Now, check the contents of the Document you just picked up.
 </t>
     <phoneticPr fontId="1"/>
@@ -904,10 +890,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Pick up the two Mystery Items in front of you.</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Now, examine the Mystery Items you just picked up.</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1072,6 +1054,24 @@
   </si>
   <si>
     <t>but let's keep going, okay? I'm counting on you, IF.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>First, obtain a Document. 
+Go ahead and open the drawer right in front of you.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>まず　ドキュメントを入手すること
+試しに目の前の引き出しを開けてごらん</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Open the two drawers right in front of you.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目の前にある2つの引き出しを開けてごらん</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1449,40 +1449,40 @@
         <v>4</v>
       </c>
       <c r="D1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G1" t="s">
         <v>98</v>
       </c>
-      <c r="E1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G1" t="s">
-        <v>100</v>
-      </c>
       <c r="H1" t="s">
+        <v>88</v>
+      </c>
+      <c r="I1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J1" t="s">
         <v>90</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>91</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>92</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>93</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>94</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>95</v>
-      </c>
-      <c r="N1" t="s">
-        <v>96</v>
-      </c>
-      <c r="O1" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:15">
@@ -1528,16 +1528,16 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D3">
         <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G3">
         <v>22</v>
@@ -1575,16 +1575,16 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D4">
         <v>22</v>
       </c>
       <c r="E4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G4">
         <v>22</v>
@@ -1628,10 +1628,10 @@
         <v>22</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G5">
         <v>22</v>
@@ -1669,16 +1669,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D6">
         <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G6">
         <v>22</v>
@@ -1722,10 +1722,10 @@
         <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F7" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G7">
         <v>22</v>
@@ -1769,10 +1769,10 @@
         <v>22</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G8">
         <v>22</v>
@@ -1816,10 +1816,10 @@
         <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F9" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G9">
         <v>22</v>
@@ -1857,16 +1857,16 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D10">
         <v>22</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F10" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G10">
         <v>22</v>
@@ -1910,10 +1910,10 @@
         <v>22</v>
       </c>
       <c r="E11" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F11" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G11">
         <v>22</v>
@@ -1957,10 +1957,10 @@
         <v>22</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F12" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G12">
         <v>22</v>
@@ -1998,16 +1998,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D13">
         <v>22</v>
       </c>
       <c r="E13" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G13">
         <v>22</v>
@@ -2045,16 +2045,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D14">
         <v>22</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F14" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G14">
         <v>22</v>
@@ -2098,10 +2098,10 @@
         <v>22</v>
       </c>
       <c r="E15" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F15" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G15">
         <v>22</v>
@@ -2145,10 +2145,10 @@
         <v>22</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F16" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G16">
         <v>22</v>
@@ -2186,16 +2186,16 @@
         <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D17">
         <v>22</v>
       </c>
       <c r="E17" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F17" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G17">
         <v>22</v>
@@ -2233,16 +2233,16 @@
         <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D18">
         <v>22</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F18" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G18">
         <v>22</v>
@@ -2286,10 +2286,10 @@
         <v>22</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F19" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G19">
         <v>22</v>
@@ -2327,16 +2327,16 @@
         <v>21</v>
       </c>
       <c r="C20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D20">
         <v>22</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F20" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G20">
         <v>22</v>
@@ -2380,7 +2380,7 @@
         <v>22</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G21">
         <v>22</v>
@@ -2424,10 +2424,10 @@
         <v>22</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F22" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G22">
         <v>22</v>
@@ -2471,10 +2471,10 @@
         <v>22</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F23" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G23">
         <v>22</v>
@@ -2512,16 +2512,16 @@
         <v>20</v>
       </c>
       <c r="C24" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D24">
         <v>22</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F24" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G24">
         <v>22</v>
@@ -2559,16 +2559,16 @@
         <v>19</v>
       </c>
       <c r="C25" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D25">
         <v>22</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F25" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G25">
         <v>22</v>
@@ -2612,10 +2612,10 @@
         <v>22</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F26" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G26">
         <v>22</v>
@@ -2659,10 +2659,10 @@
         <v>22</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F27" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G27">
         <v>22</v>
@@ -2697,7 +2697,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C28" t="s">
         <v>3</v>
@@ -2706,10 +2706,10 @@
         <v>22</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F28" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G28">
         <v>22</v>
@@ -2753,10 +2753,10 @@
         <v>22</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F29" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G29">
         <v>22</v>
@@ -2800,10 +2800,10 @@
         <v>22</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F30" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G30">
         <v>22</v>
@@ -2841,16 +2841,16 @@
         <v>33</v>
       </c>
       <c r="C31" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D31">
         <v>22</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F31" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G31">
         <v>22</v>
@@ -2888,16 +2888,16 @@
         <v>30</v>
       </c>
       <c r="C32" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D32">
         <v>22</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F32" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G32">
         <v>22</v>
@@ -2941,10 +2941,10 @@
         <v>22</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F33" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G33">
         <v>22</v>
@@ -2988,10 +2988,10 @@
         <v>22</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F34" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G34">
         <v>22</v>
@@ -3035,10 +3035,10 @@
         <v>22</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F35" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G35">
         <v>22</v>
@@ -3082,10 +3082,10 @@
         <v>22</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F36" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G36">
         <v>22</v>
@@ -3123,16 +3123,16 @@
         <v>34</v>
       </c>
       <c r="C37" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D37">
         <v>22</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F37" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G37">
         <v>22</v>
@@ -3176,10 +3176,10 @@
         <v>22</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F38" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G38">
         <v>22</v>
@@ -3258,10 +3258,10 @@
         <v>22</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F40" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G40">
         <v>22</v>
@@ -3296,7 +3296,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C41" t="s">
         <v>3</v>
@@ -3305,10 +3305,10 @@
         <v>22</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F41" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G41">
         <v>22</v>
@@ -3343,7 +3343,7 @@
         <v>40</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C42" t="s">
         <v>3</v>
@@ -3352,10 +3352,10 @@
         <v>22</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F42" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G42">
         <v>22</v>
@@ -3390,7 +3390,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C43" t="s">
         <v>3</v>
@@ -3399,10 +3399,10 @@
         <v>22</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F43" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G43">
         <v>22</v>
@@ -3437,7 +3437,7 @@
         <v>42</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>86</v>
+        <v>186</v>
       </c>
       <c r="C44" t="s">
         <v>3</v>
@@ -3446,10 +3446,10 @@
         <v>22</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>145</v>
+        <v>185</v>
       </c>
       <c r="F44" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G44">
         <v>22</v>
@@ -3493,10 +3493,10 @@
         <v>22</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F45" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G45">
         <v>22</v>
@@ -3531,7 +3531,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C46" t="s">
         <v>3</v>
@@ -3540,10 +3540,10 @@
         <v>22</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F46" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G46">
         <v>22</v>
@@ -3578,7 +3578,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>42</v>
+        <v>188</v>
       </c>
       <c r="C47" t="s">
         <v>3</v>
@@ -3587,10 +3587,10 @@
         <v>22</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>148</v>
+        <v>187</v>
       </c>
       <c r="F47" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G47">
         <v>22</v>
@@ -3625,7 +3625,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C48" t="s">
         <v>3</v>
@@ -3634,10 +3634,10 @@
         <v>22</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="F48" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G48">
         <v>22</v>
@@ -3672,7 +3672,7 @@
         <v>47</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C49" t="s">
         <v>3</v>
@@ -3681,10 +3681,10 @@
         <v>22</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F49" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G49">
         <v>22</v>
@@ -3728,10 +3728,10 @@
         <v>22</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="F50" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G50">
         <v>22</v>
@@ -3766,7 +3766,7 @@
         <v>49</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C51" t="s">
         <v>3</v>
@@ -3775,10 +3775,10 @@
         <v>22</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F51" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G51">
         <v>22</v>
@@ -3813,19 +3813,19 @@
         <v>50</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C52" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D52">
         <v>22</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="F52" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G52">
         <v>22</v>
@@ -3860,7 +3860,7 @@
         <v>51</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C53" t="s">
         <v>3</v>
@@ -3869,10 +3869,10 @@
         <v>22</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="F53" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G53">
         <v>22</v>
@@ -3910,16 +3910,16 @@
         <v>21</v>
       </c>
       <c r="C54" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D54">
         <v>22</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="F54" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G54">
         <v>22</v>
@@ -3954,7 +3954,7 @@
         <v>53</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C55" t="s">
         <v>3</v>
@@ -3963,10 +3963,10 @@
         <v>22</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="F55" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G55">
         <v>22</v>
@@ -4001,7 +4001,7 @@
         <v>54</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C56" t="s">
         <v>3</v>
@@ -4010,10 +4010,10 @@
         <v>22</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="F56" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G56">
         <v>22</v>
@@ -4048,7 +4048,7 @@
         <v>55</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C57" t="s">
         <v>3</v>
@@ -4057,10 +4057,10 @@
         <v>22</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F57" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G57">
         <v>22</v>
@@ -4095,7 +4095,7 @@
         <v>56</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C58" t="s">
         <v>3</v>
@@ -4104,10 +4104,10 @@
         <v>22</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="F58" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G58">
         <v>22</v>
@@ -4142,7 +4142,7 @@
         <v>57</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C59" t="s">
         <v>3</v>
@@ -4151,10 +4151,10 @@
         <v>22</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="F59" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G59">
         <v>22</v>
@@ -4189,19 +4189,19 @@
         <v>58</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C60" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D60">
         <v>22</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F60" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G60">
         <v>22</v>
@@ -4236,7 +4236,7 @@
         <v>59</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C61" t="s">
         <v>3</v>
@@ -4245,10 +4245,10 @@
         <v>22</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="F61" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G61">
         <v>22</v>
@@ -4283,19 +4283,19 @@
         <v>60</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C62" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D62">
         <v>22</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="F62" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G62">
         <v>22</v>
@@ -4330,7 +4330,7 @@
         <v>61</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C63" t="s">
         <v>3</v>
@@ -4339,10 +4339,10 @@
         <v>22</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F63" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G63">
         <v>22</v>
@@ -4377,19 +4377,19 @@
         <v>62</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C64" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D64">
         <v>22</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F64" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G64">
         <v>22</v>
@@ -4424,7 +4424,7 @@
         <v>63</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C65" t="s">
         <v>3</v>
@@ -4433,10 +4433,10 @@
         <v>22</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="F65" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G65">
         <v>22</v>
@@ -4471,7 +4471,7 @@
         <v>64</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C66" t="s">
         <v>3</v>
@@ -4480,10 +4480,10 @@
         <v>22</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F66" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G66">
         <v>22</v>
@@ -4518,7 +4518,7 @@
         <v>65</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C67" t="s">
         <v>3</v>
@@ -4527,10 +4527,10 @@
         <v>22</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F67" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G67">
         <v>22</v>
@@ -4565,19 +4565,19 @@
         <v>66</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C68" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D68">
         <v>22</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="F68" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G68">
         <v>22</v>
@@ -4612,7 +4612,7 @@
         <v>67</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C69" t="s">
         <v>3</v>
@@ -4621,10 +4621,10 @@
         <v>22</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="F69" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G69">
         <v>22</v>
@@ -4659,7 +4659,7 @@
         <v>68</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C70" t="s">
         <v>3</v>
@@ -4668,10 +4668,10 @@
         <v>22</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="F70" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G70">
         <v>22</v>
@@ -4741,19 +4741,19 @@
         <v>70</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C72" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D72">
         <v>22</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F72" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G72">
         <v>22</v>
@@ -4788,19 +4788,19 @@
         <v>71</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C73" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D73">
         <v>22</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="F73" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G73">
         <v>22</v>
@@ -4835,19 +4835,19 @@
         <v>72</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C74" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D74">
         <v>22</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="F74" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G74">
         <v>22</v>
@@ -4882,7 +4882,7 @@
         <v>73</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C75" t="s">
         <v>3</v>
@@ -4891,10 +4891,10 @@
         <v>22</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F75" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G75">
         <v>22</v>
@@ -4929,7 +4929,7 @@
         <v>74</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C76" t="s">
         <v>3</v>
@@ -4938,10 +4938,10 @@
         <v>22</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F76" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G76">
         <v>22</v>
@@ -4976,19 +4976,19 @@
         <v>75</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C77" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D77">
         <v>22</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F77" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G77">
         <v>22</v>
@@ -5023,19 +5023,19 @@
         <v>76</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C78" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D78">
         <v>22</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="F78" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G78">
         <v>22</v>
@@ -5070,7 +5070,7 @@
         <v>77</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C79" t="s">
         <v>3</v>
@@ -5079,10 +5079,10 @@
         <v>22</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="F79" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G79">
         <v>22</v>
@@ -5120,16 +5120,16 @@
         <v>21</v>
       </c>
       <c r="C80" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D80">
         <v>22</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="F80" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G80">
         <v>22</v>
@@ -5164,7 +5164,7 @@
         <v>79</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C81" t="s">
         <v>3</v>
@@ -5173,10 +5173,10 @@
         <v>22</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="F81" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G81">
         <v>22</v>
@@ -5211,19 +5211,19 @@
         <v>80</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C82" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D82">
         <v>22</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="F82" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G82">
         <v>22</v>
@@ -5258,7 +5258,7 @@
         <v>81</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C83" t="s">
         <v>3</v>
@@ -5267,10 +5267,10 @@
         <v>22</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="F83" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G83">
         <v>22</v>
@@ -5305,19 +5305,19 @@
         <v>82</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C84" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D84">
         <v>22</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="F84" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G84">
         <v>22</v>
@@ -5352,7 +5352,7 @@
         <v>83</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C85" t="s">
         <v>3</v>
@@ -5361,10 +5361,10 @@
         <v>22</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F85" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G85">
         <v>22</v>
@@ -5399,19 +5399,19 @@
         <v>84</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C86" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D86">
         <v>22</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="F86" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G86">
         <v>22</v>
@@ -5446,7 +5446,7 @@
         <v>85</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C87" t="s">
         <v>3</v>
@@ -5455,10 +5455,10 @@
         <v>22</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F87" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G87">
         <v>22</v>
@@ -5493,7 +5493,7 @@
         <v>86</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C88" t="s">
         <v>3</v>
@@ -5502,10 +5502,10 @@
         <v>22</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="F88" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G88">
         <v>22</v>
@@ -5540,7 +5540,7 @@
         <v>87</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C89" t="s">
         <v>3</v>
@@ -5549,10 +5549,10 @@
         <v>22</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F89" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G89">
         <v>22</v>

--- a/Assets/Originals/Excels/Talk/TalkMessage.xlsx
+++ b/Assets/Originals/Excels/Talk/TalkMessage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Talk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DC5E619-E3F7-4F8F-864F-EC1C5E6636B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE655FAF-BE08-4D9A-B61A-56949A5B5E70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="189">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -45,10 +45,6 @@
     <t>message</t>
   </si>
   <si>
-    <t>目が覚めたようだね</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>カナメ</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -57,272 +53,26 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>夢迷？</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>この常世にある巨大な迷宮のことさ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>つまり　君もそのうちの1人ということさ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>罪？</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>君は現世で"罪”を犯して死亡した
-罪を犯した人間は　みんなこの夢迷に幽閉される</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>そう　とてもとても大きな罪</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ところで　自分の名前は分かるかい？</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>えっと…名前は…</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>あれ……わからない……</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>分からなくて当然だよ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>君はこの迷宮に来る前に名前を破棄されたのだから</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>どういうこと？</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>名前を…破棄…？</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>常世で名前を破棄された者は
-自分の名前を思い出すことができないのさ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>どうして…</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>そんな…酷いよ…</t>
-    <rPh sb="4" eb="5">
-      <t>ヒド</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>え……</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>あらゆる苦痛を受けながら
-この迷宮で永遠に彷徨うことになるのさ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>君もいずれ　そうなるだろうね</t>
-    <rPh sb="0" eb="1">
-      <t>キミ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>僕の名前はカナメ
-“夢迷”の案内者さ</t>
-    <rPh sb="16" eb="17">
-      <t>モノ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ここは…どこだ…</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>そして　名前を思い出せない者は…</t>
-    <rPh sb="7" eb="8">
-      <t>オモ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>ダ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>モノ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>でも安心して</t>
-    <rPh sb="2" eb="4">
-      <t>アンシン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>罪人に名前はいらないからね</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>そうすれば　苦痛を受けることはないし
-彷徨うこともない</t>
-    <rPh sb="9" eb="10">
-      <t>ウ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>サマヨ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>でも　どうすれば脱出できるの？</t>
-    <rPh sb="8" eb="10">
-      <t>ダッシュツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>それは　僕からの試練に挑戦し乗り越えること</t>
-    <rPh sb="4" eb="5">
-      <t>ボク</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>シレン</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>チョウセン</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>ノ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>コ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>そうすれば　脱出できるよ</t>
-    <rPh sb="6" eb="8">
-      <t>ダッシュツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>……脱出したい！</t>
-    <rPh sb="2" eb="4">
-      <t>ダッシュツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>……挑戦したい！</t>
-    <rPh sb="2" eb="4">
-      <t>チョウセン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>…僕からの試練　挑戦するかい？</t>
-    <rPh sb="8" eb="10">
-      <t>チョウセン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>…分かった
-それじゃあ　試練の内容を説明するよ</t>
-    <rPh sb="1" eb="2">
-      <t>ワ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>シレン</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ナイヨウ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>セツメイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>…1つ　方法がある</t>
-    <rPh sb="4" eb="6">
-      <t>ホウホウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>…ここから脱出したいかい？</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>試練を乗り越えるためには
-2つの条件を達成する必要がある</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>今手に取ったドキュメントの中を確認してごらん</t>
-  </si>
-  <si>
-    <t>ドキュメントの内容と深い関係がある
-ミステリーアイテムを選択すること</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>今手に取ったミステリーアイテムを確認してごらん</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>1つ　この迷宮から脱出すること
-1つ　君が現世で犯した罪を思い出すこと</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>現世で犯した罪を思い出して　この迷宮から脱出できたら　
-君の名前を教えてあげるよ</t>
-    <rPh sb="16" eb="18">
-      <t>メイキュウ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>ダッシュツ</t>
-    </rPh>
-    <rPh sb="28" eb="29">
-      <t>キミ</t>
-    </rPh>
-    <rPh sb="33" eb="34">
-      <t>オシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>あれ？　僕が犯した罪についての説明はしてくれないの？</t>
-    <rPh sb="4" eb="5">
-      <t>ボク</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>オカ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>セツメイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>しないよ</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -331,70 +81,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>本当に悪いことしたと思っているなら
-すぐに罪を思い出すことができるはずさ</t>
-    <rPh sb="0" eb="2">
-      <t>ホントウ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ワル</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>オモ</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>ツミ</t>
-    </rPh>
-    <rPh sb="23" eb="24">
-      <t>オモ</t>
-    </rPh>
-    <rPh sb="25" eb="26">
-      <t>ダ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>だから説明はこれで終わり</t>
-    <rPh sb="3" eb="5">
-      <t>セツメイ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>試練の説明はこれで終わり
-なにか質問はあるかい？</t>
-    <rPh sb="0" eb="2">
-      <t>シレン</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>セツメイ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>シツモン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>あと　名前がないと不便だから
-君のことを仮で"イフ"と呼ばせてもらうよ</t>
-    <rPh sb="9" eb="11">
-      <t>フベン</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>キミ</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>カリ</t>
-    </rPh>
-    <rPh sb="27" eb="28">
-      <t>ヨ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>それでいいよね？</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -403,176 +89,18 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>最後に　この迷宮について1つ注意事項がある</t>
-    <rPh sb="6" eb="8">
-      <t>メイキュウ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>チュウイ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ジコウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>注意事項？</t>
-    <rPh sb="0" eb="4">
-      <t>チュウイジコウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>彷徨う者？</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>"彷徨う者"には絶対に捕まるな</t>
-    <rPh sb="1" eb="3">
-      <t>サマヨ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>モノ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ゼッタイ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>ツカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>イフ　とにかくその化け物に捕まっちゃダメだよ</t>
-    <rPh sb="9" eb="10">
-      <t>バ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>モノ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>ツカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>分かったかい？</t>
-    <rPh sb="0" eb="1">
-      <t>ワ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>……う…うん……</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>夢迷に潜む化け物のことさ</t>
-    <rPh sb="0" eb="1">
-      <t>ユメ</t>
-    </rPh>
-    <rPh sb="1" eb="2">
-      <t>マヨ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ヒソ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>バ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>モノ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>イフ　君が試練をクリアすることを祈っているよ</t>
-    <rPh sb="3" eb="4">
-      <t>キミ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>シレン</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>イノ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>どうして迷宮がまだ続いているの！？</t>
-    <rPh sb="4" eb="6">
-      <t>メイキュウ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>ツヅ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>そんなの決まっているじゃないか</t>
-    <rPh sb="4" eb="5">
-      <t>キ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>君がまだ迷宮から脱出できていないからさ</t>
-    <rPh sb="0" eb="1">
-      <t>キミ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>メイキュウ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ダッシュツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>もしかしてそれで終わりだと思ってる？</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ドキュメントとミステリーアイテムは
-他のエリアにもあるんだよ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>うそ…でしょ…</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>それに　イフが犯した罪もまだ思い出してないでしょ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>だから試練はまだ終わらないよ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>…脱出できてないって</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ドキュメントもミステリーアイテムも
-ちゃんと集めたじゃないか！</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>え……なに…これ……</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>…これで…やっと…この迷宮から脱出できる…</t>
-    <rPh sb="11" eb="13">
-      <t>メイキュウ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ダッシュツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>…！</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -581,34 +109,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>大変だと思うけど</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>これからも頑張ろうね　イフ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>夢迷の本当の恐ろしさはここからさ　イフ</t>
-    <rPh sb="0" eb="1">
-      <t>ユメ</t>
-    </rPh>
-    <rPh sb="1" eb="2">
-      <t>マヨ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ホントウ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>オソ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>最後に　奥にある「裁きの青玉」に触れて</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>あなた</t>
   </si>
   <si>
@@ -617,39 +117,6 @@
   </si>
   <si>
     <t>？？？</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>この迷宮から脱出する方法について説明するよ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>次に　ミステリーアイテムを入手すること</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>脱出には　"ドキュメント"と"ミステリーアイテム"を
-この迷宮のあらゆる場所から探して見つけ出す必要がある</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>それじゃあ　これから試練を始めるよ
-後ろの通路へと進んでもらおうか</t>
-    <rPh sb="10" eb="12">
-      <t>シレン</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>ハジ</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>ウシ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>ツウロ</t>
-    </rPh>
-    <rPh sb="25" eb="26">
-      <t>スス</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1062,16 +529,562 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>まず　ドキュメントを入手すること
-試しに目の前の引き出しを開けてごらん</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Open the two drawers right in front of you.</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>目の前にある2つの引き出しを開けてごらん</t>
+    <t>&lt;r="め"&gt;目&lt;/r&gt;が&lt;r="さ"&gt;覚&lt;/r&gt;めたようだね</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="ぼく"&gt;僕&lt;/r&gt;の&lt;r="なまえ"&gt;名前&lt;/r&gt;はカナメ
+“&lt;r="むめい"&gt;夢迷&lt;/r&gt;”の&lt;r="あんないしゃ"&gt;案内者&lt;/r&gt;さ</t>
+    <rPh sb="64" eb="67">
+      <t>アンナイシャ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="むめい"&gt;夢迷&lt;/r&gt;？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>この&lt;r="とこよ"&gt;常世&lt;/r&gt;にある&lt;r="きょだい"&gt;巨大&lt;/r&gt;な&lt;r="めいきゅう"&gt;迷宮&lt;/r&gt;のことさ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="きみ"&gt;君&lt;/r&gt;は&lt;r="うつしよ"&gt;現世&lt;/r&gt;で"&lt;r="つみ"&gt;罪&lt;/r&gt;”を&lt;r="おか"&gt;犯&lt;/r&gt;して&lt;r="しぼう"&gt;死亡&lt;/r&gt;した
+&lt;r="つみ"&gt;罪&lt;/r&gt;を&lt;r="おか"&gt;犯&lt;/r&gt;した&lt;r="にんげん"&gt;人間&lt;/r&gt;は　みんなこの&lt;r="むめい"&gt;夢迷&lt;/r&gt;に&lt;r="ゆうへい"&gt;幽閉&lt;/r&gt;される</t>
+    <rPh sb="40" eb="41">
+      <t>ツミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>つまり　&lt;r="きみ"&gt;君&lt;/r&gt;もそのうちの&lt;r="ひとり"&gt;1人&lt;/r&gt;ということさ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="つみ"&gt;罪&lt;/r&gt;？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>そう　とてもとても&lt;r="おお"&gt;大&lt;/r&gt;きな&lt;r="つみ"&gt;罪&lt;/r&gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ところで　&lt;r="じぶん"&gt;自分&lt;/r&gt;の&lt;r="なまえ"&gt;名前&lt;/r&gt;は&lt;r="わ"&gt;分&lt;/r&gt;かるかい？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>えっと…&lt;r="なまえ"&gt;名前&lt;/r&gt;は…</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="わ"&gt;分&lt;/r&gt;からなくて&lt;r="とうぜん"&gt;当然&lt;/r&gt;だよ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="きみ"&gt;君&lt;/r&gt;はこの&lt;r="めいきゅう"&gt;迷宮&lt;/r&gt;に来る前に&lt;r="なまえ"&gt;名前&lt;/r&gt;を&lt;r="はき"&gt;破棄&lt;/r&gt;されたのだから</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="なまえ"&gt;名前&lt;/r&gt;を…&lt;r="はき"&gt;破棄&lt;/r&gt;…？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="とこよ"&gt;常世&lt;/r&gt;で&lt;r="なまえ"&gt;名前&lt;/r&gt;を&lt;r="はき"&gt;破棄&lt;/r&gt;された&lt;r="もの"&gt;者&lt;/r&gt;は
+&lt;r="じぶん"&gt;自分&lt;/r&gt;の&lt;r="なまえ"&gt;名前&lt;/r&gt;を&lt;r="おも"&gt;思&lt;/r&gt;い&lt;r="だ"&gt;出&lt;/r&gt;すことができないのさ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>そして　&lt;r="なまえ"&gt;名前&lt;/r&gt;を&lt;r="おも"&gt;思&lt;/r&gt;い&lt;r="だ"&gt;出&lt;/r&gt;せない&lt;r="もの"&gt;者&lt;/r&gt;は…</t>
+    <rPh sb="13" eb="15">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>デ</t>
+    </rPh>
+    <rPh sb="57" eb="58">
+      <t>モノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>あらゆる&lt;r="くつう"&gt;苦痛&lt;/r&gt;を&lt;r="う"&gt;受&lt;/r&gt;けながら
+この&lt;r="めいきゅう"&gt;迷宮&lt;/r&gt;で&lt;r="えいえん"&gt;永遠&lt;/r&gt;に&lt;r="さまよ"&gt;彷徨&lt;/r&gt;うことになるのさ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="きみ"&gt;君&lt;/r&gt;もいずれ　そうなるだろうね</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>そんな…&lt;r="ひど"&gt;酷&lt;/r&gt;いよ…</t>
+    <rPh sb="12" eb="13">
+      <t>コク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="ざいにん"&gt;罪人&lt;/r&gt;に&lt;r="なまえ"&gt;名前&lt;/r&gt;はいらないからね</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>でも&lt;r="あんしん"&gt;安心&lt;/r&gt;して</t>
+    <rPh sb="12" eb="14">
+      <t>アンシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="うつしよ"&gt;現世&lt;/r&gt;で&lt;r="おか"&gt;犯&lt;/r&gt;した&lt;r="つみ"&gt;罪&lt;/r&gt;を&lt;r="おも"&gt;思&lt;/r&gt;い&lt;r="だ"&gt;出&lt;/r&gt;して　この&lt;r="めいきゅう"&gt;迷宮&lt;/r&gt;から&lt;r="だっしゅつ"&gt;脱出&lt;/r&gt;できたら　
+&lt;r="きみ"&gt;君&lt;/r&gt;の&lt;r="なまえ"&gt;名前&lt;/r&gt;を&lt;r="おし"&gt;教&lt;/r&gt;えてあげるよ</t>
+    <rPh sb="177" eb="179">
+      <t>メイキュウ</t>
+    </rPh>
+    <rPh sb="181" eb="183">
+      <t>ダッシュツ</t>
+    </rPh>
+    <rPh sb="189" eb="190">
+      <t>キミ</t>
+    </rPh>
+    <rPh sb="194" eb="195">
+      <t>オシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>そうすれば　&lt;r="くつう"&gt;苦痛&lt;/r&gt;を&lt;r="う"&gt;受&lt;/r&gt;けることはないし
+&lt;r="さまよ"&gt;彷徨&lt;/r&gt;うこともない</t>
+    <rPh sb="52" eb="54">
+      <t>ホウコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>…ここから&lt;r="だっしゅつ"&gt;脱出&lt;/r&gt;したいかい？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>でも　どうすれば&lt;r="だっしゅつ"&gt;脱出&lt;/r&gt;できるの？</t>
+    <rPh sb="19" eb="21">
+      <t>ダッシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>…1つ　&lt;r="ほうほう"&gt;方法&lt;/r&gt;がある</t>
+    <rPh sb="14" eb="16">
+      <t>ホウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>それは　&lt;r="ぼく"&gt;僕&lt;/r&gt;からの&lt;r="しれん"&gt;試練&lt;/r&gt;に&lt;r="ちょうせん"&gt;挑戦&lt;/r&gt;し&lt;r="の"&gt;乗&lt;/r&gt;り&lt;r="こ"&gt;越&lt;/r&gt;えること</t>
+    <rPh sb="12" eb="13">
+      <t>ボク</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>シレン</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>チョウセン</t>
+    </rPh>
+    <rPh sb="61" eb="62">
+      <t>ジョウ</t>
+    </rPh>
+    <rPh sb="74" eb="75">
+      <t>エツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>そうすれば　&lt;r="だっしゅつ"&gt;脱出&lt;/r&gt;できるよ</t>
+    <rPh sb="17" eb="19">
+      <t>ダッシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>……&lt;r="だっしゅつ"&gt;脱出&lt;/r&gt;したい</t>
+    <rPh sb="13" eb="15">
+      <t>ダッシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>…&lt;r="ぼく"&gt;僕&lt;/r&gt;からの&lt;r="しれん"&gt;試練&lt;/r&gt;　&lt;r="ちょうせん"&gt;挑戦&lt;/r&gt;するかい？</t>
+    <rPh sb="9" eb="10">
+      <t>ボク</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>シレン</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>チョウセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>……&lt;r="ちょうせん"&gt;挑戦&lt;/r&gt;したい</t>
+    <rPh sb="13" eb="15">
+      <t>チョウセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>…&lt;r="わ"&gt;分&lt;/r&gt;かった
+それじゃあ　&lt;r="しれん"&gt;試練&lt;/r&gt;の&lt;r="ないよう"&gt;内容&lt;/r&gt;を&lt;r="せつめい"&gt;説明&lt;/r&gt;するよ</t>
+    <rPh sb="8" eb="9">
+      <t>ブン</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>シレン</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="66" eb="68">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="しれん"&gt;試練&lt;/r&gt;を&lt;r="の"&gt;乗&lt;/r&gt;り&lt;r="こ"&gt;越&lt;/r&gt;えるためには
+2つの&lt;r="じょうけん"&gt;条件&lt;/r&gt;を&lt;r="たっせい"&gt;達成&lt;/r&gt;する&lt;r="ひつよう"&gt;必要&lt;/r&gt;がある</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1つ　この&lt;r="めいきゅう"&gt;迷宮&lt;/r&gt;から&lt;r="だっしゅつ"&gt;脱出&lt;/r&gt;すること
+1つ　&lt;r="きみ"&gt;君&lt;/r&gt;が&lt;r="うつしよ"&gt;現世&lt;/r&gt;で&lt;r="おか"&gt;犯&lt;/r&gt;した&lt;r="つみ"&gt;罪&lt;/r&gt;を&lt;r="おも"&gt;思&lt;/r&gt;い&lt;r="だ"&gt;出&lt;/r&gt;すこと</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>この&lt;r="めいきゅう"&gt;迷宮&lt;/r&gt;から&lt;r="だっしゅつ"&gt;脱出&lt;/r&gt;する&lt;r="ほうほう"&gt;方法&lt;/r&gt;について&lt;r="せつめい"&gt;説明&lt;/r&gt;するよ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="だっしゅつ"&gt;脱出&lt;/r&gt;には　"ドキュメント"と"ミステリーアイテム"を
+この&lt;r="めいきゅう"&gt;迷宮&lt;/r&gt;のあらゆる&lt;r="ばしょ"&gt;場所&lt;/r&gt;から&lt;r="さが"&gt;探&lt;/r&gt;して&lt;r="み"&gt;見&lt;/r&gt;つけ&lt;r="だ"&gt;出&lt;/r&gt;す&lt;r="ひつよう"&gt;必要&lt;/r&gt;がある</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="つぎ"&gt;次&lt;/r&gt;に　ミステリーアイテムを&lt;r="にゅうしゅ"&gt;入手&lt;/r&gt;すること</t>
+    <rPh sb="8" eb="9">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>まず　ドキュメントを&lt;r="にゅうしゅ"&gt;入手&lt;/r&gt;すること
+&lt;r="ため"&gt;試&lt;/r&gt;しに&lt;r="め"&gt;目&lt;/r&gt;の&lt;r="まえ"&gt;前&lt;/r&gt;の&lt;r="ひ"&gt;引&lt;/r&gt;き&lt;r="だ"&gt;出&lt;/r&gt;しを&lt;r="あ"&gt;開&lt;/r&gt;けてごらん</t>
+    <rPh sb="68" eb="69">
+      <t>マエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="め"&gt;目&lt;/r&gt;の&lt;r="まえ"&gt;前&lt;/r&gt;にある2つの&lt;r="ひ"&gt;引&lt;/r&gt;き&lt;r="だ"&gt;出&lt;/r&gt;しを&lt;r="あ"&gt;開&lt;/r&gt;けてごらん</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="さいご"&gt;最後&lt;/r&gt;に　&lt;r="おく"&gt;奥&lt;/r&gt;にある「&lt;r="さば"&gt;裁&lt;/r&gt;きの&lt;r="せいぎょく"&gt;青玉&lt;/r&gt;」に&lt;r="ふ"&gt;触&lt;/r&gt;れて</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="しれん"&gt;試練&lt;/r&gt;の&lt;r="せつめい"&gt;説明&lt;/r&gt;はこれで&lt;r="お"&gt;終&lt;/r&gt;わり
+なにか&lt;r="しつもん"&gt;質問&lt;/r&gt;はあるかい？</t>
+    <rPh sb="9" eb="11">
+      <t>シレン</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>シュウ</t>
+    </rPh>
+    <rPh sb="64" eb="66">
+      <t>シツモン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>あれ？　&lt;r="ぼく"&gt;僕&lt;/r&gt;が&lt;r="おか"&gt;犯&lt;/r&gt;した&lt;r="つみ"&gt;罪&lt;/r&gt;についての&lt;r="せつめい"&gt;説明&lt;/r&gt;はしてくれないの？</t>
+    <rPh sb="12" eb="13">
+      <t>ボク</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ハン</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>ツミ</t>
+    </rPh>
+    <rPh sb="61" eb="63">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="ほんとう"&gt;本当&lt;/r&gt;に&lt;r="わる"&gt;悪&lt;/r&gt;いことしたと&lt;r="おも"&gt;思&lt;/r&gt;っているなら
+すぐに&lt;r="つみ"&gt;罪&lt;/r&gt;を&lt;r="おも"&gt;思&lt;/r&gt;い&lt;r="だ"&gt;出&lt;/r&gt;すことができるはずさ</t>
+    <rPh sb="10" eb="12">
+      <t>ホントウ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>アク</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>シ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>だから&lt;r="せつめい"&gt;説明&lt;/r&gt;はこれで&lt;r="お"&gt;終&lt;/r&gt;わり</t>
+    <rPh sb="13" eb="15">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>シュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>あと　&lt;r="なまえ"&gt;名前&lt;/r&gt;がないと&lt;r="ふべん"&gt;不便&lt;/r&gt;だから
+&lt;r="きみ"&gt;君&lt;/r&gt;のことを&lt;r="かり"&gt;仮&lt;/r&gt;で"イフ"と&lt;r="よ"&gt;呼&lt;/r&gt;ばせてもらうよ</t>
+    <rPh sb="12" eb="14">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>フベン</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>キミ</t>
+    </rPh>
+    <rPh sb="66" eb="67">
+      <t>カリ</t>
+    </rPh>
+    <rPh sb="84" eb="85">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="さいご"&gt;最後&lt;/r&gt;に　この&lt;r="めいきゅう"&gt;迷宮&lt;/r&gt;について1つ&lt;r="ちゅういじこう"&gt;注意事項&lt;/r&gt;がある</t>
+    <rPh sb="9" eb="11">
+      <t>サイゴ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>メイキュウ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>チュウイ</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>ジコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="ちゅういじこう"&gt;注意事項&lt;/r&gt;？</t>
+    <rPh sb="13" eb="15">
+      <t>チュウイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ジコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>"&lt;r="さまよ"&gt;彷徨&lt;/r&gt;う&lt;r="もの"&gt;者&lt;/r&gt;"には&lt;r="ぜったい"&gt;絶対&lt;/r&gt;に&lt;r="つか"&gt;捕&lt;/r&gt;まるな</t>
+    <rPh sb="10" eb="12">
+      <t>ホウコウ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>モノ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>ゼッタイ</t>
+    </rPh>
+    <rPh sb="58" eb="59">
+      <t>ホ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="さまよ"&gt;彷徨&lt;/r&gt;う&lt;r="もの"&gt;者&lt;/r&gt;？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="わ"&gt;分&lt;/r&gt;かったかい？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>それじゃあ　これから&lt;r="しれん"&gt;試練&lt;/r&gt;を&lt;r="はじ"&gt;始&lt;/r&gt;めるよ
+&lt;r="うし"&gt;後&lt;/r&gt;ろの&lt;r="つうろ"&gt;通路&lt;/r&gt;へと&lt;r="すす"&gt;進&lt;/r&gt;んでもらおうか</t>
+    <rPh sb="19" eb="21">
+      <t>シレン</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ハジメ</t>
+    </rPh>
+    <rPh sb="51" eb="52">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="67" eb="69">
+      <t>ツウロ</t>
+    </rPh>
+    <rPh sb="83" eb="84">
+      <t>ススム</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>イフ　&lt;r="きみ"&gt;君&lt;/r&gt;が&lt;r="しれん"&gt;試練&lt;/r&gt;をクリアすることを&lt;r="いの"&gt;祈&lt;/r&gt;っているよ</t>
+    <rPh sb="11" eb="12">
+      <t>キミ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>シレン</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>…これで…やっと…この&lt;r="めいきゅう"&gt;迷宮&lt;/r&gt;から&lt;r="だっしゅつ"&gt;脱出&lt;/r&gt;できる…</t>
+    <rPh sb="22" eb="24">
+      <t>メイキュウ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ダッシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>どうして&lt;r="めいきゅう"&gt;迷宮&lt;/r&gt;がまだ&lt;r="つづ"&gt;続&lt;/r&gt;いているの！？</t>
+    <rPh sb="15" eb="17">
+      <t>メイキュウ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ゾク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>そんなの&lt;r="き"&gt;決&lt;/r&gt;まっているじゃないか</t>
+    <rPh sb="11" eb="12">
+      <t>ケッ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="きみ"&gt;君&lt;/r&gt;がまだ&lt;r="めいきゅう"&gt;迷宮&lt;/r&gt;から&lt;r="だっしゅつ"&gt;脱出&lt;/r&gt;できていないからさ</t>
+    <rPh sb="8" eb="9">
+      <t>キミ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>メイキュウ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>ダッシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>…&lt;r="だっしゅつ"&gt;脱出&lt;/r&gt;できてないって</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ドキュメントもミステリーアイテムも
+ちゃんと&lt;r="あつ"&gt;集&lt;/r&gt;めたじゃないか！</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>もしかしてそれで&lt;r="お"&gt;終&lt;/r&gt;わりだと&lt;r="おも"&gt;思&lt;/r&gt;ってる？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ドキュメントとミステリーアイテムは
+&lt;r="ほか"&gt;他&lt;/r&gt;のエリアにもあるんだよ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>それに　イフが&lt;r="おか"&gt;犯&lt;/r&gt;した&lt;r="つみ"&gt;罪&lt;/r&gt;もまだ&lt;r="おも"&gt;思&lt;/r&gt;い&lt;r="だ"&gt;出&lt;/r&gt;してないでしょ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>だから&lt;r="しれん"&gt;試練&lt;/r&gt;はまだ&lt;r="お"&gt;終&lt;/r&gt;わらないよ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="むめい"&gt;夢迷&lt;/r&gt;の&lt;r="ほんとう"&gt;本当&lt;/r&gt;の&lt;r="おそ"&gt;恐&lt;/r&gt;ろしさはここからさ　イフ</t>
+    <rPh sb="9" eb="10">
+      <t>ユメ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ホントウ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>キョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="たいへん"&gt;大変&lt;/r&gt;だと&lt;r="おも"&gt;思&lt;/r&gt;うけど</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>これからも&lt;r="がんば"&gt;頑張&lt;/r&gt;ろうね　イフ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="いま"&gt;今&lt;/r&gt;&lt;r="て"&gt;手&lt;/r&gt;に&lt;r="と"&gt;取&lt;/r&gt;ったドキュメントの&lt;r="なか"&gt;中&lt;/r&gt;を&lt;r="かくにん"&gt;確認&lt;/r&gt;してごらん</t>
+    <rPh sb="8" eb="9">
+      <t>イマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="いま"&gt;今&lt;/r&gt;&lt;r="て"&gt;手&lt;/r&gt;に&lt;r="と"&gt;取&lt;/r&gt;ったミステリーアイテムを&lt;r="かくにん"&gt;確認&lt;/r&gt;してごらん</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ドキュメントの&lt;r="ないよう"&gt;内容&lt;/r&gt;と&lt;r="ふか"&gt;深&lt;/r&gt;い&lt;r="かんけい"&gt;関係&lt;/r&gt;がある
+ミステリーアイテムを&lt;r="せんたく"&gt;選択&lt;/r&gt;すること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="むめい"&gt;夢迷&lt;/r&gt;に&lt;r="ひそ"&gt;潜&lt;/r&gt;む&lt;r="ば"&gt;化&lt;/r&gt;け&lt;r="もの"&gt;物&lt;/r&gt;のことさ</t>
+    <rPh sb="9" eb="10">
+      <t>ユメ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>セン</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>バ</t>
+    </rPh>
+    <rPh sb="51" eb="52">
+      <t>モノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>イフ　とにかくその&lt;r="ば"&gt;化&lt;/r&gt;け&lt;r="もの"&gt;物&lt;/r&gt;に&lt;r="つか"&gt;捕&lt;/r&gt;まっちゃダメだよ</t>
+    <rPh sb="44" eb="45">
+      <t>ホ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1424,7 +1437,7 @@
   <dimension ref="A1:O102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="2" max="2" width="63.625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="123.375" style="2" customWidth="1"/>
     <col min="3" max="3" width="17.625" customWidth="1"/>
     <col min="4" max="4" width="19.75" customWidth="1"/>
     <col min="5" max="5" width="47.125" customWidth="1"/>
@@ -1446,43 +1459,43 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>96</v>
+        <v>29</v>
       </c>
       <c r="E1" t="s">
-        <v>97</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>99</v>
+        <v>32</v>
       </c>
       <c r="G1" t="s">
-        <v>98</v>
+        <v>31</v>
       </c>
       <c r="H1" t="s">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I1" t="s">
-        <v>89</v>
+        <v>22</v>
       </c>
       <c r="J1" t="s">
-        <v>90</v>
+        <v>23</v>
       </c>
       <c r="K1" t="s">
-        <v>91</v>
+        <v>24</v>
       </c>
       <c r="L1" t="s">
-        <v>92</v>
+        <v>25</v>
       </c>
       <c r="M1" t="s">
-        <v>93</v>
+        <v>26</v>
       </c>
       <c r="N1" t="s">
-        <v>94</v>
+        <v>27</v>
       </c>
       <c r="O1" t="s">
-        <v>95</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:15">
@@ -1525,19 +1538,19 @@
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>19</v>
       </c>
       <c r="D3">
         <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>103</v>
+        <v>36</v>
       </c>
       <c r="F3" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="G3">
         <v>22</v>
@@ -1572,19 +1585,19 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>2</v>
+        <v>120</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>20</v>
       </c>
       <c r="D4">
         <v>22</v>
       </c>
       <c r="E4" t="s">
-        <v>104</v>
+        <v>37</v>
       </c>
       <c r="F4" t="s">
-        <v>83</v>
+        <v>20</v>
       </c>
       <c r="G4">
         <v>22</v>
@@ -1619,19 +1632,19 @@
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>24</v>
+        <v>121</v>
       </c>
       <c r="C5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5">
         <v>22</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>108</v>
+        <v>41</v>
       </c>
       <c r="F5" t="s">
-        <v>102</v>
+        <v>35</v>
       </c>
       <c r="G5">
         <v>22</v>
@@ -1666,19 +1679,19 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>5</v>
+        <v>122</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="D6">
         <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>105</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="G6">
         <v>22</v>
@@ -1713,19 +1726,19 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>6</v>
+        <v>123</v>
       </c>
       <c r="C7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7">
         <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>118</v>
+        <v>51</v>
       </c>
       <c r="F7" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G7">
         <v>22</v>
@@ -1760,19 +1773,19 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>9</v>
+        <v>124</v>
       </c>
       <c r="C8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8">
         <v>22</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>106</v>
+        <v>39</v>
       </c>
       <c r="F8" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G8">
         <v>22</v>
@@ -1807,19 +1820,19 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>7</v>
+        <v>125</v>
       </c>
       <c r="C9" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9">
         <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>107</v>
+        <v>40</v>
       </c>
       <c r="F9" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G9">
         <v>22</v>
@@ -1854,19 +1867,19 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>8</v>
+        <v>126</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="D10">
         <v>22</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>109</v>
+        <v>42</v>
       </c>
       <c r="F10" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="G10">
         <v>22</v>
@@ -1901,19 +1914,19 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>10</v>
+        <v>127</v>
       </c>
       <c r="C11" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11">
         <v>22</v>
       </c>
       <c r="E11" t="s">
-        <v>110</v>
+        <v>43</v>
       </c>
       <c r="F11" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G11">
         <v>22</v>
@@ -1948,19 +1961,19 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>11</v>
+        <v>128</v>
       </c>
       <c r="C12" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12">
         <v>22</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>111</v>
+        <v>44</v>
       </c>
       <c r="F12" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G12">
         <v>22</v>
@@ -1995,19 +2008,19 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>12</v>
+        <v>129</v>
       </c>
       <c r="C13" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="D13">
         <v>22</v>
       </c>
       <c r="E13" t="s">
-        <v>112</v>
+        <v>45</v>
       </c>
       <c r="F13" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="G13">
         <v>22</v>
@@ -2042,19 +2055,19 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C14" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="D14">
         <v>22</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>113</v>
+        <v>46</v>
       </c>
       <c r="F14" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="G14">
         <v>22</v>
@@ -2089,19 +2102,19 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>14</v>
+        <v>130</v>
       </c>
       <c r="C15" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15">
         <v>22</v>
       </c>
       <c r="E15" t="s">
-        <v>114</v>
+        <v>47</v>
       </c>
       <c r="F15" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G15">
         <v>22</v>
@@ -2136,19 +2149,19 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>15</v>
+        <v>131</v>
       </c>
       <c r="C16" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16">
         <v>22</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>115</v>
+        <v>48</v>
       </c>
       <c r="F16" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G16">
         <v>22</v>
@@ -2183,19 +2196,19 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>17</v>
+        <v>132</v>
       </c>
       <c r="C17" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="D17">
         <v>22</v>
       </c>
       <c r="E17" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="F17" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="G17">
         <v>22</v>
@@ -2230,19 +2243,19 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C18" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="D18">
         <v>22</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>117</v>
+        <v>50</v>
       </c>
       <c r="F18" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="G18">
         <v>22</v>
@@ -2277,19 +2290,19 @@
         <v>17</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>18</v>
+        <v>133</v>
       </c>
       <c r="C19" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D19">
         <v>22</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>119</v>
+        <v>52</v>
       </c>
       <c r="F19" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G19">
         <v>22</v>
@@ -2324,19 +2337,19 @@
         <v>18</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="C20" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="D20">
         <v>22</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>120</v>
+        <v>53</v>
       </c>
       <c r="F20" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="G20">
         <v>22</v>
@@ -2371,16 +2384,16 @@
         <v>19</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>26</v>
+        <v>134</v>
       </c>
       <c r="C21" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D21">
         <v>22</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>121</v>
+        <v>54</v>
       </c>
       <c r="G21">
         <v>22</v>
@@ -2415,19 +2428,19 @@
         <v>20</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>22</v>
+        <v>135</v>
       </c>
       <c r="C22" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D22">
         <v>22</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>122</v>
+        <v>55</v>
       </c>
       <c r="F22" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G22">
         <v>22</v>
@@ -2462,19 +2475,19 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>23</v>
+        <v>136</v>
       </c>
       <c r="C23" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D23">
         <v>22</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>123</v>
+        <v>56</v>
       </c>
       <c r="F23" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G23">
         <v>22</v>
@@ -2509,19 +2522,19 @@
         <v>22</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>20</v>
+        <v>137</v>
       </c>
       <c r="C24" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="D24">
         <v>22</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>124</v>
+        <v>57</v>
       </c>
       <c r="F24" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="G24">
         <v>22</v>
@@ -2556,19 +2569,19 @@
         <v>23</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C25" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="D25">
         <v>22</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>125</v>
+        <v>58</v>
       </c>
       <c r="F25" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="G25">
         <v>22</v>
@@ -2603,19 +2616,19 @@
         <v>24</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>28</v>
+        <v>138</v>
       </c>
       <c r="C26" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D26">
         <v>22</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>126</v>
+        <v>59</v>
       </c>
       <c r="F26" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G26">
         <v>22</v>
@@ -2650,19 +2663,19 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>27</v>
+        <v>139</v>
       </c>
       <c r="C27" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D27">
         <v>22</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>127</v>
+        <v>60</v>
       </c>
       <c r="F27" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G27">
         <v>22</v>
@@ -2697,19 +2710,19 @@
         <v>26</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>44</v>
+        <v>140</v>
       </c>
       <c r="C28" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D28">
         <v>22</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>139</v>
+        <v>72</v>
       </c>
       <c r="F28" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G28">
         <v>22</v>
@@ -2744,19 +2757,19 @@
         <v>27</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>29</v>
+        <v>141</v>
       </c>
       <c r="C29" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D29">
         <v>22</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>128</v>
+        <v>61</v>
       </c>
       <c r="F29" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G29">
         <v>22</v>
@@ -2791,19 +2804,19 @@
         <v>28</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>38</v>
+        <v>142</v>
       </c>
       <c r="C30" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D30">
         <v>22</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
       <c r="F30" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G30">
         <v>22</v>
@@ -2838,19 +2851,19 @@
         <v>29</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C31" t="s">
+        <v>18</v>
+      </c>
+      <c r="D31">
+        <v>22</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F31" t="s">
         <v>33</v>
-      </c>
-      <c r="C31" t="s">
-        <v>81</v>
-      </c>
-      <c r="D31">
-        <v>22</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="F31" t="s">
-        <v>100</v>
       </c>
       <c r="G31">
         <v>22</v>
@@ -2885,19 +2898,19 @@
         <v>30</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>30</v>
+        <v>143</v>
       </c>
       <c r="C32" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="D32">
         <v>22</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>131</v>
+        <v>64</v>
       </c>
       <c r="F32" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="G32">
         <v>22</v>
@@ -2932,19 +2945,19 @@
         <v>31</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>37</v>
+        <v>144</v>
       </c>
       <c r="C33" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D33">
         <v>22</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>132</v>
+        <v>65</v>
       </c>
       <c r="F33" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G33">
         <v>22</v>
@@ -2974,24 +2987,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:15">
+    <row r="34" spans="1:15" ht="37.5">
       <c r="A34">
         <v>32</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>31</v>
+        <v>145</v>
       </c>
       <c r="C34" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D34">
         <v>22</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>133</v>
+        <v>66</v>
       </c>
       <c r="F34" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G34">
         <v>22</v>
@@ -3026,19 +3039,19 @@
         <v>33</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>32</v>
+        <v>146</v>
       </c>
       <c r="C35" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D35">
         <v>22</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>134</v>
+        <v>67</v>
       </c>
       <c r="F35" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G35">
         <v>22</v>
@@ -3073,19 +3086,19 @@
         <v>34</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>35</v>
+        <v>148</v>
       </c>
       <c r="C36" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D36">
         <v>22</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>135</v>
+        <v>68</v>
       </c>
       <c r="F36" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G36">
         <v>22</v>
@@ -3120,19 +3133,19 @@
         <v>35</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>34</v>
+        <v>149</v>
       </c>
       <c r="C37" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="D37">
         <v>22</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>136</v>
+        <v>69</v>
       </c>
       <c r="F37" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="G37">
         <v>22</v>
@@ -3167,19 +3180,19 @@
         <v>36</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>36</v>
+        <v>150</v>
       </c>
       <c r="C38" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D38">
         <v>22</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>137</v>
+        <v>70</v>
       </c>
       <c r="F38" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G38">
         <v>22</v>
@@ -3249,19 +3262,19 @@
         <v>38</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>39</v>
+        <v>151</v>
       </c>
       <c r="C40" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D40">
         <v>22</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>138</v>
+        <v>71</v>
       </c>
       <c r="F40" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G40">
         <v>22</v>
@@ -3291,24 +3304,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="56.25">
+    <row r="41" spans="1:15" ht="85.5" customHeight="1">
       <c r="A41">
         <v>39</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>43</v>
+        <v>152</v>
       </c>
       <c r="C41" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D41">
         <v>22</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>140</v>
+        <v>73</v>
       </c>
       <c r="F41" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G41">
         <v>22</v>
@@ -3338,24 +3351,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:15">
+    <row r="42" spans="1:15" ht="51.75" customHeight="1">
       <c r="A42">
         <v>40</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>84</v>
+        <v>153</v>
       </c>
       <c r="C42" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D42">
         <v>22</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>141</v>
+        <v>74</v>
       </c>
       <c r="F42" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G42">
         <v>22</v>
@@ -3390,19 +3403,19 @@
         <v>41</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="C43" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D43">
         <v>22</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>142</v>
+        <v>75</v>
       </c>
       <c r="F43" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G43">
         <v>22</v>
@@ -3437,19 +3450,19 @@
         <v>42</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>186</v>
+        <v>156</v>
       </c>
       <c r="C44" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D44">
         <v>22</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>185</v>
+        <v>118</v>
       </c>
       <c r="F44" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G44">
         <v>22</v>
@@ -3484,19 +3497,19 @@
         <v>43</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>40</v>
+        <v>184</v>
       </c>
       <c r="C45" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D45">
         <v>22</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>143</v>
+        <v>76</v>
       </c>
       <c r="F45" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G45">
         <v>22</v>
@@ -3531,19 +3544,19 @@
         <v>44</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>85</v>
+        <v>155</v>
       </c>
       <c r="C46" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D46">
         <v>22</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>144</v>
+        <v>77</v>
       </c>
       <c r="F46" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G46">
         <v>22</v>
@@ -3578,19 +3591,19 @@
         <v>45</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>188</v>
+        <v>157</v>
       </c>
       <c r="C47" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D47">
         <v>22</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>187</v>
+        <v>119</v>
       </c>
       <c r="F47" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G47">
         <v>22</v>
@@ -3625,19 +3638,19 @@
         <v>46</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>42</v>
+        <v>185</v>
       </c>
       <c r="C48" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D48">
         <v>22</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>145</v>
+        <v>78</v>
       </c>
       <c r="F48" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G48">
         <v>22</v>
@@ -3672,19 +3685,19 @@
         <v>47</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>80</v>
+        <v>158</v>
       </c>
       <c r="C49" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D49">
         <v>22</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="F49" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G49">
         <v>22</v>
@@ -3719,19 +3732,19 @@
         <v>48</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>41</v>
+        <v>186</v>
       </c>
       <c r="C50" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D50">
         <v>22</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>147</v>
+        <v>80</v>
       </c>
       <c r="F50" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G50">
         <v>22</v>
@@ -3766,19 +3779,19 @@
         <v>49</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>50</v>
+        <v>159</v>
       </c>
       <c r="C51" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D51">
         <v>22</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>148</v>
+        <v>81</v>
       </c>
       <c r="F51" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G51">
         <v>22</v>
@@ -3813,19 +3826,19 @@
         <v>50</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>45</v>
+        <v>160</v>
       </c>
       <c r="C52" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="D52">
         <v>22</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>149</v>
+        <v>82</v>
       </c>
       <c r="F52" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="G52">
         <v>22</v>
@@ -3860,19 +3873,19 @@
         <v>51</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="C53" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D53">
         <v>22</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>150</v>
+        <v>83</v>
       </c>
       <c r="F53" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G53">
         <v>22</v>
@@ -3907,19 +3920,19 @@
         <v>52</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="C54" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="D54">
         <v>22</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>151</v>
+        <v>84</v>
       </c>
       <c r="F54" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="G54">
         <v>22</v>
@@ -3954,19 +3967,19 @@
         <v>53</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="C55" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D55">
         <v>22</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>152</v>
+        <v>85</v>
       </c>
       <c r="F55" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G55">
         <v>22</v>
@@ -4001,19 +4014,19 @@
         <v>54</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>48</v>
+        <v>161</v>
       </c>
       <c r="C56" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D56">
         <v>22</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>153</v>
+        <v>86</v>
       </c>
       <c r="F56" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G56">
         <v>22</v>
@@ -4048,19 +4061,19 @@
         <v>55</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>49</v>
+        <v>162</v>
       </c>
       <c r="C57" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D57">
         <v>22</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>154</v>
+        <v>87</v>
       </c>
       <c r="F57" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G57">
         <v>22</v>
@@ -4095,19 +4108,19 @@
         <v>56</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>51</v>
+        <v>163</v>
       </c>
       <c r="C58" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D58">
         <v>22</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>162</v>
+        <v>95</v>
       </c>
       <c r="F58" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G58">
         <v>22</v>
@@ -4142,19 +4155,19 @@
         <v>57</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="C59" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D59">
         <v>22</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="F59" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G59">
         <v>22</v>
@@ -4189,19 +4202,19 @@
         <v>58</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="C60" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="D60">
         <v>22</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>156</v>
+        <v>89</v>
       </c>
       <c r="F60" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="G60">
         <v>22</v>
@@ -4236,19 +4249,19 @@
         <v>59</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>54</v>
+        <v>164</v>
       </c>
       <c r="C61" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D61">
         <v>22</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>157</v>
+        <v>90</v>
       </c>
       <c r="F61" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G61">
         <v>22</v>
@@ -4283,19 +4296,19 @@
         <v>60</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>55</v>
+        <v>165</v>
       </c>
       <c r="C62" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="D62">
         <v>22</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>158</v>
+        <v>91</v>
       </c>
       <c r="F62" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="G62">
         <v>22</v>
@@ -4330,19 +4343,19 @@
         <v>61</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>57</v>
+        <v>166</v>
       </c>
       <c r="C63" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D63">
         <v>22</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>159</v>
+        <v>92</v>
       </c>
       <c r="F63" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G63">
         <v>22</v>
@@ -4377,19 +4390,19 @@
         <v>62</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>56</v>
+        <v>167</v>
       </c>
       <c r="C64" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="D64">
         <v>22</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>160</v>
+        <v>93</v>
       </c>
       <c r="F64" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="G64">
         <v>22</v>
@@ -4424,19 +4437,19 @@
         <v>63</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>61</v>
+        <v>187</v>
       </c>
       <c r="C65" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D65">
         <v>22</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>161</v>
+        <v>94</v>
       </c>
       <c r="F65" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G65">
         <v>22</v>
@@ -4471,19 +4484,19 @@
         <v>64</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>58</v>
+        <v>188</v>
       </c>
       <c r="C66" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D66">
         <v>22</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>163</v>
+        <v>96</v>
       </c>
       <c r="F66" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G66">
         <v>22</v>
@@ -4518,19 +4531,19 @@
         <v>65</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>59</v>
+        <v>168</v>
       </c>
       <c r="C67" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D67">
         <v>22</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>164</v>
+        <v>97</v>
       </c>
       <c r="F67" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G67">
         <v>22</v>
@@ -4565,19 +4578,19 @@
         <v>66</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="C68" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="D68">
         <v>22</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>165</v>
+        <v>98</v>
       </c>
       <c r="F68" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="G68">
         <v>22</v>
@@ -4612,19 +4625,19 @@
         <v>67</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>87</v>
+        <v>169</v>
       </c>
       <c r="C69" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D69">
         <v>22</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>166</v>
+        <v>99</v>
       </c>
       <c r="F69" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G69">
         <v>22</v>
@@ -4659,19 +4672,19 @@
         <v>68</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>62</v>
+        <v>170</v>
       </c>
       <c r="C70" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D70">
         <v>22</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>167</v>
+        <v>100</v>
       </c>
       <c r="F70" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G70">
         <v>22</v>
@@ -4741,19 +4754,19 @@
         <v>70</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>74</v>
+        <v>171</v>
       </c>
       <c r="C72" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="D72">
         <v>22</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>168</v>
+        <v>101</v>
       </c>
       <c r="F72" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="G72">
         <v>22</v>
@@ -4788,19 +4801,19 @@
         <v>71</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>73</v>
+        <v>15</v>
       </c>
       <c r="C73" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="D73">
         <v>22</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>169</v>
+        <v>102</v>
       </c>
       <c r="F73" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="G73">
         <v>22</v>
@@ -4835,19 +4848,19 @@
         <v>72</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>63</v>
+        <v>172</v>
       </c>
       <c r="C74" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="D74">
         <v>22</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>170</v>
+        <v>103</v>
       </c>
       <c r="F74" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="G74">
         <v>22</v>
@@ -4882,19 +4895,19 @@
         <v>73</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>64</v>
+        <v>173</v>
       </c>
       <c r="C75" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D75">
         <v>22</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>171</v>
+        <v>104</v>
       </c>
       <c r="F75" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G75">
         <v>22</v>
@@ -4929,19 +4942,19 @@
         <v>74</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>65</v>
+        <v>174</v>
       </c>
       <c r="C76" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D76">
         <v>22</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>172</v>
+        <v>105</v>
       </c>
       <c r="F76" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G76">
         <v>22</v>
@@ -4976,19 +4989,19 @@
         <v>75</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>71</v>
+        <v>175</v>
       </c>
       <c r="C77" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="D77">
         <v>22</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>173</v>
+        <v>106</v>
       </c>
       <c r="F77" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="G77">
         <v>22</v>
@@ -5023,19 +5036,19 @@
         <v>76</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>72</v>
+        <v>176</v>
       </c>
       <c r="C78" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="D78">
         <v>22</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>174</v>
+        <v>107</v>
       </c>
       <c r="F78" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="G78">
         <v>22</v>
@@ -5070,19 +5083,19 @@
         <v>77</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>66</v>
+        <v>177</v>
       </c>
       <c r="C79" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D79">
         <v>22</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>175</v>
+        <v>108</v>
       </c>
       <c r="F79" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G79">
         <v>22</v>
@@ -5117,19 +5130,19 @@
         <v>78</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="C80" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="D80">
         <v>22</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>151</v>
+        <v>84</v>
       </c>
       <c r="F80" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="G80">
         <v>22</v>
@@ -5164,19 +5177,19 @@
         <v>79</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>67</v>
+        <v>178</v>
       </c>
       <c r="C81" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D81">
         <v>22</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>176</v>
+        <v>109</v>
       </c>
       <c r="F81" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G81">
         <v>22</v>
@@ -5211,19 +5224,19 @@
         <v>80</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>68</v>
+        <v>14</v>
       </c>
       <c r="C82" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="D82">
         <v>22</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>177</v>
+        <v>110</v>
       </c>
       <c r="F82" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="G82">
         <v>22</v>
@@ -5258,19 +5271,19 @@
         <v>81</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>69</v>
+        <v>179</v>
       </c>
       <c r="C83" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D83">
         <v>22</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>178</v>
+        <v>111</v>
       </c>
       <c r="F83" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G83">
         <v>22</v>
@@ -5305,19 +5318,19 @@
         <v>82</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="C84" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="D84">
         <v>22</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>179</v>
+        <v>112</v>
       </c>
       <c r="F84" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="G84">
         <v>22</v>
@@ -5352,19 +5365,19 @@
         <v>83</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>70</v>
+        <v>180</v>
       </c>
       <c r="C85" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D85">
         <v>22</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>180</v>
+        <v>113</v>
       </c>
       <c r="F85" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G85">
         <v>22</v>
@@ -5399,19 +5412,19 @@
         <v>84</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="C86" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="D86">
         <v>22</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>181</v>
+        <v>114</v>
       </c>
       <c r="F86" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="G86">
         <v>22</v>
@@ -5446,19 +5459,19 @@
         <v>85</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>79</v>
+        <v>181</v>
       </c>
       <c r="C87" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D87">
         <v>22</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>182</v>
+        <v>115</v>
       </c>
       <c r="F87" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G87">
         <v>22</v>
@@ -5493,19 +5506,19 @@
         <v>86</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>77</v>
+        <v>182</v>
       </c>
       <c r="C88" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D88">
         <v>22</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>183</v>
+        <v>116</v>
       </c>
       <c r="F88" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G88">
         <v>22</v>
@@ -5540,19 +5553,19 @@
         <v>87</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>78</v>
+        <v>183</v>
       </c>
       <c r="C89" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D89">
         <v>22</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>184</v>
+        <v>117</v>
       </c>
       <c r="F89" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G89">
         <v>22</v>

--- a/Assets/Originals/Excels/Talk/TalkMessage.xlsx
+++ b/Assets/Originals/Excels/Talk/TalkMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Talk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE655FAF-BE08-4D9A-B61A-56949A5B5E70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C461CE1D-EE88-45C4-AF86-B7C85793B742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="talkMessage" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="189">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -643,17 +644,8 @@
   <si>
     <t>&lt;r="うつしよ"&gt;現世&lt;/r&gt;で&lt;r="おか"&gt;犯&lt;/r&gt;した&lt;r="つみ"&gt;罪&lt;/r&gt;を&lt;r="おも"&gt;思&lt;/r&gt;い&lt;r="だ"&gt;出&lt;/r&gt;して　この&lt;r="めいきゅう"&gt;迷宮&lt;/r&gt;から&lt;r="だっしゅつ"&gt;脱出&lt;/r&gt;できたら　
 &lt;r="きみ"&gt;君&lt;/r&gt;の&lt;r="なまえ"&gt;名前&lt;/r&gt;を&lt;r="おし"&gt;教&lt;/r&gt;えてあげるよ</t>
-    <rPh sb="177" eb="179">
-      <t>メイキュウ</t>
-    </rPh>
-    <rPh sb="181" eb="183">
-      <t>ダッシュツ</t>
-    </rPh>
-    <rPh sb="189" eb="190">
-      <t>キミ</t>
-    </rPh>
-    <rPh sb="194" eb="195">
-      <t>オシ</t>
+    <rPh sb="0" eb="168">
+      <t>メイキュウダッシュツキミオシ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2987,7 +2979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="37.5">
+    <row r="34" spans="1:15">
       <c r="A34">
         <v>32</v>
       </c>

--- a/Assets/Originals/Excels/Talk/TalkMessage.xlsx
+++ b/Assets/Originals/Excels/Talk/TalkMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Talk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C461CE1D-EE88-45C4-AF86-B7C85793B742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D634FB96-54BA-4837-BF8B-0014BAC3EA14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="talkMessage" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -292,10 +291,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>...I want to escape!</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>But... how do I get out?</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -313,10 +308,6 @@
   </si>
   <si>
     <t>...Will you accept my trial?</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>...I'll do it!</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1077,6 +1068,14 @@
     <rPh sb="44" eb="45">
       <t>ホ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>...I want to escape.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>...I'll do it.</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1577,7 +1576,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C4" t="s">
         <v>20</v>
@@ -1624,7 +1623,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C5" t="s">
         <v>2</v>
@@ -1671,7 +1670,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
@@ -1718,7 +1717,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C7" t="s">
         <v>2</v>
@@ -1765,7 +1764,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C8" t="s">
         <v>2</v>
@@ -1812,7 +1811,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C9" t="s">
         <v>2</v>
@@ -1859,7 +1858,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C10" t="s">
         <v>18</v>
@@ -1906,7 +1905,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C11" t="s">
         <v>2</v>
@@ -1953,7 +1952,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C12" t="s">
         <v>2</v>
@@ -2000,7 +1999,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C13" t="s">
         <v>18</v>
@@ -2094,7 +2093,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C15" t="s">
         <v>2</v>
@@ -2141,7 +2140,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C16" t="s">
         <v>2</v>
@@ -2188,7 +2187,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C17" t="s">
         <v>18</v>
@@ -2282,7 +2281,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C19" t="s">
         <v>2</v>
@@ -2376,7 +2375,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C21" t="s">
         <v>2</v>
@@ -2420,7 +2419,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C22" t="s">
         <v>2</v>
@@ -2467,7 +2466,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C23" t="s">
         <v>2</v>
@@ -2514,7 +2513,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C24" t="s">
         <v>18</v>
@@ -2608,7 +2607,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C26" t="s">
         <v>2</v>
@@ -2655,7 +2654,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C27" t="s">
         <v>2</v>
@@ -2702,7 +2701,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C28" t="s">
         <v>2</v>
@@ -2711,7 +2710,7 @@
         <v>22</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F28" t="s">
         <v>34</v>
@@ -2749,7 +2748,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C29" t="s">
         <v>2</v>
@@ -2796,7 +2795,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C30" t="s">
         <v>2</v>
@@ -2843,7 +2842,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C31" t="s">
         <v>18</v>
@@ -2852,7 +2851,7 @@
         <v>22</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>63</v>
+        <v>187</v>
       </c>
       <c r="F31" t="s">
         <v>33</v>
@@ -2890,7 +2889,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C32" t="s">
         <v>18</v>
@@ -2899,7 +2898,7 @@
         <v>22</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F32" t="s">
         <v>33</v>
@@ -2937,7 +2936,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C33" t="s">
         <v>2</v>
@@ -2946,7 +2945,7 @@
         <v>22</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F33" t="s">
         <v>34</v>
@@ -2984,7 +2983,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C34" t="s">
         <v>2</v>
@@ -2993,7 +2992,7 @@
         <v>22</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F34" t="s">
         <v>34</v>
@@ -3031,7 +3030,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C35" t="s">
         <v>2</v>
@@ -3040,7 +3039,7 @@
         <v>22</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F35" t="s">
         <v>34</v>
@@ -3078,7 +3077,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C36" t="s">
         <v>2</v>
@@ -3087,7 +3086,7 @@
         <v>22</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F36" t="s">
         <v>34</v>
@@ -3125,7 +3124,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C37" t="s">
         <v>18</v>
@@ -3134,7 +3133,7 @@
         <v>22</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>69</v>
+        <v>188</v>
       </c>
       <c r="F37" t="s">
         <v>33</v>
@@ -3172,7 +3171,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C38" t="s">
         <v>2</v>
@@ -3181,7 +3180,7 @@
         <v>22</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F38" t="s">
         <v>34</v>
@@ -3254,7 +3253,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C40" t="s">
         <v>2</v>
@@ -3263,7 +3262,7 @@
         <v>22</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F40" t="s">
         <v>34</v>
@@ -3301,7 +3300,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C41" t="s">
         <v>2</v>
@@ -3310,7 +3309,7 @@
         <v>22</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F41" t="s">
         <v>34</v>
@@ -3348,7 +3347,7 @@
         <v>40</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C42" t="s">
         <v>2</v>
@@ -3357,7 +3356,7 @@
         <v>22</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F42" t="s">
         <v>34</v>
@@ -3395,7 +3394,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C43" t="s">
         <v>2</v>
@@ -3404,7 +3403,7 @@
         <v>22</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F43" t="s">
         <v>34</v>
@@ -3442,7 +3441,7 @@
         <v>42</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C44" t="s">
         <v>2</v>
@@ -3451,7 +3450,7 @@
         <v>22</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F44" t="s">
         <v>34</v>
@@ -3489,7 +3488,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C45" t="s">
         <v>2</v>
@@ -3498,7 +3497,7 @@
         <v>22</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F45" t="s">
         <v>34</v>
@@ -3536,7 +3535,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C46" t="s">
         <v>2</v>
@@ -3545,7 +3544,7 @@
         <v>22</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F46" t="s">
         <v>34</v>
@@ -3583,7 +3582,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C47" t="s">
         <v>2</v>
@@ -3592,7 +3591,7 @@
         <v>22</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F47" t="s">
         <v>34</v>
@@ -3630,7 +3629,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C48" t="s">
         <v>2</v>
@@ -3639,7 +3638,7 @@
         <v>22</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F48" t="s">
         <v>34</v>
@@ -3677,7 +3676,7 @@
         <v>47</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C49" t="s">
         <v>2</v>
@@ -3686,7 +3685,7 @@
         <v>22</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F49" t="s">
         <v>34</v>
@@ -3724,7 +3723,7 @@
         <v>48</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C50" t="s">
         <v>2</v>
@@ -3733,7 +3732,7 @@
         <v>22</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F50" t="s">
         <v>34</v>
@@ -3771,7 +3770,7 @@
         <v>49</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C51" t="s">
         <v>2</v>
@@ -3780,7 +3779,7 @@
         <v>22</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F51" t="s">
         <v>34</v>
@@ -3818,7 +3817,7 @@
         <v>50</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C52" t="s">
         <v>18</v>
@@ -3827,7 +3826,7 @@
         <v>22</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F52" t="s">
         <v>33</v>
@@ -3874,7 +3873,7 @@
         <v>22</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F53" t="s">
         <v>34</v>
@@ -3921,7 +3920,7 @@
         <v>22</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F54" t="s">
         <v>33</v>
@@ -3968,7 +3967,7 @@
         <v>22</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F55" t="s">
         <v>34</v>
@@ -4006,7 +4005,7 @@
         <v>54</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C56" t="s">
         <v>2</v>
@@ -4015,7 +4014,7 @@
         <v>22</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F56" t="s">
         <v>34</v>
@@ -4053,7 +4052,7 @@
         <v>55</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C57" t="s">
         <v>2</v>
@@ -4062,7 +4061,7 @@
         <v>22</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F57" t="s">
         <v>34</v>
@@ -4100,7 +4099,7 @@
         <v>56</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C58" t="s">
         <v>2</v>
@@ -4109,7 +4108,7 @@
         <v>22</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F58" t="s">
         <v>34</v>
@@ -4156,7 +4155,7 @@
         <v>22</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F59" t="s">
         <v>34</v>
@@ -4203,7 +4202,7 @@
         <v>22</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F60" t="s">
         <v>33</v>
@@ -4241,7 +4240,7 @@
         <v>59</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C61" t="s">
         <v>2</v>
@@ -4250,7 +4249,7 @@
         <v>22</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F61" t="s">
         <v>34</v>
@@ -4288,7 +4287,7 @@
         <v>60</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C62" t="s">
         <v>18</v>
@@ -4297,7 +4296,7 @@
         <v>22</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F62" t="s">
         <v>33</v>
@@ -4335,7 +4334,7 @@
         <v>61</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C63" t="s">
         <v>2</v>
@@ -4344,7 +4343,7 @@
         <v>22</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F63" t="s">
         <v>34</v>
@@ -4382,7 +4381,7 @@
         <v>62</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C64" t="s">
         <v>18</v>
@@ -4391,7 +4390,7 @@
         <v>22</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F64" t="s">
         <v>33</v>
@@ -4429,7 +4428,7 @@
         <v>63</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C65" t="s">
         <v>2</v>
@@ -4438,7 +4437,7 @@
         <v>22</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F65" t="s">
         <v>34</v>
@@ -4476,7 +4475,7 @@
         <v>64</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C66" t="s">
         <v>2</v>
@@ -4485,7 +4484,7 @@
         <v>22</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F66" t="s">
         <v>34</v>
@@ -4523,7 +4522,7 @@
         <v>65</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C67" t="s">
         <v>2</v>
@@ -4532,7 +4531,7 @@
         <v>22</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F67" t="s">
         <v>34</v>
@@ -4579,7 +4578,7 @@
         <v>22</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F68" t="s">
         <v>33</v>
@@ -4617,7 +4616,7 @@
         <v>67</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C69" t="s">
         <v>2</v>
@@ -4626,7 +4625,7 @@
         <v>22</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F69" t="s">
         <v>34</v>
@@ -4664,7 +4663,7 @@
         <v>68</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C70" t="s">
         <v>2</v>
@@ -4673,7 +4672,7 @@
         <v>22</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F70" t="s">
         <v>34</v>
@@ -4746,7 +4745,7 @@
         <v>70</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C72" t="s">
         <v>18</v>
@@ -4755,7 +4754,7 @@
         <v>22</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F72" t="s">
         <v>33</v>
@@ -4802,7 +4801,7 @@
         <v>22</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F73" t="s">
         <v>33</v>
@@ -4840,7 +4839,7 @@
         <v>72</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C74" t="s">
         <v>18</v>
@@ -4849,7 +4848,7 @@
         <v>22</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F74" t="s">
         <v>33</v>
@@ -4887,7 +4886,7 @@
         <v>73</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C75" t="s">
         <v>2</v>
@@ -4896,7 +4895,7 @@
         <v>22</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F75" t="s">
         <v>34</v>
@@ -4934,7 +4933,7 @@
         <v>74</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C76" t="s">
         <v>2</v>
@@ -4943,7 +4942,7 @@
         <v>22</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F76" t="s">
         <v>34</v>
@@ -4981,7 +4980,7 @@
         <v>75</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C77" t="s">
         <v>18</v>
@@ -4990,7 +4989,7 @@
         <v>22</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F77" t="s">
         <v>33</v>
@@ -5028,7 +5027,7 @@
         <v>76</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C78" t="s">
         <v>18</v>
@@ -5037,7 +5036,7 @@
         <v>22</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F78" t="s">
         <v>33</v>
@@ -5075,7 +5074,7 @@
         <v>77</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C79" t="s">
         <v>2</v>
@@ -5084,7 +5083,7 @@
         <v>22</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F79" t="s">
         <v>34</v>
@@ -5131,7 +5130,7 @@
         <v>22</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F80" t="s">
         <v>33</v>
@@ -5169,7 +5168,7 @@
         <v>79</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C81" t="s">
         <v>2</v>
@@ -5178,7 +5177,7 @@
         <v>22</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F81" t="s">
         <v>34</v>
@@ -5225,7 +5224,7 @@
         <v>22</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F82" t="s">
         <v>33</v>
@@ -5263,7 +5262,7 @@
         <v>81</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C83" t="s">
         <v>2</v>
@@ -5272,7 +5271,7 @@
         <v>22</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F83" t="s">
         <v>34</v>
@@ -5319,7 +5318,7 @@
         <v>22</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F84" t="s">
         <v>33</v>
@@ -5357,7 +5356,7 @@
         <v>83</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C85" t="s">
         <v>2</v>
@@ -5366,7 +5365,7 @@
         <v>22</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F85" t="s">
         <v>34</v>
@@ -5413,7 +5412,7 @@
         <v>22</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F86" t="s">
         <v>33</v>
@@ -5451,7 +5450,7 @@
         <v>85</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C87" t="s">
         <v>2</v>
@@ -5460,7 +5459,7 @@
         <v>22</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F87" t="s">
         <v>34</v>
@@ -5498,7 +5497,7 @@
         <v>86</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C88" t="s">
         <v>2</v>
@@ -5507,7 +5506,7 @@
         <v>22</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F88" t="s">
         <v>34</v>
@@ -5545,7 +5544,7 @@
         <v>87</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C89" t="s">
         <v>2</v>
@@ -5554,7 +5553,7 @@
         <v>22</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F89" t="s">
         <v>34</v>

--- a/Assets/Originals/Excels/Talk/TalkMessage.xlsx
+++ b/Assets/Originals/Excels/Talk/TalkMessage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Talk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D634FB96-54BA-4837-BF8B-0014BAC3EA14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4679CA56-9EF3-4878-8CB2-B74CBE0B411A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -545,14 +545,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>&lt;r="きみ"&gt;君&lt;/r&gt;は&lt;r="うつしよ"&gt;現世&lt;/r&gt;で"&lt;r="つみ"&gt;罪&lt;/r&gt;”を&lt;r="おか"&gt;犯&lt;/r&gt;して&lt;r="しぼう"&gt;死亡&lt;/r&gt;した
-&lt;r="つみ"&gt;罪&lt;/r&gt;を&lt;r="おか"&gt;犯&lt;/r&gt;した&lt;r="にんげん"&gt;人間&lt;/r&gt;は　みんなこの&lt;r="むめい"&gt;夢迷&lt;/r&gt;に&lt;r="ゆうへい"&gt;幽閉&lt;/r&gt;される</t>
-    <rPh sb="40" eb="41">
-      <t>ツミ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>つまり　&lt;r="きみ"&gt;君&lt;/r&gt;もそのうちの&lt;r="ひとり"&gt;1人&lt;/r&gt;ということさ</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1076,6 +1068,14 @@
   </si>
   <si>
     <t>...I'll do it.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="きみ"&gt;君&lt;/r&gt;は&lt;r="うつしよ"&gt;現世&lt;/r&gt;で”&lt;r="つみ"&gt;罪&lt;/r&gt;”を&lt;r="おか"&gt;犯&lt;/r&gt;して&lt;r="しぼう"&gt;死亡&lt;/r&gt;した
+&lt;r="つみ"&gt;罪&lt;/r&gt;を&lt;r="おか"&gt;犯&lt;/r&gt;した&lt;r="にんげん"&gt;人間&lt;/r&gt;は　みんなこの&lt;r="むめい"&gt;夢迷&lt;/r&gt;に&lt;r="ゆうへい"&gt;幽閉&lt;/r&gt;される</t>
+    <rPh sb="40" eb="41">
+      <t>ツミ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1764,7 +1764,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>122</v>
+        <v>188</v>
       </c>
       <c r="C8" t="s">
         <v>2</v>
@@ -1811,7 +1811,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C9" t="s">
         <v>2</v>
@@ -1858,7 +1858,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C10" t="s">
         <v>18</v>
@@ -1905,7 +1905,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C11" t="s">
         <v>2</v>
@@ -1952,7 +1952,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C12" t="s">
         <v>2</v>
@@ -1999,7 +1999,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C13" t="s">
         <v>18</v>
@@ -2093,7 +2093,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C15" t="s">
         <v>2</v>
@@ -2140,7 +2140,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C16" t="s">
         <v>2</v>
@@ -2187,7 +2187,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C17" t="s">
         <v>18</v>
@@ -2281,7 +2281,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C19" t="s">
         <v>2</v>
@@ -2375,7 +2375,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C21" t="s">
         <v>2</v>
@@ -2419,7 +2419,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C22" t="s">
         <v>2</v>
@@ -2466,7 +2466,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C23" t="s">
         <v>2</v>
@@ -2513,7 +2513,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C24" t="s">
         <v>18</v>
@@ -2607,7 +2607,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C26" t="s">
         <v>2</v>
@@ -2654,7 +2654,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C27" t="s">
         <v>2</v>
@@ -2701,7 +2701,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C28" t="s">
         <v>2</v>
@@ -2748,7 +2748,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C29" t="s">
         <v>2</v>
@@ -2795,7 +2795,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C30" t="s">
         <v>2</v>
@@ -2842,7 +2842,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C31" t="s">
         <v>18</v>
@@ -2851,7 +2851,7 @@
         <v>22</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F31" t="s">
         <v>33</v>
@@ -2889,7 +2889,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C32" t="s">
         <v>18</v>
@@ -2936,7 +2936,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C33" t="s">
         <v>2</v>
@@ -2983,7 +2983,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C34" t="s">
         <v>2</v>
@@ -3030,7 +3030,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C35" t="s">
         <v>2</v>
@@ -3077,7 +3077,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C36" t="s">
         <v>2</v>
@@ -3124,7 +3124,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C37" t="s">
         <v>18</v>
@@ -3133,7 +3133,7 @@
         <v>22</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F37" t="s">
         <v>33</v>
@@ -3171,7 +3171,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C38" t="s">
         <v>2</v>
@@ -3253,7 +3253,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C40" t="s">
         <v>2</v>
@@ -3300,7 +3300,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C41" t="s">
         <v>2</v>
@@ -3347,7 +3347,7 @@
         <v>40</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C42" t="s">
         <v>2</v>
@@ -3394,7 +3394,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C43" t="s">
         <v>2</v>
@@ -3441,7 +3441,7 @@
         <v>42</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C44" t="s">
         <v>2</v>
@@ -3488,7 +3488,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C45" t="s">
         <v>2</v>
@@ -3535,7 +3535,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C46" t="s">
         <v>2</v>
@@ -3582,7 +3582,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C47" t="s">
         <v>2</v>
@@ -3629,7 +3629,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C48" t="s">
         <v>2</v>
@@ -3676,7 +3676,7 @@
         <v>47</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C49" t="s">
         <v>2</v>
@@ -3723,7 +3723,7 @@
         <v>48</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C50" t="s">
         <v>2</v>
@@ -3770,7 +3770,7 @@
         <v>49</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C51" t="s">
         <v>2</v>
@@ -3817,7 +3817,7 @@
         <v>50</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C52" t="s">
         <v>18</v>
@@ -4005,7 +4005,7 @@
         <v>54</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C56" t="s">
         <v>2</v>
@@ -4052,7 +4052,7 @@
         <v>55</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C57" t="s">
         <v>2</v>
@@ -4099,7 +4099,7 @@
         <v>56</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C58" t="s">
         <v>2</v>
@@ -4240,7 +4240,7 @@
         <v>59</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C61" t="s">
         <v>2</v>
@@ -4287,7 +4287,7 @@
         <v>60</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C62" t="s">
         <v>18</v>
@@ -4334,7 +4334,7 @@
         <v>61</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C63" t="s">
         <v>2</v>
@@ -4381,7 +4381,7 @@
         <v>62</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C64" t="s">
         <v>18</v>
@@ -4428,7 +4428,7 @@
         <v>63</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C65" t="s">
         <v>2</v>
@@ -4475,7 +4475,7 @@
         <v>64</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C66" t="s">
         <v>2</v>
@@ -4522,7 +4522,7 @@
         <v>65</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C67" t="s">
         <v>2</v>
@@ -4616,7 +4616,7 @@
         <v>67</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C69" t="s">
         <v>2</v>
@@ -4663,7 +4663,7 @@
         <v>68</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C70" t="s">
         <v>2</v>
@@ -4745,7 +4745,7 @@
         <v>70</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C72" t="s">
         <v>18</v>
@@ -4839,7 +4839,7 @@
         <v>72</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C74" t="s">
         <v>18</v>
@@ -4886,7 +4886,7 @@
         <v>73</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C75" t="s">
         <v>2</v>
@@ -4933,7 +4933,7 @@
         <v>74</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C76" t="s">
         <v>2</v>
@@ -4980,7 +4980,7 @@
         <v>75</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C77" t="s">
         <v>18</v>
@@ -5027,7 +5027,7 @@
         <v>76</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C78" t="s">
         <v>18</v>
@@ -5074,7 +5074,7 @@
         <v>77</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C79" t="s">
         <v>2</v>
@@ -5168,7 +5168,7 @@
         <v>79</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C81" t="s">
         <v>2</v>
@@ -5262,7 +5262,7 @@
         <v>81</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C83" t="s">
         <v>2</v>
@@ -5356,7 +5356,7 @@
         <v>83</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C85" t="s">
         <v>2</v>
@@ -5450,7 +5450,7 @@
         <v>85</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C87" t="s">
         <v>2</v>
@@ -5497,7 +5497,7 @@
         <v>86</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C88" t="s">
         <v>2</v>
@@ -5544,7 +5544,7 @@
         <v>87</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C89" t="s">
         <v>2</v>

--- a/Assets/Originals/Excels/Talk/TalkMessage.xlsx
+++ b/Assets/Originals/Excels/Talk/TalkMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Talk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4679CA56-9EF3-4878-8CB2-B74CBE0B411A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58739612-B4B9-4D7F-A495-8854DF746C85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="278">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -1076,6 +1076,294 @@
     <rPh sb="40" eb="41">
       <t>ツミ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>这里…是哪里…</t>
+  </si>
+  <si>
+    <t>你</t>
+  </si>
+  <si>
+    <t>你好像醒了呢</t>
+  </si>
+  <si>
+    <t>？？？</t>
+  </si>
+  <si>
+    <t>我叫要
+是「梦迷」的向导</t>
+  </si>
+  <si>
+    <t>要</t>
+  </si>
+  <si>
+    <t>梦迷？</t>
+  </si>
+  <si>
+    <t>就是这个常世里的巨大迷宫</t>
+  </si>
+  <si>
+    <t>你在现世犯下了「罪」而死亡
+犯下罪的人都会被幽禁在这座梦迷之中</t>
+  </si>
+  <si>
+    <t>也就是说　你也是其中一员</t>
+  </si>
+  <si>
+    <t>罪？</t>
+  </si>
+  <si>
+    <t>没错　是非常非常深重的罪</t>
+  </si>
+  <si>
+    <t>对了　你还记得自己的名字吗？</t>
+  </si>
+  <si>
+    <t>呃…我的名字是…</t>
+  </si>
+  <si>
+    <t>咦……想不起来……</t>
+  </si>
+  <si>
+    <t>想不起来也是理所当然的</t>
+  </si>
+  <si>
+    <t>因为你在来到这座迷宫之前　名字就已经被舍弃了</t>
+  </si>
+  <si>
+    <t>名字…被舍弃…？</t>
+  </si>
+  <si>
+    <t>这是什么意思？</t>
+  </si>
+  <si>
+    <t>在常世里被舍弃了名字的人
+是无法想起自己名字的</t>
+  </si>
+  <si>
+    <t>咦……</t>
+  </si>
+  <si>
+    <t>而且　想不起名字的人…</t>
+  </si>
+  <si>
+    <t>将会一边承受各种痛苦
+一边永远徘徊在这座迷宫之中</t>
+  </si>
+  <si>
+    <t>你总有一天　也会变成那样吧</t>
+  </si>
+  <si>
+    <t>怎么会…太残忍了…</t>
+  </si>
+  <si>
+    <t>为什么…</t>
+  </si>
+  <si>
+    <t>因为罪人不需要名字啊</t>
+  </si>
+  <si>
+    <t>不过你放心吧</t>
+  </si>
+  <si>
+    <t>只要你想起在现世犯下的罪　并从这座迷宫中逃脱出去　
+我就会告诉你你的名字</t>
+  </si>
+  <si>
+    <t>这样一来　你就不会再承受痛苦
+也不会再徘徊下去</t>
+  </si>
+  <si>
+    <t>…你想从这里逃脱出去吗？</t>
+  </si>
+  <si>
+    <t>……我想逃出去</t>
+  </si>
+  <si>
+    <t>可是　要怎么做才能逃出去呢？</t>
+  </si>
+  <si>
+    <t>…有一个办法</t>
+  </si>
+  <si>
+    <t>那就是挑战并克服我给你的试炼</t>
+  </si>
+  <si>
+    <t>只要做到这一点　你就能逃出去了</t>
+  </si>
+  <si>
+    <t>…我的试炼　你要挑战吗？</t>
+  </si>
+  <si>
+    <t>……我要挑战</t>
+  </si>
+  <si>
+    <t>…好的
+那么我就来说明一下试炼的内容</t>
+  </si>
+  <si>
+    <t>想要克服这场试炼
+必须达成两个条件</t>
+  </si>
+  <si>
+    <t>其一　从这座迷宫中逃脱出去
+其二　想起你在现世犯下的罪</t>
+  </si>
+  <si>
+    <t>我来说明一下从这座迷宫逃脱的方法</t>
+  </si>
+  <si>
+    <t>想要逃脱　就必须在这座迷宫的各个角落　
+找出「文件」和「神秘物品」</t>
+  </si>
+  <si>
+    <t>首先　要获得文件
+你先试着打开眼前的抽屉看看</t>
+  </si>
+  <si>
+    <t>你确认一下刚拿到手的文件内容吧</t>
+  </si>
+  <si>
+    <t>接下来　要获得神秘物品</t>
+  </si>
+  <si>
+    <t>打开眼前的两个抽屉看看</t>
+  </si>
+  <si>
+    <t>你确认一下刚拿到手的神秘物品吧</t>
+  </si>
+  <si>
+    <t>最后　触碰一下里面的「裁决之蓝玉」</t>
+  </si>
+  <si>
+    <t>选择与文件内容有着深切关联的
+神秘物品</t>
+  </si>
+  <si>
+    <t>试炼的说明到此结束
+你有什么问题吗？</t>
+  </si>
+  <si>
+    <t>咦？　你不打算告诉我关于我所犯之罪的说明吗？</t>
+  </si>
+  <si>
+    <t>不会哦</t>
+  </si>
+  <si>
+    <t>别跟我说「咦」</t>
+  </si>
+  <si>
+    <t>如果你真心觉得自己做错了事
+应该马上就能想起自己的罪才对</t>
+  </si>
+  <si>
+    <t>所以说明到此为止</t>
+  </si>
+  <si>
+    <t>另外　没有名字也不方便
+我就暂且叫你「伊芙」吧</t>
+  </si>
+  <si>
+    <t>这样可以吧？</t>
+  </si>
+  <si>
+    <t>咦……嗯…嗯……</t>
+  </si>
+  <si>
+    <t>最后　关于这座迷宫还有一件注意事项</t>
+  </si>
+  <si>
+    <t>注意事项？</t>
+  </si>
+  <si>
+    <t>绝对不能被「徘徊者」抓住</t>
+  </si>
+  <si>
+    <t>徘徊者？</t>
+  </si>
+  <si>
+    <t>就是潜伏在梦迷中的怪物</t>
+  </si>
+  <si>
+    <t>伊芙　总之绝对不能被那怪物抓住哦</t>
+  </si>
+  <si>
+    <t>明白了吗？</t>
+  </si>
+  <si>
+    <t>……嗯…嗯……</t>
+  </si>
+  <si>
+    <t>那么　现在就开始试炼吧
+请你朝后面的通道前进</t>
+  </si>
+  <si>
+    <t>伊芙　我会祈祷你能通过这场试炼的</t>
+  </si>
+  <si>
+    <t>…这样…终于…能从这座迷宫中逃脱出去了…</t>
+  </si>
+  <si>
+    <t>咦……这…是什么……</t>
+  </si>
+  <si>
+    <t>为什么迷宫还没有结束！？</t>
+  </si>
+  <si>
+    <t>那还用说吗</t>
+  </si>
+  <si>
+    <t>因为你还没有从迷宫中逃脱出去啊</t>
+  </si>
+  <si>
+    <t>…你说我还没逃出去</t>
+  </si>
+  <si>
+    <t>文件和神秘物品
+我不是都好好收集齐了吗！</t>
+  </si>
+  <si>
+    <t>你该不会以为这样就结束了吧？</t>
+  </si>
+  <si>
+    <t>文件和神秘物品
+在其他区域也有哦</t>
+  </si>
+  <si>
+    <t>骗人…的吧…</t>
+  </si>
+  <si>
+    <t>而且　伊芙你也还没想起自己所犯的罪吧</t>
+  </si>
+  <si>
+    <t>…！</t>
+  </si>
+  <si>
+    <t>所以说试炼还没有结束哦</t>
+  </si>
+  <si>
+    <t>怎么会……</t>
+  </si>
+  <si>
+    <t>梦迷真正的恐怖　现在才刚刚开始　伊芙</t>
+  </si>
+  <si>
+    <t>我知道很辛苦</t>
+  </si>
+  <si>
+    <t>但我们还是要继续加油哦　伊芙</t>
+  </si>
+  <si>
+    <t>messageChinese01</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>speakerNameChinese01</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>messageSizeChinese01</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1083,7 +1371,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1114,6 +1402,12 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1135,7 +1429,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1143,6 +1437,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1425,7 +1723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O102"/>
+  <dimension ref="A1:R102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="123.375" style="2" customWidth="1"/>
@@ -1433,16 +1731,19 @@
     <col min="4" max="4" width="19.75" customWidth="1"/>
     <col min="5" max="5" width="47.125" customWidth="1"/>
     <col min="6" max="7" width="19.75" customWidth="1"/>
-    <col min="8" max="8" width="27.75" customWidth="1"/>
+    <col min="8" max="8" width="47.125" customWidth="1"/>
     <col min="9" max="9" width="22.5" customWidth="1"/>
-    <col min="10" max="10" width="13.625" customWidth="1"/>
-    <col min="12" max="12" width="17.125" customWidth="1"/>
-    <col min="13" max="13" width="28.125" customWidth="1"/>
-    <col min="14" max="14" width="13.125" customWidth="1"/>
-    <col min="15" max="15" width="16" customWidth="1"/>
+    <col min="10" max="10" width="24.75" customWidth="1"/>
+    <col min="11" max="11" width="27.75" customWidth="1"/>
+    <col min="12" max="12" width="22.5" customWidth="1"/>
+    <col min="13" max="13" width="13.625" customWidth="1"/>
+    <col min="15" max="15" width="17.125" customWidth="1"/>
+    <col min="16" max="16" width="28.125" customWidth="1"/>
+    <col min="17" max="17" width="13.125" customWidth="1"/>
+    <col min="18" max="18" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:18" ht="37.5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1465,31 +1766,40 @@
         <v>31</v>
       </c>
       <c r="H1" t="s">
+        <v>275</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="J1" t="s">
+        <v>277</v>
+      </c>
+      <c r="K1" t="s">
         <v>21</v>
       </c>
-      <c r="I1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M1" t="s">
         <v>23</v>
       </c>
-      <c r="K1" t="s">
+      <c r="N1" t="s">
         <v>24</v>
       </c>
-      <c r="L1" t="s">
+      <c r="O1" t="s">
         <v>25</v>
       </c>
-      <c r="M1" t="s">
+      <c r="P1" t="s">
         <v>26</v>
       </c>
-      <c r="N1" t="s">
+      <c r="Q1" t="s">
         <v>27</v>
       </c>
-      <c r="O1" t="s">
+      <c r="R1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:18">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1499,12 +1809,8 @@
       <c r="G2">
         <v>0</v>
       </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
       <c r="J2">
         <v>0</v>
       </c>
@@ -1523,8 +1829,17 @@
       <c r="O2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1546,14 +1861,14 @@
       <c r="G3">
         <v>22</v>
       </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
+      <c r="H3" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K3">
         <v>0</v>
@@ -1570,8 +1885,17 @@
       <c r="O3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1593,32 +1917,41 @@
       <c r="G4">
         <v>22</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="J4">
+        <v>22</v>
+      </c>
+      <c r="K4">
         <v>1</v>
       </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
         <v>3</v>
       </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
       <c r="O4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" ht="37.5">
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="37.5">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1640,14 +1973,14 @@
       <c r="G5">
         <v>22</v>
       </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
+      <c r="H5" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K5">
         <v>0</v>
@@ -1664,8 +1997,17 @@
       <c r="O5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1687,14 +2029,14 @@
       <c r="G6">
         <v>22</v>
       </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
+      <c r="H6" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K6">
         <v>0</v>
@@ -1711,8 +2053,17 @@
       <c r="O6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1734,14 +2085,14 @@
       <c r="G7">
         <v>22</v>
       </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
+      <c r="H7" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K7">
         <v>0</v>
@@ -1758,8 +2109,17 @@
       <c r="O7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" ht="56.25">
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="56.25">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1781,14 +2141,14 @@
       <c r="G8">
         <v>22</v>
       </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
+      <c r="H8" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -1805,8 +2165,17 @@
       <c r="O8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1828,14 +2197,14 @@
       <c r="G9">
         <v>22</v>
       </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
+      <c r="H9" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -1852,8 +2221,17 @@
       <c r="O9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:15">
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1875,14 +2253,14 @@
       <c r="G10">
         <v>22</v>
       </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
+      <c r="H10" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -1899,8 +2277,17 @@
       <c r="O10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1922,14 +2309,14 @@
       <c r="G11">
         <v>22</v>
       </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
+      <c r="H11" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K11">
         <v>0</v>
@@ -1946,8 +2333,17 @@
       <c r="O11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:15">
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1969,14 +2365,14 @@
       <c r="G12">
         <v>22</v>
       </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
+      <c r="H12" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -1993,8 +2389,17 @@
       <c r="O12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:15">
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
       <c r="A13">
         <v>11</v>
       </c>
@@ -2016,21 +2421,21 @@
       <c r="G13">
         <v>22</v>
       </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
+      <c r="H13" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="J13">
+        <v>22</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
         <v>1</v>
       </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
       <c r="M13">
         <v>0</v>
       </c>
@@ -2040,8 +2445,17 @@
       <c r="O13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15">
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
       <c r="A14">
         <v>12</v>
       </c>
@@ -2063,14 +2477,14 @@
       <c r="G14">
         <v>22</v>
       </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
+      <c r="H14" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -2087,8 +2501,17 @@
       <c r="O14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:15">
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
       <c r="A15">
         <v>13</v>
       </c>
@@ -2110,14 +2533,14 @@
       <c r="G15">
         <v>22</v>
       </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
+      <c r="H15" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -2134,8 +2557,17 @@
       <c r="O15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" ht="37.5">
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="37.5">
       <c r="A16">
         <v>14</v>
       </c>
@@ -2157,14 +2589,14 @@
       <c r="G16">
         <v>22</v>
       </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
+      <c r="H16" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K16">
         <v>0</v>
@@ -2181,8 +2613,17 @@
       <c r="O16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:15">
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
       <c r="A17">
         <v>15</v>
       </c>
@@ -2204,14 +2645,14 @@
       <c r="G17">
         <v>22</v>
       </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
+      <c r="H17" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K17">
         <v>0</v>
@@ -2228,8 +2669,17 @@
       <c r="O17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:15">
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
       <c r="A18">
         <v>16</v>
       </c>
@@ -2251,14 +2701,14 @@
       <c r="G18">
         <v>22</v>
       </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
+      <c r="H18" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K18">
         <v>0</v>
@@ -2275,8 +2725,17 @@
       <c r="O18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:15" ht="56.25">
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="56.25">
       <c r="A19">
         <v>17</v>
       </c>
@@ -2298,14 +2757,14 @@
       <c r="G19">
         <v>22</v>
       </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
+      <c r="H19" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K19">
         <v>0</v>
@@ -2322,8 +2781,17 @@
       <c r="O19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:15">
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
       <c r="A20">
         <v>18</v>
       </c>
@@ -2345,14 +2813,14 @@
       <c r="G20">
         <v>22</v>
       </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
+      <c r="H20" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K20">
         <v>0</v>
@@ -2369,8 +2837,17 @@
       <c r="O20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:15">
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
       <c r="A21">
         <v>19</v>
       </c>
@@ -2389,21 +2866,21 @@
       <c r="G21">
         <v>22</v>
       </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-      <c r="I21">
+      <c r="H21" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="J21">
+        <v>22</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
         <v>1</v>
       </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21">
-        <v>0</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
       <c r="M21">
         <v>0</v>
       </c>
@@ -2413,8 +2890,17 @@
       <c r="O21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:15" ht="37.5">
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="37.5">
       <c r="A22">
         <v>20</v>
       </c>
@@ -2436,14 +2922,14 @@
       <c r="G22">
         <v>22</v>
       </c>
-      <c r="H22">
-        <v>0</v>
-      </c>
-      <c r="I22">
-        <v>0</v>
+      <c r="H22" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K22">
         <v>0</v>
@@ -2460,8 +2946,17 @@
       <c r="O22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:15">
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18">
       <c r="A23">
         <v>21</v>
       </c>
@@ -2483,14 +2978,14 @@
       <c r="G23">
         <v>22</v>
       </c>
-      <c r="H23">
-        <v>0</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
+      <c r="H23" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -2507,8 +3002,17 @@
       <c r="O23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:15">
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18">
       <c r="A24">
         <v>22</v>
       </c>
@@ -2530,14 +3034,14 @@
       <c r="G24">
         <v>22</v>
       </c>
-      <c r="H24">
-        <v>0</v>
-      </c>
-      <c r="I24">
-        <v>0</v>
+      <c r="H24" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -2554,8 +3058,17 @@
       <c r="O24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:15">
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18">
       <c r="A25">
         <v>23</v>
       </c>
@@ -2577,14 +3090,14 @@
       <c r="G25">
         <v>22</v>
       </c>
-      <c r="H25">
-        <v>0</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
+      <c r="H25" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K25">
         <v>0</v>
@@ -2601,8 +3114,17 @@
       <c r="O25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:15">
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18">
       <c r="A26">
         <v>24</v>
       </c>
@@ -2624,14 +3146,14 @@
       <c r="G26">
         <v>22</v>
       </c>
-      <c r="H26">
-        <v>0</v>
-      </c>
-      <c r="I26">
-        <v>0</v>
+      <c r="H26" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K26">
         <v>0</v>
@@ -2648,8 +3170,17 @@
       <c r="O26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:15">
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18">
       <c r="A27">
         <v>25</v>
       </c>
@@ -2671,14 +3202,14 @@
       <c r="G27">
         <v>22</v>
       </c>
-      <c r="H27">
-        <v>0</v>
-      </c>
-      <c r="I27">
-        <v>0</v>
+      <c r="H27" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K27">
         <v>0</v>
@@ -2695,8 +3226,17 @@
       <c r="O27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:15" ht="56.25">
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="56.25">
       <c r="A28">
         <v>26</v>
       </c>
@@ -2718,14 +3258,14 @@
       <c r="G28">
         <v>22</v>
       </c>
-      <c r="H28">
-        <v>0</v>
-      </c>
-      <c r="I28">
-        <v>0</v>
+      <c r="H28" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K28">
         <v>0</v>
@@ -2742,8 +3282,17 @@
       <c r="O28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:15" ht="37.5">
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="37.5">
       <c r="A29">
         <v>27</v>
       </c>
@@ -2765,32 +3314,41 @@
       <c r="G29">
         <v>22</v>
       </c>
-      <c r="H29">
-        <v>0</v>
-      </c>
-      <c r="I29">
-        <v>0</v>
+      <c r="H29" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J29">
+        <v>22</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
         <v>1</v>
       </c>
-      <c r="K29">
+      <c r="N29">
         <v>1</v>
       </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
-      <c r="M29">
-        <v>0</v>
-      </c>
-      <c r="N29">
-        <v>0</v>
-      </c>
       <c r="O29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:15">
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18">
       <c r="A30">
         <v>28</v>
       </c>
@@ -2812,14 +3370,14 @@
       <c r="G30">
         <v>22</v>
       </c>
-      <c r="H30">
-        <v>0</v>
-      </c>
-      <c r="I30">
-        <v>0</v>
+      <c r="H30" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K30">
         <v>0</v>
@@ -2836,8 +3394,17 @@
       <c r="O30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:15">
+      <c r="P30">
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18">
       <c r="A31">
         <v>29</v>
       </c>
@@ -2859,14 +3426,14 @@
       <c r="G31">
         <v>22</v>
       </c>
-      <c r="H31">
-        <v>0</v>
-      </c>
-      <c r="I31">
-        <v>0</v>
+      <c r="H31" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K31">
         <v>0</v>
@@ -2883,8 +3450,17 @@
       <c r="O31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:15">
+      <c r="P31">
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <v>0</v>
+      </c>
+      <c r="R31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18">
       <c r="A32">
         <v>30</v>
       </c>
@@ -2906,14 +3482,14 @@
       <c r="G32">
         <v>22</v>
       </c>
-      <c r="H32">
-        <v>0</v>
-      </c>
-      <c r="I32">
-        <v>0</v>
+      <c r="H32" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K32">
         <v>0</v>
@@ -2930,8 +3506,17 @@
       <c r="O32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:15">
+      <c r="P32">
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <v>0</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18">
       <c r="A33">
         <v>31</v>
       </c>
@@ -2953,14 +3538,14 @@
       <c r="G33">
         <v>22</v>
       </c>
-      <c r="H33">
-        <v>0</v>
-      </c>
-      <c r="I33">
-        <v>0</v>
+      <c r="H33" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K33">
         <v>0</v>
@@ -2977,8 +3562,17 @@
       <c r="O33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:15">
+      <c r="P33">
+        <v>0</v>
+      </c>
+      <c r="Q33">
+        <v>0</v>
+      </c>
+      <c r="R33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18">
       <c r="A34">
         <v>32</v>
       </c>
@@ -3000,14 +3594,14 @@
       <c r="G34">
         <v>22</v>
       </c>
-      <c r="H34">
-        <v>0</v>
-      </c>
-      <c r="I34">
-        <v>0</v>
+      <c r="H34" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K34">
         <v>0</v>
@@ -3024,8 +3618,17 @@
       <c r="O34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:15">
+      <c r="P34">
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <v>0</v>
+      </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18">
       <c r="A35">
         <v>33</v>
       </c>
@@ -3047,32 +3650,41 @@
       <c r="G35">
         <v>22</v>
       </c>
-      <c r="H35">
-        <v>0</v>
-      </c>
-      <c r="I35">
-        <v>0</v>
+      <c r="H35" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J35">
+        <v>22</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
         <v>1</v>
       </c>
-      <c r="K35">
+      <c r="N35">
         <v>1</v>
       </c>
-      <c r="L35">
-        <v>0</v>
-      </c>
-      <c r="M35">
-        <v>0</v>
-      </c>
-      <c r="N35">
-        <v>0</v>
-      </c>
       <c r="O35">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:15">
+      <c r="P35">
+        <v>0</v>
+      </c>
+      <c r="Q35">
+        <v>0</v>
+      </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18">
       <c r="A36">
         <v>34</v>
       </c>
@@ -3094,14 +3706,14 @@
       <c r="G36">
         <v>22</v>
       </c>
-      <c r="H36">
-        <v>0</v>
-      </c>
-      <c r="I36">
-        <v>0</v>
+      <c r="H36" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K36">
         <v>0</v>
@@ -3118,8 +3730,17 @@
       <c r="O36">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:15">
+      <c r="P36">
+        <v>0</v>
+      </c>
+      <c r="Q36">
+        <v>0</v>
+      </c>
+      <c r="R36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18">
       <c r="A37">
         <v>35</v>
       </c>
@@ -3141,14 +3762,14 @@
       <c r="G37">
         <v>22</v>
       </c>
-      <c r="H37">
-        <v>0</v>
-      </c>
-      <c r="I37">
-        <v>0</v>
+      <c r="H37" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K37">
         <v>0</v>
@@ -3165,8 +3786,17 @@
       <c r="O37">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:15" ht="37.5">
+      <c r="P37">
+        <v>0</v>
+      </c>
+      <c r="Q37">
+        <v>0</v>
+      </c>
+      <c r="R37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" ht="37.5">
       <c r="A38">
         <v>36</v>
       </c>
@@ -3188,32 +3818,41 @@
       <c r="G38">
         <v>22</v>
       </c>
-      <c r="H38">
-        <v>0</v>
-      </c>
-      <c r="I38">
-        <v>0</v>
+      <c r="H38" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K38">
         <v>0</v>
       </c>
       <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38">
         <v>1</v>
       </c>
-      <c r="M38">
+      <c r="P38">
         <v>9</v>
       </c>
-      <c r="N38">
-        <v>0</v>
-      </c>
-      <c r="O38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15">
+      <c r="Q38">
+        <v>0</v>
+      </c>
+      <c r="R38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18">
       <c r="A39">
         <v>37</v>
       </c>
@@ -3223,12 +3862,8 @@
       <c r="G39">
         <v>0</v>
       </c>
-      <c r="H39">
-        <v>0</v>
-      </c>
-      <c r="I39">
-        <v>0</v>
-      </c>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
       <c r="J39">
         <v>0</v>
       </c>
@@ -3247,8 +3882,17 @@
       <c r="O39">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:15" ht="37.5">
+      <c r="P39">
+        <v>0</v>
+      </c>
+      <c r="Q39">
+        <v>0</v>
+      </c>
+      <c r="R39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" ht="37.5">
       <c r="A40">
         <v>38</v>
       </c>
@@ -3270,14 +3914,14 @@
       <c r="G40">
         <v>22</v>
       </c>
-      <c r="H40">
-        <v>0</v>
-      </c>
-      <c r="I40">
-        <v>0</v>
+      <c r="H40" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J40">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K40">
         <v>0</v>
@@ -3294,8 +3938,17 @@
       <c r="O40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:15" ht="85.5" customHeight="1">
+      <c r="P40">
+        <v>0</v>
+      </c>
+      <c r="Q40">
+        <v>0</v>
+      </c>
+      <c r="R40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" ht="85.5" customHeight="1">
       <c r="A41">
         <v>39</v>
       </c>
@@ -3317,14 +3970,14 @@
       <c r="G41">
         <v>22</v>
       </c>
-      <c r="H41">
-        <v>0</v>
-      </c>
-      <c r="I41">
-        <v>0</v>
+      <c r="H41" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J41">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K41">
         <v>0</v>
@@ -3341,8 +3994,17 @@
       <c r="O41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:15" ht="51.75" customHeight="1">
+      <c r="P41">
+        <v>0</v>
+      </c>
+      <c r="Q41">
+        <v>0</v>
+      </c>
+      <c r="R41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" ht="51.75" customHeight="1">
       <c r="A42">
         <v>40</v>
       </c>
@@ -3364,14 +4026,14 @@
       <c r="G42">
         <v>22</v>
       </c>
-      <c r="H42">
-        <v>0</v>
-      </c>
-      <c r="I42">
-        <v>0</v>
+      <c r="H42" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J42">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K42">
         <v>0</v>
@@ -3388,8 +4050,17 @@
       <c r="O42">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:15" ht="56.25">
+      <c r="P42">
+        <v>0</v>
+      </c>
+      <c r="Q42">
+        <v>0</v>
+      </c>
+      <c r="R42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" ht="56.25">
       <c r="A43">
         <v>41</v>
       </c>
@@ -3411,14 +4082,14 @@
       <c r="G43">
         <v>22</v>
       </c>
-      <c r="H43">
-        <v>0</v>
-      </c>
-      <c r="I43">
-        <v>0</v>
+      <c r="H43" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J43">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K43">
         <v>0</v>
@@ -3435,8 +4106,17 @@
       <c r="O43">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:15" ht="37.5">
+      <c r="P43">
+        <v>0</v>
+      </c>
+      <c r="Q43">
+        <v>0</v>
+      </c>
+      <c r="R43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" ht="37.5">
       <c r="A44">
         <v>42</v>
       </c>
@@ -3458,32 +4138,41 @@
       <c r="G44">
         <v>22</v>
       </c>
-      <c r="H44">
-        <v>0</v>
-      </c>
-      <c r="I44">
-        <v>0</v>
+      <c r="H44" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J44">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K44">
         <v>0</v>
       </c>
       <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44">
         <v>2</v>
       </c>
-      <c r="M44">
+      <c r="P44">
         <v>10</v>
       </c>
-      <c r="N44">
-        <v>0</v>
-      </c>
-      <c r="O44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" ht="56.25">
+      <c r="Q44">
+        <v>0</v>
+      </c>
+      <c r="R44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" ht="56.25">
       <c r="A45">
         <v>43</v>
       </c>
@@ -3505,32 +4194,41 @@
       <c r="G45">
         <v>22</v>
       </c>
-      <c r="H45">
-        <v>0</v>
-      </c>
-      <c r="I45">
-        <v>0</v>
+      <c r="H45" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J45">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K45">
         <v>0</v>
       </c>
       <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45">
         <v>2</v>
       </c>
-      <c r="M45">
+      <c r="P45">
         <v>11</v>
       </c>
-      <c r="N45">
-        <v>0</v>
-      </c>
-      <c r="O45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15">
+      <c r="Q45">
+        <v>0</v>
+      </c>
+      <c r="R45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18">
       <c r="A46">
         <v>44</v>
       </c>
@@ -3552,14 +4250,14 @@
       <c r="G46">
         <v>22</v>
       </c>
-      <c r="H46">
-        <v>0</v>
-      </c>
-      <c r="I46">
-        <v>0</v>
+      <c r="H46" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="I46" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J46">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K46">
         <v>0</v>
@@ -3576,8 +4274,17 @@
       <c r="O46">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:15">
+      <c r="P46">
+        <v>0</v>
+      </c>
+      <c r="Q46">
+        <v>0</v>
+      </c>
+      <c r="R46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18">
       <c r="A47">
         <v>45</v>
       </c>
@@ -3599,32 +4306,41 @@
       <c r="G47">
         <v>22</v>
       </c>
-      <c r="H47">
-        <v>0</v>
-      </c>
-      <c r="I47">
-        <v>0</v>
+      <c r="H47" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="I47" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J47">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K47">
         <v>0</v>
       </c>
       <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47">
         <v>3</v>
       </c>
-      <c r="M47">
+      <c r="P47">
         <v>12</v>
       </c>
-      <c r="N47">
-        <v>0</v>
-      </c>
-      <c r="O47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15">
+      <c r="Q47">
+        <v>0</v>
+      </c>
+      <c r="R47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18">
       <c r="A48">
         <v>46</v>
       </c>
@@ -3646,32 +4362,41 @@
       <c r="G48">
         <v>22</v>
       </c>
-      <c r="H48">
-        <v>0</v>
-      </c>
-      <c r="I48">
-        <v>0</v>
+      <c r="H48" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="I48" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J48">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K48">
         <v>0</v>
       </c>
       <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48">
         <v>2</v>
       </c>
-      <c r="M48">
+      <c r="P48">
         <v>13</v>
       </c>
-      <c r="N48">
-        <v>0</v>
-      </c>
-      <c r="O48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15">
+      <c r="Q48">
+        <v>0</v>
+      </c>
+      <c r="R48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18">
       <c r="A49">
         <v>47</v>
       </c>
@@ -3693,14 +4418,14 @@
       <c r="G49">
         <v>22</v>
       </c>
-      <c r="H49">
-        <v>0</v>
-      </c>
-      <c r="I49">
-        <v>0</v>
+      <c r="H49" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="I49" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J49">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K49">
         <v>0</v>
@@ -3717,8 +4442,17 @@
       <c r="O49">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:15" ht="37.5">
+      <c r="P49">
+        <v>0</v>
+      </c>
+      <c r="Q49">
+        <v>0</v>
+      </c>
+      <c r="R49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" ht="37.5">
       <c r="A50">
         <v>48</v>
       </c>
@@ -3740,32 +4474,41 @@
       <c r="G50">
         <v>22</v>
       </c>
-      <c r="H50">
-        <v>0</v>
-      </c>
-      <c r="I50">
-        <v>0</v>
+      <c r="H50" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="I50" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J50">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K50">
         <v>0</v>
       </c>
       <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <v>0</v>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50">
         <v>2</v>
       </c>
-      <c r="M50">
+      <c r="P50">
         <v>14</v>
       </c>
-      <c r="N50">
-        <v>0</v>
-      </c>
-      <c r="O50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" ht="37.5">
+      <c r="Q50">
+        <v>0</v>
+      </c>
+      <c r="R50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" ht="37.5">
       <c r="A51">
         <v>49</v>
       </c>
@@ -3787,14 +4530,14 @@
       <c r="G51">
         <v>22</v>
       </c>
-      <c r="H51">
-        <v>0</v>
-      </c>
-      <c r="I51">
-        <v>0</v>
+      <c r="H51" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="I51" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J51">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K51">
         <v>0</v>
@@ -3811,8 +4554,17 @@
       <c r="O51">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:15">
+      <c r="P51">
+        <v>0</v>
+      </c>
+      <c r="Q51">
+        <v>0</v>
+      </c>
+      <c r="R51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18">
       <c r="A52">
         <v>50</v>
       </c>
@@ -3834,14 +4586,14 @@
       <c r="G52">
         <v>22</v>
       </c>
-      <c r="H52">
-        <v>0</v>
-      </c>
-      <c r="I52">
-        <v>0</v>
+      <c r="H52" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="I52" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="J52">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K52">
         <v>0</v>
@@ -3858,8 +4610,17 @@
       <c r="O52">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:15">
+      <c r="P52">
+        <v>0</v>
+      </c>
+      <c r="Q52">
+        <v>0</v>
+      </c>
+      <c r="R52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18">
       <c r="A53">
         <v>51</v>
       </c>
@@ -3881,14 +4642,14 @@
       <c r="G53">
         <v>22</v>
       </c>
-      <c r="H53">
-        <v>0</v>
-      </c>
-      <c r="I53">
-        <v>0</v>
+      <c r="H53" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J53">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K53">
         <v>0</v>
@@ -3905,8 +4666,17 @@
       <c r="O53">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:15">
+      <c r="P53">
+        <v>0</v>
+      </c>
+      <c r="Q53">
+        <v>0</v>
+      </c>
+      <c r="R53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18">
       <c r="A54">
         <v>52</v>
       </c>
@@ -3928,14 +4698,14 @@
       <c r="G54">
         <v>22</v>
       </c>
-      <c r="H54">
-        <v>0</v>
-      </c>
-      <c r="I54">
-        <v>0</v>
+      <c r="H54" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="I54" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="J54">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K54">
         <v>0</v>
@@ -3952,8 +4722,17 @@
       <c r="O54">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:15">
+      <c r="P54">
+        <v>0</v>
+      </c>
+      <c r="Q54">
+        <v>0</v>
+      </c>
+      <c r="R54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18">
       <c r="A55">
         <v>53</v>
       </c>
@@ -3975,14 +4754,14 @@
       <c r="G55">
         <v>22</v>
       </c>
-      <c r="H55">
-        <v>0</v>
-      </c>
-      <c r="I55">
-        <v>0</v>
+      <c r="H55" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="I55" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J55">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K55">
         <v>0</v>
@@ -3999,8 +4778,17 @@
       <c r="O55">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:15" ht="37.5">
+      <c r="P55">
+        <v>0</v>
+      </c>
+      <c r="Q55">
+        <v>0</v>
+      </c>
+      <c r="R55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" ht="37.5">
       <c r="A56">
         <v>54</v>
       </c>
@@ -4022,14 +4810,14 @@
       <c r="G56">
         <v>22</v>
       </c>
-      <c r="H56">
-        <v>0</v>
-      </c>
-      <c r="I56">
-        <v>0</v>
+      <c r="H56" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="I56" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J56">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K56">
         <v>0</v>
@@ -4046,8 +4834,17 @@
       <c r="O56">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:15">
+      <c r="P56">
+        <v>0</v>
+      </c>
+      <c r="Q56">
+        <v>0</v>
+      </c>
+      <c r="R56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18">
       <c r="A57">
         <v>55</v>
       </c>
@@ -4069,14 +4866,14 @@
       <c r="G57">
         <v>22</v>
       </c>
-      <c r="H57">
-        <v>0</v>
-      </c>
-      <c r="I57">
-        <v>0</v>
+      <c r="H57" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="I57" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J57">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K57">
         <v>0</v>
@@ -4093,8 +4890,17 @@
       <c r="O57">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:15" ht="37.5">
+      <c r="P57">
+        <v>0</v>
+      </c>
+      <c r="Q57">
+        <v>0</v>
+      </c>
+      <c r="R57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" ht="37.5">
       <c r="A58">
         <v>56</v>
       </c>
@@ -4116,14 +4922,14 @@
       <c r="G58">
         <v>22</v>
       </c>
-      <c r="H58">
-        <v>0</v>
-      </c>
-      <c r="I58">
-        <v>0</v>
+      <c r="H58" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="I58" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J58">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K58">
         <v>0</v>
@@ -4140,8 +4946,17 @@
       <c r="O58">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:15">
+      <c r="P58">
+        <v>0</v>
+      </c>
+      <c r="Q58">
+        <v>0</v>
+      </c>
+      <c r="R58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18">
       <c r="A59">
         <v>57</v>
       </c>
@@ -4163,14 +4978,14 @@
       <c r="G59">
         <v>22</v>
       </c>
-      <c r="H59">
-        <v>0</v>
-      </c>
-      <c r="I59">
-        <v>0</v>
+      <c r="H59" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="I59" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J59">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K59">
         <v>0</v>
@@ -4187,8 +5002,17 @@
       <c r="O59">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:15">
+      <c r="P59">
+        <v>0</v>
+      </c>
+      <c r="Q59">
+        <v>0</v>
+      </c>
+      <c r="R59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18">
       <c r="A60">
         <v>58</v>
       </c>
@@ -4210,14 +5034,14 @@
       <c r="G60">
         <v>22</v>
       </c>
-      <c r="H60">
-        <v>0</v>
-      </c>
-      <c r="I60">
-        <v>0</v>
+      <c r="H60" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="I60" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="J60">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K60">
         <v>0</v>
@@ -4234,8 +5058,17 @@
       <c r="O60">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:15" ht="37.5">
+      <c r="P60">
+        <v>0</v>
+      </c>
+      <c r="Q60">
+        <v>0</v>
+      </c>
+      <c r="R60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" ht="37.5">
       <c r="A61">
         <v>59</v>
       </c>
@@ -4257,14 +5090,14 @@
       <c r="G61">
         <v>22</v>
       </c>
-      <c r="H61">
-        <v>0</v>
-      </c>
-      <c r="I61">
-        <v>0</v>
+      <c r="H61" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="I61" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J61">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K61">
         <v>0</v>
@@ -4281,8 +5114,17 @@
       <c r="O61">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:15">
+      <c r="P61">
+        <v>0</v>
+      </c>
+      <c r="Q61">
+        <v>0</v>
+      </c>
+      <c r="R61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18">
       <c r="A62">
         <v>60</v>
       </c>
@@ -4304,21 +5146,21 @@
       <c r="G62">
         <v>22</v>
       </c>
-      <c r="H62">
-        <v>0</v>
-      </c>
-      <c r="I62">
+      <c r="H62" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="I62" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="J62">
+        <v>22</v>
+      </c>
+      <c r="K62">
+        <v>0</v>
+      </c>
+      <c r="L62">
         <v>1</v>
       </c>
-      <c r="J62">
-        <v>0</v>
-      </c>
-      <c r="K62">
-        <v>0</v>
-      </c>
-      <c r="L62">
-        <v>0</v>
-      </c>
       <c r="M62">
         <v>0</v>
       </c>
@@ -4328,8 +5170,17 @@
       <c r="O62">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:15">
+      <c r="P62">
+        <v>0</v>
+      </c>
+      <c r="Q62">
+        <v>0</v>
+      </c>
+      <c r="R62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18">
       <c r="A63">
         <v>61</v>
       </c>
@@ -4351,14 +5202,14 @@
       <c r="G63">
         <v>22</v>
       </c>
-      <c r="H63">
-        <v>0</v>
-      </c>
-      <c r="I63">
-        <v>0</v>
+      <c r="H63" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="I63" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J63">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K63">
         <v>0</v>
@@ -4375,8 +5226,17 @@
       <c r="O63">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:15">
+      <c r="P63">
+        <v>0</v>
+      </c>
+      <c r="Q63">
+        <v>0</v>
+      </c>
+      <c r="R63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18">
       <c r="A64">
         <v>62</v>
       </c>
@@ -4398,14 +5258,14 @@
       <c r="G64">
         <v>22</v>
       </c>
-      <c r="H64">
-        <v>0</v>
-      </c>
-      <c r="I64">
-        <v>0</v>
+      <c r="H64" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="I64" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="J64">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K64">
         <v>0</v>
@@ -4422,8 +5282,17 @@
       <c r="O64">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:15">
+      <c r="P64">
+        <v>0</v>
+      </c>
+      <c r="Q64">
+        <v>0</v>
+      </c>
+      <c r="R64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18">
       <c r="A65">
         <v>63</v>
       </c>
@@ -4445,14 +5314,14 @@
       <c r="G65">
         <v>22</v>
       </c>
-      <c r="H65">
-        <v>0</v>
-      </c>
-      <c r="I65">
-        <v>0</v>
+      <c r="H65" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="I65" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J65">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K65">
         <v>0</v>
@@ -4469,8 +5338,17 @@
       <c r="O65">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:15">
+      <c r="P65">
+        <v>0</v>
+      </c>
+      <c r="Q65">
+        <v>0</v>
+      </c>
+      <c r="R65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18">
       <c r="A66">
         <v>64</v>
       </c>
@@ -4492,14 +5370,14 @@
       <c r="G66">
         <v>22</v>
       </c>
-      <c r="H66">
-        <v>0</v>
-      </c>
-      <c r="I66">
-        <v>0</v>
+      <c r="H66" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="I66" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J66">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K66">
         <v>0</v>
@@ -4516,8 +5394,17 @@
       <c r="O66">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:15">
+      <c r="P66">
+        <v>0</v>
+      </c>
+      <c r="Q66">
+        <v>0</v>
+      </c>
+      <c r="R66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18">
       <c r="A67">
         <v>65</v>
       </c>
@@ -4539,14 +5426,14 @@
       <c r="G67">
         <v>22</v>
       </c>
-      <c r="H67">
-        <v>0</v>
-      </c>
-      <c r="I67">
-        <v>0</v>
+      <c r="H67" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="I67" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J67">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K67">
         <v>0</v>
@@ -4563,8 +5450,17 @@
       <c r="O67">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:15">
+      <c r="P67">
+        <v>0</v>
+      </c>
+      <c r="Q67">
+        <v>0</v>
+      </c>
+      <c r="R67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18">
       <c r="A68">
         <v>66</v>
       </c>
@@ -4586,14 +5482,14 @@
       <c r="G68">
         <v>22</v>
       </c>
-      <c r="H68">
-        <v>0</v>
-      </c>
-      <c r="I68">
-        <v>0</v>
+      <c r="H68" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="I68" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="J68">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K68">
         <v>0</v>
@@ -4610,8 +5506,17 @@
       <c r="O68">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="1:15" ht="37.5">
+      <c r="P68">
+        <v>0</v>
+      </c>
+      <c r="Q68">
+        <v>0</v>
+      </c>
+      <c r="R68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18" ht="37.5">
       <c r="A69">
         <v>67</v>
       </c>
@@ -4633,14 +5538,14 @@
       <c r="G69">
         <v>22</v>
       </c>
-      <c r="H69">
-        <v>0</v>
-      </c>
-      <c r="I69">
-        <v>0</v>
+      <c r="H69" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="I69" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J69">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K69">
         <v>0</v>
@@ -4657,8 +5562,17 @@
       <c r="O69">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:15">
+      <c r="P69">
+        <v>0</v>
+      </c>
+      <c r="Q69">
+        <v>0</v>
+      </c>
+      <c r="R69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18">
       <c r="A70">
         <v>68</v>
       </c>
@@ -4680,14 +5594,14 @@
       <c r="G70">
         <v>22</v>
       </c>
-      <c r="H70">
-        <v>0</v>
-      </c>
-      <c r="I70">
-        <v>0</v>
+      <c r="H70" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="I70" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J70">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K70">
         <v>0</v>
@@ -4699,13 +5613,22 @@
         <v>0</v>
       </c>
       <c r="N70">
+        <v>0</v>
+      </c>
+      <c r="O70">
+        <v>0</v>
+      </c>
+      <c r="P70">
+        <v>0</v>
+      </c>
+      <c r="Q70">
         <v>1</v>
       </c>
-      <c r="O70">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:15">
+      <c r="R70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18">
       <c r="A71">
         <v>69</v>
       </c>
@@ -4715,12 +5638,8 @@
       <c r="G71">
         <v>0</v>
       </c>
-      <c r="H71">
-        <v>0</v>
-      </c>
-      <c r="I71">
-        <v>0</v>
-      </c>
+      <c r="H71" s="5"/>
+      <c r="I71" s="5"/>
       <c r="J71">
         <v>0</v>
       </c>
@@ -4739,8 +5658,17 @@
       <c r="O71">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:15">
+      <c r="P71">
+        <v>0</v>
+      </c>
+      <c r="Q71">
+        <v>0</v>
+      </c>
+      <c r="R71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18">
       <c r="A72">
         <v>70</v>
       </c>
@@ -4762,32 +5690,41 @@
       <c r="G72">
         <v>22</v>
       </c>
-      <c r="H72">
-        <v>0</v>
-      </c>
-      <c r="I72">
-        <v>0</v>
+      <c r="H72" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="I72" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="J72">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K72">
+        <v>0</v>
+      </c>
+      <c r="L72">
+        <v>0</v>
+      </c>
+      <c r="M72">
+        <v>0</v>
+      </c>
+      <c r="N72">
         <v>1</v>
       </c>
-      <c r="L72">
-        <v>0</v>
-      </c>
-      <c r="M72">
-        <v>0</v>
-      </c>
-      <c r="N72">
-        <v>0</v>
-      </c>
       <c r="O72">
+        <v>0</v>
+      </c>
+      <c r="P72">
+        <v>0</v>
+      </c>
+      <c r="Q72">
+        <v>0</v>
+      </c>
+      <c r="R72">
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:15">
+    <row r="73" spans="1:18">
       <c r="A73">
         <v>71</v>
       </c>
@@ -4809,14 +5746,14 @@
       <c r="G73">
         <v>22</v>
       </c>
-      <c r="H73">
-        <v>0</v>
-      </c>
-      <c r="I73">
-        <v>0</v>
+      <c r="H73" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="I73" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="J73">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K73">
         <v>0</v>
@@ -4833,8 +5770,17 @@
       <c r="O73">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:15">
+      <c r="P73">
+        <v>0</v>
+      </c>
+      <c r="Q73">
+        <v>0</v>
+      </c>
+      <c r="R73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18">
       <c r="A74">
         <v>72</v>
       </c>
@@ -4856,14 +5802,14 @@
       <c r="G74">
         <v>22</v>
       </c>
-      <c r="H74">
-        <v>0</v>
-      </c>
-      <c r="I74">
-        <v>0</v>
+      <c r="H74" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="I74" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="J74">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K74">
         <v>0</v>
@@ -4880,8 +5826,17 @@
       <c r="O74">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="1:15">
+      <c r="P74">
+        <v>0</v>
+      </c>
+      <c r="Q74">
+        <v>0</v>
+      </c>
+      <c r="R74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18">
       <c r="A75">
         <v>73</v>
       </c>
@@ -4903,14 +5858,14 @@
       <c r="G75">
         <v>22</v>
       </c>
-      <c r="H75">
-        <v>0</v>
-      </c>
-      <c r="I75">
-        <v>0</v>
+      <c r="H75" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="I75" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J75">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K75">
         <v>0</v>
@@ -4927,8 +5882,17 @@
       <c r="O75">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:15">
+      <c r="P75">
+        <v>0</v>
+      </c>
+      <c r="Q75">
+        <v>0</v>
+      </c>
+      <c r="R75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18">
       <c r="A76">
         <v>74</v>
       </c>
@@ -4950,14 +5914,14 @@
       <c r="G76">
         <v>22</v>
       </c>
-      <c r="H76">
-        <v>0</v>
-      </c>
-      <c r="I76">
-        <v>0</v>
+      <c r="H76" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="I76" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J76">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K76">
         <v>0</v>
@@ -4974,8 +5938,17 @@
       <c r="O76">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:15">
+      <c r="P76">
+        <v>0</v>
+      </c>
+      <c r="Q76">
+        <v>0</v>
+      </c>
+      <c r="R76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18">
       <c r="A77">
         <v>75</v>
       </c>
@@ -4997,14 +5970,14 @@
       <c r="G77">
         <v>22</v>
       </c>
-      <c r="H77">
-        <v>0</v>
-      </c>
-      <c r="I77">
-        <v>0</v>
+      <c r="H77" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="I77" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="J77">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K77">
         <v>0</v>
@@ -5021,8 +5994,17 @@
       <c r="O77">
         <v>0</v>
       </c>
-    </row>
-    <row r="78" spans="1:15" ht="37.5">
+      <c r="P77">
+        <v>0</v>
+      </c>
+      <c r="Q77">
+        <v>0</v>
+      </c>
+      <c r="R77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" ht="37.5">
       <c r="A78">
         <v>76</v>
       </c>
@@ -5044,14 +6026,14 @@
       <c r="G78">
         <v>22</v>
       </c>
-      <c r="H78">
-        <v>0</v>
-      </c>
-      <c r="I78">
-        <v>0</v>
+      <c r="H78" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="I78" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="J78">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K78">
         <v>0</v>
@@ -5068,8 +6050,17 @@
       <c r="O78">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="1:15">
+      <c r="P78">
+        <v>0</v>
+      </c>
+      <c r="Q78">
+        <v>0</v>
+      </c>
+      <c r="R78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18">
       <c r="A79">
         <v>77</v>
       </c>
@@ -5091,14 +6082,14 @@
       <c r="G79">
         <v>22</v>
       </c>
-      <c r="H79">
-        <v>0</v>
-      </c>
-      <c r="I79">
-        <v>0</v>
+      <c r="H79" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="I79" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J79">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K79">
         <v>0</v>
@@ -5115,8 +6106,17 @@
       <c r="O79">
         <v>0</v>
       </c>
-    </row>
-    <row r="80" spans="1:15">
+      <c r="P79">
+        <v>0</v>
+      </c>
+      <c r="Q79">
+        <v>0</v>
+      </c>
+      <c r="R79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18">
       <c r="A80">
         <v>78</v>
       </c>
@@ -5138,14 +6138,14 @@
       <c r="G80">
         <v>22</v>
       </c>
-      <c r="H80">
-        <v>0</v>
-      </c>
-      <c r="I80">
-        <v>0</v>
+      <c r="H80" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="I80" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="J80">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K80">
         <v>0</v>
@@ -5162,8 +6162,17 @@
       <c r="O80">
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="1:15" ht="37.5">
+      <c r="P80">
+        <v>0</v>
+      </c>
+      <c r="Q80">
+        <v>0</v>
+      </c>
+      <c r="R80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18" ht="37.5">
       <c r="A81">
         <v>79</v>
       </c>
@@ -5185,14 +6194,14 @@
       <c r="G81">
         <v>22</v>
       </c>
-      <c r="H81">
-        <v>0</v>
-      </c>
-      <c r="I81">
-        <v>0</v>
+      <c r="H81" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="I81" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J81">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K81">
         <v>0</v>
@@ -5209,8 +6218,17 @@
       <c r="O81">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="1:15">
+      <c r="P81">
+        <v>0</v>
+      </c>
+      <c r="Q81">
+        <v>0</v>
+      </c>
+      <c r="R81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18">
       <c r="A82">
         <v>80</v>
       </c>
@@ -5232,14 +6250,14 @@
       <c r="G82">
         <v>22</v>
       </c>
-      <c r="H82">
-        <v>0</v>
-      </c>
-      <c r="I82">
-        <v>0</v>
+      <c r="H82" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="I82" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="J82">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K82">
         <v>0</v>
@@ -5256,8 +6274,17 @@
       <c r="O82">
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="1:15" ht="37.5">
+      <c r="P82">
+        <v>0</v>
+      </c>
+      <c r="Q82">
+        <v>0</v>
+      </c>
+      <c r="R82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18" ht="37.5">
       <c r="A83">
         <v>81</v>
       </c>
@@ -5279,14 +6306,14 @@
       <c r="G83">
         <v>22</v>
       </c>
-      <c r="H83">
-        <v>0</v>
-      </c>
-      <c r="I83">
-        <v>0</v>
+      <c r="H83" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="I83" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J83">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K83">
         <v>0</v>
@@ -5303,8 +6330,17 @@
       <c r="O83">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:15">
+      <c r="P83">
+        <v>0</v>
+      </c>
+      <c r="Q83">
+        <v>0</v>
+      </c>
+      <c r="R83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18">
       <c r="A84">
         <v>82</v>
       </c>
@@ -5326,14 +6362,14 @@
       <c r="G84">
         <v>22</v>
       </c>
-      <c r="H84">
-        <v>0</v>
-      </c>
-      <c r="I84">
-        <v>0</v>
+      <c r="H84" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="I84" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="J84">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K84">
         <v>0</v>
@@ -5350,8 +6386,17 @@
       <c r="O84">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:15">
+      <c r="P84">
+        <v>0</v>
+      </c>
+      <c r="Q84">
+        <v>0</v>
+      </c>
+      <c r="R84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18">
       <c r="A85">
         <v>83</v>
       </c>
@@ -5373,14 +6418,14 @@
       <c r="G85">
         <v>22</v>
       </c>
-      <c r="H85">
-        <v>0</v>
-      </c>
-      <c r="I85">
-        <v>0</v>
+      <c r="H85" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="I85" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J85">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K85">
         <v>0</v>
@@ -5397,8 +6442,17 @@
       <c r="O85">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="1:15">
+      <c r="P85">
+        <v>0</v>
+      </c>
+      <c r="Q85">
+        <v>0</v>
+      </c>
+      <c r="R85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:18">
       <c r="A86">
         <v>84</v>
       </c>
@@ -5420,14 +6474,14 @@
       <c r="G86">
         <v>22</v>
       </c>
-      <c r="H86">
-        <v>0</v>
-      </c>
-      <c r="I86">
-        <v>0</v>
+      <c r="H86" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="I86" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="J86">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K86">
         <v>0</v>
@@ -5444,8 +6498,17 @@
       <c r="O86">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="1:15">
+      <c r="P86">
+        <v>0</v>
+      </c>
+      <c r="Q86">
+        <v>0</v>
+      </c>
+      <c r="R86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:18">
       <c r="A87">
         <v>85</v>
       </c>
@@ -5467,14 +6530,14 @@
       <c r="G87">
         <v>22</v>
       </c>
-      <c r="H87">
-        <v>0</v>
-      </c>
-      <c r="I87">
-        <v>0</v>
+      <c r="H87" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="I87" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J87">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K87">
         <v>0</v>
@@ -5491,8 +6554,17 @@
       <c r="O87">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="1:15">
+      <c r="P87">
+        <v>0</v>
+      </c>
+      <c r="Q87">
+        <v>0</v>
+      </c>
+      <c r="R87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:18">
       <c r="A88">
         <v>86</v>
       </c>
@@ -5514,32 +6586,41 @@
       <c r="G88">
         <v>22</v>
       </c>
-      <c r="H88">
-        <v>0</v>
-      </c>
-      <c r="I88">
+      <c r="H88" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="I88" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="J88">
+        <v>22</v>
+      </c>
+      <c r="K88">
+        <v>0</v>
+      </c>
+      <c r="L88">
         <v>2</v>
       </c>
-      <c r="J88">
-        <v>0</v>
-      </c>
-      <c r="K88">
+      <c r="M88">
+        <v>0</v>
+      </c>
+      <c r="N88">
         <v>1</v>
       </c>
-      <c r="L88">
-        <v>0</v>
-      </c>
-      <c r="M88">
-        <v>0</v>
-      </c>
-      <c r="N88">
-        <v>0</v>
-      </c>
       <c r="O88">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="1:15">
+      <c r="P88">
+        <v>0</v>
+      </c>
+      <c r="Q88">
+        <v>0</v>
+      </c>
+      <c r="R88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18">
       <c r="A89">
         <v>87</v>
       </c>
@@ -5561,14 +6642,14 @@
       <c r="G89">
         <v>22</v>
       </c>
-      <c r="H89">
-        <v>0</v>
-      </c>
-      <c r="I89">
-        <v>0</v>
+      <c r="H89" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="I89" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J89">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K89">
         <v>0</v>
@@ -5585,20 +6666,22 @@
       <c r="O89">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="1:15">
+      <c r="P89">
+        <v>0</v>
+      </c>
+      <c r="Q89">
+        <v>0</v>
+      </c>
+      <c r="R89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18">
       <c r="A90">
         <v>88</v>
       </c>
-      <c r="H90">
-        <v>0</v>
-      </c>
-      <c r="I90">
-        <v>0</v>
-      </c>
-      <c r="J90">
-        <v>0</v>
-      </c>
+      <c r="H90" s="5"/>
+      <c r="I90" s="5"/>
       <c r="K90">
         <v>0</v>
       </c>
@@ -5614,66 +6697,99 @@
       <c r="O90">
         <v>0</v>
       </c>
-    </row>
-    <row r="91" spans="1:15">
+      <c r="P90">
+        <v>0</v>
+      </c>
+      <c r="Q90">
+        <v>0</v>
+      </c>
+      <c r="R90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18">
       <c r="A91">
         <v>89</v>
       </c>
-    </row>
-    <row r="92" spans="1:15">
+      <c r="H91" s="5"/>
+      <c r="I91" s="5"/>
+    </row>
+    <row r="92" spans="1:18">
       <c r="A92">
         <v>90</v>
       </c>
-    </row>
-    <row r="93" spans="1:15">
+      <c r="H92" s="5"/>
+      <c r="I92" s="5"/>
+    </row>
+    <row r="93" spans="1:18">
       <c r="A93">
         <v>91</v>
       </c>
-    </row>
-    <row r="94" spans="1:15">
+      <c r="H93" s="5"/>
+      <c r="I93" s="5"/>
+    </row>
+    <row r="94" spans="1:18">
       <c r="A94">
         <v>92</v>
       </c>
-    </row>
-    <row r="95" spans="1:15">
+      <c r="H94" s="5"/>
+      <c r="I94" s="5"/>
+    </row>
+    <row r="95" spans="1:18">
       <c r="A95">
         <v>93</v>
       </c>
-    </row>
-    <row r="96" spans="1:15">
+      <c r="H95" s="5"/>
+      <c r="I95" s="5"/>
+    </row>
+    <row r="96" spans="1:18">
       <c r="A96">
         <v>94</v>
       </c>
-    </row>
-    <row r="97" spans="1:1">
+      <c r="H96" s="5"/>
+      <c r="I96" s="5"/>
+    </row>
+    <row r="97" spans="1:9">
       <c r="A97">
         <v>95</v>
       </c>
-    </row>
-    <row r="98" spans="1:1">
+      <c r="H97" s="5"/>
+      <c r="I97" s="5"/>
+    </row>
+    <row r="98" spans="1:9">
       <c r="A98">
         <v>96</v>
       </c>
-    </row>
-    <row r="99" spans="1:1">
+      <c r="H98" s="5"/>
+      <c r="I98" s="5"/>
+    </row>
+    <row r="99" spans="1:9">
       <c r="A99">
         <v>97</v>
       </c>
-    </row>
-    <row r="100" spans="1:1">
+      <c r="H99" s="5"/>
+      <c r="I99" s="5"/>
+    </row>
+    <row r="100" spans="1:9">
       <c r="A100">
         <v>98</v>
       </c>
-    </row>
-    <row r="101" spans="1:1">
+      <c r="H100" s="5"/>
+      <c r="I100" s="5"/>
+    </row>
+    <row r="101" spans="1:9">
       <c r="A101">
         <v>99</v>
       </c>
-    </row>
-    <row r="102" spans="1:1">
+      <c r="H101" s="5"/>
+      <c r="I101" s="5"/>
+    </row>
+    <row r="102" spans="1:9">
       <c r="A102">
         <v>100</v>
       </c>
+      <c r="H102" s="5"/>
+      <c r="I102" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/Assets/Originals/Excels/Talk/TalkMessage.xlsx
+++ b/Assets/Originals/Excels/Talk/TalkMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Talk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58739612-B4B9-4D7F-A495-8854DF746C85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F58EF04B-480F-4466-B5EF-390B63512AC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="353">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -1364,6 +1364,252 @@
   </si>
   <si>
     <t>messageSizeChinese01</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>這裡…是哪裡…</t>
+  </si>
+  <si>
+    <t>我叫要
+是「夢迷」的嚮導</t>
+  </si>
+  <si>
+    <t>夢迷？</t>
+  </si>
+  <si>
+    <t>就是這個常世裡的巨大迷宮</t>
+  </si>
+  <si>
+    <t>你在現世犯下了「罪」而死亡
+犯下罪的人都會被幽禁在這座夢迷之中</t>
+  </si>
+  <si>
+    <t>也就是說　你也是其中一員</t>
+  </si>
+  <si>
+    <t>沒錯　是非常非常深重的罪</t>
+  </si>
+  <si>
+    <t>對了　你還記得自己的名字嗎？</t>
+  </si>
+  <si>
+    <t>咦……想不起來……</t>
+  </si>
+  <si>
+    <t>想不起來也是理所當然的</t>
+  </si>
+  <si>
+    <t>因為你在來到這座迷宮之前　名字就已經被捨棄了</t>
+  </si>
+  <si>
+    <t>名字…被捨棄…？</t>
+  </si>
+  <si>
+    <t>這是什麼意思？</t>
+  </si>
+  <si>
+    <t>在常世裡被捨棄了名字的人
+是無法想起自己名字的</t>
+  </si>
+  <si>
+    <t>將會一邊承受各種痛苦
+一邊永遠徘徊在這座迷宮之中</t>
+  </si>
+  <si>
+    <t>你總有一天　也會變成那樣吧</t>
+  </si>
+  <si>
+    <t>怎麼會…太殘忍了…</t>
+  </si>
+  <si>
+    <t>為什麼…</t>
+  </si>
+  <si>
+    <t>因為罪人不需要名字啊</t>
+  </si>
+  <si>
+    <t>不過你放心吧</t>
+  </si>
+  <si>
+    <t>只要你想起在現世犯下的罪　並從這座迷宮中逃脫出去　
+我就會告訴你你的名字</t>
+  </si>
+  <si>
+    <t>這樣一來　你就不會再承受痛苦
+也不會再徘徊下去</t>
+  </si>
+  <si>
+    <t>…你想從這裡逃脫出去嗎？</t>
+  </si>
+  <si>
+    <t>可是　要怎麼做才能逃出去呢？</t>
+  </si>
+  <si>
+    <t>…有一個辦法</t>
+  </si>
+  <si>
+    <t>那就是挑戰並克服我給你的試煉</t>
+  </si>
+  <si>
+    <t>只要做到這一點　你就能逃出去了</t>
+  </si>
+  <si>
+    <t>…我的試煉　你要挑戰嗎？</t>
+  </si>
+  <si>
+    <t>……我要挑戰</t>
+  </si>
+  <si>
+    <t>…好的
+那麼我就來說明一下試煉的內容</t>
+  </si>
+  <si>
+    <t>想要克服這場試煉
+必須達成兩個條件</t>
+  </si>
+  <si>
+    <t>其一　從這座迷宮中逃脫出去
+其二　想起你在現世犯下的罪</t>
+  </si>
+  <si>
+    <t>我來說明一下從這座迷宮逃脫的方法</t>
+  </si>
+  <si>
+    <t>想要逃脫　就必須在這座迷宮的各個角落　
+找出「檔案」和「神秘物品」</t>
+  </si>
+  <si>
+    <t>首先　要獲得檔案
+你先試著開啟眼前的抽屜看看</t>
+  </si>
+  <si>
+    <t>你確認一下剛拿到手的檔案內容吧</t>
+  </si>
+  <si>
+    <t>接下來　要獲得神秘物品</t>
+  </si>
+  <si>
+    <t>開啟眼前的兩個抽屜看看</t>
+  </si>
+  <si>
+    <t>你確認一下剛拿到手的神秘物品吧</t>
+  </si>
+  <si>
+    <t>最後　觸碰一下里面的「裁決之藍玉」</t>
+  </si>
+  <si>
+    <t>選擇與檔案內容有著深切關聯的
+神秘物品</t>
+  </si>
+  <si>
+    <t>試煉的說明到此結束
+你有什麼問題嗎？</t>
+  </si>
+  <si>
+    <t>咦？　你不打算告訴我關於我所犯之罪的說明嗎？</t>
+  </si>
+  <si>
+    <t>不會哦</t>
+  </si>
+  <si>
+    <t>別跟我說「咦」</t>
+  </si>
+  <si>
+    <t>如果你真心覺得自己做錯了事
+應該馬上就能想起自己的罪才對</t>
+  </si>
+  <si>
+    <t>所以說明到此為止</t>
+  </si>
+  <si>
+    <t>另外　沒有名字也不方便
+我就暫且叫你「伊芙」吧</t>
+  </si>
+  <si>
+    <t>這樣可以吧？</t>
+  </si>
+  <si>
+    <t>最後　關於這座迷宮還有一件注意事項</t>
+  </si>
+  <si>
+    <t>注意事項？</t>
+  </si>
+  <si>
+    <t>絕對不能被「徘徊者」抓住</t>
+  </si>
+  <si>
+    <t>就是潛伏在夢迷中的怪物</t>
+  </si>
+  <si>
+    <t>伊芙　總之絕對不能被那怪物抓住哦</t>
+  </si>
+  <si>
+    <t>明白了嗎？</t>
+  </si>
+  <si>
+    <t>那麼　現在就開始試煉吧
+請你朝後面的通道前進</t>
+  </si>
+  <si>
+    <t>伊芙　我會祈禱你能透過這場試煉的</t>
+  </si>
+  <si>
+    <t>…這樣…終於…能從這座迷宮中逃脫出去了…</t>
+  </si>
+  <si>
+    <t>咦……這…是什麼……</t>
+  </si>
+  <si>
+    <t>為什麼迷宮還沒有結束！？</t>
+  </si>
+  <si>
+    <t>那還用說嗎</t>
+  </si>
+  <si>
+    <t>因為你還沒有從迷宮中逃脫出去啊</t>
+  </si>
+  <si>
+    <t>…你說我還沒逃出去</t>
+  </si>
+  <si>
+    <t>檔案和神秘物品
+我不是都好好收集齊了嗎！</t>
+  </si>
+  <si>
+    <t>你該不會以為這樣就結束了吧？</t>
+  </si>
+  <si>
+    <t>檔案和神秘物品
+在其他區域也有哦</t>
+  </si>
+  <si>
+    <t>騙人…的吧…</t>
+  </si>
+  <si>
+    <t>而且　伊芙你也還沒想起自己所犯的罪吧</t>
+  </si>
+  <si>
+    <t>所以說試煉還沒有結束哦</t>
+  </si>
+  <si>
+    <t>怎麼會……</t>
+  </si>
+  <si>
+    <t>夢迷真正的恐怖　現在才剛剛開始　伊芙</t>
+  </si>
+  <si>
+    <t>但我們還是要繼續加油哦　伊芙</t>
+  </si>
+  <si>
+    <t>messageChinese02</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>speakerNameChinese02</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>messageSizeChinese02</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1371,7 +1617,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1408,6 +1654,12 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1429,7 +1681,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1441,6 +1693,10 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1723,7 +1979,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R102"/>
+  <dimension ref="A1:U102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="123.375" style="2" customWidth="1"/>
@@ -1734,16 +1990,19 @@
     <col min="8" max="8" width="47.125" customWidth="1"/>
     <col min="9" max="9" width="22.5" customWidth="1"/>
     <col min="10" max="10" width="24.75" customWidth="1"/>
-    <col min="11" max="11" width="27.75" customWidth="1"/>
-    <col min="12" max="12" width="22.5" customWidth="1"/>
-    <col min="13" max="13" width="13.625" customWidth="1"/>
-    <col min="15" max="15" width="17.125" customWidth="1"/>
-    <col min="16" max="16" width="28.125" customWidth="1"/>
-    <col min="17" max="17" width="13.125" customWidth="1"/>
-    <col min="18" max="18" width="16" customWidth="1"/>
+    <col min="11" max="11" width="47.125" customWidth="1"/>
+    <col min="12" max="12" width="22.75" customWidth="1"/>
+    <col min="13" max="13" width="22.5" customWidth="1"/>
+    <col min="14" max="14" width="27.75" customWidth="1"/>
+    <col min="15" max="15" width="22.5" customWidth="1"/>
+    <col min="16" max="16" width="13.625" customWidth="1"/>
+    <col min="18" max="18" width="17.125" customWidth="1"/>
+    <col min="19" max="19" width="28.125" customWidth="1"/>
+    <col min="20" max="20" width="13.125" customWidth="1"/>
+    <col min="21" max="21" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="37.5">
+    <row r="1" spans="1:21" ht="37.5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1775,31 +2034,40 @@
         <v>277</v>
       </c>
       <c r="K1" t="s">
+        <v>350</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="M1" t="s">
+        <v>352</v>
+      </c>
+      <c r="N1" t="s">
         <v>21</v>
       </c>
-      <c r="L1" t="s">
-        <v>22</v>
-      </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P1" t="s">
         <v>23</v>
       </c>
-      <c r="N1" t="s">
+      <c r="Q1" t="s">
         <v>24</v>
       </c>
-      <c r="O1" t="s">
+      <c r="R1" t="s">
         <v>25</v>
       </c>
-      <c r="P1" t="s">
+      <c r="S1" t="s">
         <v>26</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="T1" t="s">
         <v>27</v>
       </c>
-      <c r="R1" t="s">
+      <c r="U1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:21">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1814,12 +2082,8 @@
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
       <c r="M2">
         <v>0</v>
       </c>
@@ -1838,8 +2102,17 @@
       <c r="R2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:18">
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1870,14 +2143,14 @@
       <c r="J3">
         <v>22</v>
       </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
+      <c r="K3" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>190</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N3">
         <v>0</v>
@@ -1894,8 +2167,17 @@
       <c r="R3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:18">
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1926,32 +2208,41 @@
       <c r="J4">
         <v>22</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="M4">
+        <v>22</v>
+      </c>
+      <c r="N4">
         <v>1</v>
       </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
         <v>3</v>
       </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
       <c r="R4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" ht="37.5">
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="37.5">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1982,14 +2273,14 @@
       <c r="J5">
         <v>22</v>
       </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
+      <c r="K5" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -2006,8 +2297,17 @@
       <c r="R5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:18">
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2038,14 +2338,14 @@
       <c r="J6">
         <v>22</v>
       </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
+      <c r="K6" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>190</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -2062,8 +2362,17 @@
       <c r="R6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:18">
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2094,14 +2403,14 @@
       <c r="J7">
         <v>22</v>
       </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
+      <c r="K7" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -2118,8 +2427,17 @@
       <c r="R7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" ht="56.25">
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="56.25">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2150,14 +2468,14 @@
       <c r="J8">
         <v>22</v>
       </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
+      <c r="K8" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -2174,8 +2492,17 @@
       <c r="R8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:18">
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21">
       <c r="A9">
         <v>7</v>
       </c>
@@ -2206,14 +2533,14 @@
       <c r="J9">
         <v>22</v>
       </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
+      <c r="K9" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N9">
         <v>0</v>
@@ -2230,8 +2557,17 @@
       <c r="R9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:18">
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21">
       <c r="A10">
         <v>8</v>
       </c>
@@ -2262,14 +2598,14 @@
       <c r="J10">
         <v>22</v>
       </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
+      <c r="K10" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>190</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -2286,8 +2622,17 @@
       <c r="R10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:18">
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21">
       <c r="A11">
         <v>9</v>
       </c>
@@ -2318,14 +2663,14 @@
       <c r="J11">
         <v>22</v>
       </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
+      <c r="K11" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -2342,8 +2687,17 @@
       <c r="R11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:18">
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21">
       <c r="A12">
         <v>10</v>
       </c>
@@ -2374,14 +2728,14 @@
       <c r="J12">
         <v>22</v>
       </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
+      <c r="K12" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -2398,8 +2752,17 @@
       <c r="R12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:18">
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21">
       <c r="A13">
         <v>11</v>
       </c>
@@ -2430,21 +2793,21 @@
       <c r="J13">
         <v>22</v>
       </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
+      <c r="K13" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="M13">
+        <v>22</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
         <v>1</v>
       </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
       <c r="P13">
         <v>0</v>
       </c>
@@ -2454,8 +2817,17 @@
       <c r="R13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18">
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21">
       <c r="A14">
         <v>12</v>
       </c>
@@ -2486,14 +2858,14 @@
       <c r="J14">
         <v>22</v>
       </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
+      <c r="K14" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>190</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -2510,8 +2882,17 @@
       <c r="R14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18">
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21">
       <c r="A15">
         <v>13</v>
       </c>
@@ -2542,14 +2923,14 @@
       <c r="J15">
         <v>22</v>
       </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
+      <c r="K15" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -2566,8 +2947,17 @@
       <c r="R15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" ht="37.5">
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" ht="37.5">
       <c r="A16">
         <v>14</v>
       </c>
@@ -2598,14 +2988,14 @@
       <c r="J16">
         <v>22</v>
       </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
+      <c r="K16" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -2622,8 +3012,17 @@
       <c r="R16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:18">
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21">
       <c r="A17">
         <v>15</v>
       </c>
@@ -2654,14 +3053,14 @@
       <c r="J17">
         <v>22</v>
       </c>
-      <c r="K17">
-        <v>0</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
+      <c r="K17" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="L17" s="7" t="s">
+        <v>190</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -2678,8 +3077,17 @@
       <c r="R17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:18">
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21">
       <c r="A18">
         <v>16</v>
       </c>
@@ -2710,14 +3118,14 @@
       <c r="J18">
         <v>22</v>
       </c>
-      <c r="K18">
-        <v>0</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
+      <c r="K18" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="L18" s="7" t="s">
+        <v>190</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N18">
         <v>0</v>
@@ -2734,8 +3142,17 @@
       <c r="R18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:18" ht="56.25">
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" ht="56.25">
       <c r="A19">
         <v>17</v>
       </c>
@@ -2766,14 +3183,14 @@
       <c r="J19">
         <v>22</v>
       </c>
-      <c r="K19">
-        <v>0</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
+      <c r="K19" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N19">
         <v>0</v>
@@ -2790,8 +3207,17 @@
       <c r="R19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:18">
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21">
       <c r="A20">
         <v>18</v>
       </c>
@@ -2822,14 +3248,14 @@
       <c r="J20">
         <v>22</v>
       </c>
-      <c r="K20">
-        <v>0</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
+      <c r="K20" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>190</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N20">
         <v>0</v>
@@ -2846,8 +3272,17 @@
       <c r="R20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:18">
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21">
       <c r="A21">
         <v>19</v>
       </c>
@@ -2875,21 +3310,21 @@
       <c r="J21">
         <v>22</v>
       </c>
-      <c r="K21">
-        <v>0</v>
-      </c>
-      <c r="L21">
+      <c r="K21" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="M21">
+        <v>22</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
         <v>1</v>
       </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21">
-        <v>0</v>
-      </c>
       <c r="P21">
         <v>0</v>
       </c>
@@ -2899,8 +3334,17 @@
       <c r="R21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:18" ht="37.5">
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" ht="37.5">
       <c r="A22">
         <v>20</v>
       </c>
@@ -2931,14 +3375,14 @@
       <c r="J22">
         <v>22</v>
       </c>
-      <c r="K22">
-        <v>0</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
+      <c r="K22" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N22">
         <v>0</v>
@@ -2955,8 +3399,17 @@
       <c r="R22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:18">
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21">
       <c r="A23">
         <v>21</v>
       </c>
@@ -2987,14 +3440,14 @@
       <c r="J23">
         <v>22</v>
       </c>
-      <c r="K23">
-        <v>0</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
+      <c r="K23" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N23">
         <v>0</v>
@@ -3011,8 +3464,17 @@
       <c r="R23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:18">
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21">
       <c r="A24">
         <v>22</v>
       </c>
@@ -3043,14 +3505,14 @@
       <c r="J24">
         <v>22</v>
       </c>
-      <c r="K24">
-        <v>0</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
+      <c r="K24" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>190</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N24">
         <v>0</v>
@@ -3067,8 +3529,17 @@
       <c r="R24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:18">
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21">
       <c r="A25">
         <v>23</v>
       </c>
@@ -3099,14 +3570,14 @@
       <c r="J25">
         <v>22</v>
       </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
+      <c r="K25" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="L25" s="7" t="s">
+        <v>190</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N25">
         <v>0</v>
@@ -3123,8 +3594,17 @@
       <c r="R25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:18">
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21">
       <c r="A26">
         <v>24</v>
       </c>
@@ -3155,14 +3635,14 @@
       <c r="J26">
         <v>22</v>
       </c>
-      <c r="K26">
-        <v>0</v>
-      </c>
-      <c r="L26">
-        <v>0</v>
+      <c r="K26" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="L26" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N26">
         <v>0</v>
@@ -3179,8 +3659,17 @@
       <c r="R26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:18">
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21">
       <c r="A27">
         <v>25</v>
       </c>
@@ -3211,14 +3700,14 @@
       <c r="J27">
         <v>22</v>
       </c>
-      <c r="K27">
-        <v>0</v>
-      </c>
-      <c r="L27">
-        <v>0</v>
+      <c r="K27" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="L27" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N27">
         <v>0</v>
@@ -3235,8 +3724,17 @@
       <c r="R27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:18" ht="56.25">
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" ht="56.25">
       <c r="A28">
         <v>26</v>
       </c>
@@ -3267,14 +3765,14 @@
       <c r="J28">
         <v>22</v>
       </c>
-      <c r="K28">
-        <v>0</v>
-      </c>
-      <c r="L28">
-        <v>0</v>
+      <c r="K28" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="L28" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N28">
         <v>0</v>
@@ -3291,8 +3789,17 @@
       <c r="R28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:18" ht="37.5">
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" ht="37.5">
       <c r="A29">
         <v>27</v>
       </c>
@@ -3323,32 +3830,41 @@
       <c r="J29">
         <v>22</v>
       </c>
-      <c r="K29">
-        <v>0</v>
-      </c>
-      <c r="L29">
-        <v>0</v>
+      <c r="K29" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="L29" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M29">
+        <v>22</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
         <v>1</v>
       </c>
-      <c r="N29">
+      <c r="Q29">
         <v>1</v>
       </c>
-      <c r="O29">
-        <v>0</v>
-      </c>
-      <c r="P29">
-        <v>0</v>
-      </c>
-      <c r="Q29">
-        <v>0</v>
-      </c>
       <c r="R29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:18">
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21">
       <c r="A30">
         <v>28</v>
       </c>
@@ -3379,14 +3895,14 @@
       <c r="J30">
         <v>22</v>
       </c>
-      <c r="K30">
-        <v>0</v>
-      </c>
-      <c r="L30">
-        <v>0</v>
+      <c r="K30" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="L30" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N30">
         <v>0</v>
@@ -3403,8 +3919,17 @@
       <c r="R30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:18">
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>0</v>
+      </c>
+      <c r="U30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21">
       <c r="A31">
         <v>29</v>
       </c>
@@ -3435,14 +3960,14 @@
       <c r="J31">
         <v>22</v>
       </c>
-      <c r="K31">
-        <v>0</v>
-      </c>
-      <c r="L31">
-        <v>0</v>
+      <c r="K31" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="L31" s="7" t="s">
+        <v>190</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N31">
         <v>0</v>
@@ -3459,8 +3984,17 @@
       <c r="R31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:18">
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>0</v>
+      </c>
+      <c r="U31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21">
       <c r="A32">
         <v>30</v>
       </c>
@@ -3491,14 +4025,14 @@
       <c r="J32">
         <v>22</v>
       </c>
-      <c r="K32">
-        <v>0</v>
-      </c>
-      <c r="L32">
-        <v>0</v>
+      <c r="K32" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="L32" s="7" t="s">
+        <v>190</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N32">
         <v>0</v>
@@ -3515,8 +4049,17 @@
       <c r="R32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:18">
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21">
       <c r="A33">
         <v>31</v>
       </c>
@@ -3547,14 +4090,14 @@
       <c r="J33">
         <v>22</v>
       </c>
-      <c r="K33">
-        <v>0</v>
-      </c>
-      <c r="L33">
-        <v>0</v>
+      <c r="K33" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="L33" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M33">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N33">
         <v>0</v>
@@ -3571,8 +4114,17 @@
       <c r="R33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:18">
+      <c r="S33">
+        <v>0</v>
+      </c>
+      <c r="T33">
+        <v>0</v>
+      </c>
+      <c r="U33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21">
       <c r="A34">
         <v>32</v>
       </c>
@@ -3603,14 +4155,14 @@
       <c r="J34">
         <v>22</v>
       </c>
-      <c r="K34">
-        <v>0</v>
-      </c>
-      <c r="L34">
-        <v>0</v>
+      <c r="K34" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="L34" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M34">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N34">
         <v>0</v>
@@ -3627,8 +4179,17 @@
       <c r="R34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:18">
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="T34">
+        <v>0</v>
+      </c>
+      <c r="U34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21">
       <c r="A35">
         <v>33</v>
       </c>
@@ -3659,32 +4220,41 @@
       <c r="J35">
         <v>22</v>
       </c>
-      <c r="K35">
-        <v>0</v>
-      </c>
-      <c r="L35">
-        <v>0</v>
+      <c r="K35" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="L35" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M35">
+        <v>22</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
         <v>1</v>
       </c>
-      <c r="N35">
+      <c r="Q35">
         <v>1</v>
       </c>
-      <c r="O35">
-        <v>0</v>
-      </c>
-      <c r="P35">
-        <v>0</v>
-      </c>
-      <c r="Q35">
-        <v>0</v>
-      </c>
       <c r="R35">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:18">
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="T35">
+        <v>0</v>
+      </c>
+      <c r="U35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21">
       <c r="A36">
         <v>34</v>
       </c>
@@ -3715,14 +4285,14 @@
       <c r="J36">
         <v>22</v>
       </c>
-      <c r="K36">
-        <v>0</v>
-      </c>
-      <c r="L36">
-        <v>0</v>
+      <c r="K36" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="L36" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M36">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N36">
         <v>0</v>
@@ -3739,8 +4309,17 @@
       <c r="R36">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:18">
+      <c r="S36">
+        <v>0</v>
+      </c>
+      <c r="T36">
+        <v>0</v>
+      </c>
+      <c r="U36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21">
       <c r="A37">
         <v>35</v>
       </c>
@@ -3771,14 +4350,14 @@
       <c r="J37">
         <v>22</v>
       </c>
-      <c r="K37">
-        <v>0</v>
-      </c>
-      <c r="L37">
-        <v>0</v>
+      <c r="K37" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="L37" s="7" t="s">
+        <v>190</v>
       </c>
       <c r="M37">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N37">
         <v>0</v>
@@ -3795,8 +4374,17 @@
       <c r="R37">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:18" ht="37.5">
+      <c r="S37">
+        <v>0</v>
+      </c>
+      <c r="T37">
+        <v>0</v>
+      </c>
+      <c r="U37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" ht="37.5">
       <c r="A38">
         <v>36</v>
       </c>
@@ -3827,32 +4415,41 @@
       <c r="J38">
         <v>22</v>
       </c>
-      <c r="K38">
-        <v>0</v>
-      </c>
-      <c r="L38">
-        <v>0</v>
+      <c r="K38" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="L38" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M38">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N38">
         <v>0</v>
       </c>
       <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38">
+        <v>0</v>
+      </c>
+      <c r="Q38">
+        <v>0</v>
+      </c>
+      <c r="R38">
         <v>1</v>
       </c>
-      <c r="P38">
+      <c r="S38">
         <v>9</v>
       </c>
-      <c r="Q38">
-        <v>0</v>
-      </c>
-      <c r="R38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18">
+      <c r="T38">
+        <v>0</v>
+      </c>
+      <c r="U38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21">
       <c r="A39">
         <v>37</v>
       </c>
@@ -3867,12 +4464,8 @@
       <c r="J39">
         <v>0</v>
       </c>
-      <c r="K39">
-        <v>0</v>
-      </c>
-      <c r="L39">
-        <v>0</v>
-      </c>
+      <c r="K39" s="7"/>
+      <c r="L39" s="7"/>
       <c r="M39">
         <v>0</v>
       </c>
@@ -3891,8 +4484,17 @@
       <c r="R39">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:18" ht="37.5">
+      <c r="S39">
+        <v>0</v>
+      </c>
+      <c r="T39">
+        <v>0</v>
+      </c>
+      <c r="U39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21" ht="37.5">
       <c r="A40">
         <v>38</v>
       </c>
@@ -3923,14 +4525,14 @@
       <c r="J40">
         <v>22</v>
       </c>
-      <c r="K40">
-        <v>0</v>
-      </c>
-      <c r="L40">
-        <v>0</v>
+      <c r="K40" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="L40" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M40">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N40">
         <v>0</v>
@@ -3947,8 +4549,17 @@
       <c r="R40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:18" ht="85.5" customHeight="1">
+      <c r="S40">
+        <v>0</v>
+      </c>
+      <c r="T40">
+        <v>0</v>
+      </c>
+      <c r="U40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21" ht="85.5" customHeight="1">
       <c r="A41">
         <v>39</v>
       </c>
@@ -3979,14 +4590,14 @@
       <c r="J41">
         <v>22</v>
       </c>
-      <c r="K41">
-        <v>0</v>
-      </c>
-      <c r="L41">
-        <v>0</v>
+      <c r="K41" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="L41" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M41">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N41">
         <v>0</v>
@@ -4003,8 +4614,17 @@
       <c r="R41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:18" ht="51.75" customHeight="1">
+      <c r="S41">
+        <v>0</v>
+      </c>
+      <c r="T41">
+        <v>0</v>
+      </c>
+      <c r="U41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21" ht="51.75" customHeight="1">
       <c r="A42">
         <v>40</v>
       </c>
@@ -4035,14 +4655,14 @@
       <c r="J42">
         <v>22</v>
       </c>
-      <c r="K42">
-        <v>0</v>
-      </c>
-      <c r="L42">
-        <v>0</v>
+      <c r="K42" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="L42" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M42">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N42">
         <v>0</v>
@@ -4059,8 +4679,17 @@
       <c r="R42">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:18" ht="56.25">
+      <c r="S42">
+        <v>0</v>
+      </c>
+      <c r="T42">
+        <v>0</v>
+      </c>
+      <c r="U42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21" ht="56.25">
       <c r="A43">
         <v>41</v>
       </c>
@@ -4091,14 +4720,14 @@
       <c r="J43">
         <v>22</v>
       </c>
-      <c r="K43">
-        <v>0</v>
-      </c>
-      <c r="L43">
-        <v>0</v>
+      <c r="K43" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="L43" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M43">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N43">
         <v>0</v>
@@ -4115,8 +4744,17 @@
       <c r="R43">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:18" ht="37.5">
+      <c r="S43">
+        <v>0</v>
+      </c>
+      <c r="T43">
+        <v>0</v>
+      </c>
+      <c r="U43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" ht="37.5">
       <c r="A44">
         <v>42</v>
       </c>
@@ -4147,32 +4785,41 @@
       <c r="J44">
         <v>22</v>
       </c>
-      <c r="K44">
-        <v>0</v>
-      </c>
-      <c r="L44">
-        <v>0</v>
+      <c r="K44" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="L44" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M44">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N44">
         <v>0</v>
       </c>
       <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>0</v>
+      </c>
+      <c r="Q44">
+        <v>0</v>
+      </c>
+      <c r="R44">
         <v>2</v>
       </c>
-      <c r="P44">
+      <c r="S44">
         <v>10</v>
       </c>
-      <c r="Q44">
-        <v>0</v>
-      </c>
-      <c r="R44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18" ht="56.25">
+      <c r="T44">
+        <v>0</v>
+      </c>
+      <c r="U44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21" ht="56.25">
       <c r="A45">
         <v>43</v>
       </c>
@@ -4203,32 +4850,41 @@
       <c r="J45">
         <v>22</v>
       </c>
-      <c r="K45">
-        <v>0</v>
-      </c>
-      <c r="L45">
-        <v>0</v>
+      <c r="K45" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="L45" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M45">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N45">
         <v>0</v>
       </c>
       <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>0</v>
+      </c>
+      <c r="Q45">
+        <v>0</v>
+      </c>
+      <c r="R45">
         <v>2</v>
       </c>
-      <c r="P45">
+      <c r="S45">
         <v>11</v>
       </c>
-      <c r="Q45">
-        <v>0</v>
-      </c>
-      <c r="R45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:18">
+      <c r="T45">
+        <v>0</v>
+      </c>
+      <c r="U45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21">
       <c r="A46">
         <v>44</v>
       </c>
@@ -4259,14 +4915,14 @@
       <c r="J46">
         <v>22</v>
       </c>
-      <c r="K46">
-        <v>0</v>
-      </c>
-      <c r="L46">
-        <v>0</v>
+      <c r="K46" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="L46" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M46">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N46">
         <v>0</v>
@@ -4283,8 +4939,17 @@
       <c r="R46">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:18">
+      <c r="S46">
+        <v>0</v>
+      </c>
+      <c r="T46">
+        <v>0</v>
+      </c>
+      <c r="U46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21">
       <c r="A47">
         <v>45</v>
       </c>
@@ -4315,32 +4980,41 @@
       <c r="J47">
         <v>22</v>
       </c>
-      <c r="K47">
-        <v>0</v>
-      </c>
-      <c r="L47">
-        <v>0</v>
+      <c r="K47" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="L47" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M47">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N47">
         <v>0</v>
       </c>
       <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>0</v>
+      </c>
+      <c r="Q47">
+        <v>0</v>
+      </c>
+      <c r="R47">
         <v>3</v>
       </c>
-      <c r="P47">
+      <c r="S47">
         <v>12</v>
       </c>
-      <c r="Q47">
-        <v>0</v>
-      </c>
-      <c r="R47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18">
+      <c r="T47">
+        <v>0</v>
+      </c>
+      <c r="U47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21">
       <c r="A48">
         <v>46</v>
       </c>
@@ -4371,32 +5045,41 @@
       <c r="J48">
         <v>22</v>
       </c>
-      <c r="K48">
-        <v>0</v>
-      </c>
-      <c r="L48">
-        <v>0</v>
+      <c r="K48" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="L48" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M48">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N48">
         <v>0</v>
       </c>
       <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+      <c r="Q48">
+        <v>0</v>
+      </c>
+      <c r="R48">
         <v>2</v>
       </c>
-      <c r="P48">
+      <c r="S48">
         <v>13</v>
       </c>
-      <c r="Q48">
-        <v>0</v>
-      </c>
-      <c r="R48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:18">
+      <c r="T48">
+        <v>0</v>
+      </c>
+      <c r="U48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21">
       <c r="A49">
         <v>47</v>
       </c>
@@ -4427,14 +5110,14 @@
       <c r="J49">
         <v>22</v>
       </c>
-      <c r="K49">
-        <v>0</v>
-      </c>
-      <c r="L49">
-        <v>0</v>
+      <c r="K49" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="L49" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M49">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N49">
         <v>0</v>
@@ -4451,8 +5134,17 @@
       <c r="R49">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:18" ht="37.5">
+      <c r="S49">
+        <v>0</v>
+      </c>
+      <c r="T49">
+        <v>0</v>
+      </c>
+      <c r="U49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21" ht="37.5">
       <c r="A50">
         <v>48</v>
       </c>
@@ -4483,32 +5175,41 @@
       <c r="J50">
         <v>22</v>
       </c>
-      <c r="K50">
-        <v>0</v>
-      </c>
-      <c r="L50">
-        <v>0</v>
+      <c r="K50" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="L50" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M50">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N50">
         <v>0</v>
       </c>
       <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>0</v>
+      </c>
+      <c r="Q50">
+        <v>0</v>
+      </c>
+      <c r="R50">
         <v>2</v>
       </c>
-      <c r="P50">
+      <c r="S50">
         <v>14</v>
       </c>
-      <c r="Q50">
-        <v>0</v>
-      </c>
-      <c r="R50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:18" ht="37.5">
+      <c r="T50">
+        <v>0</v>
+      </c>
+      <c r="U50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21" ht="37.5">
       <c r="A51">
         <v>49</v>
       </c>
@@ -4539,14 +5240,14 @@
       <c r="J51">
         <v>22</v>
       </c>
-      <c r="K51">
-        <v>0</v>
-      </c>
-      <c r="L51">
-        <v>0</v>
+      <c r="K51" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="L51" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M51">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N51">
         <v>0</v>
@@ -4563,8 +5264,17 @@
       <c r="R51">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:18">
+      <c r="S51">
+        <v>0</v>
+      </c>
+      <c r="T51">
+        <v>0</v>
+      </c>
+      <c r="U51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21">
       <c r="A52">
         <v>50</v>
       </c>
@@ -4595,14 +5305,14 @@
       <c r="J52">
         <v>22</v>
       </c>
-      <c r="K52">
-        <v>0</v>
-      </c>
-      <c r="L52">
-        <v>0</v>
+      <c r="K52" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="L52" s="7" t="s">
+        <v>190</v>
       </c>
       <c r="M52">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N52">
         <v>0</v>
@@ -4619,8 +5329,17 @@
       <c r="R52">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:18">
+      <c r="S52">
+        <v>0</v>
+      </c>
+      <c r="T52">
+        <v>0</v>
+      </c>
+      <c r="U52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21">
       <c r="A53">
         <v>51</v>
       </c>
@@ -4651,14 +5370,14 @@
       <c r="J53">
         <v>22</v>
       </c>
-      <c r="K53">
-        <v>0</v>
-      </c>
-      <c r="L53">
-        <v>0</v>
+      <c r="K53" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="L53" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M53">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N53">
         <v>0</v>
@@ -4675,8 +5394,17 @@
       <c r="R53">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:18">
+      <c r="S53">
+        <v>0</v>
+      </c>
+      <c r="T53">
+        <v>0</v>
+      </c>
+      <c r="U53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21">
       <c r="A54">
         <v>52</v>
       </c>
@@ -4707,14 +5435,14 @@
       <c r="J54">
         <v>22</v>
       </c>
-      <c r="K54">
-        <v>0</v>
-      </c>
-      <c r="L54">
-        <v>0</v>
+      <c r="K54" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="L54" s="7" t="s">
+        <v>190</v>
       </c>
       <c r="M54">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N54">
         <v>0</v>
@@ -4731,8 +5459,17 @@
       <c r="R54">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:18">
+      <c r="S54">
+        <v>0</v>
+      </c>
+      <c r="T54">
+        <v>0</v>
+      </c>
+      <c r="U54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21">
       <c r="A55">
         <v>53</v>
       </c>
@@ -4763,14 +5500,14 @@
       <c r="J55">
         <v>22</v>
       </c>
-      <c r="K55">
-        <v>0</v>
-      </c>
-      <c r="L55">
-        <v>0</v>
+      <c r="K55" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="L55" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M55">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N55">
         <v>0</v>
@@ -4787,8 +5524,17 @@
       <c r="R55">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:18" ht="37.5">
+      <c r="S55">
+        <v>0</v>
+      </c>
+      <c r="T55">
+        <v>0</v>
+      </c>
+      <c r="U55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21" ht="37.5">
       <c r="A56">
         <v>54</v>
       </c>
@@ -4819,14 +5565,14 @@
       <c r="J56">
         <v>22</v>
       </c>
-      <c r="K56">
-        <v>0</v>
-      </c>
-      <c r="L56">
-        <v>0</v>
+      <c r="K56" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="L56" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M56">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N56">
         <v>0</v>
@@ -4843,8 +5589,17 @@
       <c r="R56">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:18">
+      <c r="S56">
+        <v>0</v>
+      </c>
+      <c r="T56">
+        <v>0</v>
+      </c>
+      <c r="U56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21">
       <c r="A57">
         <v>55</v>
       </c>
@@ -4875,14 +5630,14 @@
       <c r="J57">
         <v>22</v>
       </c>
-      <c r="K57">
-        <v>0</v>
-      </c>
-      <c r="L57">
-        <v>0</v>
+      <c r="K57" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="L57" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M57">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N57">
         <v>0</v>
@@ -4899,8 +5654,17 @@
       <c r="R57">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:18" ht="37.5">
+      <c r="S57">
+        <v>0</v>
+      </c>
+      <c r="T57">
+        <v>0</v>
+      </c>
+      <c r="U57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21" ht="37.5">
       <c r="A58">
         <v>56</v>
       </c>
@@ -4931,14 +5695,14 @@
       <c r="J58">
         <v>22</v>
       </c>
-      <c r="K58">
-        <v>0</v>
-      </c>
-      <c r="L58">
-        <v>0</v>
+      <c r="K58" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="L58" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M58">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N58">
         <v>0</v>
@@ -4955,8 +5719,17 @@
       <c r="R58">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:18">
+      <c r="S58">
+        <v>0</v>
+      </c>
+      <c r="T58">
+        <v>0</v>
+      </c>
+      <c r="U58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21">
       <c r="A59">
         <v>57</v>
       </c>
@@ -4987,14 +5760,14 @@
       <c r="J59">
         <v>22</v>
       </c>
-      <c r="K59">
-        <v>0</v>
-      </c>
-      <c r="L59">
-        <v>0</v>
+      <c r="K59" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="L59" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M59">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N59">
         <v>0</v>
@@ -5011,8 +5784,17 @@
       <c r="R59">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:18">
+      <c r="S59">
+        <v>0</v>
+      </c>
+      <c r="T59">
+        <v>0</v>
+      </c>
+      <c r="U59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21">
       <c r="A60">
         <v>58</v>
       </c>
@@ -5043,14 +5825,14 @@
       <c r="J60">
         <v>22</v>
       </c>
-      <c r="K60">
-        <v>0</v>
-      </c>
-      <c r="L60">
-        <v>0</v>
+      <c r="K60" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="L60" s="7" t="s">
+        <v>190</v>
       </c>
       <c r="M60">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N60">
         <v>0</v>
@@ -5067,8 +5849,17 @@
       <c r="R60">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:18" ht="37.5">
+      <c r="S60">
+        <v>0</v>
+      </c>
+      <c r="T60">
+        <v>0</v>
+      </c>
+      <c r="U60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21" ht="37.5">
       <c r="A61">
         <v>59</v>
       </c>
@@ -5099,14 +5890,14 @@
       <c r="J61">
         <v>22</v>
       </c>
-      <c r="K61">
-        <v>0</v>
-      </c>
-      <c r="L61">
-        <v>0</v>
+      <c r="K61" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="L61" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M61">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N61">
         <v>0</v>
@@ -5123,8 +5914,17 @@
       <c r="R61">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:18">
+      <c r="S61">
+        <v>0</v>
+      </c>
+      <c r="T61">
+        <v>0</v>
+      </c>
+      <c r="U61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21">
       <c r="A62">
         <v>60</v>
       </c>
@@ -5155,21 +5955,21 @@
       <c r="J62">
         <v>22</v>
       </c>
-      <c r="K62">
-        <v>0</v>
-      </c>
-      <c r="L62">
+      <c r="K62" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="L62" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="M62">
+        <v>22</v>
+      </c>
+      <c r="N62">
+        <v>0</v>
+      </c>
+      <c r="O62">
         <v>1</v>
       </c>
-      <c r="M62">
-        <v>0</v>
-      </c>
-      <c r="N62">
-        <v>0</v>
-      </c>
-      <c r="O62">
-        <v>0</v>
-      </c>
       <c r="P62">
         <v>0</v>
       </c>
@@ -5179,8 +5979,17 @@
       <c r="R62">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:18">
+      <c r="S62">
+        <v>0</v>
+      </c>
+      <c r="T62">
+        <v>0</v>
+      </c>
+      <c r="U62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21">
       <c r="A63">
         <v>61</v>
       </c>
@@ -5211,14 +6020,14 @@
       <c r="J63">
         <v>22</v>
       </c>
-      <c r="K63">
-        <v>0</v>
-      </c>
-      <c r="L63">
-        <v>0</v>
+      <c r="K63" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="L63" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M63">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N63">
         <v>0</v>
@@ -5235,8 +6044,17 @@
       <c r="R63">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:18">
+      <c r="S63">
+        <v>0</v>
+      </c>
+      <c r="T63">
+        <v>0</v>
+      </c>
+      <c r="U63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21">
       <c r="A64">
         <v>62</v>
       </c>
@@ -5267,14 +6085,14 @@
       <c r="J64">
         <v>22</v>
       </c>
-      <c r="K64">
-        <v>0</v>
-      </c>
-      <c r="L64">
-        <v>0</v>
+      <c r="K64" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="L64" s="7" t="s">
+        <v>190</v>
       </c>
       <c r="M64">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N64">
         <v>0</v>
@@ -5291,8 +6109,17 @@
       <c r="R64">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:18">
+      <c r="S64">
+        <v>0</v>
+      </c>
+      <c r="T64">
+        <v>0</v>
+      </c>
+      <c r="U64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21">
       <c r="A65">
         <v>63</v>
       </c>
@@ -5323,14 +6150,14 @@
       <c r="J65">
         <v>22</v>
       </c>
-      <c r="K65">
-        <v>0</v>
-      </c>
-      <c r="L65">
-        <v>0</v>
+      <c r="K65" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="L65" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M65">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N65">
         <v>0</v>
@@ -5347,8 +6174,17 @@
       <c r="R65">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:18">
+      <c r="S65">
+        <v>0</v>
+      </c>
+      <c r="T65">
+        <v>0</v>
+      </c>
+      <c r="U65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21">
       <c r="A66">
         <v>64</v>
       </c>
@@ -5379,14 +6215,14 @@
       <c r="J66">
         <v>22</v>
       </c>
-      <c r="K66">
-        <v>0</v>
-      </c>
-      <c r="L66">
-        <v>0</v>
+      <c r="K66" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="L66" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M66">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N66">
         <v>0</v>
@@ -5403,8 +6239,17 @@
       <c r="R66">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:18">
+      <c r="S66">
+        <v>0</v>
+      </c>
+      <c r="T66">
+        <v>0</v>
+      </c>
+      <c r="U66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21">
       <c r="A67">
         <v>65</v>
       </c>
@@ -5435,14 +6280,14 @@
       <c r="J67">
         <v>22</v>
       </c>
-      <c r="K67">
-        <v>0</v>
-      </c>
-      <c r="L67">
-        <v>0</v>
+      <c r="K67" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="L67" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M67">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N67">
         <v>0</v>
@@ -5459,8 +6304,17 @@
       <c r="R67">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:18">
+      <c r="S67">
+        <v>0</v>
+      </c>
+      <c r="T67">
+        <v>0</v>
+      </c>
+      <c r="U67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21">
       <c r="A68">
         <v>66</v>
       </c>
@@ -5491,14 +6345,14 @@
       <c r="J68">
         <v>22</v>
       </c>
-      <c r="K68">
-        <v>0</v>
-      </c>
-      <c r="L68">
-        <v>0</v>
+      <c r="K68" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="L68" s="7" t="s">
+        <v>190</v>
       </c>
       <c r="M68">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N68">
         <v>0</v>
@@ -5515,8 +6369,17 @@
       <c r="R68">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="1:18" ht="37.5">
+      <c r="S68">
+        <v>0</v>
+      </c>
+      <c r="T68">
+        <v>0</v>
+      </c>
+      <c r="U68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21" ht="37.5">
       <c r="A69">
         <v>67</v>
       </c>
@@ -5547,14 +6410,14 @@
       <c r="J69">
         <v>22</v>
       </c>
-      <c r="K69">
-        <v>0</v>
-      </c>
-      <c r="L69">
-        <v>0</v>
+      <c r="K69" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="L69" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M69">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N69">
         <v>0</v>
@@ -5571,8 +6434,17 @@
       <c r="R69">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:18">
+      <c r="S69">
+        <v>0</v>
+      </c>
+      <c r="T69">
+        <v>0</v>
+      </c>
+      <c r="U69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:21">
       <c r="A70">
         <v>68</v>
       </c>
@@ -5603,14 +6475,14 @@
       <c r="J70">
         <v>22</v>
       </c>
-      <c r="K70">
-        <v>0</v>
-      </c>
-      <c r="L70">
-        <v>0</v>
+      <c r="K70" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="L70" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M70">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N70">
         <v>0</v>
@@ -5622,13 +6494,22 @@
         <v>0</v>
       </c>
       <c r="Q70">
+        <v>0</v>
+      </c>
+      <c r="R70">
+        <v>0</v>
+      </c>
+      <c r="S70">
+        <v>0</v>
+      </c>
+      <c r="T70">
         <v>1</v>
       </c>
-      <c r="R70">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:18">
+      <c r="U70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:21">
       <c r="A71">
         <v>69</v>
       </c>
@@ -5643,12 +6524,8 @@
       <c r="J71">
         <v>0</v>
       </c>
-      <c r="K71">
-        <v>0</v>
-      </c>
-      <c r="L71">
-        <v>0</v>
-      </c>
+      <c r="K71" s="7"/>
+      <c r="L71" s="7"/>
       <c r="M71">
         <v>0</v>
       </c>
@@ -5667,8 +6544,17 @@
       <c r="R71">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:18">
+      <c r="S71">
+        <v>0</v>
+      </c>
+      <c r="T71">
+        <v>0</v>
+      </c>
+      <c r="U71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:21">
       <c r="A72">
         <v>70</v>
       </c>
@@ -5699,32 +6585,41 @@
       <c r="J72">
         <v>22</v>
       </c>
-      <c r="K72">
-        <v>0</v>
-      </c>
-      <c r="L72">
-        <v>0</v>
+      <c r="K72" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="L72" s="7" t="s">
+        <v>190</v>
       </c>
       <c r="M72">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N72">
+        <v>0</v>
+      </c>
+      <c r="O72">
+        <v>0</v>
+      </c>
+      <c r="P72">
+        <v>0</v>
+      </c>
+      <c r="Q72">
         <v>1</v>
       </c>
-      <c r="O72">
-        <v>0</v>
-      </c>
-      <c r="P72">
-        <v>0</v>
-      </c>
-      <c r="Q72">
-        <v>0</v>
-      </c>
       <c r="R72">
+        <v>0</v>
+      </c>
+      <c r="S72">
+        <v>0</v>
+      </c>
+      <c r="T72">
+        <v>0</v>
+      </c>
+      <c r="U72">
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:18">
+    <row r="73" spans="1:21">
       <c r="A73">
         <v>71</v>
       </c>
@@ -5755,14 +6650,14 @@
       <c r="J73">
         <v>22</v>
       </c>
-      <c r="K73">
-        <v>0</v>
-      </c>
-      <c r="L73">
-        <v>0</v>
+      <c r="K73" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="L73" s="7" t="s">
+        <v>190</v>
       </c>
       <c r="M73">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N73">
         <v>0</v>
@@ -5779,8 +6674,17 @@
       <c r="R73">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:18">
+      <c r="S73">
+        <v>0</v>
+      </c>
+      <c r="T73">
+        <v>0</v>
+      </c>
+      <c r="U73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:21">
       <c r="A74">
         <v>72</v>
       </c>
@@ -5811,14 +6715,14 @@
       <c r="J74">
         <v>22</v>
       </c>
-      <c r="K74">
-        <v>0</v>
-      </c>
-      <c r="L74">
-        <v>0</v>
+      <c r="K74" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="L74" s="7" t="s">
+        <v>190</v>
       </c>
       <c r="M74">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N74">
         <v>0</v>
@@ -5835,8 +6739,17 @@
       <c r="R74">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="1:18">
+      <c r="S74">
+        <v>0</v>
+      </c>
+      <c r="T74">
+        <v>0</v>
+      </c>
+      <c r="U74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:21">
       <c r="A75">
         <v>73</v>
       </c>
@@ -5867,14 +6780,14 @@
       <c r="J75">
         <v>22</v>
       </c>
-      <c r="K75">
-        <v>0</v>
-      </c>
-      <c r="L75">
-        <v>0</v>
+      <c r="K75" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="L75" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M75">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N75">
         <v>0</v>
@@ -5891,8 +6804,17 @@
       <c r="R75">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:18">
+      <c r="S75">
+        <v>0</v>
+      </c>
+      <c r="T75">
+        <v>0</v>
+      </c>
+      <c r="U75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:21">
       <c r="A76">
         <v>74</v>
       </c>
@@ -5923,14 +6845,14 @@
       <c r="J76">
         <v>22</v>
       </c>
-      <c r="K76">
-        <v>0</v>
-      </c>
-      <c r="L76">
-        <v>0</v>
+      <c r="K76" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="L76" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M76">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N76">
         <v>0</v>
@@ -5947,8 +6869,17 @@
       <c r="R76">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:18">
+      <c r="S76">
+        <v>0</v>
+      </c>
+      <c r="T76">
+        <v>0</v>
+      </c>
+      <c r="U76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:21">
       <c r="A77">
         <v>75</v>
       </c>
@@ -5979,14 +6910,14 @@
       <c r="J77">
         <v>22</v>
       </c>
-      <c r="K77">
-        <v>0</v>
-      </c>
-      <c r="L77">
-        <v>0</v>
+      <c r="K77" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="L77" s="7" t="s">
+        <v>190</v>
       </c>
       <c r="M77">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N77">
         <v>0</v>
@@ -6003,8 +6934,17 @@
       <c r="R77">
         <v>0</v>
       </c>
-    </row>
-    <row r="78" spans="1:18" ht="37.5">
+      <c r="S77">
+        <v>0</v>
+      </c>
+      <c r="T77">
+        <v>0</v>
+      </c>
+      <c r="U77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:21" ht="37.5">
       <c r="A78">
         <v>76</v>
       </c>
@@ -6035,14 +6975,14 @@
       <c r="J78">
         <v>22</v>
       </c>
-      <c r="K78">
-        <v>0</v>
-      </c>
-      <c r="L78">
-        <v>0</v>
+      <c r="K78" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="L78" s="7" t="s">
+        <v>190</v>
       </c>
       <c r="M78">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N78">
         <v>0</v>
@@ -6059,8 +6999,17 @@
       <c r="R78">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="1:18">
+      <c r="S78">
+        <v>0</v>
+      </c>
+      <c r="T78">
+        <v>0</v>
+      </c>
+      <c r="U78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:21">
       <c r="A79">
         <v>77</v>
       </c>
@@ -6091,14 +7040,14 @@
       <c r="J79">
         <v>22</v>
       </c>
-      <c r="K79">
-        <v>0</v>
-      </c>
-      <c r="L79">
-        <v>0</v>
+      <c r="K79" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="L79" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M79">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N79">
         <v>0</v>
@@ -6115,8 +7064,17 @@
       <c r="R79">
         <v>0</v>
       </c>
-    </row>
-    <row r="80" spans="1:18">
+      <c r="S79">
+        <v>0</v>
+      </c>
+      <c r="T79">
+        <v>0</v>
+      </c>
+      <c r="U79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:21">
       <c r="A80">
         <v>78</v>
       </c>
@@ -6147,14 +7105,14 @@
       <c r="J80">
         <v>22</v>
       </c>
-      <c r="K80">
-        <v>0</v>
-      </c>
-      <c r="L80">
-        <v>0</v>
+      <c r="K80" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="L80" s="7" t="s">
+        <v>190</v>
       </c>
       <c r="M80">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N80">
         <v>0</v>
@@ -6171,8 +7129,17 @@
       <c r="R80">
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="1:18" ht="37.5">
+      <c r="S80">
+        <v>0</v>
+      </c>
+      <c r="T80">
+        <v>0</v>
+      </c>
+      <c r="U80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:21" ht="37.5">
       <c r="A81">
         <v>79</v>
       </c>
@@ -6203,14 +7170,14 @@
       <c r="J81">
         <v>22</v>
       </c>
-      <c r="K81">
-        <v>0</v>
-      </c>
-      <c r="L81">
-        <v>0</v>
+      <c r="K81" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="L81" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M81">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N81">
         <v>0</v>
@@ -6227,8 +7194,17 @@
       <c r="R81">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="1:18">
+      <c r="S81">
+        <v>0</v>
+      </c>
+      <c r="T81">
+        <v>0</v>
+      </c>
+      <c r="U81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:21">
       <c r="A82">
         <v>80</v>
       </c>
@@ -6259,14 +7235,14 @@
       <c r="J82">
         <v>22</v>
       </c>
-      <c r="K82">
-        <v>0</v>
-      </c>
-      <c r="L82">
-        <v>0</v>
+      <c r="K82" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="L82" s="7" t="s">
+        <v>190</v>
       </c>
       <c r="M82">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N82">
         <v>0</v>
@@ -6283,8 +7259,17 @@
       <c r="R82">
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="1:18" ht="37.5">
+      <c r="S82">
+        <v>0</v>
+      </c>
+      <c r="T82">
+        <v>0</v>
+      </c>
+      <c r="U82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:21" ht="37.5">
       <c r="A83">
         <v>81</v>
       </c>
@@ -6315,14 +7300,14 @@
       <c r="J83">
         <v>22</v>
       </c>
-      <c r="K83">
-        <v>0</v>
-      </c>
-      <c r="L83">
-        <v>0</v>
+      <c r="K83" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="L83" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M83">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N83">
         <v>0</v>
@@ -6339,8 +7324,17 @@
       <c r="R83">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:18">
+      <c r="S83">
+        <v>0</v>
+      </c>
+      <c r="T83">
+        <v>0</v>
+      </c>
+      <c r="U83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:21">
       <c r="A84">
         <v>82</v>
       </c>
@@ -6371,14 +7365,14 @@
       <c r="J84">
         <v>22</v>
       </c>
-      <c r="K84">
-        <v>0</v>
-      </c>
-      <c r="L84">
-        <v>0</v>
+      <c r="K84" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="L84" s="7" t="s">
+        <v>190</v>
       </c>
       <c r="M84">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N84">
         <v>0</v>
@@ -6395,8 +7389,17 @@
       <c r="R84">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:18">
+      <c r="S84">
+        <v>0</v>
+      </c>
+      <c r="T84">
+        <v>0</v>
+      </c>
+      <c r="U84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:21">
       <c r="A85">
         <v>83</v>
       </c>
@@ -6427,14 +7430,14 @@
       <c r="J85">
         <v>22</v>
       </c>
-      <c r="K85">
-        <v>0</v>
-      </c>
-      <c r="L85">
-        <v>0</v>
+      <c r="K85" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="L85" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M85">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N85">
         <v>0</v>
@@ -6451,8 +7454,17 @@
       <c r="R85">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="1:18">
+      <c r="S85">
+        <v>0</v>
+      </c>
+      <c r="T85">
+        <v>0</v>
+      </c>
+      <c r="U85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:21">
       <c r="A86">
         <v>84</v>
       </c>
@@ -6483,14 +7495,14 @@
       <c r="J86">
         <v>22</v>
       </c>
-      <c r="K86">
-        <v>0</v>
-      </c>
-      <c r="L86">
-        <v>0</v>
+      <c r="K86" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="L86" s="7" t="s">
+        <v>190</v>
       </c>
       <c r="M86">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N86">
         <v>0</v>
@@ -6507,8 +7519,17 @@
       <c r="R86">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="1:18">
+      <c r="S86">
+        <v>0</v>
+      </c>
+      <c r="T86">
+        <v>0</v>
+      </c>
+      <c r="U86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:21">
       <c r="A87">
         <v>85</v>
       </c>
@@ -6539,14 +7560,14 @@
       <c r="J87">
         <v>22</v>
       </c>
-      <c r="K87">
-        <v>0</v>
-      </c>
-      <c r="L87">
-        <v>0</v>
+      <c r="K87" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="L87" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M87">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N87">
         <v>0</v>
@@ -6563,8 +7584,17 @@
       <c r="R87">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="1:18">
+      <c r="S87">
+        <v>0</v>
+      </c>
+      <c r="T87">
+        <v>0</v>
+      </c>
+      <c r="U87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:21">
       <c r="A88">
         <v>86</v>
       </c>
@@ -6595,32 +7625,41 @@
       <c r="J88">
         <v>22</v>
       </c>
-      <c r="K88">
-        <v>0</v>
-      </c>
-      <c r="L88">
+      <c r="K88" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="L88" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="M88">
+        <v>22</v>
+      </c>
+      <c r="N88">
+        <v>0</v>
+      </c>
+      <c r="O88">
         <v>2</v>
       </c>
-      <c r="M88">
-        <v>0</v>
-      </c>
-      <c r="N88">
+      <c r="P88">
+        <v>0</v>
+      </c>
+      <c r="Q88">
         <v>1</v>
       </c>
-      <c r="O88">
-        <v>0</v>
-      </c>
-      <c r="P88">
-        <v>0</v>
-      </c>
-      <c r="Q88">
-        <v>0</v>
-      </c>
       <c r="R88">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="1:18">
+      <c r="S88">
+        <v>0</v>
+      </c>
+      <c r="T88">
+        <v>0</v>
+      </c>
+      <c r="U88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:21">
       <c r="A89">
         <v>87</v>
       </c>
@@ -6651,14 +7690,14 @@
       <c r="J89">
         <v>22</v>
       </c>
-      <c r="K89">
-        <v>0</v>
-      </c>
-      <c r="L89">
-        <v>0</v>
+      <c r="K89" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="L89" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="M89">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N89">
         <v>0</v>
@@ -6675,22 +7714,24 @@
       <c r="R89">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="1:18">
+      <c r="S89">
+        <v>0</v>
+      </c>
+      <c r="T89">
+        <v>0</v>
+      </c>
+      <c r="U89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:21">
       <c r="A90">
         <v>88</v>
       </c>
       <c r="H90" s="5"/>
       <c r="I90" s="5"/>
-      <c r="K90">
-        <v>0</v>
-      </c>
-      <c r="L90">
-        <v>0</v>
-      </c>
-      <c r="M90">
-        <v>0</v>
-      </c>
+      <c r="K90" s="7"/>
+      <c r="L90" s="7"/>
       <c r="N90">
         <v>0</v>
       </c>
@@ -6706,90 +7747,123 @@
       <c r="R90">
         <v>0</v>
       </c>
-    </row>
-    <row r="91" spans="1:18">
+      <c r="S90">
+        <v>0</v>
+      </c>
+      <c r="T90">
+        <v>0</v>
+      </c>
+      <c r="U90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:21">
       <c r="A91">
         <v>89</v>
       </c>
       <c r="H91" s="5"/>
       <c r="I91" s="5"/>
-    </row>
-    <row r="92" spans="1:18">
+      <c r="K91" s="7"/>
+      <c r="L91" s="7"/>
+    </row>
+    <row r="92" spans="1:21">
       <c r="A92">
         <v>90</v>
       </c>
       <c r="H92" s="5"/>
       <c r="I92" s="5"/>
-    </row>
-    <row r="93" spans="1:18">
+      <c r="K92" s="7"/>
+      <c r="L92" s="7"/>
+    </row>
+    <row r="93" spans="1:21">
       <c r="A93">
         <v>91</v>
       </c>
       <c r="H93" s="5"/>
       <c r="I93" s="5"/>
-    </row>
-    <row r="94" spans="1:18">
+      <c r="K93" s="7"/>
+      <c r="L93" s="7"/>
+    </row>
+    <row r="94" spans="1:21">
       <c r="A94">
         <v>92</v>
       </c>
       <c r="H94" s="5"/>
       <c r="I94" s="5"/>
-    </row>
-    <row r="95" spans="1:18">
+      <c r="K94" s="7"/>
+      <c r="L94" s="7"/>
+    </row>
+    <row r="95" spans="1:21">
       <c r="A95">
         <v>93</v>
       </c>
       <c r="H95" s="5"/>
       <c r="I95" s="5"/>
-    </row>
-    <row r="96" spans="1:18">
+      <c r="K95" s="7"/>
+      <c r="L95" s="7"/>
+    </row>
+    <row r="96" spans="1:21">
       <c r="A96">
         <v>94</v>
       </c>
       <c r="H96" s="5"/>
       <c r="I96" s="5"/>
-    </row>
-    <row r="97" spans="1:9">
+      <c r="K96" s="7"/>
+      <c r="L96" s="7"/>
+    </row>
+    <row r="97" spans="1:12">
       <c r="A97">
         <v>95</v>
       </c>
       <c r="H97" s="5"/>
       <c r="I97" s="5"/>
-    </row>
-    <row r="98" spans="1:9">
+      <c r="K97" s="7"/>
+      <c r="L97" s="7"/>
+    </row>
+    <row r="98" spans="1:12">
       <c r="A98">
         <v>96</v>
       </c>
       <c r="H98" s="5"/>
       <c r="I98" s="5"/>
-    </row>
-    <row r="99" spans="1:9">
+      <c r="K98" s="7"/>
+      <c r="L98" s="7"/>
+    </row>
+    <row r="99" spans="1:12">
       <c r="A99">
         <v>97</v>
       </c>
       <c r="H99" s="5"/>
       <c r="I99" s="5"/>
-    </row>
-    <row r="100" spans="1:9">
+      <c r="K99" s="7"/>
+      <c r="L99" s="7"/>
+    </row>
+    <row r="100" spans="1:12">
       <c r="A100">
         <v>98</v>
       </c>
       <c r="H100" s="5"/>
       <c r="I100" s="5"/>
-    </row>
-    <row r="101" spans="1:9">
+      <c r="K100" s="7"/>
+      <c r="L100" s="7"/>
+    </row>
+    <row r="101" spans="1:12">
       <c r="A101">
         <v>99</v>
       </c>
       <c r="H101" s="5"/>
       <c r="I101" s="5"/>
-    </row>
-    <row r="102" spans="1:9">
+      <c r="K101" s="7"/>
+      <c r="L101" s="7"/>
+    </row>
+    <row r="102" spans="1:12">
       <c r="A102">
         <v>100</v>
       </c>
       <c r="H102" s="5"/>
       <c r="I102" s="5"/>
+      <c r="K102" s="7"/>
+      <c r="L102" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/Assets/Originals/Excels/Talk/TalkMessage.xlsx
+++ b/Assets/Originals/Excels/Talk/TalkMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Talk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F58EF04B-480F-4466-B5EF-390B63512AC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D5B1138-752E-4C0C-A903-BED3F796DF88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="439">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -1611,6 +1611,281 @@
   <si>
     <t>messageSizeChinese02</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>messageSpanish</t>
+  </si>
+  <si>
+    <t>speakerNameSpanish</t>
+  </si>
+  <si>
+    <t>messageSizeSpanish</t>
+  </si>
+  <si>
+    <t>¿Dónde... dónde estoy...?</t>
+  </si>
+  <si>
+    <t>Tú</t>
+  </si>
+  <si>
+    <t>Parece que has despertado.</t>
+  </si>
+  <si>
+    <t>Me llamo Kaname.
+Soy tu guía en «Mumei».</t>
+  </si>
+  <si>
+    <t>¿Mumei?</t>
+  </si>
+  <si>
+    <t>Es el enorme laberinto que se encuentra en este mundo eterno.</t>
+  </si>
+  <si>
+    <t>Moriste en el mundo de los vivos tras cometer un «pecado».
+Todo aquel que comete un pecado queda encerrado en este Mumei.</t>
+  </si>
+  <si>
+    <t>Es decir, que tú también eres uno de ellos.</t>
+  </si>
+  <si>
+    <t>¿Un pecado?</t>
+  </si>
+  <si>
+    <t>Así es. Un pecado muy, muy grave.</t>
+  </si>
+  <si>
+    <t>Por cierto, ¿recuerdas tu propio nombre?</t>
+  </si>
+  <si>
+    <t>Eh... mi nombre es...</t>
+  </si>
+  <si>
+    <t>¿Eh...? No lo recuerdo...</t>
+  </si>
+  <si>
+    <t>Es normal que no lo recuerdes.</t>
+  </si>
+  <si>
+    <t>Porque tu nombre fue descartado antes de que llegaras a este laberinto.</t>
+  </si>
+  <si>
+    <t>¿Mi nombre... descartado...?</t>
+  </si>
+  <si>
+    <t>¿Qué quieres decir?</t>
+  </si>
+  <si>
+    <t>Quien pierde su nombre en el mundo eterno
+ya no puede recordarlo jamás.</t>
+  </si>
+  <si>
+    <t>¿Eh...?</t>
+  </si>
+  <si>
+    <t>Y aquellos que no pueden recordar su nombre...</t>
+  </si>
+  <si>
+    <t>...vagarán eternamente por este laberinto,
+soportando todo tipo de sufrimiento.</t>
+  </si>
+  <si>
+    <t>Tarde o temprano, tú también acabarás así.</t>
+  </si>
+  <si>
+    <t>No... eso es muy cruel...</t>
+  </si>
+  <si>
+    <t>¿Por qué...?</t>
+  </si>
+  <si>
+    <t>Porque los pecadores no necesitan nombre.</t>
+  </si>
+  <si>
+    <t>Pero no te preocupes.</t>
+  </si>
+  <si>
+    <t>Si logras recordar el pecado que cometiste en el mundo de los vivos y escapas de este laberinto,
+te diré cuál es tu nombre.</t>
+  </si>
+  <si>
+    <t>Así no tendrás que sufrir
+ni vagar sin rumbo.</t>
+  </si>
+  <si>
+    <t>...¿Quieres escapar de aquí?</t>
+  </si>
+  <si>
+    <t>...Quiero escapar.</t>
+  </si>
+  <si>
+    <t>Pero... ¿cómo puedo escapar?</t>
+  </si>
+  <si>
+    <t>...Hay una manera.</t>
+  </si>
+  <si>
+    <t>Consiste en superar la prueba que te voy a proponer.</t>
+  </si>
+  <si>
+    <t>Si lo consigues, podrás escapar.</t>
+  </si>
+  <si>
+    <t>...¿Aceptas mi prueba?</t>
+  </si>
+  <si>
+    <t>...La aceptaré.</t>
+  </si>
+  <si>
+    <t>...De acuerdo.
+Entonces te explicaré en qué consiste la prueba.</t>
+  </si>
+  <si>
+    <t>Para superar la prueba,
+debes cumplir dos condiciones.</t>
+  </si>
+  <si>
+    <t>Primera: escapar de este laberinto.
+Segunda: recordar el pecado que cometiste en el mundo de los vivos.</t>
+  </si>
+  <si>
+    <t>Te explicaré cómo escapar de este laberinto.</t>
+  </si>
+  <si>
+    <t>Para escapar, debes encontrar los «Documentos» y los «Objetos Misteriosos»
+repartidos por todos los rincones de este laberinto.</t>
+  </si>
+  <si>
+    <t>Primero, consigue un Documento.
+Prueba a abrir el cajón que tienes delante.</t>
+  </si>
+  <si>
+    <t>Revisa el contenido del Documento que acabas de recoger.</t>
+  </si>
+  <si>
+    <t>A continuación, consigue un Objeto Misterioso.</t>
+  </si>
+  <si>
+    <t>Abre los dos cajones que tienes delante.</t>
+  </si>
+  <si>
+    <t>Examina el Objeto Misterioso que acabas de recoger.</t>
+  </si>
+  <si>
+    <t>Por último, toca la «Esfera Azul del Juicio» que hay al fondo.</t>
+  </si>
+  <si>
+    <t>Debes elegir el Objeto Misterioso
+que tenga una relación profunda con el contenido del Documento.</t>
+  </si>
+  <si>
+    <t>Con esto termina la explicación de la prueba.
+¿Tienes alguna pregunta?</t>
+  </si>
+  <si>
+    <t>¿Eh? ¿No vas a explicarme nada sobre el pecado que cometí?</t>
+  </si>
+  <si>
+    <t>No.</t>
+  </si>
+  <si>
+    <t>No me digas «eh».</t>
+  </si>
+  <si>
+    <t>Si de verdad crees que hiciste algo malo,
+deberías poder recordar tu pecado enseguida.</t>
+  </si>
+  <si>
+    <t>Por eso, la explicación termina aquí.</t>
+  </si>
+  <si>
+    <t>Además, como no tener nombre es un inconveniente,
+te llamaré «If» de forma provisional.</t>
+  </si>
+  <si>
+    <t>¿Te parece bien?</t>
+  </si>
+  <si>
+    <t>Eh... s-sí...</t>
+  </si>
+  <si>
+    <t>Por último, hay una advertencia sobre este laberinto.</t>
+  </si>
+  <si>
+    <t>¿Una advertencia?</t>
+  </si>
+  <si>
+    <t>Nunca dejes que te atrapen los «Errantes».</t>
+  </si>
+  <si>
+    <t>¿Los Errantes?</t>
+  </si>
+  <si>
+    <t>Son los monstruos que acechan en Mumei.</t>
+  </si>
+  <si>
+    <t>If, sea como sea, no dejes que ese monstruo te atrape.</t>
+  </si>
+  <si>
+    <t>¿Entendido?</t>
+  </si>
+  <si>
+    <t>...S-sí...</t>
+  </si>
+  <si>
+    <t>Bien, ahora comenzará la prueba.
+Avanza por el pasillo que tienes detrás.</t>
+  </si>
+  <si>
+    <t>If, espero de corazón que superes la prueba.</t>
+  </si>
+  <si>
+    <t>...Con esto... por fin... podré escapar de este laberinto...</t>
+  </si>
+  <si>
+    <t>¿Eh...? ¿Qué... es esto...?</t>
+  </si>
+  <si>
+    <t>¡¿Por qué el laberinto sigue continuando?!</t>
+  </si>
+  <si>
+    <t>¿No es obvio?</t>
+  </si>
+  <si>
+    <t>Porque todavía no has escapado del laberinto.</t>
+  </si>
+  <si>
+    <t>...¿Cómo que no he escapado?</t>
+  </si>
+  <si>
+    <t>¡He recogido todos los Documentos y los Objetos Misteriosos!</t>
+  </si>
+  <si>
+    <t>¿De verdad creías que con eso bastaba?</t>
+  </si>
+  <si>
+    <t>También hay Documentos y Objetos Misteriosos
+en otras zonas.</t>
+  </si>
+  <si>
+    <t>No puede ser...</t>
+  </si>
+  <si>
+    <t>Además, tú tampoco has recordado aún el pecado que cometiste, ¿verdad?</t>
+  </si>
+  <si>
+    <t>...!</t>
+  </si>
+  <si>
+    <t>Por eso la prueba todavía no ha terminado.</t>
+  </si>
+  <si>
+    <t>El verdadero horror de Mumei empieza justo aquí, If.</t>
+  </si>
+  <si>
+    <t>Sé que será duro,</t>
+  </si>
+  <si>
+    <t>pero sigamos esforzándonos, If. Cuento contigo.</t>
   </si>
 </sst>
 </file>
@@ -1979,7 +2254,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U102"/>
+  <dimension ref="A1:X102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="123.375" style="2" customWidth="1"/>
@@ -1993,16 +2268,19 @@
     <col min="11" max="11" width="47.125" customWidth="1"/>
     <col min="12" max="12" width="22.75" customWidth="1"/>
     <col min="13" max="13" width="22.5" customWidth="1"/>
-    <col min="14" max="14" width="27.75" customWidth="1"/>
-    <col min="15" max="15" width="22.5" customWidth="1"/>
-    <col min="16" max="16" width="13.625" customWidth="1"/>
-    <col min="18" max="18" width="17.125" customWidth="1"/>
-    <col min="19" max="19" width="28.125" customWidth="1"/>
-    <col min="20" max="20" width="13.125" customWidth="1"/>
-    <col min="21" max="21" width="16" customWidth="1"/>
+    <col min="14" max="14" width="47.125" customWidth="1"/>
+    <col min="15" max="15" width="17.625" customWidth="1"/>
+    <col min="16" max="16" width="19.75" customWidth="1"/>
+    <col min="17" max="17" width="27.75" customWidth="1"/>
+    <col min="18" max="18" width="22.5" customWidth="1"/>
+    <col min="19" max="19" width="13.625" customWidth="1"/>
+    <col min="21" max="21" width="17.125" customWidth="1"/>
+    <col min="22" max="22" width="28.125" customWidth="1"/>
+    <col min="23" max="23" width="13.125" customWidth="1"/>
+    <col min="24" max="24" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="37.5">
+    <row r="1" spans="1:24" ht="37.5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2043,31 +2321,40 @@
         <v>352</v>
       </c>
       <c r="N1" t="s">
+        <v>353</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="P1" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q1" t="s">
         <v>21</v>
       </c>
-      <c r="O1" t="s">
-        <v>22</v>
-      </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
+        <v>22</v>
+      </c>
+      <c r="S1" t="s">
         <v>23</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="T1" t="s">
         <v>24</v>
       </c>
-      <c r="R1" t="s">
+      <c r="U1" t="s">
         <v>25</v>
       </c>
-      <c r="S1" t="s">
+      <c r="V1" t="s">
         <v>26</v>
       </c>
-      <c r="T1" t="s">
+      <c r="W1" t="s">
         <v>27</v>
       </c>
-      <c r="U1" t="s">
+      <c r="X1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:24">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2087,12 +2374,6 @@
       <c r="M2">
         <v>0</v>
       </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
       <c r="P2">
         <v>0</v>
       </c>
@@ -2111,8 +2392,17 @@
       <c r="U2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:21">
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2152,14 +2442,14 @@
       <c r="M3">
         <v>22</v>
       </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
+      <c r="N3" t="s">
+        <v>356</v>
+      </c>
+      <c r="O3" t="s">
+        <v>357</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -2176,8 +2466,17 @@
       <c r="U3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:21">
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2217,32 +2516,41 @@
       <c r="M4">
         <v>22</v>
       </c>
-      <c r="N4">
+      <c r="N4" t="s">
+        <v>358</v>
+      </c>
+      <c r="O4" t="s">
+        <v>192</v>
+      </c>
+      <c r="P4">
+        <v>22</v>
+      </c>
+      <c r="Q4">
         <v>1</v>
       </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
         <v>3</v>
       </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:21" ht="37.5">
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" ht="37.5">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2282,14 +2590,14 @@
       <c r="M5">
         <v>22</v>
       </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
+      <c r="N5" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="O5" t="s">
+        <v>34</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -2306,8 +2614,17 @@
       <c r="U5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:21">
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2347,14 +2664,14 @@
       <c r="M6">
         <v>22</v>
       </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
+      <c r="N6" t="s">
+        <v>360</v>
+      </c>
+      <c r="O6" t="s">
+        <v>357</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -2371,8 +2688,17 @@
       <c r="U6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:21">
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2412,14 +2738,14 @@
       <c r="M7">
         <v>22</v>
       </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
+      <c r="N7" t="s">
+        <v>361</v>
+      </c>
+      <c r="O7" t="s">
+        <v>34</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -2436,8 +2762,17 @@
       <c r="U7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" ht="56.25">
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" ht="75">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2477,14 +2812,14 @@
       <c r="M8">
         <v>22</v>
       </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
+      <c r="N8" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="O8" t="s">
+        <v>34</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -2501,8 +2836,17 @@
       <c r="U8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:21">
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24">
       <c r="A9">
         <v>7</v>
       </c>
@@ -2542,14 +2886,14 @@
       <c r="M9">
         <v>22</v>
       </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
+      <c r="N9" t="s">
+        <v>363</v>
+      </c>
+      <c r="O9" t="s">
+        <v>34</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -2566,8 +2910,17 @@
       <c r="U9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:21">
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24">
       <c r="A10">
         <v>8</v>
       </c>
@@ -2607,14 +2960,14 @@
       <c r="M10">
         <v>22</v>
       </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
+      <c r="N10" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="O10" t="s">
+        <v>357</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2631,8 +2984,17 @@
       <c r="U10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:21">
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24">
       <c r="A11">
         <v>9</v>
       </c>
@@ -2672,14 +3034,14 @@
       <c r="M11">
         <v>22</v>
       </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
+      <c r="N11" t="s">
+        <v>365</v>
+      </c>
+      <c r="O11" t="s">
+        <v>34</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2696,8 +3058,17 @@
       <c r="U11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:21">
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24">
       <c r="A12">
         <v>10</v>
       </c>
@@ -2737,14 +3108,14 @@
       <c r="M12">
         <v>22</v>
       </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
+      <c r="N12" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="O12" t="s">
+        <v>34</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -2761,8 +3132,17 @@
       <c r="U12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:21">
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24">
       <c r="A13">
         <v>11</v>
       </c>
@@ -2802,21 +3182,21 @@
       <c r="M13">
         <v>22</v>
       </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13">
+      <c r="N13" t="s">
+        <v>367</v>
+      </c>
+      <c r="O13" t="s">
+        <v>357</v>
+      </c>
+      <c r="P13">
+        <v>22</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
         <v>1</v>
       </c>
-      <c r="P13">
-        <v>0</v>
-      </c>
-      <c r="Q13">
-        <v>0</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
       <c r="S13">
         <v>0</v>
       </c>
@@ -2826,8 +3206,17 @@
       <c r="U13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21">
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24">
       <c r="A14">
         <v>12</v>
       </c>
@@ -2867,14 +3256,14 @@
       <c r="M14">
         <v>22</v>
       </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14">
-        <v>0</v>
+      <c r="N14" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="O14" t="s">
+        <v>357</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2891,8 +3280,17 @@
       <c r="U14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21">
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24">
       <c r="A15">
         <v>13</v>
       </c>
@@ -2932,14 +3330,14 @@
       <c r="M15">
         <v>22</v>
       </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15">
-        <v>0</v>
+      <c r="N15" t="s">
+        <v>369</v>
+      </c>
+      <c r="O15" t="s">
+        <v>34</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2956,8 +3354,17 @@
       <c r="U15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" ht="37.5">
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" ht="37.5">
       <c r="A16">
         <v>14</v>
       </c>
@@ -2997,14 +3404,14 @@
       <c r="M16">
         <v>22</v>
       </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16">
-        <v>0</v>
+      <c r="N16" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="O16" t="s">
+        <v>34</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -3021,8 +3428,17 @@
       <c r="U16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:21">
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24">
       <c r="A17">
         <v>15</v>
       </c>
@@ -3062,14 +3478,14 @@
       <c r="M17">
         <v>22</v>
       </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17">
-        <v>0</v>
+      <c r="N17" t="s">
+        <v>371</v>
+      </c>
+      <c r="O17" t="s">
+        <v>357</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3086,8 +3502,17 @@
       <c r="U17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:21">
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24">
       <c r="A18">
         <v>16</v>
       </c>
@@ -3127,14 +3552,14 @@
       <c r="M18">
         <v>22</v>
       </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
-      <c r="O18">
-        <v>0</v>
+      <c r="N18" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="O18" t="s">
+        <v>357</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3151,8 +3576,17 @@
       <c r="U18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:21" ht="56.25">
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" ht="56.25">
       <c r="A19">
         <v>17</v>
       </c>
@@ -3192,14 +3626,14 @@
       <c r="M19">
         <v>22</v>
       </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="O19">
-        <v>0</v>
+      <c r="N19" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="O19" t="s">
+        <v>34</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3216,8 +3650,17 @@
       <c r="U19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:21">
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24">
       <c r="A20">
         <v>18</v>
       </c>
@@ -3257,14 +3700,14 @@
       <c r="M20">
         <v>22</v>
       </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20">
-        <v>0</v>
+      <c r="N20" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="O20" t="s">
+        <v>357</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3281,8 +3724,17 @@
       <c r="U20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:21">
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24">
       <c r="A21">
         <v>19</v>
       </c>
@@ -3319,21 +3771,21 @@
       <c r="M21">
         <v>22</v>
       </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21">
+      <c r="N21" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="O21" t="s">
+        <v>34</v>
+      </c>
+      <c r="P21">
+        <v>22</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
         <v>1</v>
       </c>
-      <c r="P21">
-        <v>0</v>
-      </c>
-      <c r="Q21">
-        <v>0</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
       <c r="S21">
         <v>0</v>
       </c>
@@ -3343,8 +3795,17 @@
       <c r="U21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:21" ht="37.5">
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" ht="37.5">
       <c r="A22">
         <v>20</v>
       </c>
@@ -3384,14 +3845,14 @@
       <c r="M22">
         <v>22</v>
       </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
-      <c r="O22">
-        <v>0</v>
+      <c r="N22" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="O22" t="s">
+        <v>34</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -3408,8 +3869,17 @@
       <c r="U22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:21">
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24">
       <c r="A23">
         <v>21</v>
       </c>
@@ -3449,14 +3919,14 @@
       <c r="M23">
         <v>22</v>
       </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
-      <c r="O23">
-        <v>0</v>
+      <c r="N23" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="O23" t="s">
+        <v>34</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -3473,8 +3943,17 @@
       <c r="U23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:21">
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24">
       <c r="A24">
         <v>22</v>
       </c>
@@ -3514,14 +3993,14 @@
       <c r="M24">
         <v>22</v>
       </c>
-      <c r="N24">
-        <v>0</v>
-      </c>
-      <c r="O24">
-        <v>0</v>
+      <c r="N24" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="O24" t="s">
+        <v>357</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -3538,8 +4017,17 @@
       <c r="U24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:21">
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24">
       <c r="A25">
         <v>23</v>
       </c>
@@ -3579,14 +4067,14 @@
       <c r="M25">
         <v>22</v>
       </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
-      <c r="O25">
-        <v>0</v>
+      <c r="N25" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="O25" t="s">
+        <v>357</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -3603,8 +4091,17 @@
       <c r="U25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:21">
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24">
       <c r="A26">
         <v>24</v>
       </c>
@@ -3644,14 +4141,14 @@
       <c r="M26">
         <v>22</v>
       </c>
-      <c r="N26">
-        <v>0</v>
-      </c>
-      <c r="O26">
-        <v>0</v>
+      <c r="N26" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="O26" t="s">
+        <v>34</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -3668,8 +4165,17 @@
       <c r="U26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:21">
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24">
       <c r="A27">
         <v>25</v>
       </c>
@@ -3709,14 +4215,14 @@
       <c r="M27">
         <v>22</v>
       </c>
-      <c r="N27">
-        <v>0</v>
-      </c>
-      <c r="O27">
-        <v>0</v>
+      <c r="N27" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="O27" t="s">
+        <v>34</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -3733,8 +4239,17 @@
       <c r="U27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:21" ht="56.25">
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" ht="56.25">
       <c r="A28">
         <v>26</v>
       </c>
@@ -3774,14 +4289,14 @@
       <c r="M28">
         <v>22</v>
       </c>
-      <c r="N28">
-        <v>0</v>
-      </c>
-      <c r="O28">
-        <v>0</v>
+      <c r="N28" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="O28" t="s">
+        <v>34</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -3798,8 +4313,17 @@
       <c r="U28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:21" ht="37.5">
+      <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>0</v>
+      </c>
+      <c r="X28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" ht="37.5">
       <c r="A29">
         <v>27</v>
       </c>
@@ -3839,32 +4363,41 @@
       <c r="M29">
         <v>22</v>
       </c>
-      <c r="N29">
-        <v>0</v>
-      </c>
-      <c r="O29">
-        <v>0</v>
+      <c r="N29" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="O29" t="s">
+        <v>34</v>
       </c>
       <c r="P29">
+        <v>22</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
         <v>1</v>
       </c>
-      <c r="Q29">
+      <c r="T29">
         <v>1</v>
       </c>
-      <c r="R29">
-        <v>0</v>
-      </c>
-      <c r="S29">
-        <v>0</v>
-      </c>
-      <c r="T29">
-        <v>0</v>
-      </c>
       <c r="U29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:21">
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <v>0</v>
+      </c>
+      <c r="X29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24">
       <c r="A30">
         <v>28</v>
       </c>
@@ -3904,14 +4437,14 @@
       <c r="M30">
         <v>22</v>
       </c>
-      <c r="N30">
-        <v>0</v>
-      </c>
-      <c r="O30">
-        <v>0</v>
+      <c r="N30" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="O30" t="s">
+        <v>34</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -3928,8 +4461,17 @@
       <c r="U30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:21">
+      <c r="V30">
+        <v>0</v>
+      </c>
+      <c r="W30">
+        <v>0</v>
+      </c>
+      <c r="X30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24">
       <c r="A31">
         <v>29</v>
       </c>
@@ -3969,14 +4511,14 @@
       <c r="M31">
         <v>22</v>
       </c>
-      <c r="N31">
-        <v>0</v>
-      </c>
-      <c r="O31">
-        <v>0</v>
+      <c r="N31" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="O31" t="s">
+        <v>357</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -3993,8 +4535,17 @@
       <c r="U31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:21">
+      <c r="V31">
+        <v>0</v>
+      </c>
+      <c r="W31">
+        <v>0</v>
+      </c>
+      <c r="X31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24">
       <c r="A32">
         <v>30</v>
       </c>
@@ -4034,14 +4585,14 @@
       <c r="M32">
         <v>22</v>
       </c>
-      <c r="N32">
-        <v>0</v>
-      </c>
-      <c r="O32">
-        <v>0</v>
+      <c r="N32" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="O32" t="s">
+        <v>357</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -4058,8 +4609,17 @@
       <c r="U32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:21">
+      <c r="V32">
+        <v>0</v>
+      </c>
+      <c r="W32">
+        <v>0</v>
+      </c>
+      <c r="X32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:24">
       <c r="A33">
         <v>31</v>
       </c>
@@ -4099,14 +4659,14 @@
       <c r="M33">
         <v>22</v>
       </c>
-      <c r="N33">
-        <v>0</v>
-      </c>
-      <c r="O33">
-        <v>0</v>
+      <c r="N33" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="O33" t="s">
+        <v>34</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -4123,8 +4683,17 @@
       <c r="U33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:21">
+      <c r="V33">
+        <v>0</v>
+      </c>
+      <c r="W33">
+        <v>0</v>
+      </c>
+      <c r="X33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:24">
       <c r="A34">
         <v>32</v>
       </c>
@@ -4164,14 +4733,14 @@
       <c r="M34">
         <v>22</v>
       </c>
-      <c r="N34">
-        <v>0</v>
-      </c>
-      <c r="O34">
-        <v>0</v>
+      <c r="N34" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="O34" t="s">
+        <v>34</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -4188,8 +4757,17 @@
       <c r="U34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:21">
+      <c r="V34">
+        <v>0</v>
+      </c>
+      <c r="W34">
+        <v>0</v>
+      </c>
+      <c r="X34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:24">
       <c r="A35">
         <v>33</v>
       </c>
@@ -4229,32 +4807,41 @@
       <c r="M35">
         <v>22</v>
       </c>
-      <c r="N35">
-        <v>0</v>
-      </c>
-      <c r="O35">
-        <v>0</v>
+      <c r="N35" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="O35" t="s">
+        <v>34</v>
       </c>
       <c r="P35">
+        <v>22</v>
+      </c>
+      <c r="Q35">
+        <v>0</v>
+      </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35">
         <v>1</v>
       </c>
-      <c r="Q35">
+      <c r="T35">
         <v>1</v>
       </c>
-      <c r="R35">
-        <v>0</v>
-      </c>
-      <c r="S35">
-        <v>0</v>
-      </c>
-      <c r="T35">
-        <v>0</v>
-      </c>
       <c r="U35">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:21">
+      <c r="V35">
+        <v>0</v>
+      </c>
+      <c r="W35">
+        <v>0</v>
+      </c>
+      <c r="X35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24">
       <c r="A36">
         <v>34</v>
       </c>
@@ -4294,14 +4881,14 @@
       <c r="M36">
         <v>22</v>
       </c>
-      <c r="N36">
-        <v>0</v>
-      </c>
-      <c r="O36">
-        <v>0</v>
+      <c r="N36" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="O36" t="s">
+        <v>34</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -4318,8 +4905,17 @@
       <c r="U36">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:21">
+      <c r="V36">
+        <v>0</v>
+      </c>
+      <c r="W36">
+        <v>0</v>
+      </c>
+      <c r="X36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24">
       <c r="A37">
         <v>35</v>
       </c>
@@ -4359,14 +4955,14 @@
       <c r="M37">
         <v>22</v>
       </c>
-      <c r="N37">
-        <v>0</v>
-      </c>
-      <c r="O37">
-        <v>0</v>
+      <c r="N37" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="O37" t="s">
+        <v>357</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -4383,8 +4979,17 @@
       <c r="U37">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:21" ht="37.5">
+      <c r="V37">
+        <v>0</v>
+      </c>
+      <c r="W37">
+        <v>0</v>
+      </c>
+      <c r="X37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:24" ht="37.5">
       <c r="A38">
         <v>36</v>
       </c>
@@ -4424,32 +5029,41 @@
       <c r="M38">
         <v>22</v>
       </c>
-      <c r="N38">
-        <v>0</v>
-      </c>
-      <c r="O38">
-        <v>0</v>
+      <c r="N38" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="O38" t="s">
+        <v>34</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q38">
         <v>0</v>
       </c>
       <c r="R38">
+        <v>0</v>
+      </c>
+      <c r="S38">
+        <v>0</v>
+      </c>
+      <c r="T38">
+        <v>0</v>
+      </c>
+      <c r="U38">
         <v>1</v>
       </c>
-      <c r="S38">
+      <c r="V38">
         <v>9</v>
       </c>
-      <c r="T38">
-        <v>0</v>
-      </c>
-      <c r="U38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:21">
+      <c r="W38">
+        <v>0</v>
+      </c>
+      <c r="X38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:24">
       <c r="A39">
         <v>37</v>
       </c>
@@ -4469,12 +5083,6 @@
       <c r="M39">
         <v>0</v>
       </c>
-      <c r="N39">
-        <v>0</v>
-      </c>
-      <c r="O39">
-        <v>0</v>
-      </c>
       <c r="P39">
         <v>0</v>
       </c>
@@ -4493,8 +5101,17 @@
       <c r="U39">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:21" ht="37.5">
+      <c r="V39">
+        <v>0</v>
+      </c>
+      <c r="W39">
+        <v>0</v>
+      </c>
+      <c r="X39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24" ht="37.5">
       <c r="A40">
         <v>38</v>
       </c>
@@ -4534,14 +5151,14 @@
       <c r="M40">
         <v>22</v>
       </c>
-      <c r="N40">
-        <v>0</v>
-      </c>
-      <c r="O40">
-        <v>0</v>
+      <c r="N40" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="O40" t="s">
+        <v>34</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -4558,8 +5175,17 @@
       <c r="U40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:21" ht="85.5" customHeight="1">
+      <c r="V40">
+        <v>0</v>
+      </c>
+      <c r="W40">
+        <v>0</v>
+      </c>
+      <c r="X40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24" ht="85.5" customHeight="1">
       <c r="A41">
         <v>39</v>
       </c>
@@ -4599,14 +5225,14 @@
       <c r="M41">
         <v>22</v>
       </c>
-      <c r="N41">
-        <v>0</v>
-      </c>
-      <c r="O41">
-        <v>0</v>
+      <c r="N41" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="O41" t="s">
+        <v>34</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -4623,8 +5249,17 @@
       <c r="U41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:21" ht="51.75" customHeight="1">
+      <c r="V41">
+        <v>0</v>
+      </c>
+      <c r="W41">
+        <v>0</v>
+      </c>
+      <c r="X41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:24" ht="51.75" customHeight="1">
       <c r="A42">
         <v>40</v>
       </c>
@@ -4664,14 +5299,14 @@
       <c r="M42">
         <v>22</v>
       </c>
-      <c r="N42">
-        <v>0</v>
-      </c>
-      <c r="O42">
-        <v>0</v>
+      <c r="N42" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="O42" t="s">
+        <v>34</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -4688,8 +5323,17 @@
       <c r="U42">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:21" ht="56.25">
+      <c r="V42">
+        <v>0</v>
+      </c>
+      <c r="W42">
+        <v>0</v>
+      </c>
+      <c r="X42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:24" ht="56.25">
       <c r="A43">
         <v>41</v>
       </c>
@@ -4729,14 +5373,14 @@
       <c r="M43">
         <v>22</v>
       </c>
-      <c r="N43">
-        <v>0</v>
-      </c>
-      <c r="O43">
-        <v>0</v>
+      <c r="N43" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="O43" t="s">
+        <v>34</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -4753,8 +5397,17 @@
       <c r="U43">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:21" ht="37.5">
+      <c r="V43">
+        <v>0</v>
+      </c>
+      <c r="W43">
+        <v>0</v>
+      </c>
+      <c r="X43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:24" ht="37.5">
       <c r="A44">
         <v>42</v>
       </c>
@@ -4794,32 +5447,41 @@
       <c r="M44">
         <v>22</v>
       </c>
-      <c r="N44">
-        <v>0</v>
-      </c>
-      <c r="O44">
-        <v>0</v>
+      <c r="N44" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="O44" t="s">
+        <v>34</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q44">
         <v>0</v>
       </c>
       <c r="R44">
+        <v>0</v>
+      </c>
+      <c r="S44">
+        <v>0</v>
+      </c>
+      <c r="T44">
+        <v>0</v>
+      </c>
+      <c r="U44">
         <v>2</v>
       </c>
-      <c r="S44">
+      <c r="V44">
         <v>10</v>
       </c>
-      <c r="T44">
-        <v>0</v>
-      </c>
-      <c r="U44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:21" ht="56.25">
+      <c r="W44">
+        <v>0</v>
+      </c>
+      <c r="X44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:24" ht="56.25">
       <c r="A45">
         <v>43</v>
       </c>
@@ -4859,32 +5521,41 @@
       <c r="M45">
         <v>22</v>
       </c>
-      <c r="N45">
-        <v>0</v>
-      </c>
-      <c r="O45">
-        <v>0</v>
+      <c r="N45" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="O45" t="s">
+        <v>34</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q45">
         <v>0</v>
       </c>
       <c r="R45">
+        <v>0</v>
+      </c>
+      <c r="S45">
+        <v>0</v>
+      </c>
+      <c r="T45">
+        <v>0</v>
+      </c>
+      <c r="U45">
         <v>2</v>
       </c>
-      <c r="S45">
+      <c r="V45">
         <v>11</v>
       </c>
-      <c r="T45">
-        <v>0</v>
-      </c>
-      <c r="U45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:21">
+      <c r="W45">
+        <v>0</v>
+      </c>
+      <c r="X45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:24">
       <c r="A46">
         <v>44</v>
       </c>
@@ -4924,14 +5595,14 @@
       <c r="M46">
         <v>22</v>
       </c>
-      <c r="N46">
-        <v>0</v>
-      </c>
-      <c r="O46">
-        <v>0</v>
+      <c r="N46" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="O46" t="s">
+        <v>34</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q46">
         <v>0</v>
@@ -4948,8 +5619,17 @@
       <c r="U46">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:21">
+      <c r="V46">
+        <v>0</v>
+      </c>
+      <c r="W46">
+        <v>0</v>
+      </c>
+      <c r="X46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:24">
       <c r="A47">
         <v>45</v>
       </c>
@@ -4989,32 +5669,41 @@
       <c r="M47">
         <v>22</v>
       </c>
-      <c r="N47">
-        <v>0</v>
-      </c>
-      <c r="O47">
-        <v>0</v>
+      <c r="N47" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="O47" t="s">
+        <v>34</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q47">
         <v>0</v>
       </c>
       <c r="R47">
+        <v>0</v>
+      </c>
+      <c r="S47">
+        <v>0</v>
+      </c>
+      <c r="T47">
+        <v>0</v>
+      </c>
+      <c r="U47">
         <v>3</v>
       </c>
-      <c r="S47">
+      <c r="V47">
         <v>12</v>
       </c>
-      <c r="T47">
-        <v>0</v>
-      </c>
-      <c r="U47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:21">
+      <c r="W47">
+        <v>0</v>
+      </c>
+      <c r="X47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:24">
       <c r="A48">
         <v>46</v>
       </c>
@@ -5054,32 +5743,41 @@
       <c r="M48">
         <v>22</v>
       </c>
-      <c r="N48">
-        <v>0</v>
-      </c>
-      <c r="O48">
-        <v>0</v>
+      <c r="N48" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="O48" t="s">
+        <v>34</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q48">
         <v>0</v>
       </c>
       <c r="R48">
+        <v>0</v>
+      </c>
+      <c r="S48">
+        <v>0</v>
+      </c>
+      <c r="T48">
+        <v>0</v>
+      </c>
+      <c r="U48">
         <v>2</v>
       </c>
-      <c r="S48">
+      <c r="V48">
         <v>13</v>
       </c>
-      <c r="T48">
-        <v>0</v>
-      </c>
-      <c r="U48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:21">
+      <c r="W48">
+        <v>0</v>
+      </c>
+      <c r="X48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:24" ht="37.5">
       <c r="A49">
         <v>47</v>
       </c>
@@ -5119,14 +5817,14 @@
       <c r="M49">
         <v>22</v>
       </c>
-      <c r="N49">
-        <v>0</v>
-      </c>
-      <c r="O49">
-        <v>0</v>
+      <c r="N49" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="O49" t="s">
+        <v>34</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -5143,8 +5841,17 @@
       <c r="U49">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:21" ht="37.5">
+      <c r="V49">
+        <v>0</v>
+      </c>
+      <c r="W49">
+        <v>0</v>
+      </c>
+      <c r="X49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:24" ht="56.25">
       <c r="A50">
         <v>48</v>
       </c>
@@ -5184,32 +5891,41 @@
       <c r="M50">
         <v>22</v>
       </c>
-      <c r="N50">
-        <v>0</v>
-      </c>
-      <c r="O50">
-        <v>0</v>
+      <c r="N50" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="O50" t="s">
+        <v>34</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q50">
         <v>0</v>
       </c>
       <c r="R50">
+        <v>0</v>
+      </c>
+      <c r="S50">
+        <v>0</v>
+      </c>
+      <c r="T50">
+        <v>0</v>
+      </c>
+      <c r="U50">
         <v>2</v>
       </c>
-      <c r="S50">
+      <c r="V50">
         <v>14</v>
       </c>
-      <c r="T50">
-        <v>0</v>
-      </c>
-      <c r="U50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:21" ht="37.5">
+      <c r="W50">
+        <v>0</v>
+      </c>
+      <c r="X50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:24" ht="37.5">
       <c r="A51">
         <v>49</v>
       </c>
@@ -5249,14 +5965,14 @@
       <c r="M51">
         <v>22</v>
       </c>
-      <c r="N51">
-        <v>0</v>
-      </c>
-      <c r="O51">
-        <v>0</v>
+      <c r="N51" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="O51" t="s">
+        <v>34</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -5273,8 +5989,17 @@
       <c r="U51">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:21">
+      <c r="V51">
+        <v>0</v>
+      </c>
+      <c r="W51">
+        <v>0</v>
+      </c>
+      <c r="X51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:24" ht="37.5">
       <c r="A52">
         <v>50</v>
       </c>
@@ -5314,14 +6039,14 @@
       <c r="M52">
         <v>22</v>
       </c>
-      <c r="N52">
-        <v>0</v>
-      </c>
-      <c r="O52">
-        <v>0</v>
+      <c r="N52" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="O52" t="s">
+        <v>357</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -5338,8 +6063,17 @@
       <c r="U52">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:21">
+      <c r="V52">
+        <v>0</v>
+      </c>
+      <c r="W52">
+        <v>0</v>
+      </c>
+      <c r="X52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:24">
       <c r="A53">
         <v>51</v>
       </c>
@@ -5379,14 +6113,14 @@
       <c r="M53">
         <v>22</v>
       </c>
-      <c r="N53">
-        <v>0</v>
-      </c>
-      <c r="O53">
-        <v>0</v>
+      <c r="N53" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="O53" t="s">
+        <v>34</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q53">
         <v>0</v>
@@ -5403,8 +6137,17 @@
       <c r="U53">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:21">
+      <c r="V53">
+        <v>0</v>
+      </c>
+      <c r="W53">
+        <v>0</v>
+      </c>
+      <c r="X53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:24">
       <c r="A54">
         <v>52</v>
       </c>
@@ -5444,14 +6187,14 @@
       <c r="M54">
         <v>22</v>
       </c>
-      <c r="N54">
-        <v>0</v>
-      </c>
-      <c r="O54">
-        <v>0</v>
+      <c r="N54" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="O54" t="s">
+        <v>357</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -5468,8 +6211,17 @@
       <c r="U54">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:21">
+      <c r="V54">
+        <v>0</v>
+      </c>
+      <c r="W54">
+        <v>0</v>
+      </c>
+      <c r="X54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:24">
       <c r="A55">
         <v>53</v>
       </c>
@@ -5509,14 +6261,14 @@
       <c r="M55">
         <v>22</v>
       </c>
-      <c r="N55">
-        <v>0</v>
-      </c>
-      <c r="O55">
-        <v>0</v>
+      <c r="N55" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="O55" t="s">
+        <v>34</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -5533,8 +6285,17 @@
       <c r="U55">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:21" ht="37.5">
+      <c r="V55">
+        <v>0</v>
+      </c>
+      <c r="W55">
+        <v>0</v>
+      </c>
+      <c r="X55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:24" ht="37.5">
       <c r="A56">
         <v>54</v>
       </c>
@@ -5574,14 +6335,14 @@
       <c r="M56">
         <v>22</v>
       </c>
-      <c r="N56">
-        <v>0</v>
-      </c>
-      <c r="O56">
-        <v>0</v>
+      <c r="N56" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="O56" t="s">
+        <v>34</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -5598,8 +6359,17 @@
       <c r="U56">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:21">
+      <c r="V56">
+        <v>0</v>
+      </c>
+      <c r="W56">
+        <v>0</v>
+      </c>
+      <c r="X56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:24">
       <c r="A57">
         <v>55</v>
       </c>
@@ -5639,14 +6409,14 @@
       <c r="M57">
         <v>22</v>
       </c>
-      <c r="N57">
-        <v>0</v>
-      </c>
-      <c r="O57">
-        <v>0</v>
+      <c r="N57" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="O57" t="s">
+        <v>34</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -5663,8 +6433,17 @@
       <c r="U57">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:21" ht="37.5">
+      <c r="V57">
+        <v>0</v>
+      </c>
+      <c r="W57">
+        <v>0</v>
+      </c>
+      <c r="X57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:24" ht="37.5">
       <c r="A58">
         <v>56</v>
       </c>
@@ -5704,14 +6483,14 @@
       <c r="M58">
         <v>22</v>
       </c>
-      <c r="N58">
-        <v>0</v>
-      </c>
-      <c r="O58">
-        <v>0</v>
+      <c r="N58" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="O58" t="s">
+        <v>34</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -5728,8 +6507,17 @@
       <c r="U58">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:21">
+      <c r="V58">
+        <v>0</v>
+      </c>
+      <c r="W58">
+        <v>0</v>
+      </c>
+      <c r="X58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:24">
       <c r="A59">
         <v>57</v>
       </c>
@@ -5769,14 +6557,14 @@
       <c r="M59">
         <v>22</v>
       </c>
-      <c r="N59">
-        <v>0</v>
-      </c>
-      <c r="O59">
-        <v>0</v>
+      <c r="N59" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="O59" t="s">
+        <v>34</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -5793,8 +6581,17 @@
       <c r="U59">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:21">
+      <c r="V59">
+        <v>0</v>
+      </c>
+      <c r="W59">
+        <v>0</v>
+      </c>
+      <c r="X59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:24">
       <c r="A60">
         <v>58</v>
       </c>
@@ -5834,14 +6631,14 @@
       <c r="M60">
         <v>22</v>
       </c>
-      <c r="N60">
-        <v>0</v>
-      </c>
-      <c r="O60">
-        <v>0</v>
+      <c r="N60" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="O60" t="s">
+        <v>357</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -5858,8 +6655,17 @@
       <c r="U60">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:21" ht="37.5">
+      <c r="V60">
+        <v>0</v>
+      </c>
+      <c r="W60">
+        <v>0</v>
+      </c>
+      <c r="X60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:24" ht="37.5">
       <c r="A61">
         <v>59</v>
       </c>
@@ -5899,14 +6705,14 @@
       <c r="M61">
         <v>22</v>
       </c>
-      <c r="N61">
-        <v>0</v>
-      </c>
-      <c r="O61">
-        <v>0</v>
+      <c r="N61" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="O61" t="s">
+        <v>34</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q61">
         <v>0</v>
@@ -5923,8 +6729,17 @@
       <c r="U61">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:21">
+      <c r="V61">
+        <v>0</v>
+      </c>
+      <c r="W61">
+        <v>0</v>
+      </c>
+      <c r="X61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:24">
       <c r="A62">
         <v>60</v>
       </c>
@@ -5964,21 +6779,21 @@
       <c r="M62">
         <v>22</v>
       </c>
-      <c r="N62">
-        <v>0</v>
-      </c>
-      <c r="O62">
+      <c r="N62" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="O62" t="s">
+        <v>357</v>
+      </c>
+      <c r="P62">
+        <v>22</v>
+      </c>
+      <c r="Q62">
+        <v>0</v>
+      </c>
+      <c r="R62">
         <v>1</v>
       </c>
-      <c r="P62">
-        <v>0</v>
-      </c>
-      <c r="Q62">
-        <v>0</v>
-      </c>
-      <c r="R62">
-        <v>0</v>
-      </c>
       <c r="S62">
         <v>0</v>
       </c>
@@ -5988,8 +6803,17 @@
       <c r="U62">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:21">
+      <c r="V62">
+        <v>0</v>
+      </c>
+      <c r="W62">
+        <v>0</v>
+      </c>
+      <c r="X62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:24">
       <c r="A63">
         <v>61</v>
       </c>
@@ -6029,14 +6853,14 @@
       <c r="M63">
         <v>22</v>
       </c>
-      <c r="N63">
-        <v>0</v>
-      </c>
-      <c r="O63">
-        <v>0</v>
+      <c r="N63" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="O63" t="s">
+        <v>34</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -6053,8 +6877,17 @@
       <c r="U63">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:21">
+      <c r="V63">
+        <v>0</v>
+      </c>
+      <c r="W63">
+        <v>0</v>
+      </c>
+      <c r="X63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:24">
       <c r="A64">
         <v>62</v>
       </c>
@@ -6094,14 +6927,14 @@
       <c r="M64">
         <v>22</v>
       </c>
-      <c r="N64">
-        <v>0</v>
-      </c>
-      <c r="O64">
-        <v>0</v>
+      <c r="N64" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="O64" t="s">
+        <v>357</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -6118,8 +6951,17 @@
       <c r="U64">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:21">
+      <c r="V64">
+        <v>0</v>
+      </c>
+      <c r="W64">
+        <v>0</v>
+      </c>
+      <c r="X64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:24">
       <c r="A65">
         <v>63</v>
       </c>
@@ -6159,14 +7001,14 @@
       <c r="M65">
         <v>22</v>
       </c>
-      <c r="N65">
-        <v>0</v>
-      </c>
-      <c r="O65">
-        <v>0</v>
+      <c r="N65" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="O65" t="s">
+        <v>34</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q65">
         <v>0</v>
@@ -6183,8 +7025,17 @@
       <c r="U65">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:21">
+      <c r="V65">
+        <v>0</v>
+      </c>
+      <c r="W65">
+        <v>0</v>
+      </c>
+      <c r="X65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:24">
       <c r="A66">
         <v>64</v>
       </c>
@@ -6224,14 +7075,14 @@
       <c r="M66">
         <v>22</v>
       </c>
-      <c r="N66">
-        <v>0</v>
-      </c>
-      <c r="O66">
-        <v>0</v>
+      <c r="N66" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="O66" t="s">
+        <v>34</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -6248,8 +7099,17 @@
       <c r="U66">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:21">
+      <c r="V66">
+        <v>0</v>
+      </c>
+      <c r="W66">
+        <v>0</v>
+      </c>
+      <c r="X66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:24">
       <c r="A67">
         <v>65</v>
       </c>
@@ -6289,14 +7149,14 @@
       <c r="M67">
         <v>22</v>
       </c>
-      <c r="N67">
-        <v>0</v>
-      </c>
-      <c r="O67">
-        <v>0</v>
+      <c r="N67" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="O67" t="s">
+        <v>34</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -6313,8 +7173,17 @@
       <c r="U67">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:21">
+      <c r="V67">
+        <v>0</v>
+      </c>
+      <c r="W67">
+        <v>0</v>
+      </c>
+      <c r="X67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:24">
       <c r="A68">
         <v>66</v>
       </c>
@@ -6354,14 +7223,14 @@
       <c r="M68">
         <v>22</v>
       </c>
-      <c r="N68">
-        <v>0</v>
-      </c>
-      <c r="O68">
-        <v>0</v>
+      <c r="N68" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="O68" t="s">
+        <v>357</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q68">
         <v>0</v>
@@ -6378,8 +7247,17 @@
       <c r="U68">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="1:21" ht="37.5">
+      <c r="V68">
+        <v>0</v>
+      </c>
+      <c r="W68">
+        <v>0</v>
+      </c>
+      <c r="X68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:24" ht="37.5">
       <c r="A69">
         <v>67</v>
       </c>
@@ -6419,14 +7297,14 @@
       <c r="M69">
         <v>22</v>
       </c>
-      <c r="N69">
-        <v>0</v>
-      </c>
-      <c r="O69">
-        <v>0</v>
+      <c r="N69" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="O69" t="s">
+        <v>34</v>
       </c>
       <c r="P69">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -6443,8 +7321,17 @@
       <c r="U69">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:21">
+      <c r="V69">
+        <v>0</v>
+      </c>
+      <c r="W69">
+        <v>0</v>
+      </c>
+      <c r="X69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:24">
       <c r="A70">
         <v>68</v>
       </c>
@@ -6484,14 +7371,14 @@
       <c r="M70">
         <v>22</v>
       </c>
-      <c r="N70">
-        <v>0</v>
-      </c>
-      <c r="O70">
-        <v>0</v>
+      <c r="N70" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="O70" t="s">
+        <v>34</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -6503,13 +7390,22 @@
         <v>0</v>
       </c>
       <c r="T70">
+        <v>0</v>
+      </c>
+      <c r="U70">
+        <v>0</v>
+      </c>
+      <c r="V70">
+        <v>0</v>
+      </c>
+      <c r="W70">
         <v>1</v>
       </c>
-      <c r="U70">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:21">
+      <c r="X70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:24">
       <c r="A71">
         <v>69</v>
       </c>
@@ -6529,12 +7425,6 @@
       <c r="M71">
         <v>0</v>
       </c>
-      <c r="N71">
-        <v>0</v>
-      </c>
-      <c r="O71">
-        <v>0</v>
-      </c>
       <c r="P71">
         <v>0</v>
       </c>
@@ -6553,8 +7443,17 @@
       <c r="U71">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:21">
+      <c r="V71">
+        <v>0</v>
+      </c>
+      <c r="W71">
+        <v>0</v>
+      </c>
+      <c r="X71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:24" ht="37.5">
       <c r="A72">
         <v>70</v>
       </c>
@@ -6594,32 +7493,41 @@
       <c r="M72">
         <v>22</v>
       </c>
-      <c r="N72">
-        <v>0</v>
-      </c>
-      <c r="O72">
-        <v>0</v>
+      <c r="N72" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="O72" t="s">
+        <v>357</v>
       </c>
       <c r="P72">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q72">
+        <v>0</v>
+      </c>
+      <c r="R72">
+        <v>0</v>
+      </c>
+      <c r="S72">
+        <v>0</v>
+      </c>
+      <c r="T72">
         <v>1</v>
       </c>
-      <c r="R72">
-        <v>0</v>
-      </c>
-      <c r="S72">
-        <v>0</v>
-      </c>
-      <c r="T72">
-        <v>0</v>
-      </c>
       <c r="U72">
+        <v>0</v>
+      </c>
+      <c r="V72">
+        <v>0</v>
+      </c>
+      <c r="W72">
+        <v>0</v>
+      </c>
+      <c r="X72">
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:21">
+    <row r="73" spans="1:24">
       <c r="A73">
         <v>71</v>
       </c>
@@ -6659,14 +7567,14 @@
       <c r="M73">
         <v>22</v>
       </c>
-      <c r="N73">
-        <v>0</v>
-      </c>
-      <c r="O73">
-        <v>0</v>
+      <c r="N73" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="O73" t="s">
+        <v>357</v>
       </c>
       <c r="P73">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q73">
         <v>0</v>
@@ -6683,8 +7591,17 @@
       <c r="U73">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:21">
+      <c r="V73">
+        <v>0</v>
+      </c>
+      <c r="W73">
+        <v>0</v>
+      </c>
+      <c r="X73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:24">
       <c r="A74">
         <v>72</v>
       </c>
@@ -6724,14 +7641,14 @@
       <c r="M74">
         <v>22</v>
       </c>
-      <c r="N74">
-        <v>0</v>
-      </c>
-      <c r="O74">
-        <v>0</v>
+      <c r="N74" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="O74" t="s">
+        <v>357</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -6748,8 +7665,17 @@
       <c r="U74">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="1:21">
+      <c r="V74">
+        <v>0</v>
+      </c>
+      <c r="W74">
+        <v>0</v>
+      </c>
+      <c r="X74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:24">
       <c r="A75">
         <v>73</v>
       </c>
@@ -6789,14 +7715,14 @@
       <c r="M75">
         <v>22</v>
       </c>
-      <c r="N75">
-        <v>0</v>
-      </c>
-      <c r="O75">
-        <v>0</v>
+      <c r="N75" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="O75" t="s">
+        <v>34</v>
       </c>
       <c r="P75">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -6813,8 +7739,17 @@
       <c r="U75">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:21">
+      <c r="V75">
+        <v>0</v>
+      </c>
+      <c r="W75">
+        <v>0</v>
+      </c>
+      <c r="X75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:24">
       <c r="A76">
         <v>74</v>
       </c>
@@ -6854,14 +7789,14 @@
       <c r="M76">
         <v>22</v>
       </c>
-      <c r="N76">
-        <v>0</v>
-      </c>
-      <c r="O76">
-        <v>0</v>
+      <c r="N76" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="O76" t="s">
+        <v>34</v>
       </c>
       <c r="P76">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -6878,8 +7813,17 @@
       <c r="U76">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:21">
+      <c r="V76">
+        <v>0</v>
+      </c>
+      <c r="W76">
+        <v>0</v>
+      </c>
+      <c r="X76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:24">
       <c r="A77">
         <v>75</v>
       </c>
@@ -6919,14 +7863,14 @@
       <c r="M77">
         <v>22</v>
       </c>
-      <c r="N77">
-        <v>0</v>
-      </c>
-      <c r="O77">
-        <v>0</v>
+      <c r="N77" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="O77" t="s">
+        <v>357</v>
       </c>
       <c r="P77">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q77">
         <v>0</v>
@@ -6943,8 +7887,17 @@
       <c r="U77">
         <v>0</v>
       </c>
-    </row>
-    <row r="78" spans="1:21" ht="37.5">
+      <c r="V77">
+        <v>0</v>
+      </c>
+      <c r="W77">
+        <v>0</v>
+      </c>
+      <c r="X77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:24" ht="37.5">
       <c r="A78">
         <v>76</v>
       </c>
@@ -6984,14 +7937,14 @@
       <c r="M78">
         <v>22</v>
       </c>
-      <c r="N78">
-        <v>0</v>
-      </c>
-      <c r="O78">
-        <v>0</v>
+      <c r="N78" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="O78" t="s">
+        <v>357</v>
       </c>
       <c r="P78">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q78">
         <v>0</v>
@@ -7008,8 +7961,17 @@
       <c r="U78">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="1:21">
+      <c r="V78">
+        <v>0</v>
+      </c>
+      <c r="W78">
+        <v>0</v>
+      </c>
+      <c r="X78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:24">
       <c r="A79">
         <v>77</v>
       </c>
@@ -7049,14 +8011,14 @@
       <c r="M79">
         <v>22</v>
       </c>
-      <c r="N79">
-        <v>0</v>
-      </c>
-      <c r="O79">
-        <v>0</v>
+      <c r="N79" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="O79" t="s">
+        <v>34</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q79">
         <v>0</v>
@@ -7073,8 +8035,17 @@
       <c r="U79">
         <v>0</v>
       </c>
-    </row>
-    <row r="80" spans="1:21">
+      <c r="V79">
+        <v>0</v>
+      </c>
+      <c r="W79">
+        <v>0</v>
+      </c>
+      <c r="X79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:24">
       <c r="A80">
         <v>78</v>
       </c>
@@ -7114,14 +8085,14 @@
       <c r="M80">
         <v>22</v>
       </c>
-      <c r="N80">
-        <v>0</v>
-      </c>
-      <c r="O80">
-        <v>0</v>
+      <c r="N80" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="O80" t="s">
+        <v>357</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q80">
         <v>0</v>
@@ -7138,8 +8109,17 @@
       <c r="U80">
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="1:21" ht="37.5">
+      <c r="V80">
+        <v>0</v>
+      </c>
+      <c r="W80">
+        <v>0</v>
+      </c>
+      <c r="X80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:24" ht="37.5">
       <c r="A81">
         <v>79</v>
       </c>
@@ -7179,14 +8159,14 @@
       <c r="M81">
         <v>22</v>
       </c>
-      <c r="N81">
-        <v>0</v>
-      </c>
-      <c r="O81">
-        <v>0</v>
+      <c r="N81" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="O81" t="s">
+        <v>34</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -7203,8 +8183,17 @@
       <c r="U81">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="1:21">
+      <c r="V81">
+        <v>0</v>
+      </c>
+      <c r="W81">
+        <v>0</v>
+      </c>
+      <c r="X81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:24">
       <c r="A82">
         <v>80</v>
       </c>
@@ -7244,14 +8233,14 @@
       <c r="M82">
         <v>22</v>
       </c>
-      <c r="N82">
-        <v>0</v>
-      </c>
-      <c r="O82">
-        <v>0</v>
+      <c r="N82" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="O82" t="s">
+        <v>357</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q82">
         <v>0</v>
@@ -7268,8 +8257,17 @@
       <c r="U82">
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="1:21" ht="37.5">
+      <c r="V82">
+        <v>0</v>
+      </c>
+      <c r="W82">
+        <v>0</v>
+      </c>
+      <c r="X82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:24" ht="37.5">
       <c r="A83">
         <v>81</v>
       </c>
@@ -7309,14 +8307,14 @@
       <c r="M83">
         <v>22</v>
       </c>
-      <c r="N83">
-        <v>0</v>
-      </c>
-      <c r="O83">
-        <v>0</v>
+      <c r="N83" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="O83" t="s">
+        <v>34</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q83">
         <v>0</v>
@@ -7333,8 +8331,17 @@
       <c r="U83">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:21">
+      <c r="V83">
+        <v>0</v>
+      </c>
+      <c r="W83">
+        <v>0</v>
+      </c>
+      <c r="X83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:24">
       <c r="A84">
         <v>82</v>
       </c>
@@ -7374,14 +8381,14 @@
       <c r="M84">
         <v>22</v>
       </c>
-      <c r="N84">
-        <v>0</v>
-      </c>
-      <c r="O84">
-        <v>0</v>
+      <c r="N84" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="O84" t="s">
+        <v>357</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q84">
         <v>0</v>
@@ -7398,8 +8405,17 @@
       <c r="U84">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:21">
+      <c r="V84">
+        <v>0</v>
+      </c>
+      <c r="W84">
+        <v>0</v>
+      </c>
+      <c r="X84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:24">
       <c r="A85">
         <v>83</v>
       </c>
@@ -7439,14 +8455,14 @@
       <c r="M85">
         <v>22</v>
       </c>
-      <c r="N85">
-        <v>0</v>
-      </c>
-      <c r="O85">
-        <v>0</v>
+      <c r="N85" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="O85" t="s">
+        <v>34</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q85">
         <v>0</v>
@@ -7463,8 +8479,17 @@
       <c r="U85">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="1:21">
+      <c r="V85">
+        <v>0</v>
+      </c>
+      <c r="W85">
+        <v>0</v>
+      </c>
+      <c r="X85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:24">
       <c r="A86">
         <v>84</v>
       </c>
@@ -7504,14 +8529,14 @@
       <c r="M86">
         <v>22</v>
       </c>
-      <c r="N86">
-        <v>0</v>
-      </c>
-      <c r="O86">
-        <v>0</v>
+      <c r="N86" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="O86" t="s">
+        <v>357</v>
       </c>
       <c r="P86">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q86">
         <v>0</v>
@@ -7528,8 +8553,17 @@
       <c r="U86">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="1:21">
+      <c r="V86">
+        <v>0</v>
+      </c>
+      <c r="W86">
+        <v>0</v>
+      </c>
+      <c r="X86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:24">
       <c r="A87">
         <v>85</v>
       </c>
@@ -7569,14 +8603,14 @@
       <c r="M87">
         <v>22</v>
       </c>
-      <c r="N87">
-        <v>0</v>
-      </c>
-      <c r="O87">
-        <v>0</v>
+      <c r="N87" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="O87" t="s">
+        <v>34</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -7593,8 +8627,17 @@
       <c r="U87">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="1:21">
+      <c r="V87">
+        <v>0</v>
+      </c>
+      <c r="W87">
+        <v>0</v>
+      </c>
+      <c r="X87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:24">
       <c r="A88">
         <v>86</v>
       </c>
@@ -7634,32 +8677,41 @@
       <c r="M88">
         <v>22</v>
       </c>
-      <c r="N88">
-        <v>0</v>
-      </c>
-      <c r="O88">
+      <c r="N88" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="O88" t="s">
+        <v>34</v>
+      </c>
+      <c r="P88">
+        <v>22</v>
+      </c>
+      <c r="Q88">
+        <v>0</v>
+      </c>
+      <c r="R88">
         <v>2</v>
       </c>
-      <c r="P88">
-        <v>0</v>
-      </c>
-      <c r="Q88">
+      <c r="S88">
+        <v>0</v>
+      </c>
+      <c r="T88">
         <v>1</v>
       </c>
-      <c r="R88">
-        <v>0</v>
-      </c>
-      <c r="S88">
-        <v>0</v>
-      </c>
-      <c r="T88">
-        <v>0</v>
-      </c>
       <c r="U88">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="1:21">
+      <c r="V88">
+        <v>0</v>
+      </c>
+      <c r="W88">
+        <v>0</v>
+      </c>
+      <c r="X88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:24">
       <c r="A89">
         <v>87</v>
       </c>
@@ -7699,14 +8751,14 @@
       <c r="M89">
         <v>22</v>
       </c>
-      <c r="N89">
-        <v>0</v>
-      </c>
-      <c r="O89">
-        <v>0</v>
+      <c r="N89" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="O89" t="s">
+        <v>34</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -7723,8 +8775,17 @@
       <c r="U89">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="1:21">
+      <c r="V89">
+        <v>0</v>
+      </c>
+      <c r="W89">
+        <v>0</v>
+      </c>
+      <c r="X89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:24">
       <c r="A90">
         <v>88</v>
       </c>
@@ -7732,15 +8793,6 @@
       <c r="I90" s="5"/>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
-      <c r="N90">
-        <v>0</v>
-      </c>
-      <c r="O90">
-        <v>0</v>
-      </c>
-      <c r="P90">
-        <v>0</v>
-      </c>
       <c r="Q90">
         <v>0</v>
       </c>
@@ -7756,8 +8808,17 @@
       <c r="U90">
         <v>0</v>
       </c>
-    </row>
-    <row r="91" spans="1:21">
+      <c r="V90">
+        <v>0</v>
+      </c>
+      <c r="W90">
+        <v>0</v>
+      </c>
+      <c r="X90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:24">
       <c r="A91">
         <v>89</v>
       </c>
@@ -7766,7 +8827,7 @@
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
     </row>
-    <row r="92" spans="1:21">
+    <row r="92" spans="1:24">
       <c r="A92">
         <v>90</v>
       </c>
@@ -7775,7 +8836,7 @@
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
     </row>
-    <row r="93" spans="1:21">
+    <row r="93" spans="1:24">
       <c r="A93">
         <v>91</v>
       </c>
@@ -7784,7 +8845,7 @@
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
     </row>
-    <row r="94" spans="1:21">
+    <row r="94" spans="1:24">
       <c r="A94">
         <v>92</v>
       </c>
@@ -7793,7 +8854,7 @@
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
     </row>
-    <row r="95" spans="1:21">
+    <row r="95" spans="1:24">
       <c r="A95">
         <v>93</v>
       </c>
@@ -7802,7 +8863,7 @@
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
     </row>
-    <row r="96" spans="1:21">
+    <row r="96" spans="1:24">
       <c r="A96">
         <v>94</v>
       </c>

--- a/Assets/Originals/Excels/Talk/TalkMessage.xlsx
+++ b/Assets/Originals/Excels/Talk/TalkMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Talk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D5B1138-752E-4C0C-A903-BED3F796DF88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{825BB9C3-9BE8-4E42-8787-FF86C8FA5E8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1046" uniqueCount="524">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -1886,6 +1886,278 @@
   </si>
   <si>
     <t>pero sigamos esforzándonos, If. Cuento contigo.</t>
+  </si>
+  <si>
+    <t>messagePortuguese</t>
+  </si>
+  <si>
+    <t>speakerNamePortuguese</t>
+  </si>
+  <si>
+    <t>messageSizePortuguese</t>
+  </si>
+  <si>
+    <t>Onde... onde eu estou...?</t>
+  </si>
+  <si>
+    <t>Você</t>
+  </si>
+  <si>
+    <t>Parece que você acordou.</t>
+  </si>
+  <si>
+    <t>Meu nome é Kaname.
+Sou o seu guia em «Mumei».</t>
+  </si>
+  <si>
+    <t>Mumei?</t>
+  </si>
+  <si>
+    <t>É o enorme labirinto que existe neste mundo eterno.</t>
+  </si>
+  <si>
+    <t>Você morreu no mundo dos vivos depois de cometer um «pecado».
+Todos os que cometem um pecado são aprisionados neste Mumei.</t>
+  </si>
+  <si>
+    <t>Ou seja, você também é um deles.</t>
+  </si>
+  <si>
+    <t>Um pecado?</t>
+  </si>
+  <si>
+    <t>Isso mesmo. Um pecado muito, muito grave.</t>
+  </si>
+  <si>
+    <t>Aliás, você se lembra do seu próprio nome?</t>
+  </si>
+  <si>
+    <t>Bem... meu nome é...</t>
+  </si>
+  <si>
+    <t>Hã...? Não consigo lembrar...</t>
+  </si>
+  <si>
+    <t>É natural que você não se lembre.</t>
+  </si>
+  <si>
+    <t>Porque seu nome foi descartado antes de você chegar a este labirinto.</t>
+  </si>
+  <si>
+    <t>Meu nome... descartado...?</t>
+  </si>
+  <si>
+    <t>Como assim?</t>
+  </si>
+  <si>
+    <t>Quem tem o nome descartado no mundo eterno
+nunca mais consegue se lembrar dele.</t>
+  </si>
+  <si>
+    <t>Hã...?</t>
+  </si>
+  <si>
+    <t>E aqueles que não conseguem se lembrar do nome...</t>
+  </si>
+  <si>
+    <t>...vagarão para sempre por este labirinto,
+sofrendo todo tipo de dor.</t>
+  </si>
+  <si>
+    <t>Mais cedo ou mais tarde, você também vai acabar assim.</t>
+  </si>
+  <si>
+    <t>Não... isso é muito cruel...</t>
+  </si>
+  <si>
+    <t>Por quê...?</t>
+  </si>
+  <si>
+    <t>Porque pecadores não precisam de nome.</t>
+  </si>
+  <si>
+    <t>Mas fique tranquilo(a).</t>
+  </si>
+  <si>
+    <t>Se você conseguir se lembrar do pecado que cometeu no mundo dos vivos e escapar deste labirinto,
+eu te direi qual é o seu nome.</t>
+  </si>
+  <si>
+    <t>Assim, você não vai sofrer
+nem vagar sem rumo.</t>
+  </si>
+  <si>
+    <t>...Você quer escapar daqui?</t>
+  </si>
+  <si>
+    <t>...Eu quero escapar.</t>
+  </si>
+  <si>
+    <t>Mas... como posso escapar?</t>
+  </si>
+  <si>
+    <t>...Existe uma maneira.</t>
+  </si>
+  <si>
+    <t>Consiste em enfrentar e superar a provação que vou te propor.</t>
+  </si>
+  <si>
+    <t>Se conseguir isso, você poderá escapar.</t>
+  </si>
+  <si>
+    <t>...Você aceita a minha provação?</t>
+  </si>
+  <si>
+    <t>...Eu aceito.</t>
+  </si>
+  <si>
+    <t>...Entendido.
+Então vou explicar do que se trata a provação.</t>
+  </si>
+  <si>
+    <t>Para superar a provação,
+você precisa cumprir duas condições.</t>
+  </si>
+  <si>
+    <t>Primeira: escapar deste labirinto.
+Segunda: se lembrar do pecado que cometeu no mundo dos vivos.</t>
+  </si>
+  <si>
+    <t>Vou explicar como escapar deste labirinto.</t>
+  </si>
+  <si>
+    <t>Para escapar, você precisa encontrar os «Documentos» e os «Itens Misteriosos»
+espalhados por todos os cantos deste labirinto.</t>
+  </si>
+  <si>
+    <t>Primeiro, consiga um Documento.
+Tente abrir a gaveta na sua frente.</t>
+  </si>
+  <si>
+    <t>Confira o conteúdo do Documento que você acabou de pegar.</t>
+  </si>
+  <si>
+    <t>Em seguida, consiga um Item Misterioso.</t>
+  </si>
+  <si>
+    <t>Abra as duas gavetas na sua frente.</t>
+  </si>
+  <si>
+    <t>Examine o Item Misterioso que você acabou de pegar.</t>
+  </si>
+  <si>
+    <t>Por fim, toque na «Esfera Azul do Julgamento» que está ao fundo.</t>
+  </si>
+  <si>
+    <t>Escolha o Item Misterioso
+que tenha uma relação profunda com o conteúdo do Documento.</t>
+  </si>
+  <si>
+    <t>Isso encerra a explicação sobre a provação.
+Alguma pergunta?</t>
+  </si>
+  <si>
+    <t>Hã? Você não vai me explicar nada sobre o pecado que cometi?</t>
+  </si>
+  <si>
+    <t>Não.</t>
+  </si>
+  <si>
+    <t>Não me venha com «hã».</t>
+  </si>
+  <si>
+    <t>Se você realmente acha que fez algo errado,
+deveria conseguir se lembrar do seu pecado imediatamente.</t>
+  </si>
+  <si>
+    <t>Por isso, a explicação termina aqui.</t>
+  </si>
+  <si>
+    <t>Além disso, como não ter nome é inconveniente,
+vou te chamar provisoriamente de «If».</t>
+  </si>
+  <si>
+    <t>Tudo bem assim, não é?</t>
+  </si>
+  <si>
+    <t>Hã... s-sim...</t>
+  </si>
+  <si>
+    <t>Por último, há um aviso sobre este labirinto.</t>
+  </si>
+  <si>
+    <t>Um aviso?</t>
+  </si>
+  <si>
+    <t>Nunca deixe que os «Errantes» te capturem.</t>
+  </si>
+  <si>
+    <t>Errantes?</t>
+  </si>
+  <si>
+    <t>São os monstros que espreitam em Mumei.</t>
+  </si>
+  <si>
+    <t>If, de qualquer forma, não deixe aquele monstro te capturar.</t>
+  </si>
+  <si>
+    <t>Entendeu?</t>
+  </si>
+  <si>
+    <t>...S-sim...</t>
+  </si>
+  <si>
+    <t>Muito bem, a provação vai começar agora.
+Siga pelo corredor atrás de você.</t>
+  </si>
+  <si>
+    <t>If, estou torcendo para que você consiga superar a provação.</t>
+  </si>
+  <si>
+    <t>...Com isso... finalmente... poderei escapar deste labirinto...</t>
+  </si>
+  <si>
+    <t>Hã...? O que... é isso...?</t>
+  </si>
+  <si>
+    <t>Por que o labirinto ainda continua?!</t>
+  </si>
+  <si>
+    <t>Não é óbvio?</t>
+  </si>
+  <si>
+    <t>Porque você ainda não escapou do labirinto.</t>
+  </si>
+  <si>
+    <t>...Como assim eu não escapei?</t>
+  </si>
+  <si>
+    <t>Eu recolhi todos os Documentos e Itens Misteriosos direitinho!</t>
+  </si>
+  <si>
+    <t>Por acaso você achou que era só isso?</t>
+  </si>
+  <si>
+    <t>Também há Documentos e Itens Misteriosos
+em outras áreas.</t>
+  </si>
+  <si>
+    <t>Não pode ser...</t>
+  </si>
+  <si>
+    <t>Além disso, você também ainda não se lembrou do pecado que cometeu, não é?</t>
+  </si>
+  <si>
+    <t>Por isso a provação ainda não terminou.</t>
+  </si>
+  <si>
+    <t>O verdadeiro terror de Mumei começa agora, If.</t>
+  </si>
+  <si>
+    <t>Eu sei que vai ser difícil,</t>
+  </si>
+  <si>
+    <t>mas vamos continuar em frente, If. Conto com você.</t>
   </si>
 </sst>
 </file>
@@ -2254,7 +2526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X102"/>
+  <dimension ref="A1:AA102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="123.375" style="2" customWidth="1"/>
@@ -2271,16 +2543,19 @@
     <col min="14" max="14" width="47.125" customWidth="1"/>
     <col min="15" max="15" width="17.625" customWidth="1"/>
     <col min="16" max="16" width="19.75" customWidth="1"/>
-    <col min="17" max="17" width="27.75" customWidth="1"/>
-    <col min="18" max="18" width="22.5" customWidth="1"/>
-    <col min="19" max="19" width="13.625" customWidth="1"/>
-    <col min="21" max="21" width="17.125" customWidth="1"/>
-    <col min="22" max="22" width="28.125" customWidth="1"/>
-    <col min="23" max="23" width="13.125" customWidth="1"/>
-    <col min="24" max="24" width="16" customWidth="1"/>
+    <col min="17" max="17" width="47.125" customWidth="1"/>
+    <col min="18" max="18" width="17.625" customWidth="1"/>
+    <col min="19" max="19" width="29.375" customWidth="1"/>
+    <col min="20" max="20" width="27.75" customWidth="1"/>
+    <col min="21" max="21" width="22.5" customWidth="1"/>
+    <col min="22" max="22" width="13.625" customWidth="1"/>
+    <col min="24" max="24" width="17.125" customWidth="1"/>
+    <col min="25" max="25" width="28.125" customWidth="1"/>
+    <col min="26" max="26" width="13.125" customWidth="1"/>
+    <col min="27" max="27" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="37.5">
+    <row r="1" spans="1:27" ht="37.5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2330,31 +2605,40 @@
         <v>355</v>
       </c>
       <c r="Q1" t="s">
+        <v>439</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="S1" t="s">
+        <v>441</v>
+      </c>
+      <c r="T1" t="s">
         <v>21</v>
       </c>
-      <c r="R1" t="s">
-        <v>22</v>
-      </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
+        <v>22</v>
+      </c>
+      <c r="V1" t="s">
         <v>23</v>
       </c>
-      <c r="T1" t="s">
+      <c r="W1" t="s">
         <v>24</v>
       </c>
-      <c r="U1" t="s">
+      <c r="X1" t="s">
         <v>25</v>
       </c>
-      <c r="V1" t="s">
+      <c r="Y1" t="s">
         <v>26</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Z1" t="s">
         <v>27</v>
       </c>
-      <c r="X1" t="s">
+      <c r="AA1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:27">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2377,12 +2661,6 @@
       <c r="P2">
         <v>0</v>
       </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
       <c r="S2">
         <v>0</v>
       </c>
@@ -2401,8 +2679,17 @@
       <c r="X2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:24">
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2451,14 +2738,14 @@
       <c r="P3">
         <v>22</v>
       </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
+      <c r="Q3" t="s">
+        <v>442</v>
+      </c>
+      <c r="R3" t="s">
+        <v>443</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -2475,8 +2762,17 @@
       <c r="X3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:24">
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2525,32 +2821,41 @@
       <c r="P4">
         <v>22</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" t="s">
+        <v>444</v>
+      </c>
+      <c r="R4" t="s">
+        <v>192</v>
+      </c>
+      <c r="S4">
+        <v>22</v>
+      </c>
+      <c r="T4">
         <v>1</v>
       </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
         <v>3</v>
       </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
-      <c r="W4">
-        <v>0</v>
-      </c>
       <c r="X4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:24" ht="37.5">
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" ht="37.5">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2599,14 +2904,14 @@
       <c r="P5">
         <v>22</v>
       </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
+      <c r="Q5" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="R5" t="s">
+        <v>34</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -2623,8 +2928,17 @@
       <c r="X5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:24">
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2673,14 +2987,14 @@
       <c r="P6">
         <v>22</v>
       </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
+      <c r="Q6" t="s">
+        <v>446</v>
+      </c>
+      <c r="R6" t="s">
+        <v>443</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -2697,8 +3011,17 @@
       <c r="X6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:24">
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2747,14 +3070,14 @@
       <c r="P7">
         <v>22</v>
       </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
+      <c r="Q7" t="s">
+        <v>447</v>
+      </c>
+      <c r="R7" t="s">
+        <v>34</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -2771,8 +3094,17 @@
       <c r="X7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" ht="75">
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" ht="75">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2821,14 +3153,14 @@
       <c r="P8">
         <v>22</v>
       </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
+      <c r="Q8" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="R8" t="s">
+        <v>34</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -2845,8 +3177,17 @@
       <c r="X8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:24">
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27">
       <c r="A9">
         <v>7</v>
       </c>
@@ -2895,14 +3236,14 @@
       <c r="P9">
         <v>22</v>
       </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
+      <c r="Q9" t="s">
+        <v>449</v>
+      </c>
+      <c r="R9" t="s">
+        <v>34</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -2919,8 +3260,17 @@
       <c r="X9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:24">
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27">
       <c r="A10">
         <v>8</v>
       </c>
@@ -2969,14 +3319,14 @@
       <c r="P10">
         <v>22</v>
       </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
+      <c r="Q10" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="R10" t="s">
+        <v>443</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T10">
         <v>0</v>
@@ -2993,8 +3343,17 @@
       <c r="X10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:24">
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27">
       <c r="A11">
         <v>9</v>
       </c>
@@ -3043,14 +3402,14 @@
       <c r="P11">
         <v>22</v>
       </c>
-      <c r="Q11">
-        <v>0</v>
-      </c>
-      <c r="R11">
-        <v>0</v>
+      <c r="Q11" t="s">
+        <v>451</v>
+      </c>
+      <c r="R11" t="s">
+        <v>34</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T11">
         <v>0</v>
@@ -3067,8 +3426,17 @@
       <c r="X11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:24">
+      <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27">
       <c r="A12">
         <v>10</v>
       </c>
@@ -3117,14 +3485,14 @@
       <c r="P12">
         <v>22</v>
       </c>
-      <c r="Q12">
-        <v>0</v>
-      </c>
-      <c r="R12">
-        <v>0</v>
+      <c r="Q12" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="R12" t="s">
+        <v>34</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T12">
         <v>0</v>
@@ -3141,8 +3509,17 @@
       <c r="X12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:24">
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27">
       <c r="A13">
         <v>11</v>
       </c>
@@ -3191,21 +3568,21 @@
       <c r="P13">
         <v>22</v>
       </c>
-      <c r="Q13">
-        <v>0</v>
-      </c>
-      <c r="R13">
+      <c r="Q13" t="s">
+        <v>453</v>
+      </c>
+      <c r="R13" t="s">
+        <v>443</v>
+      </c>
+      <c r="S13">
+        <v>22</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
         <v>1</v>
       </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>0</v>
-      </c>
       <c r="V13">
         <v>0</v>
       </c>
@@ -3215,8 +3592,17 @@
       <c r="X13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24">
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27">
       <c r="A14">
         <v>12</v>
       </c>
@@ -3265,14 +3651,14 @@
       <c r="P14">
         <v>22</v>
       </c>
-      <c r="Q14">
-        <v>0</v>
-      </c>
-      <c r="R14">
-        <v>0</v>
+      <c r="Q14" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="R14" t="s">
+        <v>443</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T14">
         <v>0</v>
@@ -3289,8 +3675,17 @@
       <c r="X14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24">
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27">
       <c r="A15">
         <v>13</v>
       </c>
@@ -3339,14 +3734,14 @@
       <c r="P15">
         <v>22</v>
       </c>
-      <c r="Q15">
-        <v>0</v>
-      </c>
-      <c r="R15">
-        <v>0</v>
+      <c r="Q15" t="s">
+        <v>455</v>
+      </c>
+      <c r="R15" t="s">
+        <v>34</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T15">
         <v>0</v>
@@ -3363,8 +3758,17 @@
       <c r="X15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" ht="37.5">
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" ht="37.5">
       <c r="A16">
         <v>14</v>
       </c>
@@ -3413,14 +3817,14 @@
       <c r="P16">
         <v>22</v>
       </c>
-      <c r="Q16">
-        <v>0</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
+      <c r="Q16" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="R16" t="s">
+        <v>34</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T16">
         <v>0</v>
@@ -3437,8 +3841,17 @@
       <c r="X16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:24">
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27">
       <c r="A17">
         <v>15</v>
       </c>
@@ -3487,14 +3900,14 @@
       <c r="P17">
         <v>22</v>
       </c>
-      <c r="Q17">
-        <v>0</v>
-      </c>
-      <c r="R17">
-        <v>0</v>
+      <c r="Q17" t="s">
+        <v>457</v>
+      </c>
+      <c r="R17" t="s">
+        <v>443</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T17">
         <v>0</v>
@@ -3511,8 +3924,17 @@
       <c r="X17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:24">
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27">
       <c r="A18">
         <v>16</v>
       </c>
@@ -3561,14 +3983,14 @@
       <c r="P18">
         <v>22</v>
       </c>
-      <c r="Q18">
-        <v>0</v>
-      </c>
-      <c r="R18">
-        <v>0</v>
+      <c r="Q18" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="R18" t="s">
+        <v>443</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T18">
         <v>0</v>
@@ -3585,8 +4007,17 @@
       <c r="X18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:24" ht="56.25">
+      <c r="Y18">
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" ht="56.25">
       <c r="A19">
         <v>17</v>
       </c>
@@ -3635,14 +4066,14 @@
       <c r="P19">
         <v>22</v>
       </c>
-      <c r="Q19">
-        <v>0</v>
-      </c>
-      <c r="R19">
-        <v>0</v>
+      <c r="Q19" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="R19" t="s">
+        <v>34</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T19">
         <v>0</v>
@@ -3659,8 +4090,17 @@
       <c r="X19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:24">
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27">
       <c r="A20">
         <v>18</v>
       </c>
@@ -3709,14 +4149,14 @@
       <c r="P20">
         <v>22</v>
       </c>
-      <c r="Q20">
-        <v>0</v>
-      </c>
-      <c r="R20">
-        <v>0</v>
+      <c r="Q20" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="R20" t="s">
+        <v>443</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T20">
         <v>0</v>
@@ -3733,8 +4173,17 @@
       <c r="X20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:24">
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27">
       <c r="A21">
         <v>19</v>
       </c>
@@ -3780,21 +4229,21 @@
       <c r="P21">
         <v>22</v>
       </c>
-      <c r="Q21">
-        <v>0</v>
-      </c>
-      <c r="R21">
+      <c r="Q21" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="R21" t="s">
+        <v>34</v>
+      </c>
+      <c r="S21">
+        <v>22</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
         <v>1</v>
       </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="T21">
-        <v>0</v>
-      </c>
-      <c r="U21">
-        <v>0</v>
-      </c>
       <c r="V21">
         <v>0</v>
       </c>
@@ -3804,8 +4253,17 @@
       <c r="X21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:24" ht="37.5">
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27" ht="37.5">
       <c r="A22">
         <v>20</v>
       </c>
@@ -3854,14 +4312,14 @@
       <c r="P22">
         <v>22</v>
       </c>
-      <c r="Q22">
-        <v>0</v>
-      </c>
-      <c r="R22">
-        <v>0</v>
+      <c r="Q22" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="R22" t="s">
+        <v>34</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T22">
         <v>0</v>
@@ -3878,8 +4336,17 @@
       <c r="X22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:24">
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27" ht="37.5">
       <c r="A23">
         <v>21</v>
       </c>
@@ -3928,14 +4395,14 @@
       <c r="P23">
         <v>22</v>
       </c>
-      <c r="Q23">
-        <v>0</v>
-      </c>
-      <c r="R23">
-        <v>0</v>
+      <c r="Q23" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="R23" t="s">
+        <v>34</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T23">
         <v>0</v>
@@ -3952,8 +4419,17 @@
       <c r="X23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:24">
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27">
       <c r="A24">
         <v>22</v>
       </c>
@@ -4002,14 +4478,14 @@
       <c r="P24">
         <v>22</v>
       </c>
-      <c r="Q24">
-        <v>0</v>
-      </c>
-      <c r="R24">
-        <v>0</v>
+      <c r="Q24" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="R24" t="s">
+        <v>443</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T24">
         <v>0</v>
@@ -4026,8 +4502,17 @@
       <c r="X24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:24">
+      <c r="Y24">
+        <v>0</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+      <c r="AA24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27">
       <c r="A25">
         <v>23</v>
       </c>
@@ -4076,14 +4561,14 @@
       <c r="P25">
         <v>22</v>
       </c>
-      <c r="Q25">
-        <v>0</v>
-      </c>
-      <c r="R25">
-        <v>0</v>
+      <c r="Q25" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="R25" t="s">
+        <v>443</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T25">
         <v>0</v>
@@ -4100,8 +4585,17 @@
       <c r="X25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:24">
+      <c r="Y25">
+        <v>0</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27">
       <c r="A26">
         <v>24</v>
       </c>
@@ -4150,14 +4644,14 @@
       <c r="P26">
         <v>22</v>
       </c>
-      <c r="Q26">
-        <v>0</v>
-      </c>
-      <c r="R26">
-        <v>0</v>
+      <c r="Q26" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="R26" t="s">
+        <v>34</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T26">
         <v>0</v>
@@ -4174,8 +4668,17 @@
       <c r="X26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:24">
+      <c r="Y26">
+        <v>0</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+      <c r="AA26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27">
       <c r="A27">
         <v>25</v>
       </c>
@@ -4224,14 +4727,14 @@
       <c r="P27">
         <v>22</v>
       </c>
-      <c r="Q27">
-        <v>0</v>
-      </c>
-      <c r="R27">
-        <v>0</v>
+      <c r="Q27" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="R27" t="s">
+        <v>34</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T27">
         <v>0</v>
@@ -4248,8 +4751,17 @@
       <c r="X27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:24" ht="56.25">
+      <c r="Y27">
+        <v>0</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+      <c r="AA27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27" ht="56.25">
       <c r="A28">
         <v>26</v>
       </c>
@@ -4298,14 +4810,14 @@
       <c r="P28">
         <v>22</v>
       </c>
-      <c r="Q28">
-        <v>0</v>
-      </c>
-      <c r="R28">
-        <v>0</v>
+      <c r="Q28" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="R28" t="s">
+        <v>34</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T28">
         <v>0</v>
@@ -4322,8 +4834,17 @@
       <c r="X28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:24" ht="37.5">
+      <c r="Y28">
+        <v>0</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27" ht="37.5">
       <c r="A29">
         <v>27</v>
       </c>
@@ -4372,32 +4893,41 @@
       <c r="P29">
         <v>22</v>
       </c>
-      <c r="Q29">
-        <v>0</v>
-      </c>
-      <c r="R29">
-        <v>0</v>
+      <c r="Q29" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="R29" t="s">
+        <v>34</v>
       </c>
       <c r="S29">
+        <v>22</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>0</v>
+      </c>
+      <c r="V29">
         <v>1</v>
       </c>
-      <c r="T29">
+      <c r="W29">
         <v>1</v>
       </c>
-      <c r="U29">
-        <v>0</v>
-      </c>
-      <c r="V29">
-        <v>0</v>
-      </c>
-      <c r="W29">
-        <v>0</v>
-      </c>
       <c r="X29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:24">
+      <c r="Y29">
+        <v>0</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+      <c r="AA29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:27">
       <c r="A30">
         <v>28</v>
       </c>
@@ -4446,14 +4976,14 @@
       <c r="P30">
         <v>22</v>
       </c>
-      <c r="Q30">
-        <v>0</v>
-      </c>
-      <c r="R30">
-        <v>0</v>
+      <c r="Q30" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="R30" t="s">
+        <v>34</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T30">
         <v>0</v>
@@ -4470,8 +5000,17 @@
       <c r="X30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:24">
+      <c r="Y30">
+        <v>0</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+      <c r="AA30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:27">
       <c r="A31">
         <v>29</v>
       </c>
@@ -4520,14 +5059,14 @@
       <c r="P31">
         <v>22</v>
       </c>
-      <c r="Q31">
-        <v>0</v>
-      </c>
-      <c r="R31">
-        <v>0</v>
+      <c r="Q31" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="R31" t="s">
+        <v>443</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T31">
         <v>0</v>
@@ -4544,8 +5083,17 @@
       <c r="X31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:24">
+      <c r="Y31">
+        <v>0</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+      <c r="AA31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:27">
       <c r="A32">
         <v>30</v>
       </c>
@@ -4594,14 +5142,14 @@
       <c r="P32">
         <v>22</v>
       </c>
-      <c r="Q32">
-        <v>0</v>
-      </c>
-      <c r="R32">
-        <v>0</v>
+      <c r="Q32" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="R32" t="s">
+        <v>443</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T32">
         <v>0</v>
@@ -4618,8 +5166,17 @@
       <c r="X32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:24">
+      <c r="Y32">
+        <v>0</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+      <c r="AA32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:27">
       <c r="A33">
         <v>31</v>
       </c>
@@ -4668,14 +5225,14 @@
       <c r="P33">
         <v>22</v>
       </c>
-      <c r="Q33">
-        <v>0</v>
-      </c>
-      <c r="R33">
-        <v>0</v>
+      <c r="Q33" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="R33" t="s">
+        <v>34</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T33">
         <v>0</v>
@@ -4692,8 +5249,17 @@
       <c r="X33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:24">
+      <c r="Y33">
+        <v>0</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+      <c r="AA33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:27" ht="37.5">
       <c r="A34">
         <v>32</v>
       </c>
@@ -4742,14 +5308,14 @@
       <c r="P34">
         <v>22</v>
       </c>
-      <c r="Q34">
-        <v>0</v>
-      </c>
-      <c r="R34">
-        <v>0</v>
+      <c r="Q34" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="R34" t="s">
+        <v>34</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T34">
         <v>0</v>
@@ -4766,8 +5332,17 @@
       <c r="X34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:24">
+      <c r="Y34">
+        <v>0</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+      <c r="AA34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:27">
       <c r="A35">
         <v>33</v>
       </c>
@@ -4816,32 +5391,41 @@
       <c r="P35">
         <v>22</v>
       </c>
-      <c r="Q35">
-        <v>0</v>
-      </c>
-      <c r="R35">
-        <v>0</v>
+      <c r="Q35" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="R35" t="s">
+        <v>34</v>
       </c>
       <c r="S35">
+        <v>22</v>
+      </c>
+      <c r="T35">
+        <v>0</v>
+      </c>
+      <c r="U35">
+        <v>0</v>
+      </c>
+      <c r="V35">
         <v>1</v>
       </c>
-      <c r="T35">
+      <c r="W35">
         <v>1</v>
       </c>
-      <c r="U35">
-        <v>0</v>
-      </c>
-      <c r="V35">
-        <v>0</v>
-      </c>
-      <c r="W35">
-        <v>0</v>
-      </c>
       <c r="X35">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:24">
+      <c r="Y35">
+        <v>0</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+      <c r="AA35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:27">
       <c r="A36">
         <v>34</v>
       </c>
@@ -4890,14 +5474,14 @@
       <c r="P36">
         <v>22</v>
       </c>
-      <c r="Q36">
-        <v>0</v>
-      </c>
-      <c r="R36">
-        <v>0</v>
+      <c r="Q36" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="R36" t="s">
+        <v>34</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T36">
         <v>0</v>
@@ -4914,8 +5498,17 @@
       <c r="X36">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:24">
+      <c r="Y36">
+        <v>0</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+      <c r="AA36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:27">
       <c r="A37">
         <v>35</v>
       </c>
@@ -4964,14 +5557,14 @@
       <c r="P37">
         <v>22</v>
       </c>
-      <c r="Q37">
-        <v>0</v>
-      </c>
-      <c r="R37">
-        <v>0</v>
+      <c r="Q37" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="R37" t="s">
+        <v>443</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T37">
         <v>0</v>
@@ -4988,8 +5581,17 @@
       <c r="X37">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:24" ht="37.5">
+      <c r="Y37">
+        <v>0</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+      <c r="AA37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:27" ht="37.5">
       <c r="A38">
         <v>36</v>
       </c>
@@ -5038,32 +5640,41 @@
       <c r="P38">
         <v>22</v>
       </c>
-      <c r="Q38">
-        <v>0</v>
-      </c>
-      <c r="R38">
-        <v>0</v>
+      <c r="Q38" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="R38" t="s">
+        <v>34</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T38">
         <v>0</v>
       </c>
       <c r="U38">
+        <v>0</v>
+      </c>
+      <c r="V38">
+        <v>0</v>
+      </c>
+      <c r="W38">
+        <v>0</v>
+      </c>
+      <c r="X38">
         <v>1</v>
       </c>
-      <c r="V38">
+      <c r="Y38">
         <v>9</v>
       </c>
-      <c r="W38">
-        <v>0</v>
-      </c>
-      <c r="X38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:24">
+      <c r="Z38">
+        <v>0</v>
+      </c>
+      <c r="AA38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:27">
       <c r="A39">
         <v>37</v>
       </c>
@@ -5086,12 +5697,6 @@
       <c r="P39">
         <v>0</v>
       </c>
-      <c r="Q39">
-        <v>0</v>
-      </c>
-      <c r="R39">
-        <v>0</v>
-      </c>
       <c r="S39">
         <v>0</v>
       </c>
@@ -5110,8 +5715,17 @@
       <c r="X39">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:24" ht="37.5">
+      <c r="Y39">
+        <v>0</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+      <c r="AA39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:27" ht="37.5">
       <c r="A40">
         <v>38</v>
       </c>
@@ -5160,14 +5774,14 @@
       <c r="P40">
         <v>22</v>
       </c>
-      <c r="Q40">
-        <v>0</v>
-      </c>
-      <c r="R40">
-        <v>0</v>
+      <c r="Q40" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="R40" t="s">
+        <v>34</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T40">
         <v>0</v>
@@ -5184,8 +5798,17 @@
       <c r="X40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:24" ht="85.5" customHeight="1">
+      <c r="Y40">
+        <v>0</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+      <c r="AA40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:27" ht="85.5" customHeight="1">
       <c r="A41">
         <v>39</v>
       </c>
@@ -5234,14 +5857,14 @@
       <c r="P41">
         <v>22</v>
       </c>
-      <c r="Q41">
-        <v>0</v>
-      </c>
-      <c r="R41">
-        <v>0</v>
+      <c r="Q41" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="R41" t="s">
+        <v>34</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T41">
         <v>0</v>
@@ -5258,8 +5881,17 @@
       <c r="X41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:24" ht="51.75" customHeight="1">
+      <c r="Y41">
+        <v>0</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+      <c r="AA41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:27" ht="51.75" customHeight="1">
       <c r="A42">
         <v>40</v>
       </c>
@@ -5308,14 +5940,14 @@
       <c r="P42">
         <v>22</v>
       </c>
-      <c r="Q42">
-        <v>0</v>
-      </c>
-      <c r="R42">
-        <v>0</v>
+      <c r="Q42" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="R42" t="s">
+        <v>34</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T42">
         <v>0</v>
@@ -5332,8 +5964,17 @@
       <c r="X42">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:24" ht="56.25">
+      <c r="Y42">
+        <v>0</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+      <c r="AA42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:27" ht="56.25">
       <c r="A43">
         <v>41</v>
       </c>
@@ -5382,14 +6023,14 @@
       <c r="P43">
         <v>22</v>
       </c>
-      <c r="Q43">
-        <v>0</v>
-      </c>
-      <c r="R43">
-        <v>0</v>
+      <c r="Q43" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="R43" t="s">
+        <v>34</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T43">
         <v>0</v>
@@ -5406,8 +6047,17 @@
       <c r="X43">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:24" ht="37.5">
+      <c r="Y43">
+        <v>0</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+      <c r="AA43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:27" ht="37.5">
       <c r="A44">
         <v>42</v>
       </c>
@@ -5456,32 +6106,41 @@
       <c r="P44">
         <v>22</v>
       </c>
-      <c r="Q44">
-        <v>0</v>
-      </c>
-      <c r="R44">
-        <v>0</v>
+      <c r="Q44" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="R44" t="s">
+        <v>34</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T44">
         <v>0</v>
       </c>
       <c r="U44">
+        <v>0</v>
+      </c>
+      <c r="V44">
+        <v>0</v>
+      </c>
+      <c r="W44">
+        <v>0</v>
+      </c>
+      <c r="X44">
         <v>2</v>
       </c>
-      <c r="V44">
+      <c r="Y44">
         <v>10</v>
       </c>
-      <c r="W44">
-        <v>0</v>
-      </c>
-      <c r="X44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:24" ht="56.25">
+      <c r="Z44">
+        <v>0</v>
+      </c>
+      <c r="AA44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:27" ht="56.25">
       <c r="A45">
         <v>43</v>
       </c>
@@ -5530,32 +6189,41 @@
       <c r="P45">
         <v>22</v>
       </c>
-      <c r="Q45">
-        <v>0</v>
-      </c>
-      <c r="R45">
-        <v>0</v>
+      <c r="Q45" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="R45" t="s">
+        <v>34</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T45">
         <v>0</v>
       </c>
       <c r="U45">
+        <v>0</v>
+      </c>
+      <c r="V45">
+        <v>0</v>
+      </c>
+      <c r="W45">
+        <v>0</v>
+      </c>
+      <c r="X45">
         <v>2</v>
       </c>
-      <c r="V45">
+      <c r="Y45">
         <v>11</v>
       </c>
-      <c r="W45">
-        <v>0</v>
-      </c>
-      <c r="X45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:24">
+      <c r="Z45">
+        <v>0</v>
+      </c>
+      <c r="AA45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:27">
       <c r="A46">
         <v>44</v>
       </c>
@@ -5604,14 +6272,14 @@
       <c r="P46">
         <v>22</v>
       </c>
-      <c r="Q46">
-        <v>0</v>
-      </c>
-      <c r="R46">
-        <v>0</v>
+      <c r="Q46" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="R46" t="s">
+        <v>34</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T46">
         <v>0</v>
@@ -5628,8 +6296,17 @@
       <c r="X46">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:24">
+      <c r="Y46">
+        <v>0</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+      <c r="AA46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:27">
       <c r="A47">
         <v>45</v>
       </c>
@@ -5678,32 +6355,41 @@
       <c r="P47">
         <v>22</v>
       </c>
-      <c r="Q47">
-        <v>0</v>
-      </c>
-      <c r="R47">
-        <v>0</v>
+      <c r="Q47" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="R47" t="s">
+        <v>34</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T47">
         <v>0</v>
       </c>
       <c r="U47">
+        <v>0</v>
+      </c>
+      <c r="V47">
+        <v>0</v>
+      </c>
+      <c r="W47">
+        <v>0</v>
+      </c>
+      <c r="X47">
         <v>3</v>
       </c>
-      <c r="V47">
+      <c r="Y47">
         <v>12</v>
       </c>
-      <c r="W47">
-        <v>0</v>
-      </c>
-      <c r="X47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:24">
+      <c r="Z47">
+        <v>0</v>
+      </c>
+      <c r="AA47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:27">
       <c r="A48">
         <v>46</v>
       </c>
@@ -5752,32 +6438,41 @@
       <c r="P48">
         <v>22</v>
       </c>
-      <c r="Q48">
-        <v>0</v>
-      </c>
-      <c r="R48">
-        <v>0</v>
+      <c r="Q48" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="R48" t="s">
+        <v>34</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T48">
         <v>0</v>
       </c>
       <c r="U48">
+        <v>0</v>
+      </c>
+      <c r="V48">
+        <v>0</v>
+      </c>
+      <c r="W48">
+        <v>0</v>
+      </c>
+      <c r="X48">
         <v>2</v>
       </c>
-      <c r="V48">
+      <c r="Y48">
         <v>13</v>
       </c>
-      <c r="W48">
-        <v>0</v>
-      </c>
-      <c r="X48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:24" ht="37.5">
+      <c r="Z48">
+        <v>0</v>
+      </c>
+      <c r="AA48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:27" ht="37.5">
       <c r="A49">
         <v>47</v>
       </c>
@@ -5826,14 +6521,14 @@
       <c r="P49">
         <v>22</v>
       </c>
-      <c r="Q49">
-        <v>0</v>
-      </c>
-      <c r="R49">
-        <v>0</v>
+      <c r="Q49" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="R49" t="s">
+        <v>34</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T49">
         <v>0</v>
@@ -5850,8 +6545,17 @@
       <c r="X49">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:24" ht="56.25">
+      <c r="Y49">
+        <v>0</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+      <c r="AA49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:27" ht="56.25">
       <c r="A50">
         <v>48</v>
       </c>
@@ -5900,32 +6604,41 @@
       <c r="P50">
         <v>22</v>
       </c>
-      <c r="Q50">
-        <v>0</v>
-      </c>
-      <c r="R50">
-        <v>0</v>
+      <c r="Q50" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="R50" t="s">
+        <v>34</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T50">
         <v>0</v>
       </c>
       <c r="U50">
+        <v>0</v>
+      </c>
+      <c r="V50">
+        <v>0</v>
+      </c>
+      <c r="W50">
+        <v>0</v>
+      </c>
+      <c r="X50">
         <v>2</v>
       </c>
-      <c r="V50">
+      <c r="Y50">
         <v>14</v>
       </c>
-      <c r="W50">
-        <v>0</v>
-      </c>
-      <c r="X50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:24" ht="37.5">
+      <c r="Z50">
+        <v>0</v>
+      </c>
+      <c r="AA50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:27" ht="37.5">
       <c r="A51">
         <v>49</v>
       </c>
@@ -5974,14 +6687,14 @@
       <c r="P51">
         <v>22</v>
       </c>
-      <c r="Q51">
-        <v>0</v>
-      </c>
-      <c r="R51">
-        <v>0</v>
+      <c r="Q51" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="R51" t="s">
+        <v>34</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T51">
         <v>0</v>
@@ -5998,8 +6711,17 @@
       <c r="X51">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:24" ht="37.5">
+      <c r="Y51">
+        <v>0</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+      <c r="AA51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:27" ht="37.5">
       <c r="A52">
         <v>50</v>
       </c>
@@ -6048,14 +6770,14 @@
       <c r="P52">
         <v>22</v>
       </c>
-      <c r="Q52">
-        <v>0</v>
-      </c>
-      <c r="R52">
-        <v>0</v>
+      <c r="Q52" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="R52" t="s">
+        <v>443</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T52">
         <v>0</v>
@@ -6072,8 +6794,17 @@
       <c r="X52">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:24">
+      <c r="Y52">
+        <v>0</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+      <c r="AA52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:27">
       <c r="A53">
         <v>51</v>
       </c>
@@ -6122,14 +6853,14 @@
       <c r="P53">
         <v>22</v>
       </c>
-      <c r="Q53">
-        <v>0</v>
-      </c>
-      <c r="R53">
-        <v>0</v>
+      <c r="Q53" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="R53" t="s">
+        <v>34</v>
       </c>
       <c r="S53">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T53">
         <v>0</v>
@@ -6146,8 +6877,17 @@
       <c r="X53">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:24">
+      <c r="Y53">
+        <v>0</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+      <c r="AA53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:27">
       <c r="A54">
         <v>52</v>
       </c>
@@ -6196,14 +6936,14 @@
       <c r="P54">
         <v>22</v>
       </c>
-      <c r="Q54">
-        <v>0</v>
-      </c>
-      <c r="R54">
-        <v>0</v>
+      <c r="Q54" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="R54" t="s">
+        <v>443</v>
       </c>
       <c r="S54">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T54">
         <v>0</v>
@@ -6220,8 +6960,17 @@
       <c r="X54">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:24">
+      <c r="Y54">
+        <v>0</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+      <c r="AA54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:27">
       <c r="A55">
         <v>53</v>
       </c>
@@ -6270,14 +7019,14 @@
       <c r="P55">
         <v>22</v>
       </c>
-      <c r="Q55">
-        <v>0</v>
-      </c>
-      <c r="R55">
-        <v>0</v>
+      <c r="Q55" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="R55" t="s">
+        <v>34</v>
       </c>
       <c r="S55">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T55">
         <v>0</v>
@@ -6294,8 +7043,17 @@
       <c r="X55">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:24" ht="37.5">
+      <c r="Y55">
+        <v>0</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+      <c r="AA55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:27" ht="56.25">
       <c r="A56">
         <v>54</v>
       </c>
@@ -6344,14 +7102,14 @@
       <c r="P56">
         <v>22</v>
       </c>
-      <c r="Q56">
-        <v>0</v>
-      </c>
-      <c r="R56">
-        <v>0</v>
+      <c r="Q56" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="R56" t="s">
+        <v>34</v>
       </c>
       <c r="S56">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T56">
         <v>0</v>
@@ -6368,8 +7126,17 @@
       <c r="X56">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:24">
+      <c r="Y56">
+        <v>0</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+      <c r="AA56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:27">
       <c r="A57">
         <v>55</v>
       </c>
@@ -6418,14 +7185,14 @@
       <c r="P57">
         <v>22</v>
       </c>
-      <c r="Q57">
-        <v>0</v>
-      </c>
-      <c r="R57">
-        <v>0</v>
+      <c r="Q57" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="R57" t="s">
+        <v>34</v>
       </c>
       <c r="S57">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T57">
         <v>0</v>
@@ -6442,8 +7209,17 @@
       <c r="X57">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:24" ht="37.5">
+      <c r="Y57">
+        <v>0</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+      <c r="AA57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:27" ht="37.5">
       <c r="A58">
         <v>56</v>
       </c>
@@ -6492,14 +7268,14 @@
       <c r="P58">
         <v>22</v>
       </c>
-      <c r="Q58">
-        <v>0</v>
-      </c>
-      <c r="R58">
-        <v>0</v>
+      <c r="Q58" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="R58" t="s">
+        <v>34</v>
       </c>
       <c r="S58">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T58">
         <v>0</v>
@@ -6516,8 +7292,17 @@
       <c r="X58">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:24">
+      <c r="Y58">
+        <v>0</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+      <c r="AA58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:27">
       <c r="A59">
         <v>57</v>
       </c>
@@ -6566,14 +7351,14 @@
       <c r="P59">
         <v>22</v>
       </c>
-      <c r="Q59">
-        <v>0</v>
-      </c>
-      <c r="R59">
-        <v>0</v>
+      <c r="Q59" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="R59" t="s">
+        <v>34</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T59">
         <v>0</v>
@@ -6590,8 +7375,17 @@
       <c r="X59">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:24">
+      <c r="Y59">
+        <v>0</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+      <c r="AA59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:27">
       <c r="A60">
         <v>58</v>
       </c>
@@ -6640,14 +7434,14 @@
       <c r="P60">
         <v>22</v>
       </c>
-      <c r="Q60">
-        <v>0</v>
-      </c>
-      <c r="R60">
-        <v>0</v>
+      <c r="Q60" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="R60" t="s">
+        <v>443</v>
       </c>
       <c r="S60">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T60">
         <v>0</v>
@@ -6664,8 +7458,17 @@
       <c r="X60">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:24" ht="37.5">
+      <c r="Y60">
+        <v>0</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+      <c r="AA60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:27" ht="37.5">
       <c r="A61">
         <v>59</v>
       </c>
@@ -6714,14 +7517,14 @@
       <c r="P61">
         <v>22</v>
       </c>
-      <c r="Q61">
-        <v>0</v>
-      </c>
-      <c r="R61">
-        <v>0</v>
+      <c r="Q61" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="R61" t="s">
+        <v>34</v>
       </c>
       <c r="S61">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T61">
         <v>0</v>
@@ -6738,8 +7541,17 @@
       <c r="X61">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:24">
+      <c r="Y61">
+        <v>0</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+      <c r="AA61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:27">
       <c r="A62">
         <v>60</v>
       </c>
@@ -6788,21 +7600,21 @@
       <c r="P62">
         <v>22</v>
       </c>
-      <c r="Q62">
-        <v>0</v>
-      </c>
-      <c r="R62">
+      <c r="Q62" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="R62" t="s">
+        <v>443</v>
+      </c>
+      <c r="S62">
+        <v>22</v>
+      </c>
+      <c r="T62">
+        <v>0</v>
+      </c>
+      <c r="U62">
         <v>1</v>
       </c>
-      <c r="S62">
-        <v>0</v>
-      </c>
-      <c r="T62">
-        <v>0</v>
-      </c>
-      <c r="U62">
-        <v>0</v>
-      </c>
       <c r="V62">
         <v>0</v>
       </c>
@@ -6812,8 +7624,17 @@
       <c r="X62">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:24">
+      <c r="Y62">
+        <v>0</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+      <c r="AA62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:27">
       <c r="A63">
         <v>61</v>
       </c>
@@ -6862,14 +7683,14 @@
       <c r="P63">
         <v>22</v>
       </c>
-      <c r="Q63">
-        <v>0</v>
-      </c>
-      <c r="R63">
-        <v>0</v>
+      <c r="Q63" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="R63" t="s">
+        <v>34</v>
       </c>
       <c r="S63">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T63">
         <v>0</v>
@@ -6886,8 +7707,17 @@
       <c r="X63">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:24">
+      <c r="Y63">
+        <v>0</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+      <c r="AA63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:27">
       <c r="A64">
         <v>62</v>
       </c>
@@ -6936,14 +7766,14 @@
       <c r="P64">
         <v>22</v>
       </c>
-      <c r="Q64">
-        <v>0</v>
-      </c>
-      <c r="R64">
-        <v>0</v>
+      <c r="Q64" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="R64" t="s">
+        <v>443</v>
       </c>
       <c r="S64">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T64">
         <v>0</v>
@@ -6960,8 +7790,17 @@
       <c r="X64">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:24">
+      <c r="Y64">
+        <v>0</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+      <c r="AA64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:27">
       <c r="A65">
         <v>63</v>
       </c>
@@ -7010,14 +7849,14 @@
       <c r="P65">
         <v>22</v>
       </c>
-      <c r="Q65">
-        <v>0</v>
-      </c>
-      <c r="R65">
-        <v>0</v>
+      <c r="Q65" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="R65" t="s">
+        <v>34</v>
       </c>
       <c r="S65">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T65">
         <v>0</v>
@@ -7034,8 +7873,17 @@
       <c r="X65">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:24">
+      <c r="Y65">
+        <v>0</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+      <c r="AA65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:27" ht="37.5">
       <c r="A66">
         <v>64</v>
       </c>
@@ -7084,14 +7932,14 @@
       <c r="P66">
         <v>22</v>
       </c>
-      <c r="Q66">
-        <v>0</v>
-      </c>
-      <c r="R66">
-        <v>0</v>
+      <c r="Q66" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="R66" t="s">
+        <v>34</v>
       </c>
       <c r="S66">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T66">
         <v>0</v>
@@ -7108,8 +7956,17 @@
       <c r="X66">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:24">
+      <c r="Y66">
+        <v>0</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+      <c r="AA66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:27">
       <c r="A67">
         <v>65</v>
       </c>
@@ -7158,14 +8015,14 @@
       <c r="P67">
         <v>22</v>
       </c>
-      <c r="Q67">
-        <v>0</v>
-      </c>
-      <c r="R67">
-        <v>0</v>
+      <c r="Q67" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="R67" t="s">
+        <v>34</v>
       </c>
       <c r="S67">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T67">
         <v>0</v>
@@ -7182,8 +8039,17 @@
       <c r="X67">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:24">
+      <c r="Y67">
+        <v>0</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+      <c r="AA67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:27">
       <c r="A68">
         <v>66</v>
       </c>
@@ -7232,14 +8098,14 @@
       <c r="P68">
         <v>22</v>
       </c>
-      <c r="Q68">
-        <v>0</v>
-      </c>
-      <c r="R68">
-        <v>0</v>
+      <c r="Q68" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="R68" t="s">
+        <v>443</v>
       </c>
       <c r="S68">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T68">
         <v>0</v>
@@ -7256,8 +8122,17 @@
       <c r="X68">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="1:24" ht="37.5">
+      <c r="Y68">
+        <v>0</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+      <c r="AA68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:27" ht="37.5">
       <c r="A69">
         <v>67</v>
       </c>
@@ -7306,14 +8181,14 @@
       <c r="P69">
         <v>22</v>
       </c>
-      <c r="Q69">
-        <v>0</v>
-      </c>
-      <c r="R69">
-        <v>0</v>
+      <c r="Q69" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="R69" t="s">
+        <v>34</v>
       </c>
       <c r="S69">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T69">
         <v>0</v>
@@ -7330,8 +8205,17 @@
       <c r="X69">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:24">
+      <c r="Y69">
+        <v>0</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+      <c r="AA69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:27" ht="37.5">
       <c r="A70">
         <v>68</v>
       </c>
@@ -7380,14 +8264,14 @@
       <c r="P70">
         <v>22</v>
       </c>
-      <c r="Q70">
-        <v>0</v>
-      </c>
-      <c r="R70">
-        <v>0</v>
+      <c r="Q70" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="R70" t="s">
+        <v>34</v>
       </c>
       <c r="S70">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T70">
         <v>0</v>
@@ -7399,13 +8283,22 @@
         <v>0</v>
       </c>
       <c r="W70">
+        <v>0</v>
+      </c>
+      <c r="X70">
+        <v>0</v>
+      </c>
+      <c r="Y70">
+        <v>0</v>
+      </c>
+      <c r="Z70">
         <v>1</v>
       </c>
-      <c r="X70">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:24">
+      <c r="AA70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:27">
       <c r="A71">
         <v>69</v>
       </c>
@@ -7428,12 +8321,6 @@
       <c r="P71">
         <v>0</v>
       </c>
-      <c r="Q71">
-        <v>0</v>
-      </c>
-      <c r="R71">
-        <v>0</v>
-      </c>
       <c r="S71">
         <v>0</v>
       </c>
@@ -7452,8 +8339,17 @@
       <c r="X71">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:24" ht="37.5">
+      <c r="Y71">
+        <v>0</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+      <c r="AA71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:27" ht="37.5">
       <c r="A72">
         <v>70</v>
       </c>
@@ -7502,32 +8398,41 @@
       <c r="P72">
         <v>22</v>
       </c>
-      <c r="Q72">
-        <v>0</v>
-      </c>
-      <c r="R72">
-        <v>0</v>
+      <c r="Q72" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="R72" t="s">
+        <v>443</v>
       </c>
       <c r="S72">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T72">
+        <v>0</v>
+      </c>
+      <c r="U72">
+        <v>0</v>
+      </c>
+      <c r="V72">
+        <v>0</v>
+      </c>
+      <c r="W72">
         <v>1</v>
       </c>
-      <c r="U72">
-        <v>0</v>
-      </c>
-      <c r="V72">
-        <v>0</v>
-      </c>
-      <c r="W72">
-        <v>0</v>
-      </c>
       <c r="X72">
+        <v>0</v>
+      </c>
+      <c r="Y72">
+        <v>0</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+      <c r="AA72">
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:24">
+    <row r="73" spans="1:27">
       <c r="A73">
         <v>71</v>
       </c>
@@ -7576,14 +8481,14 @@
       <c r="P73">
         <v>22</v>
       </c>
-      <c r="Q73">
-        <v>0</v>
-      </c>
-      <c r="R73">
-        <v>0</v>
+      <c r="Q73" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="R73" t="s">
+        <v>443</v>
       </c>
       <c r="S73">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T73">
         <v>0</v>
@@ -7600,8 +8505,17 @@
       <c r="X73">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:24">
+      <c r="Y73">
+        <v>0</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+      <c r="AA73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:27">
       <c r="A74">
         <v>72</v>
       </c>
@@ -7650,14 +8564,14 @@
       <c r="P74">
         <v>22</v>
       </c>
-      <c r="Q74">
-        <v>0</v>
-      </c>
-      <c r="R74">
-        <v>0</v>
+      <c r="Q74" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="R74" t="s">
+        <v>443</v>
       </c>
       <c r="S74">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T74">
         <v>0</v>
@@ -7674,8 +8588,17 @@
       <c r="X74">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="1:24">
+      <c r="Y74">
+        <v>0</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+      <c r="AA74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:27">
       <c r="A75">
         <v>73</v>
       </c>
@@ -7724,14 +8647,14 @@
       <c r="P75">
         <v>22</v>
       </c>
-      <c r="Q75">
-        <v>0</v>
-      </c>
-      <c r="R75">
-        <v>0</v>
+      <c r="Q75" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="R75" t="s">
+        <v>34</v>
       </c>
       <c r="S75">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T75">
         <v>0</v>
@@ -7748,8 +8671,17 @@
       <c r="X75">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:24">
+      <c r="Y75">
+        <v>0</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+      <c r="AA75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:27">
       <c r="A76">
         <v>74</v>
       </c>
@@ -7798,14 +8730,14 @@
       <c r="P76">
         <v>22</v>
       </c>
-      <c r="Q76">
-        <v>0</v>
-      </c>
-      <c r="R76">
-        <v>0</v>
+      <c r="Q76" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="R76" t="s">
+        <v>34</v>
       </c>
       <c r="S76">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T76">
         <v>0</v>
@@ -7822,8 +8754,17 @@
       <c r="X76">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:24">
+      <c r="Y76">
+        <v>0</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+      <c r="AA76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:27">
       <c r="A77">
         <v>75</v>
       </c>
@@ -7872,14 +8813,14 @@
       <c r="P77">
         <v>22</v>
       </c>
-      <c r="Q77">
-        <v>0</v>
-      </c>
-      <c r="R77">
-        <v>0</v>
+      <c r="Q77" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="R77" t="s">
+        <v>443</v>
       </c>
       <c r="S77">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T77">
         <v>0</v>
@@ -7896,8 +8837,17 @@
       <c r="X77">
         <v>0</v>
       </c>
-    </row>
-    <row r="78" spans="1:24" ht="37.5">
+      <c r="Y77">
+        <v>0</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+      <c r="AA77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:27" ht="37.5">
       <c r="A78">
         <v>76</v>
       </c>
@@ -7946,14 +8896,14 @@
       <c r="P78">
         <v>22</v>
       </c>
-      <c r="Q78">
-        <v>0</v>
-      </c>
-      <c r="R78">
-        <v>0</v>
+      <c r="Q78" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="R78" t="s">
+        <v>443</v>
       </c>
       <c r="S78">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T78">
         <v>0</v>
@@ -7970,8 +8920,17 @@
       <c r="X78">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="1:24">
+      <c r="Y78">
+        <v>0</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+      <c r="AA78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:27">
       <c r="A79">
         <v>77</v>
       </c>
@@ -8020,14 +8979,14 @@
       <c r="P79">
         <v>22</v>
       </c>
-      <c r="Q79">
-        <v>0</v>
-      </c>
-      <c r="R79">
-        <v>0</v>
+      <c r="Q79" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="R79" t="s">
+        <v>34</v>
       </c>
       <c r="S79">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T79">
         <v>0</v>
@@ -8044,8 +9003,17 @@
       <c r="X79">
         <v>0</v>
       </c>
-    </row>
-    <row r="80" spans="1:24">
+      <c r="Y79">
+        <v>0</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+      <c r="AA79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:27">
       <c r="A80">
         <v>78</v>
       </c>
@@ -8094,14 +9062,14 @@
       <c r="P80">
         <v>22</v>
       </c>
-      <c r="Q80">
-        <v>0</v>
-      </c>
-      <c r="R80">
-        <v>0</v>
+      <c r="Q80" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="R80" t="s">
+        <v>443</v>
       </c>
       <c r="S80">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T80">
         <v>0</v>
@@ -8118,8 +9086,17 @@
       <c r="X80">
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="1:24" ht="37.5">
+      <c r="Y80">
+        <v>0</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+      <c r="AA80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:27" ht="37.5">
       <c r="A81">
         <v>79</v>
       </c>
@@ -8168,14 +9145,14 @@
       <c r="P81">
         <v>22</v>
       </c>
-      <c r="Q81">
-        <v>0</v>
-      </c>
-      <c r="R81">
-        <v>0</v>
+      <c r="Q81" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="R81" t="s">
+        <v>34</v>
       </c>
       <c r="S81">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T81">
         <v>0</v>
@@ -8192,8 +9169,17 @@
       <c r="X81">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="1:24">
+      <c r="Y81">
+        <v>0</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+      <c r="AA81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:27">
       <c r="A82">
         <v>80</v>
       </c>
@@ -8242,14 +9228,14 @@
       <c r="P82">
         <v>22</v>
       </c>
-      <c r="Q82">
-        <v>0</v>
-      </c>
-      <c r="R82">
-        <v>0</v>
+      <c r="Q82" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="R82" t="s">
+        <v>443</v>
       </c>
       <c r="S82">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T82">
         <v>0</v>
@@ -8266,8 +9252,17 @@
       <c r="X82">
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="1:24" ht="37.5">
+      <c r="Y82">
+        <v>0</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+      <c r="AA82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:27" ht="37.5">
       <c r="A83">
         <v>81</v>
       </c>
@@ -8316,14 +9311,14 @@
       <c r="P83">
         <v>22</v>
       </c>
-      <c r="Q83">
-        <v>0</v>
-      </c>
-      <c r="R83">
-        <v>0</v>
+      <c r="Q83" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="R83" t="s">
+        <v>34</v>
       </c>
       <c r="S83">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T83">
         <v>0</v>
@@ -8340,8 +9335,17 @@
       <c r="X83">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:24">
+      <c r="Y83">
+        <v>0</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+      <c r="AA83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:27">
       <c r="A84">
         <v>82</v>
       </c>
@@ -8390,14 +9394,14 @@
       <c r="P84">
         <v>22</v>
       </c>
-      <c r="Q84">
-        <v>0</v>
-      </c>
-      <c r="R84">
-        <v>0</v>
+      <c r="Q84" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="R84" t="s">
+        <v>443</v>
       </c>
       <c r="S84">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T84">
         <v>0</v>
@@ -8414,8 +9418,17 @@
       <c r="X84">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:24">
+      <c r="Y84">
+        <v>0</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+      <c r="AA84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:27">
       <c r="A85">
         <v>83</v>
       </c>
@@ -8464,14 +9477,14 @@
       <c r="P85">
         <v>22</v>
       </c>
-      <c r="Q85">
-        <v>0</v>
-      </c>
-      <c r="R85">
-        <v>0</v>
+      <c r="Q85" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="R85" t="s">
+        <v>34</v>
       </c>
       <c r="S85">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T85">
         <v>0</v>
@@ -8488,8 +9501,17 @@
       <c r="X85">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="1:24">
+      <c r="Y85">
+        <v>0</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+      <c r="AA85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:27">
       <c r="A86">
         <v>84</v>
       </c>
@@ -8538,14 +9560,14 @@
       <c r="P86">
         <v>22</v>
       </c>
-      <c r="Q86">
-        <v>0</v>
-      </c>
-      <c r="R86">
-        <v>0</v>
+      <c r="Q86" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="R86" t="s">
+        <v>443</v>
       </c>
       <c r="S86">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T86">
         <v>0</v>
@@ -8562,8 +9584,17 @@
       <c r="X86">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="1:24">
+      <c r="Y86">
+        <v>0</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+      <c r="AA86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:27">
       <c r="A87">
         <v>85</v>
       </c>
@@ -8612,14 +9643,14 @@
       <c r="P87">
         <v>22</v>
       </c>
-      <c r="Q87">
-        <v>0</v>
-      </c>
-      <c r="R87">
-        <v>0</v>
+      <c r="Q87" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="R87" t="s">
+        <v>34</v>
       </c>
       <c r="S87">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T87">
         <v>0</v>
@@ -8636,8 +9667,17 @@
       <c r="X87">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="1:24">
+      <c r="Y87">
+        <v>0</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+      <c r="AA87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:27">
       <c r="A88">
         <v>86</v>
       </c>
@@ -8686,32 +9726,41 @@
       <c r="P88">
         <v>22</v>
       </c>
-      <c r="Q88">
-        <v>0</v>
-      </c>
-      <c r="R88">
+      <c r="Q88" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="R88" t="s">
+        <v>34</v>
+      </c>
+      <c r="S88">
+        <v>22</v>
+      </c>
+      <c r="T88">
+        <v>0</v>
+      </c>
+      <c r="U88">
         <v>2</v>
       </c>
-      <c r="S88">
-        <v>0</v>
-      </c>
-      <c r="T88">
+      <c r="V88">
+        <v>0</v>
+      </c>
+      <c r="W88">
         <v>1</v>
       </c>
-      <c r="U88">
-        <v>0</v>
-      </c>
-      <c r="V88">
-        <v>0</v>
-      </c>
-      <c r="W88">
-        <v>0</v>
-      </c>
       <c r="X88">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="1:24">
+      <c r="Y88">
+        <v>0</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+      <c r="AA88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:27">
       <c r="A89">
         <v>87</v>
       </c>
@@ -8760,14 +9809,14 @@
       <c r="P89">
         <v>22</v>
       </c>
-      <c r="Q89">
-        <v>0</v>
-      </c>
-      <c r="R89">
-        <v>0</v>
+      <c r="Q89" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="R89" t="s">
+        <v>34</v>
       </c>
       <c r="S89">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T89">
         <v>0</v>
@@ -8784,8 +9833,17 @@
       <c r="X89">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="1:24">
+      <c r="Y89">
+        <v>0</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+      <c r="AA89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:27">
       <c r="A90">
         <v>88</v>
       </c>
@@ -8793,15 +9851,6 @@
       <c r="I90" s="5"/>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
-      <c r="Q90">
-        <v>0</v>
-      </c>
-      <c r="R90">
-        <v>0</v>
-      </c>
-      <c r="S90">
-        <v>0</v>
-      </c>
       <c r="T90">
         <v>0</v>
       </c>
@@ -8817,8 +9866,17 @@
       <c r="X90">
         <v>0</v>
       </c>
-    </row>
-    <row r="91" spans="1:24">
+      <c r="Y90">
+        <v>0</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+      <c r="AA90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:27">
       <c r="A91">
         <v>89</v>
       </c>
@@ -8827,7 +9885,7 @@
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
     </row>
-    <row r="92" spans="1:24">
+    <row r="92" spans="1:27">
       <c r="A92">
         <v>90</v>
       </c>
@@ -8836,7 +9894,7 @@
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
     </row>
-    <row r="93" spans="1:24">
+    <row r="93" spans="1:27">
       <c r="A93">
         <v>91</v>
       </c>
@@ -8845,7 +9903,7 @@
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
     </row>
-    <row r="94" spans="1:24">
+    <row r="94" spans="1:27">
       <c r="A94">
         <v>92</v>
       </c>
@@ -8854,7 +9912,7 @@
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
     </row>
-    <row r="95" spans="1:24">
+    <row r="95" spans="1:27">
       <c r="A95">
         <v>93</v>
       </c>
@@ -8863,7 +9921,7 @@
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
     </row>
-    <row r="96" spans="1:24">
+    <row r="96" spans="1:27">
       <c r="A96">
         <v>94</v>
       </c>

--- a/Assets/Originals/Excels/Talk/TalkMessage.xlsx
+++ b/Assets/Originals/Excels/Talk/TalkMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Talk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{825BB9C3-9BE8-4E42-8787-FF86C8FA5E8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE653196-7526-4785-BDA3-BD3FBE46A98C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1613,15 +1613,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>messageSpanish</t>
-  </si>
-  <si>
-    <t>speakerNameSpanish</t>
-  </si>
-  <si>
-    <t>messageSizeSpanish</t>
-  </si>
-  <si>
     <t>¿Dónde... dónde estoy...?</t>
   </si>
   <si>
@@ -1888,15 +1879,6 @@
     <t>pero sigamos esforzándonos, If. Cuento contigo.</t>
   </si>
   <si>
-    <t>messagePortuguese</t>
-  </si>
-  <si>
-    <t>speakerNamePortuguese</t>
-  </si>
-  <si>
-    <t>messageSizePortuguese</t>
-  </si>
-  <si>
     <t>Onde... onde eu estou...?</t>
   </si>
   <si>
@@ -2158,6 +2140,30 @@
   </si>
   <si>
     <t>mas vamos continuar em frente, If. Conto com você.</t>
+  </si>
+  <si>
+    <t>messageSpanish</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>messageSizeSpanish</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>speakerNamePortuguese</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>messagePortuguese</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>speakerNameSpanish</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>messageSizePortuguese</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -2541,10 +2547,10 @@
     <col min="12" max="12" width="22.75" customWidth="1"/>
     <col min="13" max="13" width="22.5" customWidth="1"/>
     <col min="14" max="14" width="47.125" customWidth="1"/>
-    <col min="15" max="15" width="17.625" customWidth="1"/>
+    <col min="15" max="15" width="23.75" customWidth="1"/>
     <col min="16" max="16" width="19.75" customWidth="1"/>
     <col min="17" max="17" width="47.125" customWidth="1"/>
-    <col min="18" max="18" width="17.625" customWidth="1"/>
+    <col min="18" max="18" width="24.875" customWidth="1"/>
     <col min="19" max="19" width="29.375" customWidth="1"/>
     <col min="20" max="20" width="27.75" customWidth="1"/>
     <col min="21" max="21" width="22.5" customWidth="1"/>
@@ -2555,7 +2561,7 @@
     <col min="27" max="27" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="37.5">
+    <row r="1" spans="1:27">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2596,22 +2602,22 @@
         <v>352</v>
       </c>
       <c r="N1" t="s">
-        <v>353</v>
+        <v>518</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>354</v>
+        <v>522</v>
       </c>
       <c r="P1" t="s">
-        <v>355</v>
+        <v>519</v>
       </c>
       <c r="Q1" t="s">
-        <v>439</v>
+        <v>521</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>440</v>
+        <v>520</v>
       </c>
       <c r="S1" t="s">
-        <v>441</v>
+        <v>523</v>
       </c>
       <c r="T1" t="s">
         <v>21</v>
@@ -2730,19 +2736,19 @@
         <v>22</v>
       </c>
       <c r="N3" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="O3" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="P3">
         <v>22</v>
       </c>
       <c r="Q3" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="R3" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="S3">
         <v>22</v>
@@ -2813,7 +2819,7 @@
         <v>22</v>
       </c>
       <c r="N4" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="O4" t="s">
         <v>192</v>
@@ -2822,7 +2828,7 @@
         <v>22</v>
       </c>
       <c r="Q4" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="R4" t="s">
         <v>192</v>
@@ -2896,7 +2902,7 @@
         <v>22</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="O5" t="s">
         <v>34</v>
@@ -2905,7 +2911,7 @@
         <v>22</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="R5" t="s">
         <v>34</v>
@@ -2979,19 +2985,19 @@
         <v>22</v>
       </c>
       <c r="N6" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="O6" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="P6">
         <v>22</v>
       </c>
       <c r="Q6" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="R6" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="S6">
         <v>22</v>
@@ -3062,7 +3068,7 @@
         <v>22</v>
       </c>
       <c r="N7" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="O7" t="s">
         <v>34</v>
@@ -3071,7 +3077,7 @@
         <v>22</v>
       </c>
       <c r="Q7" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="R7" t="s">
         <v>34</v>
@@ -3145,7 +3151,7 @@
         <v>22</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="O8" t="s">
         <v>34</v>
@@ -3154,7 +3160,7 @@
         <v>22</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="R8" t="s">
         <v>34</v>
@@ -3228,7 +3234,7 @@
         <v>22</v>
       </c>
       <c r="N9" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="O9" t="s">
         <v>34</v>
@@ -3237,7 +3243,7 @@
         <v>22</v>
       </c>
       <c r="Q9" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="R9" t="s">
         <v>34</v>
@@ -3311,19 +3317,19 @@
         <v>22</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="O10" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="P10">
         <v>22</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="R10" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="S10">
         <v>22</v>
@@ -3394,7 +3400,7 @@
         <v>22</v>
       </c>
       <c r="N11" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="O11" t="s">
         <v>34</v>
@@ -3403,7 +3409,7 @@
         <v>22</v>
       </c>
       <c r="Q11" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="R11" t="s">
         <v>34</v>
@@ -3477,7 +3483,7 @@
         <v>22</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="O12" t="s">
         <v>34</v>
@@ -3486,7 +3492,7 @@
         <v>22</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="R12" t="s">
         <v>34</v>
@@ -3560,19 +3566,19 @@
         <v>22</v>
       </c>
       <c r="N13" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="O13" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="P13">
         <v>22</v>
       </c>
       <c r="Q13" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="R13" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="S13">
         <v>22</v>
@@ -3643,19 +3649,19 @@
         <v>22</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="O14" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="P14">
         <v>22</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="R14" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="S14">
         <v>22</v>
@@ -3726,7 +3732,7 @@
         <v>22</v>
       </c>
       <c r="N15" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="O15" t="s">
         <v>34</v>
@@ -3735,7 +3741,7 @@
         <v>22</v>
       </c>
       <c r="Q15" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="R15" t="s">
         <v>34</v>
@@ -3809,7 +3815,7 @@
         <v>22</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="O16" t="s">
         <v>34</v>
@@ -3818,7 +3824,7 @@
         <v>22</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="R16" t="s">
         <v>34</v>
@@ -3892,19 +3898,19 @@
         <v>22</v>
       </c>
       <c r="N17" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="O17" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="P17">
         <v>22</v>
       </c>
       <c r="Q17" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="R17" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="S17">
         <v>22</v>
@@ -3975,19 +3981,19 @@
         <v>22</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="O18" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="P18">
         <v>22</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="R18" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="S18">
         <v>22</v>
@@ -4058,7 +4064,7 @@
         <v>22</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="O19" t="s">
         <v>34</v>
@@ -4067,7 +4073,7 @@
         <v>22</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="R19" t="s">
         <v>34</v>
@@ -4141,19 +4147,19 @@
         <v>22</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="O20" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="P20">
         <v>22</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="R20" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="S20">
         <v>22</v>
@@ -4221,7 +4227,7 @@
         <v>22</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="O21" t="s">
         <v>34</v>
@@ -4230,7 +4236,7 @@
         <v>22</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="R21" t="s">
         <v>34</v>
@@ -4304,7 +4310,7 @@
         <v>22</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="O22" t="s">
         <v>34</v>
@@ -4313,7 +4319,7 @@
         <v>22</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="R22" t="s">
         <v>34</v>
@@ -4387,7 +4393,7 @@
         <v>22</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="O23" t="s">
         <v>34</v>
@@ -4396,7 +4402,7 @@
         <v>22</v>
       </c>
       <c r="Q23" s="1" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="R23" t="s">
         <v>34</v>
@@ -4470,19 +4476,19 @@
         <v>22</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="O24" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="P24">
         <v>22</v>
       </c>
       <c r="Q24" s="1" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="R24" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="S24">
         <v>22</v>
@@ -4553,19 +4559,19 @@
         <v>22</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="O25" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="P25">
         <v>22</v>
       </c>
       <c r="Q25" s="1" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="R25" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="S25">
         <v>22</v>
@@ -4636,7 +4642,7 @@
         <v>22</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="O26" t="s">
         <v>34</v>
@@ -4645,7 +4651,7 @@
         <v>22</v>
       </c>
       <c r="Q26" s="1" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="R26" t="s">
         <v>34</v>
@@ -4719,7 +4725,7 @@
         <v>22</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="O27" t="s">
         <v>34</v>
@@ -4728,7 +4734,7 @@
         <v>22</v>
       </c>
       <c r="Q27" s="1" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="R27" t="s">
         <v>34</v>
@@ -4802,7 +4808,7 @@
         <v>22</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="O28" t="s">
         <v>34</v>
@@ -4811,7 +4817,7 @@
         <v>22</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="R28" t="s">
         <v>34</v>
@@ -4885,7 +4891,7 @@
         <v>22</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="O29" t="s">
         <v>34</v>
@@ -4894,7 +4900,7 @@
         <v>22</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="R29" t="s">
         <v>34</v>
@@ -4968,7 +4974,7 @@
         <v>22</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="O30" t="s">
         <v>34</v>
@@ -4977,7 +4983,7 @@
         <v>22</v>
       </c>
       <c r="Q30" s="1" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="R30" t="s">
         <v>34</v>
@@ -5051,19 +5057,19 @@
         <v>22</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="O31" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="P31">
         <v>22</v>
       </c>
       <c r="Q31" s="1" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="R31" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="S31">
         <v>22</v>
@@ -5134,19 +5140,19 @@
         <v>22</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="O32" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="P32">
         <v>22</v>
       </c>
       <c r="Q32" s="1" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="R32" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="S32">
         <v>22</v>
@@ -5217,7 +5223,7 @@
         <v>22</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="O33" t="s">
         <v>34</v>
@@ -5226,7 +5232,7 @@
         <v>22</v>
       </c>
       <c r="Q33" s="1" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="R33" t="s">
         <v>34</v>
@@ -5300,7 +5306,7 @@
         <v>22</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="O34" t="s">
         <v>34</v>
@@ -5309,7 +5315,7 @@
         <v>22</v>
       </c>
       <c r="Q34" s="1" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="R34" t="s">
         <v>34</v>
@@ -5383,7 +5389,7 @@
         <v>22</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="O35" t="s">
         <v>34</v>
@@ -5392,7 +5398,7 @@
         <v>22</v>
       </c>
       <c r="Q35" s="1" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="R35" t="s">
         <v>34</v>
@@ -5466,7 +5472,7 @@
         <v>22</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="O36" t="s">
         <v>34</v>
@@ -5475,7 +5481,7 @@
         <v>22</v>
       </c>
       <c r="Q36" s="1" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="R36" t="s">
         <v>34</v>
@@ -5549,19 +5555,19 @@
         <v>22</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="O37" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="P37">
         <v>22</v>
       </c>
       <c r="Q37" s="1" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="R37" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="S37">
         <v>22</v>
@@ -5632,7 +5638,7 @@
         <v>22</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="O38" t="s">
         <v>34</v>
@@ -5641,7 +5647,7 @@
         <v>22</v>
       </c>
       <c r="Q38" s="1" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="R38" t="s">
         <v>34</v>
@@ -5766,7 +5772,7 @@
         <v>22</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="O40" t="s">
         <v>34</v>
@@ -5775,7 +5781,7 @@
         <v>22</v>
       </c>
       <c r="Q40" s="1" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="R40" t="s">
         <v>34</v>
@@ -5849,7 +5855,7 @@
         <v>22</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="O41" t="s">
         <v>34</v>
@@ -5858,7 +5864,7 @@
         <v>22</v>
       </c>
       <c r="Q41" s="1" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="R41" t="s">
         <v>34</v>
@@ -5932,7 +5938,7 @@
         <v>22</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="O42" t="s">
         <v>34</v>
@@ -5941,7 +5947,7 @@
         <v>22</v>
       </c>
       <c r="Q42" s="1" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="R42" t="s">
         <v>34</v>
@@ -6015,7 +6021,7 @@
         <v>22</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="O43" t="s">
         <v>34</v>
@@ -6024,7 +6030,7 @@
         <v>22</v>
       </c>
       <c r="Q43" s="1" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="R43" t="s">
         <v>34</v>
@@ -6098,7 +6104,7 @@
         <v>22</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="O44" t="s">
         <v>34</v>
@@ -6107,7 +6113,7 @@
         <v>22</v>
       </c>
       <c r="Q44" s="1" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="R44" t="s">
         <v>34</v>
@@ -6181,7 +6187,7 @@
         <v>22</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="O45" t="s">
         <v>34</v>
@@ -6190,7 +6196,7 @@
         <v>22</v>
       </c>
       <c r="Q45" s="1" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="R45" t="s">
         <v>34</v>
@@ -6264,7 +6270,7 @@
         <v>22</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O46" t="s">
         <v>34</v>
@@ -6273,7 +6279,7 @@
         <v>22</v>
       </c>
       <c r="Q46" s="1" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="R46" t="s">
         <v>34</v>
@@ -6347,7 +6353,7 @@
         <v>22</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="O47" t="s">
         <v>34</v>
@@ -6356,7 +6362,7 @@
         <v>22</v>
       </c>
       <c r="Q47" s="1" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="R47" t="s">
         <v>34</v>
@@ -6430,7 +6436,7 @@
         <v>22</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="O48" t="s">
         <v>34</v>
@@ -6439,7 +6445,7 @@
         <v>22</v>
       </c>
       <c r="Q48" s="1" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="R48" t="s">
         <v>34</v>
@@ -6513,7 +6519,7 @@
         <v>22</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="O49" t="s">
         <v>34</v>
@@ -6522,7 +6528,7 @@
         <v>22</v>
       </c>
       <c r="Q49" s="1" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="R49" t="s">
         <v>34</v>
@@ -6596,7 +6602,7 @@
         <v>22</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="O50" t="s">
         <v>34</v>
@@ -6605,7 +6611,7 @@
         <v>22</v>
       </c>
       <c r="Q50" s="1" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="R50" t="s">
         <v>34</v>
@@ -6679,7 +6685,7 @@
         <v>22</v>
       </c>
       <c r="N51" s="1" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="O51" t="s">
         <v>34</v>
@@ -6688,7 +6694,7 @@
         <v>22</v>
       </c>
       <c r="Q51" s="1" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="R51" t="s">
         <v>34</v>
@@ -6762,19 +6768,19 @@
         <v>22</v>
       </c>
       <c r="N52" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="O52" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="P52">
         <v>22</v>
       </c>
       <c r="Q52" s="1" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="R52" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="S52">
         <v>22</v>
@@ -6845,7 +6851,7 @@
         <v>22</v>
       </c>
       <c r="N53" s="1" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="O53" t="s">
         <v>34</v>
@@ -6854,7 +6860,7 @@
         <v>22</v>
       </c>
       <c r="Q53" s="1" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="R53" t="s">
         <v>34</v>
@@ -6928,19 +6934,19 @@
         <v>22</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="O54" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="P54">
         <v>22</v>
       </c>
       <c r="Q54" s="1" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="R54" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="S54">
         <v>22</v>
@@ -7011,7 +7017,7 @@
         <v>22</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="O55" t="s">
         <v>34</v>
@@ -7020,7 +7026,7 @@
         <v>22</v>
       </c>
       <c r="Q55" s="1" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="R55" t="s">
         <v>34</v>
@@ -7094,7 +7100,7 @@
         <v>22</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="O56" t="s">
         <v>34</v>
@@ -7103,7 +7109,7 @@
         <v>22</v>
       </c>
       <c r="Q56" s="1" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="R56" t="s">
         <v>34</v>
@@ -7177,7 +7183,7 @@
         <v>22</v>
       </c>
       <c r="N57" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="O57" t="s">
         <v>34</v>
@@ -7186,7 +7192,7 @@
         <v>22</v>
       </c>
       <c r="Q57" s="1" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="R57" t="s">
         <v>34</v>
@@ -7260,7 +7266,7 @@
         <v>22</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="O58" t="s">
         <v>34</v>
@@ -7269,7 +7275,7 @@
         <v>22</v>
       </c>
       <c r="Q58" s="1" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="R58" t="s">
         <v>34</v>
@@ -7343,7 +7349,7 @@
         <v>22</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="O59" t="s">
         <v>34</v>
@@ -7352,7 +7358,7 @@
         <v>22</v>
       </c>
       <c r="Q59" s="1" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="R59" t="s">
         <v>34</v>
@@ -7426,19 +7432,19 @@
         <v>22</v>
       </c>
       <c r="N60" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="O60" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="P60">
         <v>22</v>
       </c>
       <c r="Q60" s="1" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="R60" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="S60">
         <v>22</v>
@@ -7509,7 +7515,7 @@
         <v>22</v>
       </c>
       <c r="N61" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="O61" t="s">
         <v>34</v>
@@ -7518,7 +7524,7 @@
         <v>22</v>
       </c>
       <c r="Q61" s="1" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="R61" t="s">
         <v>34</v>
@@ -7592,19 +7598,19 @@
         <v>22</v>
       </c>
       <c r="N62" s="1" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="O62" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="P62">
         <v>22</v>
       </c>
       <c r="Q62" s="1" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="R62" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="S62">
         <v>22</v>
@@ -7675,7 +7681,7 @@
         <v>22</v>
       </c>
       <c r="N63" s="1" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="O63" t="s">
         <v>34</v>
@@ -7684,7 +7690,7 @@
         <v>22</v>
       </c>
       <c r="Q63" s="1" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="R63" t="s">
         <v>34</v>
@@ -7758,19 +7764,19 @@
         <v>22</v>
       </c>
       <c r="N64" s="1" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="O64" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="P64">
         <v>22</v>
       </c>
       <c r="Q64" s="1" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="R64" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="S64">
         <v>22</v>
@@ -7841,7 +7847,7 @@
         <v>22</v>
       </c>
       <c r="N65" s="1" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="O65" t="s">
         <v>34</v>
@@ -7850,7 +7856,7 @@
         <v>22</v>
       </c>
       <c r="Q65" s="1" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="R65" t="s">
         <v>34</v>
@@ -7924,7 +7930,7 @@
         <v>22</v>
       </c>
       <c r="N66" s="1" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="O66" t="s">
         <v>34</v>
@@ -7933,7 +7939,7 @@
         <v>22</v>
       </c>
       <c r="Q66" s="1" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="R66" t="s">
         <v>34</v>
@@ -8007,7 +8013,7 @@
         <v>22</v>
       </c>
       <c r="N67" s="1" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="O67" t="s">
         <v>34</v>
@@ -8016,7 +8022,7 @@
         <v>22</v>
       </c>
       <c r="Q67" s="1" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="R67" t="s">
         <v>34</v>
@@ -8090,19 +8096,19 @@
         <v>22</v>
       </c>
       <c r="N68" s="1" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="O68" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="P68">
         <v>22</v>
       </c>
       <c r="Q68" s="1" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="R68" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="S68">
         <v>22</v>
@@ -8173,7 +8179,7 @@
         <v>22</v>
       </c>
       <c r="N69" s="1" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="O69" t="s">
         <v>34</v>
@@ -8182,7 +8188,7 @@
         <v>22</v>
       </c>
       <c r="Q69" s="1" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="R69" t="s">
         <v>34</v>
@@ -8256,7 +8262,7 @@
         <v>22</v>
       </c>
       <c r="N70" s="1" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="O70" t="s">
         <v>34</v>
@@ -8265,7 +8271,7 @@
         <v>22</v>
       </c>
       <c r="Q70" s="1" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="R70" t="s">
         <v>34</v>
@@ -8390,19 +8396,19 @@
         <v>22</v>
       </c>
       <c r="N72" s="1" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="O72" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="P72">
         <v>22</v>
       </c>
       <c r="Q72" s="1" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="R72" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="S72">
         <v>22</v>
@@ -8473,19 +8479,19 @@
         <v>22</v>
       </c>
       <c r="N73" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="O73" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="P73">
         <v>22</v>
       </c>
       <c r="Q73" s="1" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="R73" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="S73">
         <v>22</v>
@@ -8556,19 +8562,19 @@
         <v>22</v>
       </c>
       <c r="N74" s="1" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="O74" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="P74">
         <v>22</v>
       </c>
       <c r="Q74" s="1" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="R74" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="S74">
         <v>22</v>
@@ -8639,7 +8645,7 @@
         <v>22</v>
       </c>
       <c r="N75" s="1" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="O75" t="s">
         <v>34</v>
@@ -8648,7 +8654,7 @@
         <v>22</v>
       </c>
       <c r="Q75" s="1" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="R75" t="s">
         <v>34</v>
@@ -8722,7 +8728,7 @@
         <v>22</v>
       </c>
       <c r="N76" s="1" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="O76" t="s">
         <v>34</v>
@@ -8731,7 +8737,7 @@
         <v>22</v>
       </c>
       <c r="Q76" s="1" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="R76" t="s">
         <v>34</v>
@@ -8805,19 +8811,19 @@
         <v>22</v>
       </c>
       <c r="N77" s="1" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="O77" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="P77">
         <v>22</v>
       </c>
       <c r="Q77" s="1" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="R77" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="S77">
         <v>22</v>
@@ -8888,19 +8894,19 @@
         <v>22</v>
       </c>
       <c r="N78" s="1" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="O78" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="P78">
         <v>22</v>
       </c>
       <c r="Q78" s="1" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="R78" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="S78">
         <v>22</v>
@@ -8971,7 +8977,7 @@
         <v>22</v>
       </c>
       <c r="N79" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="O79" t="s">
         <v>34</v>
@@ -8980,7 +8986,7 @@
         <v>22</v>
       </c>
       <c r="Q79" s="1" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="R79" t="s">
         <v>34</v>
@@ -9054,19 +9060,19 @@
         <v>22</v>
       </c>
       <c r="N80" s="1" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="O80" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="P80">
         <v>22</v>
       </c>
       <c r="Q80" s="1" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="R80" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="S80">
         <v>22</v>
@@ -9137,7 +9143,7 @@
         <v>22</v>
       </c>
       <c r="N81" s="1" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="O81" t="s">
         <v>34</v>
@@ -9146,7 +9152,7 @@
         <v>22</v>
       </c>
       <c r="Q81" s="1" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="R81" t="s">
         <v>34</v>
@@ -9220,19 +9226,19 @@
         <v>22</v>
       </c>
       <c r="N82" s="1" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="O82" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="P82">
         <v>22</v>
       </c>
       <c r="Q82" s="1" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="R82" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="S82">
         <v>22</v>
@@ -9303,7 +9309,7 @@
         <v>22</v>
       </c>
       <c r="N83" s="1" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="O83" t="s">
         <v>34</v>
@@ -9312,7 +9318,7 @@
         <v>22</v>
       </c>
       <c r="Q83" s="1" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="R83" t="s">
         <v>34</v>
@@ -9386,19 +9392,19 @@
         <v>22</v>
       </c>
       <c r="N84" s="1" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="O84" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="P84">
         <v>22</v>
       </c>
       <c r="Q84" s="1" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="R84" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="S84">
         <v>22</v>
@@ -9469,7 +9475,7 @@
         <v>22</v>
       </c>
       <c r="N85" s="1" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="O85" t="s">
         <v>34</v>
@@ -9478,7 +9484,7 @@
         <v>22</v>
       </c>
       <c r="Q85" s="1" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="R85" t="s">
         <v>34</v>
@@ -9552,19 +9558,19 @@
         <v>22</v>
       </c>
       <c r="N86" s="1" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="O86" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="P86">
         <v>22</v>
       </c>
       <c r="Q86" s="1" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="R86" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="S86">
         <v>22</v>
@@ -9635,7 +9641,7 @@
         <v>22</v>
       </c>
       <c r="N87" s="1" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="O87" t="s">
         <v>34</v>
@@ -9644,7 +9650,7 @@
         <v>22</v>
       </c>
       <c r="Q87" s="1" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="R87" t="s">
         <v>34</v>
@@ -9718,7 +9724,7 @@
         <v>22</v>
       </c>
       <c r="N88" s="1" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="O88" t="s">
         <v>34</v>
@@ -9727,7 +9733,7 @@
         <v>22</v>
       </c>
       <c r="Q88" s="1" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="R88" t="s">
         <v>34</v>
@@ -9801,7 +9807,7 @@
         <v>22</v>
       </c>
       <c r="N89" s="1" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="O89" t="s">
         <v>34</v>
@@ -9810,7 +9816,7 @@
         <v>22</v>
       </c>
       <c r="Q89" s="1" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="R89" t="s">
         <v>34</v>

--- a/Assets/Originals/Excels/Talk/TalkMessage.xlsx
+++ b/Assets/Originals/Excels/Talk/TalkMessage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Talk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE653196-7526-4785-BDA3-BD3FBE46A98C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D6DD825-C787-42F6-B89E-E6C0C591DEBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1277,9 +1277,6 @@
     <t>注意事项？</t>
   </si>
   <si>
-    <t>绝对不能被「徘徊者」抓住</t>
-  </si>
-  <si>
     <t>徘徊者？</t>
   </si>
   <si>
@@ -1535,9 +1532,6 @@
     <t>注意事項？</t>
   </si>
   <si>
-    <t>絕對不能被「徘徊者」抓住</t>
-  </si>
-  <si>
     <t>就是潛伏在夢迷中的怪物</t>
   </si>
   <si>
@@ -2163,6 +2157,14 @@
   </si>
   <si>
     <t>messageSizePortuguese</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>绝对不能被「彷徨者 」抓住</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>絕對不能被「彷徨者 」抓住</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2584,40 +2586,40 @@
         <v>31</v>
       </c>
       <c r="H1" t="s">
+        <v>274</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" t="s">
         <v>276</v>
       </c>
-      <c r="J1" t="s">
-        <v>277</v>
-      </c>
       <c r="K1" t="s">
+        <v>348</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="M1" t="s">
         <v>350</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="M1" t="s">
-        <v>352</v>
-      </c>
       <c r="N1" t="s">
+        <v>516</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="P1" t="s">
+        <v>517</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>519</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="O1" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="P1" t="s">
-        <v>519</v>
-      </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>521</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="S1" t="s">
-        <v>523</v>
       </c>
       <c r="T1" t="s">
         <v>21</v>
@@ -2727,7 +2729,7 @@
         <v>22</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="L3" s="7" t="s">
         <v>190</v>
@@ -2736,19 +2738,19 @@
         <v>22</v>
       </c>
       <c r="N3" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="O3" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="P3">
         <v>22</v>
       </c>
       <c r="Q3" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="R3" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="S3">
         <v>22</v>
@@ -2819,7 +2821,7 @@
         <v>22</v>
       </c>
       <c r="N4" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="O4" t="s">
         <v>192</v>
@@ -2828,7 +2830,7 @@
         <v>22</v>
       </c>
       <c r="Q4" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="R4" t="s">
         <v>192</v>
@@ -2893,7 +2895,7 @@
         <v>22</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="L5" s="7" t="s">
         <v>194</v>
@@ -2902,7 +2904,7 @@
         <v>22</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="O5" t="s">
         <v>34</v>
@@ -2911,7 +2913,7 @@
         <v>22</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="R5" t="s">
         <v>34</v>
@@ -2976,7 +2978,7 @@
         <v>22</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>190</v>
@@ -2985,19 +2987,19 @@
         <v>22</v>
       </c>
       <c r="N6" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="O6" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="P6">
         <v>22</v>
       </c>
       <c r="Q6" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="R6" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="S6">
         <v>22</v>
@@ -3059,7 +3061,7 @@
         <v>22</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L7" s="7" t="s">
         <v>194</v>
@@ -3068,7 +3070,7 @@
         <v>22</v>
       </c>
       <c r="N7" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="O7" t="s">
         <v>34</v>
@@ -3077,7 +3079,7 @@
         <v>22</v>
       </c>
       <c r="Q7" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="R7" t="s">
         <v>34</v>
@@ -3142,7 +3144,7 @@
         <v>22</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="L8" s="7" t="s">
         <v>194</v>
@@ -3151,7 +3153,7 @@
         <v>22</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="O8" t="s">
         <v>34</v>
@@ -3160,7 +3162,7 @@
         <v>22</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="R8" t="s">
         <v>34</v>
@@ -3225,7 +3227,7 @@
         <v>22</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L9" s="7" t="s">
         <v>194</v>
@@ -3234,7 +3236,7 @@
         <v>22</v>
       </c>
       <c r="N9" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="O9" t="s">
         <v>34</v>
@@ -3243,7 +3245,7 @@
         <v>22</v>
       </c>
       <c r="Q9" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="R9" t="s">
         <v>34</v>
@@ -3317,19 +3319,19 @@
         <v>22</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="O10" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="P10">
         <v>22</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="R10" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="S10">
         <v>22</v>
@@ -3391,7 +3393,7 @@
         <v>22</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L11" s="7" t="s">
         <v>194</v>
@@ -3400,7 +3402,7 @@
         <v>22</v>
       </c>
       <c r="N11" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="O11" t="s">
         <v>34</v>
@@ -3409,7 +3411,7 @@
         <v>22</v>
       </c>
       <c r="Q11" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="R11" t="s">
         <v>34</v>
@@ -3474,7 +3476,7 @@
         <v>22</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="L12" s="7" t="s">
         <v>194</v>
@@ -3483,7 +3485,7 @@
         <v>22</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="O12" t="s">
         <v>34</v>
@@ -3492,7 +3494,7 @@
         <v>22</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="R12" t="s">
         <v>34</v>
@@ -3566,19 +3568,19 @@
         <v>22</v>
       </c>
       <c r="N13" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="O13" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="P13">
         <v>22</v>
       </c>
       <c r="Q13" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="R13" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="S13">
         <v>22</v>
@@ -3640,7 +3642,7 @@
         <v>22</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="L14" s="7" t="s">
         <v>190</v>
@@ -3649,19 +3651,19 @@
         <v>22</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="O14" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="P14">
         <v>22</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="R14" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="S14">
         <v>22</v>
@@ -3723,7 +3725,7 @@
         <v>22</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="L15" s="7" t="s">
         <v>194</v>
@@ -3732,7 +3734,7 @@
         <v>22</v>
       </c>
       <c r="N15" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="O15" t="s">
         <v>34</v>
@@ -3741,7 +3743,7 @@
         <v>22</v>
       </c>
       <c r="Q15" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="R15" t="s">
         <v>34</v>
@@ -3806,7 +3808,7 @@
         <v>22</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L16" s="7" t="s">
         <v>194</v>
@@ -3815,7 +3817,7 @@
         <v>22</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="O16" t="s">
         <v>34</v>
@@ -3824,7 +3826,7 @@
         <v>22</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="R16" t="s">
         <v>34</v>
@@ -3889,7 +3891,7 @@
         <v>22</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="L17" s="7" t="s">
         <v>190</v>
@@ -3898,19 +3900,19 @@
         <v>22</v>
       </c>
       <c r="N17" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="O17" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="P17">
         <v>22</v>
       </c>
       <c r="Q17" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="R17" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="S17">
         <v>22</v>
@@ -3972,7 +3974,7 @@
         <v>22</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="L18" s="7" t="s">
         <v>190</v>
@@ -3981,19 +3983,19 @@
         <v>22</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="O18" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="P18">
         <v>22</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="R18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="S18">
         <v>22</v>
@@ -4055,7 +4057,7 @@
         <v>22</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L19" s="7" t="s">
         <v>194</v>
@@ -4064,7 +4066,7 @@
         <v>22</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="O19" t="s">
         <v>34</v>
@@ -4073,7 +4075,7 @@
         <v>22</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="R19" t="s">
         <v>34</v>
@@ -4147,19 +4149,19 @@
         <v>22</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="O20" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="P20">
         <v>22</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="R20" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="S20">
         <v>22</v>
@@ -4227,7 +4229,7 @@
         <v>22</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="O21" t="s">
         <v>34</v>
@@ -4236,7 +4238,7 @@
         <v>22</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="R21" t="s">
         <v>34</v>
@@ -4301,7 +4303,7 @@
         <v>22</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="L22" s="7" t="s">
         <v>194</v>
@@ -4310,7 +4312,7 @@
         <v>22</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="O22" t="s">
         <v>34</v>
@@ -4319,7 +4321,7 @@
         <v>22</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="R22" t="s">
         <v>34</v>
@@ -4384,7 +4386,7 @@
         <v>22</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L23" s="7" t="s">
         <v>194</v>
@@ -4393,7 +4395,7 @@
         <v>22</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="O23" t="s">
         <v>34</v>
@@ -4402,7 +4404,7 @@
         <v>22</v>
       </c>
       <c r="Q23" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="R23" t="s">
         <v>34</v>
@@ -4467,7 +4469,7 @@
         <v>22</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="L24" s="7" t="s">
         <v>190</v>
@@ -4476,19 +4478,19 @@
         <v>22</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="O24" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="P24">
         <v>22</v>
       </c>
       <c r="Q24" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="R24" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="S24">
         <v>22</v>
@@ -4550,7 +4552,7 @@
         <v>22</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="L25" s="7" t="s">
         <v>190</v>
@@ -4559,19 +4561,19 @@
         <v>22</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="O25" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="P25">
         <v>22</v>
       </c>
       <c r="Q25" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="R25" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="S25">
         <v>22</v>
@@ -4633,7 +4635,7 @@
         <v>22</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="L26" s="7" t="s">
         <v>194</v>
@@ -4642,7 +4644,7 @@
         <v>22</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="O26" t="s">
         <v>34</v>
@@ -4651,7 +4653,7 @@
         <v>22</v>
       </c>
       <c r="Q26" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="R26" t="s">
         <v>34</v>
@@ -4716,7 +4718,7 @@
         <v>22</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="L27" s="7" t="s">
         <v>194</v>
@@ -4725,7 +4727,7 @@
         <v>22</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="O27" t="s">
         <v>34</v>
@@ -4734,7 +4736,7 @@
         <v>22</v>
       </c>
       <c r="Q27" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="R27" t="s">
         <v>34</v>
@@ -4799,7 +4801,7 @@
         <v>22</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="L28" s="7" t="s">
         <v>194</v>
@@ -4808,7 +4810,7 @@
         <v>22</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="O28" t="s">
         <v>34</v>
@@ -4817,7 +4819,7 @@
         <v>22</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="R28" t="s">
         <v>34</v>
@@ -4882,7 +4884,7 @@
         <v>22</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="L29" s="7" t="s">
         <v>194</v>
@@ -4891,7 +4893,7 @@
         <v>22</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="O29" t="s">
         <v>34</v>
@@ -4900,7 +4902,7 @@
         <v>22</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="R29" t="s">
         <v>34</v>
@@ -4965,7 +4967,7 @@
         <v>22</v>
       </c>
       <c r="K30" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="L30" s="7" t="s">
         <v>194</v>
@@ -4974,7 +4976,7 @@
         <v>22</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="O30" t="s">
         <v>34</v>
@@ -4983,7 +4985,7 @@
         <v>22</v>
       </c>
       <c r="Q30" s="1" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="R30" t="s">
         <v>34</v>
@@ -5057,19 +5059,19 @@
         <v>22</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="O31" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="P31">
         <v>22</v>
       </c>
       <c r="Q31" s="1" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="R31" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="S31">
         <v>22</v>
@@ -5131,7 +5133,7 @@
         <v>22</v>
       </c>
       <c r="K32" s="7" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="L32" s="7" t="s">
         <v>190</v>
@@ -5140,19 +5142,19 @@
         <v>22</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="O32" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="P32">
         <v>22</v>
       </c>
       <c r="Q32" s="1" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="R32" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="S32">
         <v>22</v>
@@ -5214,7 +5216,7 @@
         <v>22</v>
       </c>
       <c r="K33" s="7" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L33" s="7" t="s">
         <v>194</v>
@@ -5223,7 +5225,7 @@
         <v>22</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="O33" t="s">
         <v>34</v>
@@ -5232,7 +5234,7 @@
         <v>22</v>
       </c>
       <c r="Q33" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="R33" t="s">
         <v>34</v>
@@ -5297,7 +5299,7 @@
         <v>22</v>
       </c>
       <c r="K34" s="8" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="L34" s="7" t="s">
         <v>194</v>
@@ -5306,7 +5308,7 @@
         <v>22</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="O34" t="s">
         <v>34</v>
@@ -5315,7 +5317,7 @@
         <v>22</v>
       </c>
       <c r="Q34" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="R34" t="s">
         <v>34</v>
@@ -5380,7 +5382,7 @@
         <v>22</v>
       </c>
       <c r="K35" s="7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="L35" s="7" t="s">
         <v>194</v>
@@ -5389,7 +5391,7 @@
         <v>22</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="O35" t="s">
         <v>34</v>
@@ -5398,7 +5400,7 @@
         <v>22</v>
       </c>
       <c r="Q35" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="R35" t="s">
         <v>34</v>
@@ -5463,7 +5465,7 @@
         <v>22</v>
       </c>
       <c r="K36" s="7" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="L36" s="7" t="s">
         <v>194</v>
@@ -5472,7 +5474,7 @@
         <v>22</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="O36" t="s">
         <v>34</v>
@@ -5481,7 +5483,7 @@
         <v>22</v>
       </c>
       <c r="Q36" s="1" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="R36" t="s">
         <v>34</v>
@@ -5546,7 +5548,7 @@
         <v>22</v>
       </c>
       <c r="K37" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="L37" s="7" t="s">
         <v>190</v>
@@ -5555,19 +5557,19 @@
         <v>22</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="O37" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="P37">
         <v>22</v>
       </c>
       <c r="Q37" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="R37" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="S37">
         <v>22</v>
@@ -5629,7 +5631,7 @@
         <v>22</v>
       </c>
       <c r="K38" s="8" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L38" s="7" t="s">
         <v>194</v>
@@ -5638,7 +5640,7 @@
         <v>22</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="O38" t="s">
         <v>34</v>
@@ -5647,7 +5649,7 @@
         <v>22</v>
       </c>
       <c r="Q38" s="1" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="R38" t="s">
         <v>34</v>
@@ -5763,7 +5765,7 @@
         <v>22</v>
       </c>
       <c r="K40" s="8" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L40" s="7" t="s">
         <v>194</v>
@@ -5772,7 +5774,7 @@
         <v>22</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="O40" t="s">
         <v>34</v>
@@ -5781,7 +5783,7 @@
         <v>22</v>
       </c>
       <c r="Q40" s="1" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="R40" t="s">
         <v>34</v>
@@ -5846,7 +5848,7 @@
         <v>22</v>
       </c>
       <c r="K41" s="8" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L41" s="7" t="s">
         <v>194</v>
@@ -5855,7 +5857,7 @@
         <v>22</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="O41" t="s">
         <v>34</v>
@@ -5864,7 +5866,7 @@
         <v>22</v>
       </c>
       <c r="Q41" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="R41" t="s">
         <v>34</v>
@@ -5929,7 +5931,7 @@
         <v>22</v>
       </c>
       <c r="K42" s="7" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="L42" s="7" t="s">
         <v>194</v>
@@ -5938,7 +5940,7 @@
         <v>22</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="O42" t="s">
         <v>34</v>
@@ -5947,7 +5949,7 @@
         <v>22</v>
       </c>
       <c r="Q42" s="1" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="R42" t="s">
         <v>34</v>
@@ -6012,7 +6014,7 @@
         <v>22</v>
       </c>
       <c r="K43" s="8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="L43" s="7" t="s">
         <v>194</v>
@@ -6021,7 +6023,7 @@
         <v>22</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="O43" t="s">
         <v>34</v>
@@ -6030,7 +6032,7 @@
         <v>22</v>
       </c>
       <c r="Q43" s="1" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="R43" t="s">
         <v>34</v>
@@ -6095,7 +6097,7 @@
         <v>22</v>
       </c>
       <c r="K44" s="8" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="L44" s="7" t="s">
         <v>194</v>
@@ -6104,7 +6106,7 @@
         <v>22</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="O44" t="s">
         <v>34</v>
@@ -6113,7 +6115,7 @@
         <v>22</v>
       </c>
       <c r="Q44" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="R44" t="s">
         <v>34</v>
@@ -6178,7 +6180,7 @@
         <v>22</v>
       </c>
       <c r="K45" s="7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="L45" s="7" t="s">
         <v>194</v>
@@ -6187,7 +6189,7 @@
         <v>22</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="O45" t="s">
         <v>34</v>
@@ -6196,7 +6198,7 @@
         <v>22</v>
       </c>
       <c r="Q45" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="R45" t="s">
         <v>34</v>
@@ -6261,7 +6263,7 @@
         <v>22</v>
       </c>
       <c r="K46" s="7" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="L46" s="7" t="s">
         <v>194</v>
@@ -6270,7 +6272,7 @@
         <v>22</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="O46" t="s">
         <v>34</v>
@@ -6279,7 +6281,7 @@
         <v>22</v>
       </c>
       <c r="Q46" s="1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="R46" t="s">
         <v>34</v>
@@ -6344,7 +6346,7 @@
         <v>22</v>
       </c>
       <c r="K47" s="7" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="L47" s="7" t="s">
         <v>194</v>
@@ -6353,7 +6355,7 @@
         <v>22</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="O47" t="s">
         <v>34</v>
@@ -6362,7 +6364,7 @@
         <v>22</v>
       </c>
       <c r="Q47" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="R47" t="s">
         <v>34</v>
@@ -6427,7 +6429,7 @@
         <v>22</v>
       </c>
       <c r="K48" s="7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="L48" s="7" t="s">
         <v>194</v>
@@ -6436,7 +6438,7 @@
         <v>22</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="O48" t="s">
         <v>34</v>
@@ -6445,7 +6447,7 @@
         <v>22</v>
       </c>
       <c r="Q48" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="R48" t="s">
         <v>34</v>
@@ -6510,7 +6512,7 @@
         <v>22</v>
       </c>
       <c r="K49" s="8" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="L49" s="7" t="s">
         <v>194</v>
@@ -6519,7 +6521,7 @@
         <v>22</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="O49" t="s">
         <v>34</v>
@@ -6528,7 +6530,7 @@
         <v>22</v>
       </c>
       <c r="Q49" s="1" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="R49" t="s">
         <v>34</v>
@@ -6593,7 +6595,7 @@
         <v>22</v>
       </c>
       <c r="K50" s="8" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="L50" s="7" t="s">
         <v>194</v>
@@ -6602,7 +6604,7 @@
         <v>22</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="O50" t="s">
         <v>34</v>
@@ -6611,7 +6613,7 @@
         <v>22</v>
       </c>
       <c r="Q50" s="1" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="R50" t="s">
         <v>34</v>
@@ -6676,7 +6678,7 @@
         <v>22</v>
       </c>
       <c r="K51" s="8" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="L51" s="7" t="s">
         <v>194</v>
@@ -6685,7 +6687,7 @@
         <v>22</v>
       </c>
       <c r="N51" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="O51" t="s">
         <v>34</v>
@@ -6694,7 +6696,7 @@
         <v>22</v>
       </c>
       <c r="Q51" s="1" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="R51" t="s">
         <v>34</v>
@@ -6759,7 +6761,7 @@
         <v>22</v>
       </c>
       <c r="K52" s="7" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="L52" s="7" t="s">
         <v>190</v>
@@ -6768,19 +6770,19 @@
         <v>22</v>
       </c>
       <c r="N52" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="O52" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="P52">
         <v>22</v>
       </c>
       <c r="Q52" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="R52" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="S52">
         <v>22</v>
@@ -6842,7 +6844,7 @@
         <v>22</v>
       </c>
       <c r="K53" s="7" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="L53" s="7" t="s">
         <v>194</v>
@@ -6851,7 +6853,7 @@
         <v>22</v>
       </c>
       <c r="N53" s="1" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="O53" t="s">
         <v>34</v>
@@ -6860,7 +6862,7 @@
         <v>22</v>
       </c>
       <c r="Q53" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="R53" t="s">
         <v>34</v>
@@ -6934,19 +6936,19 @@
         <v>22</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="O54" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="P54">
         <v>22</v>
       </c>
       <c r="Q54" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="R54" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="S54">
         <v>22</v>
@@ -7008,7 +7010,7 @@
         <v>22</v>
       </c>
       <c r="K55" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="L55" s="7" t="s">
         <v>194</v>
@@ -7017,7 +7019,7 @@
         <v>22</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="O55" t="s">
         <v>34</v>
@@ -7026,7 +7028,7 @@
         <v>22</v>
       </c>
       <c r="Q55" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="R55" t="s">
         <v>34</v>
@@ -7091,7 +7093,7 @@
         <v>22</v>
       </c>
       <c r="K56" s="8" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="L56" s="7" t="s">
         <v>194</v>
@@ -7100,7 +7102,7 @@
         <v>22</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="O56" t="s">
         <v>34</v>
@@ -7109,7 +7111,7 @@
         <v>22</v>
       </c>
       <c r="Q56" s="1" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="R56" t="s">
         <v>34</v>
@@ -7174,7 +7176,7 @@
         <v>22</v>
       </c>
       <c r="K57" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="L57" s="7" t="s">
         <v>194</v>
@@ -7183,7 +7185,7 @@
         <v>22</v>
       </c>
       <c r="N57" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="O57" t="s">
         <v>34</v>
@@ -7192,7 +7194,7 @@
         <v>22</v>
       </c>
       <c r="Q57" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="R57" t="s">
         <v>34</v>
@@ -7257,7 +7259,7 @@
         <v>22</v>
       </c>
       <c r="K58" s="8" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="L58" s="7" t="s">
         <v>194</v>
@@ -7266,7 +7268,7 @@
         <v>22</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="O58" t="s">
         <v>34</v>
@@ -7275,7 +7277,7 @@
         <v>22</v>
       </c>
       <c r="Q58" s="1" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="R58" t="s">
         <v>34</v>
@@ -7340,7 +7342,7 @@
         <v>22</v>
       </c>
       <c r="K59" s="7" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L59" s="7" t="s">
         <v>194</v>
@@ -7349,7 +7351,7 @@
         <v>22</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="O59" t="s">
         <v>34</v>
@@ -7358,7 +7360,7 @@
         <v>22</v>
       </c>
       <c r="Q59" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="R59" t="s">
         <v>34</v>
@@ -7432,19 +7434,19 @@
         <v>22</v>
       </c>
       <c r="N60" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="O60" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="P60">
         <v>22</v>
       </c>
       <c r="Q60" s="1" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="R60" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="S60">
         <v>22</v>
@@ -7506,7 +7508,7 @@
         <v>22</v>
       </c>
       <c r="K61" s="7" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="L61" s="7" t="s">
         <v>194</v>
@@ -7515,7 +7517,7 @@
         <v>22</v>
       </c>
       <c r="N61" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="O61" t="s">
         <v>34</v>
@@ -7524,7 +7526,7 @@
         <v>22</v>
       </c>
       <c r="Q61" s="1" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="R61" t="s">
         <v>34</v>
@@ -7589,7 +7591,7 @@
         <v>22</v>
       </c>
       <c r="K62" s="8" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="L62" s="7" t="s">
         <v>190</v>
@@ -7598,19 +7600,19 @@
         <v>22</v>
       </c>
       <c r="N62" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="O62" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="P62">
         <v>22</v>
       </c>
       <c r="Q62" s="1" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="R62" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="S62">
         <v>22</v>
@@ -7663,7 +7665,7 @@
         <v>22</v>
       </c>
       <c r="H63" s="5" t="s">
-        <v>250</v>
+        <v>522</v>
       </c>
       <c r="I63" s="5" t="s">
         <v>194</v>
@@ -7672,7 +7674,7 @@
         <v>22</v>
       </c>
       <c r="K63" s="7" t="s">
-        <v>329</v>
+        <v>523</v>
       </c>
       <c r="L63" s="7" t="s">
         <v>194</v>
@@ -7681,7 +7683,7 @@
         <v>22</v>
       </c>
       <c r="N63" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="O63" t="s">
         <v>34</v>
@@ -7690,7 +7692,7 @@
         <v>22</v>
       </c>
       <c r="Q63" s="1" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="R63" t="s">
         <v>34</v>
@@ -7746,7 +7748,7 @@
         <v>22</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I64" s="5" t="s">
         <v>190</v>
@@ -7755,7 +7757,7 @@
         <v>22</v>
       </c>
       <c r="K64" s="8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L64" s="7" t="s">
         <v>190</v>
@@ -7764,19 +7766,19 @@
         <v>22</v>
       </c>
       <c r="N64" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="O64" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="P64">
         <v>22</v>
       </c>
       <c r="Q64" s="1" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="R64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="S64">
         <v>22</v>
@@ -7829,7 +7831,7 @@
         <v>22</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I65" s="5" t="s">
         <v>194</v>
@@ -7838,7 +7840,7 @@
         <v>22</v>
       </c>
       <c r="K65" s="7" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="L65" s="7" t="s">
         <v>194</v>
@@ -7847,7 +7849,7 @@
         <v>22</v>
       </c>
       <c r="N65" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="O65" t="s">
         <v>34</v>
@@ -7856,7 +7858,7 @@
         <v>22</v>
       </c>
       <c r="Q65" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="R65" t="s">
         <v>34</v>
@@ -7912,7 +7914,7 @@
         <v>22</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I66" s="5" t="s">
         <v>194</v>
@@ -7921,7 +7923,7 @@
         <v>22</v>
       </c>
       <c r="K66" s="8" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="L66" s="7" t="s">
         <v>194</v>
@@ -7930,7 +7932,7 @@
         <v>22</v>
       </c>
       <c r="N66" s="1" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="O66" t="s">
         <v>34</v>
@@ -7939,7 +7941,7 @@
         <v>22</v>
       </c>
       <c r="Q66" s="1" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="R66" t="s">
         <v>34</v>
@@ -7995,7 +7997,7 @@
         <v>22</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I67" s="5" t="s">
         <v>194</v>
@@ -8004,7 +8006,7 @@
         <v>22</v>
       </c>
       <c r="K67" s="8" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="L67" s="7" t="s">
         <v>194</v>
@@ -8013,7 +8015,7 @@
         <v>22</v>
       </c>
       <c r="N67" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="O67" t="s">
         <v>34</v>
@@ -8022,7 +8024,7 @@
         <v>22</v>
       </c>
       <c r="Q67" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="R67" t="s">
         <v>34</v>
@@ -8078,7 +8080,7 @@
         <v>22</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="I68" s="5" t="s">
         <v>190</v>
@@ -8087,7 +8089,7 @@
         <v>22</v>
       </c>
       <c r="K68" s="8" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="L68" s="7" t="s">
         <v>190</v>
@@ -8096,19 +8098,19 @@
         <v>22</v>
       </c>
       <c r="N68" s="1" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="O68" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="P68">
         <v>22</v>
       </c>
       <c r="Q68" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="R68" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="S68">
         <v>22</v>
@@ -8161,7 +8163,7 @@
         <v>22</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I69" s="5" t="s">
         <v>194</v>
@@ -8170,7 +8172,7 @@
         <v>22</v>
       </c>
       <c r="K69" s="8" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="L69" s="7" t="s">
         <v>194</v>
@@ -8179,7 +8181,7 @@
         <v>22</v>
       </c>
       <c r="N69" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="O69" t="s">
         <v>34</v>
@@ -8188,7 +8190,7 @@
         <v>22</v>
       </c>
       <c r="Q69" s="1" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="R69" t="s">
         <v>34</v>
@@ -8244,7 +8246,7 @@
         <v>22</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I70" s="5" t="s">
         <v>194</v>
@@ -8253,7 +8255,7 @@
         <v>22</v>
       </c>
       <c r="K70" s="8" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="L70" s="7" t="s">
         <v>194</v>
@@ -8262,7 +8264,7 @@
         <v>22</v>
       </c>
       <c r="N70" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="O70" t="s">
         <v>34</v>
@@ -8271,7 +8273,7 @@
         <v>22</v>
       </c>
       <c r="Q70" s="1" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="R70" t="s">
         <v>34</v>
@@ -8378,7 +8380,7 @@
         <v>22</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="I72" s="5" t="s">
         <v>190</v>
@@ -8387,7 +8389,7 @@
         <v>22</v>
       </c>
       <c r="K72" s="8" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="L72" s="7" t="s">
         <v>190</v>
@@ -8396,19 +8398,19 @@
         <v>22</v>
       </c>
       <c r="N72" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="O72" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="P72">
         <v>22</v>
       </c>
       <c r="Q72" s="1" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="R72" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="S72">
         <v>22</v>
@@ -8461,7 +8463,7 @@
         <v>22</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I73" s="5" t="s">
         <v>190</v>
@@ -8470,7 +8472,7 @@
         <v>22</v>
       </c>
       <c r="K73" s="8" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="L73" s="7" t="s">
         <v>190</v>
@@ -8479,19 +8481,19 @@
         <v>22</v>
       </c>
       <c r="N73" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="O73" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="P73">
         <v>22</v>
       </c>
       <c r="Q73" s="1" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="R73" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="S73">
         <v>22</v>
@@ -8544,7 +8546,7 @@
         <v>22</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="I74" s="5" t="s">
         <v>190</v>
@@ -8553,7 +8555,7 @@
         <v>22</v>
       </c>
       <c r="K74" s="8" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="L74" s="7" t="s">
         <v>190</v>
@@ -8562,19 +8564,19 @@
         <v>22</v>
       </c>
       <c r="N74" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="O74" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="P74">
         <v>22</v>
       </c>
       <c r="Q74" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="R74" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="S74">
         <v>22</v>
@@ -8627,7 +8629,7 @@
         <v>22</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I75" s="5" t="s">
         <v>194</v>
@@ -8636,7 +8638,7 @@
         <v>22</v>
       </c>
       <c r="K75" s="8" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="L75" s="7" t="s">
         <v>194</v>
@@ -8645,7 +8647,7 @@
         <v>22</v>
       </c>
       <c r="N75" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="O75" t="s">
         <v>34</v>
@@ -8654,7 +8656,7 @@
         <v>22</v>
       </c>
       <c r="Q75" s="1" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="R75" t="s">
         <v>34</v>
@@ -8710,7 +8712,7 @@
         <v>22</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I76" s="5" t="s">
         <v>194</v>
@@ -8719,7 +8721,7 @@
         <v>22</v>
       </c>
       <c r="K76" s="8" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="L76" s="7" t="s">
         <v>194</v>
@@ -8728,7 +8730,7 @@
         <v>22</v>
       </c>
       <c r="N76" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="O76" t="s">
         <v>34</v>
@@ -8737,7 +8739,7 @@
         <v>22</v>
       </c>
       <c r="Q76" s="1" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="R76" t="s">
         <v>34</v>
@@ -8793,7 +8795,7 @@
         <v>22</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I77" s="5" t="s">
         <v>190</v>
@@ -8802,7 +8804,7 @@
         <v>22</v>
       </c>
       <c r="K77" s="8" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="L77" s="7" t="s">
         <v>190</v>
@@ -8811,19 +8813,19 @@
         <v>22</v>
       </c>
       <c r="N77" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="O77" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="P77">
         <v>22</v>
       </c>
       <c r="Q77" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="R77" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="S77">
         <v>22</v>
@@ -8876,7 +8878,7 @@
         <v>22</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="I78" s="5" t="s">
         <v>190</v>
@@ -8885,7 +8887,7 @@
         <v>22</v>
       </c>
       <c r="K78" s="8" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="L78" s="7" t="s">
         <v>190</v>
@@ -8894,19 +8896,19 @@
         <v>22</v>
       </c>
       <c r="N78" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="O78" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="P78">
         <v>22</v>
       </c>
       <c r="Q78" s="1" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R78" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="S78">
         <v>22</v>
@@ -8959,7 +8961,7 @@
         <v>22</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="I79" s="5" t="s">
         <v>194</v>
@@ -8968,7 +8970,7 @@
         <v>22</v>
       </c>
       <c r="K79" s="8" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="L79" s="7" t="s">
         <v>194</v>
@@ -8977,7 +8979,7 @@
         <v>22</v>
       </c>
       <c r="N79" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="O79" t="s">
         <v>34</v>
@@ -8986,7 +8988,7 @@
         <v>22</v>
       </c>
       <c r="Q79" s="1" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="R79" t="s">
         <v>34</v>
@@ -9060,19 +9062,19 @@
         <v>22</v>
       </c>
       <c r="N80" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="O80" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="P80">
         <v>22</v>
       </c>
       <c r="Q80" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="R80" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="S80">
         <v>22</v>
@@ -9125,7 +9127,7 @@
         <v>22</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I81" s="5" t="s">
         <v>194</v>
@@ -9134,7 +9136,7 @@
         <v>22</v>
       </c>
       <c r="K81" s="8" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="L81" s="7" t="s">
         <v>194</v>
@@ -9143,7 +9145,7 @@
         <v>22</v>
       </c>
       <c r="N81" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="O81" t="s">
         <v>34</v>
@@ -9152,7 +9154,7 @@
         <v>22</v>
       </c>
       <c r="Q81" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="R81" t="s">
         <v>34</v>
@@ -9208,7 +9210,7 @@
         <v>22</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I82" s="5" t="s">
         <v>190</v>
@@ -9217,7 +9219,7 @@
         <v>22</v>
       </c>
       <c r="K82" s="8" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="L82" s="7" t="s">
         <v>190</v>
@@ -9226,19 +9228,19 @@
         <v>22</v>
       </c>
       <c r="N82" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="O82" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="P82">
         <v>22</v>
       </c>
       <c r="Q82" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="R82" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="S82">
         <v>22</v>
@@ -9291,7 +9293,7 @@
         <v>22</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="I83" s="5" t="s">
         <v>194</v>
@@ -9300,7 +9302,7 @@
         <v>22</v>
       </c>
       <c r="K83" s="8" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="L83" s="7" t="s">
         <v>194</v>
@@ -9309,7 +9311,7 @@
         <v>22</v>
       </c>
       <c r="N83" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="O83" t="s">
         <v>34</v>
@@ -9318,7 +9320,7 @@
         <v>22</v>
       </c>
       <c r="Q83" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="R83" t="s">
         <v>34</v>
@@ -9374,7 +9376,7 @@
         <v>22</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="I84" s="5" t="s">
         <v>190</v>
@@ -9383,7 +9385,7 @@
         <v>22</v>
       </c>
       <c r="K84" s="8" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="L84" s="7" t="s">
         <v>190</v>
@@ -9392,19 +9394,19 @@
         <v>22</v>
       </c>
       <c r="N84" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="O84" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="P84">
         <v>22</v>
       </c>
       <c r="Q84" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="R84" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="S84">
         <v>22</v>
@@ -9457,7 +9459,7 @@
         <v>22</v>
       </c>
       <c r="H85" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I85" s="5" t="s">
         <v>194</v>
@@ -9466,7 +9468,7 @@
         <v>22</v>
       </c>
       <c r="K85" s="8" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="L85" s="7" t="s">
         <v>194</v>
@@ -9475,7 +9477,7 @@
         <v>22</v>
       </c>
       <c r="N85" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="O85" t="s">
         <v>34</v>
@@ -9484,7 +9486,7 @@
         <v>22</v>
       </c>
       <c r="Q85" s="1" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="R85" t="s">
         <v>34</v>
@@ -9540,7 +9542,7 @@
         <v>22</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I86" s="5" t="s">
         <v>190</v>
@@ -9549,7 +9551,7 @@
         <v>22</v>
       </c>
       <c r="K86" s="8" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="L86" s="7" t="s">
         <v>190</v>
@@ -9558,19 +9560,19 @@
         <v>22</v>
       </c>
       <c r="N86" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="O86" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="P86">
         <v>22</v>
       </c>
       <c r="Q86" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="R86" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="S86">
         <v>22</v>
@@ -9623,7 +9625,7 @@
         <v>22</v>
       </c>
       <c r="H87" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I87" s="5" t="s">
         <v>194</v>
@@ -9632,7 +9634,7 @@
         <v>22</v>
       </c>
       <c r="K87" s="8" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="L87" s="7" t="s">
         <v>194</v>
@@ -9641,7 +9643,7 @@
         <v>22</v>
       </c>
       <c r="N87" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="O87" t="s">
         <v>34</v>
@@ -9650,7 +9652,7 @@
         <v>22</v>
       </c>
       <c r="Q87" s="1" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R87" t="s">
         <v>34</v>
@@ -9706,7 +9708,7 @@
         <v>22</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I88" s="5" t="s">
         <v>194</v>
@@ -9715,7 +9717,7 @@
         <v>22</v>
       </c>
       <c r="K88" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="L88" s="7" t="s">
         <v>194</v>
@@ -9724,7 +9726,7 @@
         <v>22</v>
       </c>
       <c r="N88" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="O88" t="s">
         <v>34</v>
@@ -9733,7 +9735,7 @@
         <v>22</v>
       </c>
       <c r="Q88" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="R88" t="s">
         <v>34</v>
@@ -9789,7 +9791,7 @@
         <v>22</v>
       </c>
       <c r="H89" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I89" s="5" t="s">
         <v>194</v>
@@ -9798,7 +9800,7 @@
         <v>22</v>
       </c>
       <c r="K89" s="8" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="L89" s="7" t="s">
         <v>194</v>
@@ -9807,7 +9809,7 @@
         <v>22</v>
       </c>
       <c r="N89" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="O89" t="s">
         <v>34</v>
@@ -9816,7 +9818,7 @@
         <v>22</v>
       </c>
       <c r="Q89" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="R89" t="s">
         <v>34</v>
